--- a/Översikt VIMMERBY.xlsx
+++ b/Översikt VIMMERBY.xlsx
@@ -567,7 +567,7 @@
         <v>44811</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
         <v>44811</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44811</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44811</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>45314</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>45738.79180555556</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>44939</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>45301.67922453704</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>45755</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45377.54726851852</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>45678.64175925926</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>45121.60543981481</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>45748</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>45821</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>44245</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>44811</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>45020</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>45628</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>45742</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>44424</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>44426.64793981481</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44386</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>45048</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>45786.52827546297</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>45008.60878472222</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>44943</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>45760.34877314815</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>45072</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>44371</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>45077</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>45224</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>44403</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>44377.61104166666</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>44082</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>45399.71412037037</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>45125</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>45104</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>45574.42767361111</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>45168</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>45168</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>45667</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>44236</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>45649</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>45821</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>45825.58484953704</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>45713</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>44075</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>44057</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>44064</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>44068</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>44083</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>44054</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         <v>44102</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>44130</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>44281.79269675926</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         <v>44270.67071759259</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>44287.33261574074</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>44210</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>44447</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>44490.38613425926</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>44481.47483796296</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>44375.39033564815</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>44350</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>44614</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>44215</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         <v>44670</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>44670</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>44070.39203703704</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>44063</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>44307</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         <v>44350</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>44105</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>44054</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>44225</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>44070</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
         <v>44327.47658564815</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>44509</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>44406</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>44230.58883101852</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>44480</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>44063</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>44238</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>44585.51829861111</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>44824.53434027778</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>44418</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>44785.40800925926</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>44578.47597222222</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>44516.59703703703</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>44862</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>44603</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>44588</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>44826.68010416667</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>44404.87505787037</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>44483.58295138889</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>44494</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>44542.8859375</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>44354</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         <v>44512.70245370371</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>44090</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>44221.39408564815</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
         <v>44790</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>44530.38055555556</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>44261</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>44588</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
         <v>44588</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         <v>44790</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>44790.47628472222</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8286,7 +8286,7 @@
         <v>44175.3815625</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>44175.40881944444</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>44062</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>44475</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>44385</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8571,7 +8571,7 @@
         <v>44124.59795138889</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         <v>44237.8550925926</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         <v>44312</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         <v>44410.71038194445</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>44279.33400462963</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>44670</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8913,7 +8913,7 @@
         <v>44365</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>44175</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>44169</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>44273</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>44301.36048611111</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>44271.37226851852</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>44729.28226851852</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>44340.54472222222</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         <v>44340</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>44057</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>44774</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>44063</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>44061</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>44733</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         <v>44733</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>44154</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>44371.62743055556</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9887,7 +9887,7 @@
         <v>44386.40783564815</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         <v>44480</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>44245</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>44070.40998842593</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         <v>44337</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>44102</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>44463.29439814815</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10286,7 +10286,7 @@
         <v>44588</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10343,7 +10343,7 @@
         <v>44789</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10400,7 +10400,7 @@
         <v>44117</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10457,7 +10457,7 @@
         <v>44377</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10514,7 +10514,7 @@
         <v>44379</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10576,7 +10576,7 @@
         <v>44508</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>44294</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10695,7 +10695,7 @@
         <v>44294</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10752,7 +10752,7 @@
         <v>44676.85248842592</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>44604</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>44091</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>44305</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>44634.69703703704</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>44851.95016203704</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
         <v>44480</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11151,7 +11151,7 @@
         <v>44769.45422453704</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11208,7 +11208,7 @@
         <v>44340.58002314815</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         <v>44085</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11322,7 +11322,7 @@
         <v>44092</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11379,7 +11379,7 @@
         <v>44612.86762731482</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11436,7 +11436,7 @@
         <v>44142</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11493,7 +11493,7 @@
         <v>44644</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>44383</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11607,7 +11607,7 @@
         <v>44305.40046296296</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>44476</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         <v>44447</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>44517</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
         <v>44418</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         <v>44854</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11954,7 +11954,7 @@
         <v>44824</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12011,7 +12011,7 @@
         <v>44369</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>44742</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12125,7 +12125,7 @@
         <v>44819</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12182,7 +12182,7 @@
         <v>44832.67608796297</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12239,7 +12239,7 @@
         <v>44451.8375</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12296,7 +12296,7 @@
         <v>44823</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>44621</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>44217.79856481482</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>44270</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>44341</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>44070</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12638,7 +12638,7 @@
         <v>44608</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>44447.34237268518</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         <v>44172</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>44384</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>44790.48503472222</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>44294</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>44116</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>44854.59157407407</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>44876.48346064815</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>44733.43092592592</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>44620</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>44480</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>44089.78633101852</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>44609</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13436,7 +13436,7 @@
         <v>44284.42348379629</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13493,7 +13493,7 @@
         <v>44088</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         <v>44088</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         <v>44421</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13664,7 +13664,7 @@
         <v>44186</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>44203</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         <v>44054</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13835,7 +13835,7 @@
         <v>44525.63913194444</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>44273</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>44278.63479166666</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>44279.64934027778</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>44662</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>44095</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>44070</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14249,7 +14249,7 @@
         <v>44266.7240625</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14311,7 +14311,7 @@
         <v>44375.38789351852</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>44270.49743055556</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>44612.86554398148</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14487,7 +14487,7 @@
         <v>44466.34726851852</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14544,7 +14544,7 @@
         <v>44866.81100694444</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>44564</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>44470.44232638889</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
         <v>44776</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14777,7 +14777,7 @@
         <v>44386</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
         <v>44634</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
         <v>44427</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14948,7 +14948,7 @@
         <v>44722.48768518519</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15005,7 +15005,7 @@
         <v>44379</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>44608.50458333334</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>44284.44574074074</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15181,7 +15181,7 @@
         <v>44817</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15238,7 +15238,7 @@
         <v>45201.39996527778</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15295,7 +15295,7 @@
         <v>44060</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>44991.30547453704</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15409,7 +15409,7 @@
         <v>44991</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15466,7 +15466,7 @@
         <v>44292</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>44636</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         <v>45113.41633101852</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>45483.82834490741</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15699,7 +15699,7 @@
         <v>45238.4328587963</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15756,7 +15756,7 @@
         <v>45090.38012731481</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15813,7 +15813,7 @@
         <v>45138</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>45063.508125</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>45219.40528935185</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
         <v>44817.57988425926</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16041,7 +16041,7 @@
         <v>44895.46524305556</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>45674.74094907408</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16155,7 +16155,7 @@
         <v>45747.39189814815</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         <v>45700.68672453704</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>45735.56751157407</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16326,7 +16326,7 @@
         <v>44440</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
         <v>45163</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16440,7 +16440,7 @@
         <v>45754.33641203704</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16497,7 +16497,7 @@
         <v>45453.36067129629</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>44963.44769675926</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16611,7 +16611,7 @@
         <v>44944.71386574074</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16668,7 +16668,7 @@
         <v>44944.72100694444</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16725,7 +16725,7 @@
         <v>45698.53725694444</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>45114.47895833333</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16839,7 +16839,7 @@
         <v>45482.49870370371</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16896,7 +16896,7 @@
         <v>45482.54844907407</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>45533.38870370371</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17010,7 +17010,7 @@
         <v>45732.79925925926</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17067,7 +17067,7 @@
         <v>45250.5278587963</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17124,7 +17124,7 @@
         <v>45111.30824074074</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17181,7 +17181,7 @@
         <v>44466.34962962963</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17238,7 +17238,7 @@
         <v>45105</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17295,7 +17295,7 @@
         <v>44803.59118055556</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>44278.54855324074</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
         <v>45153.32778935185</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
         <v>45761.39600694444</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17523,7 +17523,7 @@
         <v>44377.49684027778</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
         <v>44833.60123842592</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17642,7 +17642,7 @@
         <v>45215.59743055556</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         <v>44789</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17756,7 +17756,7 @@
         <v>44431.84840277778</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>44910.41346064815</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17870,7 +17870,7 @@
         <v>44910</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>45106</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17984,7 +17984,7 @@
         <v>45106.2610300926</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18041,7 +18041,7 @@
         <v>44598.7384837963</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18098,7 +18098,7 @@
         <v>44931</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18160,7 +18160,7 @@
         <v>45699.60055555555</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18217,7 +18217,7 @@
         <v>45027.59450231482</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18279,7 +18279,7 @@
         <v>45112.33599537037</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18336,7 +18336,7 @@
         <v>44111</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>44440.60415509259</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18450,7 +18450,7 @@
         <v>45411.47335648148</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18507,7 +18507,7 @@
         <v>45658.78774305555</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18564,7 +18564,7 @@
         <v>45377.40043981482</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18621,7 +18621,7 @@
         <v>45630.45069444444</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18678,7 +18678,7 @@
         <v>45698.51711805556</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         <v>45211.43555555555</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
         <v>45029</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18849,7 +18849,7 @@
         <v>44302</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18906,7 +18906,7 @@
         <v>45224</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18963,7 +18963,7 @@
         <v>45224.64659722222</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19025,7 +19025,7 @@
         <v>44943.57309027778</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19082,7 +19082,7 @@
         <v>45097.40524305555</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19144,7 +19144,7 @@
         <v>45100.4062962963</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>45425.57538194444</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>44451</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19315,7 +19315,7 @@
         <v>45121.5965162037</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19377,7 +19377,7 @@
         <v>45121.59954861111</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>45121.6096875</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>45558.44914351852</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>44984</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>45346.67184027778</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19672,7 +19672,7 @@
         <v>45624.60141203704</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>45434.55471064815</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19791,7 +19791,7 @@
         <v>44312</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>45090</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         <v>44984.45895833334</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
         <v>44984</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20019,7 +20019,7 @@
         <v>45749.60487268519</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>45245.5735300926</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>45698.52806712963</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>44966</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20252,7 +20252,7 @@
         <v>45450.51092592593</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20309,7 +20309,7 @@
         <v>45054.6750462963</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20366,7 +20366,7 @@
         <v>44903.33363425926</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>44895.62296296296</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20480,7 +20480,7 @@
         <v>45308.61152777778</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20537,7 +20537,7 @@
         <v>45299.47513888889</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20594,7 +20594,7 @@
         <v>45350.53306712963</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
         <v>45660</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>44578.62943287037</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20765,7 +20765,7 @@
         <v>45539.66027777778</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20822,7 +20822,7 @@
         <v>44258</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20879,7 +20879,7 @@
         <v>45369.62780092593</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20936,7 +20936,7 @@
         <v>44867</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20993,7 +20993,7 @@
         <v>44879.55940972222</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21050,7 +21050,7 @@
         <v>44903</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21107,7 +21107,7 @@
         <v>45554.63225694445</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21164,7 +21164,7 @@
         <v>45722.48915509259</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21221,7 +21221,7 @@
         <v>45635.4874537037</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21278,7 +21278,7 @@
         <v>45545.49508101852</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21335,7 +21335,7 @@
         <v>45569.47494212963</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>44896</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21449,7 +21449,7 @@
         <v>44890</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21506,7 +21506,7 @@
         <v>44852</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21563,7 +21563,7 @@
         <v>45384.66917824074</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21620,7 +21620,7 @@
         <v>44588.37998842593</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21677,7 +21677,7 @@
         <v>44588</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21734,7 +21734,7 @@
         <v>45114.55136574074</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>44992</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>44175.39748842592</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>45070.3665625</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>45070</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>45215.60199074074</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>45720.44217592593</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22138,7 +22138,7 @@
         <v>44991.89657407408</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>45257.70313657408</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22252,7 +22252,7 @@
         <v>45361.90282407407</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>45224.6515162037</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22371,7 +22371,7 @@
         <v>44392</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22433,7 +22433,7 @@
         <v>44994.46908564815</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22490,7 +22490,7 @@
         <v>45149.60917824074</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22547,7 +22547,7 @@
         <v>44754</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22604,7 +22604,7 @@
         <v>45169</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22661,7 +22661,7 @@
         <v>45106.25025462963</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22718,7 +22718,7 @@
         <v>45266.32614583334</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22775,7 +22775,7 @@
         <v>45100.85270833333</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22832,7 +22832,7 @@
         <v>45317.40372685185</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22894,7 +22894,7 @@
         <v>44064</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22951,7 +22951,7 @@
         <v>45309.59487268519</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23008,7 +23008,7 @@
         <v>45415.57682870371</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23065,7 +23065,7 @@
         <v>45359.44837962963</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>44488.35878472222</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23179,7 +23179,7 @@
         <v>45278</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23241,7 +23241,7 @@
         <v>44467.83386574074</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23298,7 +23298,7 @@
         <v>45482.52887731481</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         <v>45456.59289351852</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23412,7 +23412,7 @@
         <v>45371.36359953704</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23469,7 +23469,7 @@
         <v>45371.45865740741</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>45359.45038194444</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>45002</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23640,7 +23640,7 @@
         <v>44861.52505787037</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23697,7 +23697,7 @@
         <v>45533.54429398148</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>45533.60232638889</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>45533.60770833334</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23878,7 +23878,7 @@
         <v>44517</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23935,7 +23935,7 @@
         <v>45174.40454861111</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23992,7 +23992,7 @@
         <v>45446.36774305555</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
         <v>45533.56108796296</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24111,7 +24111,7 @@
         <v>45533.58302083334</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24173,7 +24173,7 @@
         <v>45705.73300925926</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24230,7 +24230,7 @@
         <v>44965.4815162037</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         <v>45147.67096064815</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>45147.67172453704</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24401,7 +24401,7 @@
         <v>44063</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>44875.27736111111</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>45108.703125</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>45171.77335648148</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         <v>45110.4275</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>45475.49018518518</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         <v>45196</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24800,7 +24800,7 @@
         <v>45061</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>44510.60921296296</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>44607</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>45301</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
         <v>45301.68237268519</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25095,7 +25095,7 @@
         <v>45475.48303240741</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25152,7 +25152,7 @@
         <v>44949</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25214,7 +25214,7 @@
         <v>45121.58699074074</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25276,7 +25276,7 @@
         <v>45526.3865625</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>45569.44684027778</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>45243.84869212963</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25452,7 +25452,7 @@
         <v>45124</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25509,7 +25509,7 @@
         <v>45446.36482638889</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25571,7 +25571,7 @@
         <v>45391.41310185185</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25628,7 +25628,7 @@
         <v>45759.38987268518</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25685,7 +25685,7 @@
         <v>45755.44333333334</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25742,7 +25742,7 @@
         <v>45086.63194444445</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25799,7 +25799,7 @@
         <v>45530.33202546297</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25856,7 +25856,7 @@
         <v>45086.63334490741</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25913,7 +25913,7 @@
         <v>45667.39670138889</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25970,7 +25970,7 @@
         <v>45086</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26027,7 +26027,7 @@
         <v>45128.58414351852</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26084,7 +26084,7 @@
         <v>44083</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26141,7 +26141,7 @@
         <v>44949</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26198,7 +26198,7 @@
         <v>44588</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>44720.53898148148</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26312,7 +26312,7 @@
         <v>44243</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26369,7 +26369,7 @@
         <v>45171.96248842592</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26426,7 +26426,7 @@
         <v>44539</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26483,7 +26483,7 @@
         <v>45232</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26540,7 +26540,7 @@
         <v>45525.41762731481</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26597,7 +26597,7 @@
         <v>45030.71012731481</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26654,7 +26654,7 @@
         <v>45565.40657407408</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26711,7 +26711,7 @@
         <v>45728.54832175926</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26768,7 +26768,7 @@
         <v>44510.52157407408</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>44984</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26882,7 +26882,7 @@
         <v>44553</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>44598</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26996,7 +26996,7 @@
         <v>44938</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>45483.82479166667</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         <v>44964.5115162037</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27172,7 +27172,7 @@
         <v>45498</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27229,7 +27229,7 @@
         <v>44879</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27286,7 +27286,7 @@
         <v>45257.67958333333</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27343,7 +27343,7 @@
         <v>45018</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27400,7 +27400,7 @@
         <v>45607.56773148148</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27457,7 +27457,7 @@
         <v>44867</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>45301.67736111111</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>45482.54108796296</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27628,7 +27628,7 @@
         <v>45513.55840277778</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>45513.56527777778</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27742,7 +27742,7 @@
         <v>45110.4184375</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27799,7 +27799,7 @@
         <v>45096.45247685185</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27856,7 +27856,7 @@
         <v>45111.48395833333</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27913,7 +27913,7 @@
         <v>45415.47848379629</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27970,7 +27970,7 @@
         <v>45391.41976851852</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28027,7 +28027,7 @@
         <v>45111.48787037037</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28084,7 +28084,7 @@
         <v>45588.65545138889</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28141,7 +28141,7 @@
         <v>45485.45778935185</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28198,7 +28198,7 @@
         <v>45618.56787037037</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>44967.45122685185</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28312,7 +28312,7 @@
         <v>45467.74417824074</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28369,7 +28369,7 @@
         <v>45481.58048611111</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28426,7 +28426,7 @@
         <v>45086</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28483,7 +28483,7 @@
         <v>44159</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28540,7 +28540,7 @@
         <v>44918.50106481482</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28597,7 +28597,7 @@
         <v>45632.37459490741</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28654,7 +28654,7 @@
         <v>45378.32185185186</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>45498.673125</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>44893</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28825,7 +28825,7 @@
         <v>45275.32266203704</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28882,7 +28882,7 @@
         <v>45540.50098379629</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>45581.57016203704</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>44127</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29053,7 +29053,7 @@
         <v>45481.55984953704</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>45539.38744212963</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29167,7 +29167,7 @@
         <v>44630</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29224,7 +29224,7 @@
         <v>45539.65212962963</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29281,7 +29281,7 @@
         <v>44893</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29338,7 +29338,7 @@
         <v>45784.74996527778</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>45699.45671296296</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>45463</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>45630.47564814815</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
         <v>44994.40635416667</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>45574.35809027778</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29680,7 +29680,7 @@
         <v>45559.38876157408</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>44587</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29794,7 +29794,7 @@
         <v>45000.47998842593</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>45552.36759259259</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29908,7 +29908,7 @@
         <v>45098.30535879629</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29965,7 +29965,7 @@
         <v>44935</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30022,7 +30022,7 @@
         <v>44603</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30079,7 +30079,7 @@
         <v>44999.86172453704</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30136,7 +30136,7 @@
         <v>44999.8625</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30193,7 +30193,7 @@
         <v>44964.50894675926</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>45113.56574074074</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30307,7 +30307,7 @@
         <v>45517.8162037037</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>45518.40657407408</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30421,7 +30421,7 @@
         <v>44638.55256944444</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30478,7 +30478,7 @@
         <v>45747.42633101852</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
         <v>45747.42958333333</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30592,7 +30592,7 @@
         <v>45726.44471064815</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>45786.52931712963</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30706,7 +30706,7 @@
         <v>45786.52996527778</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30763,7 +30763,7 @@
         <v>44788</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30820,7 +30820,7 @@
         <v>45666</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30877,7 +30877,7 @@
         <v>45581.57958333333</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30934,7 +30934,7 @@
         <v>45548</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30991,7 +30991,7 @@
         <v>45001.59209490741</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31048,7 +31048,7 @@
         <v>44587.48847222222</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31105,7 +31105,7 @@
         <v>45020</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31162,7 +31162,7 @@
         <v>45569.44295138889</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31219,7 +31219,7 @@
         <v>45415.48979166667</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31276,7 +31276,7 @@
         <v>44918</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>45009</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31390,7 +31390,7 @@
         <v>44959.66407407408</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31447,7 +31447,7 @@
         <v>44966</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31504,7 +31504,7 @@
         <v>44564.62598379629</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31561,7 +31561,7 @@
         <v>45786.52878472222</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31618,7 +31618,7 @@
         <v>45495</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>44600</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31732,7 +31732,7 @@
         <v>45111.48225694444</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31789,7 +31789,7 @@
         <v>45111.48636574074</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31846,7 +31846,7 @@
         <v>45621.46103009259</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31903,7 +31903,7 @@
         <v>45114.58148148148</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31960,7 +31960,7 @@
         <v>45026.82216435186</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32017,7 +32017,7 @@
         <v>45460.62172453704</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>44910.54231481482</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32131,7 +32131,7 @@
         <v>45567.42011574074</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>45554.62944444444</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32245,7 +32245,7 @@
         <v>45533.61996527778</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32307,7 +32307,7 @@
         <v>45790.44976851852</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>45726.62721064815</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32421,7 +32421,7 @@
         <v>45698.69016203703</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32478,7 +32478,7 @@
         <v>45632.44886574074</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>45741.37270833334</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32592,7 +32592,7 @@
         <v>45567</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>45552.36484953704</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32706,7 +32706,7 @@
         <v>45145</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32763,7 +32763,7 @@
         <v>45271.66576388889</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32820,7 +32820,7 @@
         <v>45791.89865740741</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32877,7 +32877,7 @@
         <v>45632.72635416667</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32934,7 +32934,7 @@
         <v>45582.41200231481</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32991,7 +32991,7 @@
         <v>44585.51060185185</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33048,7 +33048,7 @@
         <v>45572.48293981481</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33105,7 +33105,7 @@
         <v>44475</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33162,7 +33162,7 @@
         <v>45001.43854166667</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33219,7 +33219,7 @@
         <v>45182.78834490741</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33276,7 +33276,7 @@
         <v>45202.4209837963</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33333,7 +33333,7 @@
         <v>45837.77701388889</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33390,7 +33390,7 @@
         <v>45835.48267361111</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33447,7 +33447,7 @@
         <v>45835.48445601852</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33504,7 +33504,7 @@
         <v>45835.48862268519</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33561,7 +33561,7 @@
         <v>45835.4924537037</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33618,7 +33618,7 @@
         <v>45377</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33675,7 +33675,7 @@
         <v>44943.62954861111</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33732,7 +33732,7 @@
         <v>44944.73487268519</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33789,7 +33789,7 @@
         <v>45671.46746527778</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33846,7 +33846,7 @@
         <v>45835.45099537037</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33903,7 +33903,7 @@
         <v>45837.77916666667</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33960,7 +33960,7 @@
         <v>45761.35990740741</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34017,7 +34017,7 @@
         <v>45761.4566550926</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34074,7 +34074,7 @@
         <v>45722.56731481481</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>45796</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34188,7 +34188,7 @@
         <v>44579.62225694444</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34245,7 +34245,7 @@
         <v>45835.44732638889</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34302,7 +34302,7 @@
         <v>45835.36229166666</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34364,7 +34364,7 @@
         <v>45394.50028935185</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34421,7 +34421,7 @@
         <v>45581.58418981481</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>44867</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34535,7 +34535,7 @@
         <v>45581.57333333333</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34592,7 +34592,7 @@
         <v>44643</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34649,7 +34649,7 @@
         <v>45835.44709490741</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34706,7 +34706,7 @@
         <v>45533.63056712963</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34768,7 +34768,7 @@
         <v>45328.38755787037</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34825,7 +34825,7 @@
         <v>45713.92412037037</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34882,7 +34882,7 @@
         <v>45588.67070601852</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34939,7 +34939,7 @@
         <v>44784.42528935185</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34996,7 +34996,7 @@
         <v>45176.72427083334</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35053,7 +35053,7 @@
         <v>45071</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35110,7 +35110,7 @@
         <v>45569.45017361111</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35167,7 +35167,7 @@
         <v>44999.35858796296</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35224,7 +35224,7 @@
         <v>45713.45311342592</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35281,7 +35281,7 @@
         <v>45170</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35338,7 +35338,7 @@
         <v>45735.58024305556</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35395,7 +35395,7 @@
         <v>44746.38834490741</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35452,7 +35452,7 @@
         <v>45840.59474537037</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35509,7 +35509,7 @@
         <v>45840.59853009259</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35566,7 +35566,7 @@
         <v>44795</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35623,7 +35623,7 @@
         <v>45168.89298611111</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35680,7 +35680,7 @@
         <v>45052</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35737,7 +35737,7 @@
         <v>45622</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35794,7 +35794,7 @@
         <v>45562.46342592593</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35851,7 +35851,7 @@
         <v>45434.55831018519</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35913,7 +35913,7 @@
         <v>45434.56398148148</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35975,7 +35975,7 @@
         <v>45075.43059027778</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36032,7 +36032,7 @@
         <v>45603.74959490741</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36089,7 +36089,7 @@
         <v>44784.62724537037</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36146,7 +36146,7 @@
         <v>45755.64450231481</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36203,7 +36203,7 @@
         <v>45623.95947916667</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36260,7 +36260,7 @@
         <v>44635</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36317,7 +36317,7 @@
         <v>45343.68038194445</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36374,7 +36374,7 @@
         <v>45527.68784722222</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>45841.7072337963</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36488,7 +36488,7 @@
         <v>45574.49298611111</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36545,7 +36545,7 @@
         <v>45715.44159722222</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36602,7 +36602,7 @@
         <v>44270.39765046296</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>44595.583125</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>45121.61318287037</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36783,7 +36783,7 @@
         <v>44992.4255787037</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36840,7 +36840,7 @@
         <v>45617.47570601852</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36897,7 +36897,7 @@
         <v>45841.70569444444</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36954,7 +36954,7 @@
         <v>45841.70868055556</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37011,7 +37011,7 @@
         <v>45211.52642361111</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37068,7 +37068,7 @@
         <v>45211.541875</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37125,7 +37125,7 @@
         <v>45650.37370370371</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37182,7 +37182,7 @@
         <v>45195.58452546296</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37239,7 +37239,7 @@
         <v>45845.49414351852</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37296,7 +37296,7 @@
         <v>45635.66409722222</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37353,7 +37353,7 @@
         <v>45351.6062962963</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37410,7 +37410,7 @@
         <v>45845.43803240741</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37467,7 +37467,7 @@
         <v>44981.58834490741</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37524,7 +37524,7 @@
         <v>45401.53033564815</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37581,7 +37581,7 @@
         <v>45208</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37638,7 +37638,7 @@
         <v>45804.6953587963</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37700,7 +37700,7 @@
         <v>45729.36868055556</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37757,7 +37757,7 @@
         <v>45804.708125</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37819,7 +37819,7 @@
         <v>45804.39141203704</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37876,7 +37876,7 @@
         <v>45845.42015046296</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37933,7 +37933,7 @@
         <v>45567</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37990,7 +37990,7 @@
         <v>45148</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38047,7 +38047,7 @@
         <v>45148</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38104,7 +38104,7 @@
         <v>45163.41376157408</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38161,7 +38161,7 @@
         <v>44994.42113425926</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38218,7 +38218,7 @@
         <v>45434.56291666667</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38280,7 +38280,7 @@
         <v>45804.67065972222</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38337,7 +38337,7 @@
         <v>45079.87827546296</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38394,7 +38394,7 @@
         <v>45804.44519675926</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38451,7 +38451,7 @@
         <v>45805.39247685186</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>45254.62489583333</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38570,7 +38570,7 @@
         <v>44958.61047453704</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38627,7 +38627,7 @@
         <v>44965</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38684,7 +38684,7 @@
         <v>45113.43921296296</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38741,7 +38741,7 @@
         <v>45334.78826388889</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38798,7 +38798,7 @@
         <v>45805</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>44973.43075231482</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38912,7 +38912,7 @@
         <v>44340</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38969,7 +38969,7 @@
         <v>44825.4336574074</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39026,7 +39026,7 @@
         <v>45847.91280092593</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39083,7 +39083,7 @@
         <v>45805.52983796296</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39140,7 +39140,7 @@
         <v>45128</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39197,7 +39197,7 @@
         <v>44977</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39254,7 +39254,7 @@
         <v>45196.57247685185</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39311,7 +39311,7 @@
         <v>44964.44356481481</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39368,7 +39368,7 @@
         <v>44974.56377314815</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>45610.59094907407</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39487,7 +39487,7 @@
         <v>45236</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39544,7 +39544,7 @@
         <v>44663</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39601,7 +39601,7 @@
         <v>45187</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39658,7 +39658,7 @@
         <v>45187.42854166667</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>44894.49538194444</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39772,7 +39772,7 @@
         <v>44992</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39829,7 +39829,7 @@
         <v>45707.3793287037</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39886,7 +39886,7 @@
         <v>45736.50743055555</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39943,7 +39943,7 @@
         <v>45020</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40000,7 +40000,7 @@
         <v>44172</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40057,7 +40057,7 @@
         <v>45114.49505787037</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40114,7 +40114,7 @@
         <v>45041</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40171,7 +40171,7 @@
         <v>45810.00048611111</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40228,7 +40228,7 @@
         <v>45632.36706018518</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40285,7 +40285,7 @@
         <v>44745.84396990741</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40342,7 +40342,7 @@
         <v>45163.63621527778</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40404,7 +40404,7 @@
         <v>45308.59001157407</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40461,7 +40461,7 @@
         <v>45699.44291666667</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40518,7 +40518,7 @@
         <v>45174</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40575,7 +40575,7 @@
         <v>45615.48927083334</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40632,7 +40632,7 @@
         <v>45853.87112268519</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40689,7 +40689,7 @@
         <v>45811.45460648148</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40746,7 +40746,7 @@
         <v>45722.48634259259</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40803,7 +40803,7 @@
         <v>45811.66133101852</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40860,7 +40860,7 @@
         <v>45853.87599537037</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40917,7 +40917,7 @@
         <v>45853.88070601852</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40974,7 +40974,7 @@
         <v>45811.65975694444</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41031,7 +41031,7 @@
         <v>45635.66695601852</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41088,7 +41088,7 @@
         <v>45719.84378472222</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41145,7 +41145,7 @@
         <v>45568.30189814815</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41202,7 +41202,7 @@
         <v>45033.76043981482</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41259,7 +41259,7 @@
         <v>45698.7259837963</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41316,7 +41316,7 @@
         <v>45699.45392361111</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41373,7 +41373,7 @@
         <v>45154.49831018518</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>45761.4437962963</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41487,7 +41487,7 @@
         <v>45299.62576388889</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41544,7 +41544,7 @@
         <v>45630.35827546296</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41601,7 +41601,7 @@
         <v>45700.68289351852</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41658,7 +41658,7 @@
         <v>44176</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41715,7 +41715,7 @@
         <v>45814.3865625</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41772,7 +41772,7 @@
         <v>45814.38221064815</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41829,7 +41829,7 @@
         <v>45623.9525462963</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41886,7 +41886,7 @@
         <v>44790.49523148148</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41943,7 +41943,7 @@
         <v>45260.4716550926</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42000,7 +42000,7 @@
         <v>44820</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42057,7 +42057,7 @@
         <v>44693.62822916666</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42119,7 +42119,7 @@
         <v>45769</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42176,7 +42176,7 @@
         <v>45245.63574074074</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42233,7 +42233,7 @@
         <v>45858.60641203704</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
         <v>45818.59261574074</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         <v>45280.66769675926</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42409,7 +42409,7 @@
         <v>44956</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42471,7 +42471,7 @@
         <v>45317</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42533,7 +42533,7 @@
         <v>45818.5862037037</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42595,7 +42595,7 @@
         <v>45818.58993055556</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>45858.66019675926</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42714,7 +42714,7 @@
         <v>45219.69356481481</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42771,7 +42771,7 @@
         <v>45189</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42828,7 +42828,7 @@
         <v>45379</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42885,7 +42885,7 @@
         <v>45225.60192129629</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42942,7 +42942,7 @@
         <v>45658.80232638889</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42999,7 +42999,7 @@
         <v>45658.80827546296</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43056,7 +43056,7 @@
         <v>45063.49936342592</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43113,7 +43113,7 @@
         <v>45237.63225694445</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43170,7 +43170,7 @@
         <v>45237.64408564815</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43227,7 +43227,7 @@
         <v>44769.45805555556</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43284,7 +43284,7 @@
         <v>45818.58769675926</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43346,7 +43346,7 @@
         <v>45818.595625</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43408,7 +43408,7 @@
         <v>45817.88496527778</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43465,7 +43465,7 @@
         <v>45301.67554398148</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43522,7 +43522,7 @@
         <v>45768.65611111111</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43579,7 +43579,7 @@
         <v>44546</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43636,7 +43636,7 @@
         <v>44732.3659837963</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43693,7 +43693,7 @@
         <v>45743.40881944444</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43750,7 +43750,7 @@
         <v>45224.60075231481</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43812,7 +43812,7 @@
         <v>45646.38200231481</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43869,7 +43869,7 @@
         <v>45820.33930555556</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43926,7 +43926,7 @@
         <v>44377</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43983,7 +43983,7 @@
         <v>44790.49040509259</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44040,7 +44040,7 @@
         <v>45820.03518518519</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44097,7 +44097,7 @@
         <v>45820.03976851852</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44154,7 +44154,7 @@
         <v>45820.33708333333</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44211,7 +44211,7 @@
         <v>45820.34128472222</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>45323.53744212963</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44325,7 +44325,7 @@
         <v>45819.61060185185</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44382,7 +44382,7 @@
         <v>45533.55362268518</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44439,7 +44439,7 @@
         <v>44988</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44496,7 +44496,7 @@
         <v>45764.44931712963</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44558,7 +44558,7 @@
         <v>45763.59436342592</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44615,7 +44615,7 @@
         <v>45355.54138888889</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44672,7 +44672,7 @@
         <v>45361.87975694444</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44729,7 +44729,7 @@
         <v>45330</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44786,7 +44786,7 @@
         <v>45330</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44843,7 +44843,7 @@
         <v>44270.38002314815</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44905,7 +44905,7 @@
         <v>44839.4528125</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44962,7 +44962,7 @@
         <v>45217.47834490741</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45019,7 +45019,7 @@
         <v>45121</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45076,7 +45076,7 @@
         <v>44502</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45133,7 +45133,7 @@
         <v>44578.32717592592</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45190,7 +45190,7 @@
         <v>44897</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45247,7 +45247,7 @@
         <v>45825.5796875</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45304,7 +45304,7 @@
         <v>45747.43196759259</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45361,7 +45361,7 @@
         <v>45825.58672453704</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45418,7 +45418,7 @@
         <v>45867.51630787037</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45475,7 +45475,7 @@
         <v>45867.56320601852</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45532,7 +45532,7 @@
         <v>45867.63094907408</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45589,7 +45589,7 @@
         <v>45867.50792824074</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45646,7 +45646,7 @@
         <v>45867.68625</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45703,7 +45703,7 @@
         <v>45867.69346064814</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45760,7 +45760,7 @@
         <v>45091.67936342592</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45817,7 +45817,7 @@
         <v>45259.51916666667</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45879,7 +45879,7 @@
         <v>45259.52020833334</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45941,7 +45941,7 @@
         <v>45734.62017361111</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45998,7 +45998,7 @@
         <v>45867.64663194444</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46055,7 +46055,7 @@
         <v>45825.57805555555</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46112,7 +46112,7 @@
         <v>45825.50280092593</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46169,7 +46169,7 @@
         <v>45825.57680555555</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46226,7 +46226,7 @@
         <v>45826.66646990741</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46283,7 +46283,7 @@
         <v>45698.53336805556</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46340,7 +46340,7 @@
         <v>44418</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46397,7 +46397,7 @@
         <v>45827</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46454,7 +46454,7 @@
         <v>45870.52111111111</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46511,7 +46511,7 @@
         <v>45870.51708333333</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46568,7 +46568,7 @@
         <v>45870.52005787037</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46625,7 +46625,7 @@
         <v>45870.52142361111</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46682,7 +46682,7 @@
         <v>45870.51958333333</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46739,7 +46739,7 @@
         <v>45869.62276620371</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46796,7 +46796,7 @@
         <v>45749.56196759259</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46858,7 +46858,7 @@
         <v>45827</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46915,7 +46915,7 @@
         <v>45349.54434027777</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46972,7 +46972,7 @@
         <v>45345.83557870371</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47029,7 +47029,7 @@
         <v>45831</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47086,7 +47086,7 @@
         <v>45832.46649305556</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47143,7 +47143,7 @@
         <v>45732.75637731481</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47200,7 +47200,7 @@
         <v>45732.76936342593</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47257,7 +47257,7 @@
         <v>45090.89653935185</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47314,7 +47314,7 @@
         <v>45090.89880787037</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47371,7 +47371,7 @@
         <v>44599</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47428,7 +47428,7 @@
         <v>45201</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47485,7 +47485,7 @@
         <v>45674.71810185185</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47542,7 +47542,7 @@
         <v>45588.66457175926</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47599,7 +47599,7 @@
         <v>45275.41833333333</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47656,7 +47656,7 @@
         <v>44495</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47713,7 +47713,7 @@
         <v>45874.57109953704</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47770,7 +47770,7 @@
         <v>45832.34540509259</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47827,7 +47827,7 @@
         <v>45832.46146990741</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47884,7 +47884,7 @@
         <v>44848.59133101852</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47941,7 +47941,7 @@
         <v>45440.28329861111</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47998,7 +47998,7 @@
         <v>44790.45876157407</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48055,7 +48055,7 @@
         <v>44861</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48112,7 +48112,7 @@
         <v>44879.62173611111</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48169,7 +48169,7 @@
         <v>45833.64563657407</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48226,7 +48226,7 @@
         <v>45833.64814814815</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48283,7 +48283,7 @@
         <v>45147</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48340,7 +48340,7 @@
         <v>45875.47454861111</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48397,7 +48397,7 @@
         <v>44987.54104166666</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48454,7 +48454,7 @@
         <v>45875.45716435185</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48511,7 +48511,7 @@
         <v>44060</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48568,7 +48568,7 @@
         <v>45834.64667824074</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48630,7 +48630,7 @@
         <v>45761.44584490741</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48687,7 +48687,7 @@
         <v>45875.42716435185</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48744,7 +48744,7 @@
         <v>45709.62280092593</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48801,7 +48801,7 @@
         <v>45834.65040509259</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48863,7 +48863,7 @@
         <v>45834.65197916667</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48925,7 +48925,7 @@
         <v>45833.64237268519</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48982,7 +48982,7 @@
         <v>45128.37305555555</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49039,7 +49039,7 @@
         <v>45481.56722222222</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49096,7 +49096,7 @@
         <v>44900.57393518519</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49153,7 +49153,7 @@
         <v>45394.66887731481</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49210,7 +49210,7 @@
         <v>44857.65989583333</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49267,7 +49267,7 @@
         <v>44585.50431712963</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49324,7 +49324,7 @@
         <v>44992.34151620371</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49386,7 +49386,7 @@
         <v>44542.90072916666</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>44453.56578703703</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49500,7 +49500,7 @@
         <v>44431</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49557,7 +49557,7 @@
         <v>44566</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49614,7 +49614,7 @@
         <v>45743.41148148148</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49671,7 +49671,7 @@
         <v>45261.44914351852</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49728,7 +49728,7 @@
         <v>45048.59699074074</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49785,7 +49785,7 @@
         <v>45503.5658912037</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49842,7 +49842,7 @@
         <v>44596</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49899,7 +49899,7 @@
         <v>45568.36879629629</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49956,7 +49956,7 @@
         <v>44077</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50013,7 +50013,7 @@
         <v>44952.35775462963</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50070,7 +50070,7 @@
         <v>45093.62777777778</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50132,7 +50132,7 @@
         <v>45215.5959375</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50189,7 +50189,7 @@
         <v>44992.62498842592</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50246,7 +50246,7 @@
         <v>44967.44255787037</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>44600</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50360,7 +50360,7 @@
         <v>45187.60813657408</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50417,7 +50417,7 @@
         <v>44237</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50474,7 +50474,7 @@
         <v>44452</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50531,7 +50531,7 @@
         <v>45009.4671875</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50588,7 +50588,7 @@
         <v>45705.74418981482</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50645,7 +50645,7 @@
         <v>44410</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50702,7 +50702,7 @@
         <v>45111</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50759,7 +50759,7 @@
         <v>44909</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50816,7 +50816,7 @@
         <v>45637.66542824074</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>44310</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50930,7 +50930,7 @@
         <v>45041.63380787037</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50987,7 +50987,7 @@
         <v>44961</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51044,7 +51044,7 @@
         <v>44916.55414351852</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51101,7 +51101,7 @@
         <v>45722.56422453704</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51158,7 +51158,7 @@
         <v>45300.3794212963</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51215,7 +51215,7 @@
         <v>45245.36174768519</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51272,7 +51272,7 @@
         <v>44061</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51329,7 +51329,7 @@
         <v>44999.36081018519</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51386,7 +51386,7 @@
         <v>45495</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51443,7 +51443,7 @@
         <v>45128.9325</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51500,7 +51500,7 @@
         <v>45128.93540509259</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51557,7 +51557,7 @@
         <v>45320.89128472222</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51614,7 +51614,7 @@
         <v>44613</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51671,7 +51671,7 @@
         <v>44992</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51728,7 +51728,7 @@
         <v>45028</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51785,7 +51785,7 @@
         <v>45453.36854166666</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51842,7 +51842,7 @@
         <v>45211.55472222222</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51904,7 +51904,7 @@
         <v>45639.56185185185</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51961,7 +51961,7 @@
         <v>44540</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52018,7 +52018,7 @@
         <v>45174.31395833333</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52075,7 +52075,7 @@
         <v>45446.36865740741</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52137,7 +52137,7 @@
         <v>44981.64725694444</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>

--- a/Översikt VIMMERBY.xlsx
+++ b/Översikt VIMMERBY.xlsx
@@ -567,7 +567,7 @@
         <v>44811</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
         <v>44811</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44811</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44811</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>45314</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>45738.79180555556</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>44939</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>45301.67922453704</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>45755</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45377.54726851852</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>45678.64175925926</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>45121.60543981481</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>45748</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>45821</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>44245</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>44811</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>45020</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>45628</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>45742</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>44424</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>44426.64793981481</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44386</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>45048</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>45786.52827546297</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>45008.60878472222</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>44943</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>45760.34877314815</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>45072</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>44371</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>45077</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>45224</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>44403</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>44377.61104166666</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>44082</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>45399.71412037037</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>45125</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>45104</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>45574.42767361111</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>45168</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>45168</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>45667</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>44236</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>45649</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>45821</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>45825.58484953704</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>45713</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>44075</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>44057</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>44064</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>44068</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>44083</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>44054</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         <v>44102</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>44130</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>44281.79269675926</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         <v>44270.67071759259</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>44287.33261574074</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>44210</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>44447</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>44490.38613425926</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>44481.47483796296</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>44375.39033564815</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>44350</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>44614</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>44215</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         <v>44670</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>44670</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>44070.39203703704</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>44063</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>44307</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         <v>44350</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>44105</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>44054</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>44225</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>44070</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
         <v>44327.47658564815</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>44509</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>44406</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>44230.58883101852</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>44480</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>44063</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>44238</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>44585.51829861111</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>44824.53434027778</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>44418</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>44785.40800925926</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>44578.47597222222</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>44516.59703703703</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>44862</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>44603</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>44588</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>44826.68010416667</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>44404.87505787037</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>44483.58295138889</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>44494</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>44542.8859375</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>44354</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         <v>44512.70245370371</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>44090</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>44221.39408564815</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
         <v>44790</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>44530.38055555556</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>44261</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>44588</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
         <v>44588</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         <v>44790</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>44790.47628472222</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8286,7 +8286,7 @@
         <v>44175.3815625</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>44175.40881944444</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>44062</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>44475</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>44385</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8571,7 +8571,7 @@
         <v>44124.59795138889</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         <v>44237.8550925926</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         <v>44312</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         <v>44410.71038194445</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>44279.33400462963</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>44670</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8913,7 +8913,7 @@
         <v>44365</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>44175</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>44169</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>44273</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>44301.36048611111</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>44271.37226851852</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>44729.28226851852</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>44340.54472222222</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         <v>44340</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>44057</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>44774</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>44063</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>44061</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>44733</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         <v>44733</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>44154</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>44371.62743055556</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9887,7 +9887,7 @@
         <v>44386.40783564815</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         <v>44480</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>44245</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>44070.40998842593</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         <v>44337</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>44102</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>44463.29439814815</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10286,7 +10286,7 @@
         <v>44588</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10343,7 +10343,7 @@
         <v>44789</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10400,7 +10400,7 @@
         <v>44117</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10457,7 +10457,7 @@
         <v>44377</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10514,7 +10514,7 @@
         <v>44379</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10576,7 +10576,7 @@
         <v>44508</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>44294</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10695,7 +10695,7 @@
         <v>44294</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10752,7 +10752,7 @@
         <v>44676.85248842592</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>44604</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>44091</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>44305</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>44634.69703703704</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>44851.95016203704</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
         <v>44480</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11151,7 +11151,7 @@
         <v>44769.45422453704</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11208,7 +11208,7 @@
         <v>44340.58002314815</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         <v>44085</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11322,7 +11322,7 @@
         <v>44092</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11379,7 +11379,7 @@
         <v>44612.86762731482</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11436,7 +11436,7 @@
         <v>44142</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11493,7 +11493,7 @@
         <v>44644</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>44383</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11607,7 +11607,7 @@
         <v>44305.40046296296</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>44476</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         <v>44447</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>44517</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
         <v>44418</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         <v>44854</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11954,7 +11954,7 @@
         <v>44824</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12011,7 +12011,7 @@
         <v>44369</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>44742</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12125,7 +12125,7 @@
         <v>44819</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12182,7 +12182,7 @@
         <v>44832.67608796297</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12239,7 +12239,7 @@
         <v>44451.8375</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12296,7 +12296,7 @@
         <v>44823</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>44621</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>44217.79856481482</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>44270</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>44341</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>44070</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12638,7 +12638,7 @@
         <v>44608</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>44447.34237268518</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         <v>44172</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>44384</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>44790.48503472222</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>44294</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>44116</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>44854.59157407407</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>44876.48346064815</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>44733.43092592592</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>44620</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>44480</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>44089.78633101852</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>44609</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13436,7 +13436,7 @@
         <v>44284.42348379629</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13493,7 +13493,7 @@
         <v>44088</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         <v>44088</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         <v>44421</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13664,7 +13664,7 @@
         <v>44186</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>44203</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         <v>44054</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13835,7 +13835,7 @@
         <v>44525.63913194444</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>44273</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>44278.63479166666</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>44279.64934027778</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>44662</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>44095</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>44070</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14249,7 +14249,7 @@
         <v>44266.7240625</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14311,7 +14311,7 @@
         <v>44375.38789351852</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>44270.49743055556</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>44612.86554398148</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14487,7 +14487,7 @@
         <v>44466.34726851852</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14544,7 +14544,7 @@
         <v>44866.81100694444</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>44564</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>44470.44232638889</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
         <v>44776</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14777,7 +14777,7 @@
         <v>44386</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
         <v>44634</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
         <v>44427</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14948,7 +14948,7 @@
         <v>44722.48768518519</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15005,7 +15005,7 @@
         <v>44379</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>44608.50458333334</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>44284.44574074074</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15181,7 +15181,7 @@
         <v>44817</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15238,7 +15238,7 @@
         <v>45201.39996527778</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15295,7 +15295,7 @@
         <v>44060</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>44991.30547453704</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15409,7 +15409,7 @@
         <v>44991</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15466,7 +15466,7 @@
         <v>44292</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>44636</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         <v>45113.41633101852</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>45483.82834490741</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15699,7 +15699,7 @@
         <v>45238.4328587963</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15756,7 +15756,7 @@
         <v>45090.38012731481</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15813,7 +15813,7 @@
         <v>45138</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>45063.508125</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>45219.40528935185</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
         <v>44817.57988425926</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16041,7 +16041,7 @@
         <v>44895.46524305556</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>45674.74094907408</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16155,7 +16155,7 @@
         <v>45747.39189814815</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         <v>45700.68672453704</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>45735.56751157407</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16326,7 +16326,7 @@
         <v>44440</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
         <v>45163</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16440,7 +16440,7 @@
         <v>45754.33641203704</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16497,7 +16497,7 @@
         <v>45453.36067129629</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>44963.44769675926</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16611,7 +16611,7 @@
         <v>44944.71386574074</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16668,7 +16668,7 @@
         <v>44944.72100694444</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16725,7 +16725,7 @@
         <v>45698.53725694444</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>45114.47895833333</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16839,7 +16839,7 @@
         <v>45482.49870370371</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16896,7 +16896,7 @@
         <v>45482.54844907407</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>45533.38870370371</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17010,7 +17010,7 @@
         <v>45732.79925925926</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17067,7 +17067,7 @@
         <v>45250.5278587963</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17124,7 +17124,7 @@
         <v>45111.30824074074</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17181,7 +17181,7 @@
         <v>44466.34962962963</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17238,7 +17238,7 @@
         <v>45105</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17295,7 +17295,7 @@
         <v>44803.59118055556</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>44278.54855324074</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
         <v>45153.32778935185</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
         <v>45761.39600694444</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17523,7 +17523,7 @@
         <v>44377.49684027778</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
         <v>44833.60123842592</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17642,7 +17642,7 @@
         <v>45215.59743055556</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         <v>44789</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17756,7 +17756,7 @@
         <v>44431.84840277778</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>44910.41346064815</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17870,7 +17870,7 @@
         <v>44910</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>45106</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17984,7 +17984,7 @@
         <v>45106.2610300926</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18041,7 +18041,7 @@
         <v>44598.7384837963</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18098,7 +18098,7 @@
         <v>44931</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18160,7 +18160,7 @@
         <v>45699.60055555555</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18217,7 +18217,7 @@
         <v>45027.59450231482</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18279,7 +18279,7 @@
         <v>45112.33599537037</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18336,7 +18336,7 @@
         <v>44111</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>44440.60415509259</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18450,7 +18450,7 @@
         <v>45411.47335648148</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18507,7 +18507,7 @@
         <v>45658.78774305555</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18564,7 +18564,7 @@
         <v>45377.40043981482</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18621,7 +18621,7 @@
         <v>45630.45069444444</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18678,7 +18678,7 @@
         <v>45698.51711805556</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         <v>45211.43555555555</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
         <v>45029</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18849,7 +18849,7 @@
         <v>44302</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18906,7 +18906,7 @@
         <v>45224</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18963,7 +18963,7 @@
         <v>45224.64659722222</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19025,7 +19025,7 @@
         <v>44943.57309027778</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19082,7 +19082,7 @@
         <v>45097.40524305555</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19144,7 +19144,7 @@
         <v>45100.4062962963</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>45425.57538194444</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>44451</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19315,7 +19315,7 @@
         <v>45121.5965162037</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19377,7 +19377,7 @@
         <v>45121.59954861111</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>45121.6096875</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>45558.44914351852</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>44984</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>45346.67184027778</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19672,7 +19672,7 @@
         <v>45624.60141203704</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>45434.55471064815</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19791,7 +19791,7 @@
         <v>44312</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>45090</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         <v>44984.45895833334</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
         <v>44984</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20019,7 +20019,7 @@
         <v>45749.60487268519</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>45245.5735300926</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>45698.52806712963</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>44966</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20252,7 +20252,7 @@
         <v>45450.51092592593</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20309,7 +20309,7 @@
         <v>45054.6750462963</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20366,7 +20366,7 @@
         <v>44903.33363425926</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>44895.62296296296</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20480,7 +20480,7 @@
         <v>45308.61152777778</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20537,7 +20537,7 @@
         <v>45299.47513888889</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20594,7 +20594,7 @@
         <v>45350.53306712963</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
         <v>45660</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>44578.62943287037</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20765,7 +20765,7 @@
         <v>45539.66027777778</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20822,7 +20822,7 @@
         <v>44258</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20879,7 +20879,7 @@
         <v>45369.62780092593</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20936,7 +20936,7 @@
         <v>44867</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20993,7 +20993,7 @@
         <v>44879.55940972222</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21050,7 +21050,7 @@
         <v>44903</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21107,7 +21107,7 @@
         <v>45554.63225694445</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21164,7 +21164,7 @@
         <v>45722.48915509259</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21221,7 +21221,7 @@
         <v>45635.4874537037</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21278,7 +21278,7 @@
         <v>45545.49508101852</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21335,7 +21335,7 @@
         <v>45569.47494212963</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>44896</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21449,7 +21449,7 @@
         <v>44890</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21506,7 +21506,7 @@
         <v>44852</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21563,7 +21563,7 @@
         <v>45384.66917824074</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21620,7 +21620,7 @@
         <v>44588.37998842593</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21677,7 +21677,7 @@
         <v>44588</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21734,7 +21734,7 @@
         <v>45114.55136574074</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>44992</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>44175.39748842592</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>45070.3665625</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>45070</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>45215.60199074074</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>45720.44217592593</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22138,7 +22138,7 @@
         <v>44991.89657407408</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>45257.70313657408</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22252,7 +22252,7 @@
         <v>45361.90282407407</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>45224.6515162037</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22371,7 +22371,7 @@
         <v>44392</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22433,7 +22433,7 @@
         <v>44994.46908564815</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22490,7 +22490,7 @@
         <v>45149.60917824074</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22547,7 +22547,7 @@
         <v>44754</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22604,7 +22604,7 @@
         <v>45169</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22661,7 +22661,7 @@
         <v>45106.25025462963</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22718,7 +22718,7 @@
         <v>45266.32614583334</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22775,7 +22775,7 @@
         <v>45100.85270833333</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22832,7 +22832,7 @@
         <v>45317.40372685185</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22894,7 +22894,7 @@
         <v>44064</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22951,7 +22951,7 @@
         <v>45309.59487268519</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23008,7 +23008,7 @@
         <v>45415.57682870371</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23065,7 +23065,7 @@
         <v>45359.44837962963</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>44488.35878472222</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23179,7 +23179,7 @@
         <v>45278</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23241,7 +23241,7 @@
         <v>44467.83386574074</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23298,7 +23298,7 @@
         <v>45482.52887731481</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         <v>45456.59289351852</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23412,7 +23412,7 @@
         <v>45371.36359953704</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23469,7 +23469,7 @@
         <v>45371.45865740741</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>45359.45038194444</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>45002</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23640,7 +23640,7 @@
         <v>44861.52505787037</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23697,7 +23697,7 @@
         <v>45533.54429398148</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>45533.60232638889</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>45533.60770833334</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23878,7 +23878,7 @@
         <v>44517</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23935,7 +23935,7 @@
         <v>45174.40454861111</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23992,7 +23992,7 @@
         <v>45446.36774305555</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
         <v>45533.56108796296</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24111,7 +24111,7 @@
         <v>45533.58302083334</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24173,7 +24173,7 @@
         <v>45705.73300925926</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24230,7 +24230,7 @@
         <v>44965.4815162037</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         <v>45147.67096064815</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>45147.67172453704</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24401,7 +24401,7 @@
         <v>44063</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>44875.27736111111</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>45108.703125</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>45171.77335648148</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         <v>45110.4275</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>45475.49018518518</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         <v>45196</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24800,7 +24800,7 @@
         <v>45061</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>44510.60921296296</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>44607</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>45301</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
         <v>45301.68237268519</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25095,7 +25095,7 @@
         <v>45475.48303240741</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25152,7 +25152,7 @@
         <v>44949</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25214,7 +25214,7 @@
         <v>45121.58699074074</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25276,7 +25276,7 @@
         <v>45526.3865625</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>45569.44684027778</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>45243.84869212963</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25452,7 +25452,7 @@
         <v>45124</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25509,7 +25509,7 @@
         <v>45446.36482638889</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25571,7 +25571,7 @@
         <v>45391.41310185185</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25628,7 +25628,7 @@
         <v>45759.38987268518</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25685,7 +25685,7 @@
         <v>45755.44333333334</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25742,7 +25742,7 @@
         <v>45086.63194444445</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25799,7 +25799,7 @@
         <v>45530.33202546297</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25856,7 +25856,7 @@
         <v>45086.63334490741</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25913,7 +25913,7 @@
         <v>45667.39670138889</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25970,7 +25970,7 @@
         <v>45086</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26027,7 +26027,7 @@
         <v>45128.58414351852</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26084,7 +26084,7 @@
         <v>44083</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26141,7 +26141,7 @@
         <v>44949</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26198,7 +26198,7 @@
         <v>44588</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>44720.53898148148</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26312,7 +26312,7 @@
         <v>44243</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26369,7 +26369,7 @@
         <v>45171.96248842592</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26426,7 +26426,7 @@
         <v>44539</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26483,7 +26483,7 @@
         <v>45232</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26540,7 +26540,7 @@
         <v>45525.41762731481</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26597,7 +26597,7 @@
         <v>45030.71012731481</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26654,7 +26654,7 @@
         <v>45565.40657407408</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26711,7 +26711,7 @@
         <v>45728.54832175926</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26768,7 +26768,7 @@
         <v>44510.52157407408</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>44984</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26882,7 +26882,7 @@
         <v>44553</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>44598</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26996,7 +26996,7 @@
         <v>44938</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>45483.82479166667</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         <v>44964.5115162037</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27172,7 +27172,7 @@
         <v>45498</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27229,7 +27229,7 @@
         <v>44879</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27286,7 +27286,7 @@
         <v>45257.67958333333</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27343,7 +27343,7 @@
         <v>45018</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27400,7 +27400,7 @@
         <v>45607.56773148148</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27457,7 +27457,7 @@
         <v>44867</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>45301.67736111111</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>45482.54108796296</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27628,7 +27628,7 @@
         <v>45513.55840277778</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>45513.56527777778</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27742,7 +27742,7 @@
         <v>45110.4184375</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27799,7 +27799,7 @@
         <v>45096.45247685185</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27856,7 +27856,7 @@
         <v>45111.48395833333</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27913,7 +27913,7 @@
         <v>45415.47848379629</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27970,7 +27970,7 @@
         <v>45391.41976851852</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28027,7 +28027,7 @@
         <v>45111.48787037037</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28084,7 +28084,7 @@
         <v>45588.65545138889</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28141,7 +28141,7 @@
         <v>45485.45778935185</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28198,7 +28198,7 @@
         <v>45618.56787037037</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>44967.45122685185</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28312,7 +28312,7 @@
         <v>45467.74417824074</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28369,7 +28369,7 @@
         <v>45481.58048611111</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28426,7 +28426,7 @@
         <v>45086</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28483,7 +28483,7 @@
         <v>44159</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28540,7 +28540,7 @@
         <v>44918.50106481482</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28597,7 +28597,7 @@
         <v>45632.37459490741</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28654,7 +28654,7 @@
         <v>45378.32185185186</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>45498.673125</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>44893</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28825,7 +28825,7 @@
         <v>45275.32266203704</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28882,7 +28882,7 @@
         <v>45540.50098379629</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>45581.57016203704</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>44127</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29053,7 +29053,7 @@
         <v>45481.55984953704</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>45539.38744212963</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29167,7 +29167,7 @@
         <v>44630</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29224,7 +29224,7 @@
         <v>45539.65212962963</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29281,7 +29281,7 @@
         <v>44893</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29338,7 +29338,7 @@
         <v>45784.74996527778</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>45699.45671296296</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>45463</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>45630.47564814815</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
         <v>44994.40635416667</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>45574.35809027778</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29680,7 +29680,7 @@
         <v>45559.38876157408</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>44587</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29794,7 +29794,7 @@
         <v>45000.47998842593</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>45552.36759259259</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29908,7 +29908,7 @@
         <v>45098.30535879629</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29965,7 +29965,7 @@
         <v>44935</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30022,7 +30022,7 @@
         <v>44603</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30079,7 +30079,7 @@
         <v>44999.86172453704</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30136,7 +30136,7 @@
         <v>44999.8625</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30193,7 +30193,7 @@
         <v>44964.50894675926</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>45113.56574074074</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30307,7 +30307,7 @@
         <v>45517.8162037037</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>45518.40657407408</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30421,7 +30421,7 @@
         <v>44638.55256944444</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30478,7 +30478,7 @@
         <v>45747.42633101852</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
         <v>45747.42958333333</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30592,7 +30592,7 @@
         <v>45726.44471064815</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>45786.52931712963</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30706,7 +30706,7 @@
         <v>45786.52996527778</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30763,7 +30763,7 @@
         <v>44788</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30820,7 +30820,7 @@
         <v>45666</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30877,7 +30877,7 @@
         <v>45581.57958333333</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30934,7 +30934,7 @@
         <v>45548</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30991,7 +30991,7 @@
         <v>45001.59209490741</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31048,7 +31048,7 @@
         <v>44587.48847222222</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31105,7 +31105,7 @@
         <v>45020</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31162,7 +31162,7 @@
         <v>45569.44295138889</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31219,7 +31219,7 @@
         <v>45415.48979166667</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31276,7 +31276,7 @@
         <v>44918</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>45009</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31390,7 +31390,7 @@
         <v>44959.66407407408</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31447,7 +31447,7 @@
         <v>44966</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31504,7 +31504,7 @@
         <v>44564.62598379629</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31561,7 +31561,7 @@
         <v>45786.52878472222</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31618,7 +31618,7 @@
         <v>45495</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>44600</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31732,7 +31732,7 @@
         <v>45111.48225694444</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31789,7 +31789,7 @@
         <v>45111.48636574074</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31846,7 +31846,7 @@
         <v>45621.46103009259</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31903,7 +31903,7 @@
         <v>45114.58148148148</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31960,7 +31960,7 @@
         <v>45026.82216435186</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32017,7 +32017,7 @@
         <v>45460.62172453704</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>44910.54231481482</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32131,7 +32131,7 @@
         <v>45567.42011574074</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>45554.62944444444</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32245,7 +32245,7 @@
         <v>45533.61996527778</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32307,7 +32307,7 @@
         <v>45790.44976851852</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>45726.62721064815</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32421,7 +32421,7 @@
         <v>45698.69016203703</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32478,7 +32478,7 @@
         <v>45632.44886574074</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>45741.37270833334</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32592,7 +32592,7 @@
         <v>45567</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>45552.36484953704</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32706,7 +32706,7 @@
         <v>45145</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32763,7 +32763,7 @@
         <v>45271.66576388889</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32820,7 +32820,7 @@
         <v>45791.89865740741</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32877,7 +32877,7 @@
         <v>45632.72635416667</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32934,7 +32934,7 @@
         <v>45582.41200231481</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32991,7 +32991,7 @@
         <v>44585.51060185185</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33048,7 +33048,7 @@
         <v>45572.48293981481</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33105,7 +33105,7 @@
         <v>44475</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33162,7 +33162,7 @@
         <v>45001.43854166667</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33219,7 +33219,7 @@
         <v>45182.78834490741</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33276,7 +33276,7 @@
         <v>45202.4209837963</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33333,7 +33333,7 @@
         <v>45837.77701388889</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33390,7 +33390,7 @@
         <v>45835.48267361111</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33447,7 +33447,7 @@
         <v>45835.48445601852</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33504,7 +33504,7 @@
         <v>45835.48862268519</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33561,7 +33561,7 @@
         <v>45835.4924537037</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33618,7 +33618,7 @@
         <v>45377</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33675,7 +33675,7 @@
         <v>44943.62954861111</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33732,7 +33732,7 @@
         <v>44944.73487268519</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33789,7 +33789,7 @@
         <v>45671.46746527778</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33846,7 +33846,7 @@
         <v>45835.45099537037</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33903,7 +33903,7 @@
         <v>45837.77916666667</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33960,7 +33960,7 @@
         <v>45761.35990740741</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34017,7 +34017,7 @@
         <v>45761.4566550926</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34074,7 +34074,7 @@
         <v>45722.56731481481</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>45796</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34188,7 +34188,7 @@
         <v>44579.62225694444</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34245,7 +34245,7 @@
         <v>45835.44732638889</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34302,7 +34302,7 @@
         <v>45835.36229166666</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34364,7 +34364,7 @@
         <v>45394.50028935185</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34421,7 +34421,7 @@
         <v>45581.58418981481</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>44867</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34535,7 +34535,7 @@
         <v>45581.57333333333</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34592,7 +34592,7 @@
         <v>44643</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34649,7 +34649,7 @@
         <v>45835.44709490741</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34706,7 +34706,7 @@
         <v>45533.63056712963</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34768,7 +34768,7 @@
         <v>45328.38755787037</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34825,7 +34825,7 @@
         <v>45713.92412037037</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34882,7 +34882,7 @@
         <v>45588.67070601852</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34939,7 +34939,7 @@
         <v>44784.42528935185</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34996,7 +34996,7 @@
         <v>45176.72427083334</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35053,7 +35053,7 @@
         <v>45071</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35110,7 +35110,7 @@
         <v>45569.45017361111</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35167,7 +35167,7 @@
         <v>44999.35858796296</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35224,7 +35224,7 @@
         <v>45713.45311342592</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35281,7 +35281,7 @@
         <v>45170</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35338,7 +35338,7 @@
         <v>45735.58024305556</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35395,7 +35395,7 @@
         <v>44746.38834490741</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35452,7 +35452,7 @@
         <v>45840.59474537037</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35509,7 +35509,7 @@
         <v>45840.59853009259</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35566,7 +35566,7 @@
         <v>44795</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35623,7 +35623,7 @@
         <v>45168.89298611111</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35680,7 +35680,7 @@
         <v>45052</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35737,7 +35737,7 @@
         <v>45622</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35794,7 +35794,7 @@
         <v>45562.46342592593</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35851,7 +35851,7 @@
         <v>45434.55831018519</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35913,7 +35913,7 @@
         <v>45434.56398148148</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35975,7 +35975,7 @@
         <v>45075.43059027778</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36032,7 +36032,7 @@
         <v>45603.74959490741</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36089,7 +36089,7 @@
         <v>44784.62724537037</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36146,7 +36146,7 @@
         <v>45755.64450231481</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36203,7 +36203,7 @@
         <v>45623.95947916667</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36260,7 +36260,7 @@
         <v>44635</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36317,7 +36317,7 @@
         <v>45343.68038194445</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36374,7 +36374,7 @@
         <v>45527.68784722222</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>45841.7072337963</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36488,7 +36488,7 @@
         <v>45574.49298611111</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36545,7 +36545,7 @@
         <v>45715.44159722222</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36602,7 +36602,7 @@
         <v>44270.39765046296</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>44595.583125</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>45121.61318287037</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36783,7 +36783,7 @@
         <v>44992.4255787037</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36840,7 +36840,7 @@
         <v>45617.47570601852</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36897,7 +36897,7 @@
         <v>45841.70569444444</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36954,7 +36954,7 @@
         <v>45841.70868055556</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37011,7 +37011,7 @@
         <v>45211.52642361111</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37068,7 +37068,7 @@
         <v>45211.541875</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37125,7 +37125,7 @@
         <v>45650.37370370371</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37182,7 +37182,7 @@
         <v>45195.58452546296</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37239,7 +37239,7 @@
         <v>45845.49414351852</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37296,7 +37296,7 @@
         <v>45635.66409722222</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37353,7 +37353,7 @@
         <v>45351.6062962963</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37410,7 +37410,7 @@
         <v>45845.43803240741</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37467,7 +37467,7 @@
         <v>44981.58834490741</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37524,7 +37524,7 @@
         <v>45401.53033564815</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37581,7 +37581,7 @@
         <v>45208</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37638,7 +37638,7 @@
         <v>45804.6953587963</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37700,7 +37700,7 @@
         <v>45729.36868055556</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37757,7 +37757,7 @@
         <v>45804.708125</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37819,7 +37819,7 @@
         <v>45804.39141203704</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37876,7 +37876,7 @@
         <v>45845.42015046296</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37933,7 +37933,7 @@
         <v>45567</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37990,7 +37990,7 @@
         <v>45148</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38047,7 +38047,7 @@
         <v>45148</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38104,7 +38104,7 @@
         <v>45163.41376157408</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38161,7 +38161,7 @@
         <v>44994.42113425926</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38218,7 +38218,7 @@
         <v>45434.56291666667</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38280,7 +38280,7 @@
         <v>45804.67065972222</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38337,7 +38337,7 @@
         <v>45079.87827546296</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38394,7 +38394,7 @@
         <v>45804.44519675926</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38451,7 +38451,7 @@
         <v>45805.39247685186</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>45254.62489583333</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38570,7 +38570,7 @@
         <v>44958.61047453704</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38627,7 +38627,7 @@
         <v>44965</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38684,7 +38684,7 @@
         <v>45113.43921296296</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38741,7 +38741,7 @@
         <v>45334.78826388889</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38798,7 +38798,7 @@
         <v>45805</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>44973.43075231482</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38912,7 +38912,7 @@
         <v>44340</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38969,7 +38969,7 @@
         <v>44825.4336574074</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39026,7 +39026,7 @@
         <v>45847.91280092593</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39083,7 +39083,7 @@
         <v>45805.52983796296</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39140,7 +39140,7 @@
         <v>45128</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39197,7 +39197,7 @@
         <v>44977</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39254,7 +39254,7 @@
         <v>45196.57247685185</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39311,7 +39311,7 @@
         <v>44964.44356481481</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39368,7 +39368,7 @@
         <v>44974.56377314815</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>45610.59094907407</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39487,7 +39487,7 @@
         <v>45236</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39544,7 +39544,7 @@
         <v>44663</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39601,7 +39601,7 @@
         <v>45187</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39658,7 +39658,7 @@
         <v>45187.42854166667</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>44894.49538194444</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39772,7 +39772,7 @@
         <v>44992</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39829,7 +39829,7 @@
         <v>45707.3793287037</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39886,7 +39886,7 @@
         <v>45736.50743055555</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39943,7 +39943,7 @@
         <v>45020</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40000,7 +40000,7 @@
         <v>44172</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40057,7 +40057,7 @@
         <v>45114.49505787037</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40114,7 +40114,7 @@
         <v>45041</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40171,7 +40171,7 @@
         <v>45810.00048611111</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40228,7 +40228,7 @@
         <v>45632.36706018518</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40285,7 +40285,7 @@
         <v>44745.84396990741</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40342,7 +40342,7 @@
         <v>45163.63621527778</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40404,7 +40404,7 @@
         <v>45308.59001157407</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40461,7 +40461,7 @@
         <v>45699.44291666667</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40518,7 +40518,7 @@
         <v>45174</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40575,7 +40575,7 @@
         <v>45615.48927083334</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40632,7 +40632,7 @@
         <v>45853.87112268519</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40689,7 +40689,7 @@
         <v>45811.45460648148</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40746,7 +40746,7 @@
         <v>45722.48634259259</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40803,7 +40803,7 @@
         <v>45811.66133101852</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40860,7 +40860,7 @@
         <v>45853.87599537037</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40917,7 +40917,7 @@
         <v>45853.88070601852</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40974,7 +40974,7 @@
         <v>45811.65975694444</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41031,7 +41031,7 @@
         <v>45635.66695601852</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41088,7 +41088,7 @@
         <v>45719.84378472222</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41145,7 +41145,7 @@
         <v>45568.30189814815</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41202,7 +41202,7 @@
         <v>45033.76043981482</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41259,7 +41259,7 @@
         <v>45698.7259837963</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41316,7 +41316,7 @@
         <v>45699.45392361111</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41373,7 +41373,7 @@
         <v>45154.49831018518</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>45761.4437962963</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41487,7 +41487,7 @@
         <v>45299.62576388889</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41544,7 +41544,7 @@
         <v>45630.35827546296</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41601,7 +41601,7 @@
         <v>45700.68289351852</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41658,7 +41658,7 @@
         <v>44176</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41715,7 +41715,7 @@
         <v>45814.3865625</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41772,7 +41772,7 @@
         <v>45814.38221064815</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41829,7 +41829,7 @@
         <v>45623.9525462963</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41886,7 +41886,7 @@
         <v>44790.49523148148</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41943,7 +41943,7 @@
         <v>45260.4716550926</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42000,7 +42000,7 @@
         <v>44820</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42057,7 +42057,7 @@
         <v>44693.62822916666</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42119,7 +42119,7 @@
         <v>45769</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42176,7 +42176,7 @@
         <v>45245.63574074074</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42233,7 +42233,7 @@
         <v>45858.60641203704</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
         <v>45818.59261574074</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         <v>45280.66769675926</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42409,7 +42409,7 @@
         <v>44956</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42471,7 +42471,7 @@
         <v>45317</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42533,7 +42533,7 @@
         <v>45818.5862037037</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42595,7 +42595,7 @@
         <v>45818.58993055556</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>45858.66019675926</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42714,7 +42714,7 @@
         <v>45219.69356481481</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42771,7 +42771,7 @@
         <v>45189</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42828,7 +42828,7 @@
         <v>45379</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42885,7 +42885,7 @@
         <v>45225.60192129629</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42942,7 +42942,7 @@
         <v>45658.80232638889</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42999,7 +42999,7 @@
         <v>45658.80827546296</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43056,7 +43056,7 @@
         <v>45063.49936342592</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43113,7 +43113,7 @@
         <v>45237.63225694445</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43170,7 +43170,7 @@
         <v>45237.64408564815</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43227,7 +43227,7 @@
         <v>44769.45805555556</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43284,7 +43284,7 @@
         <v>45818.58769675926</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43346,7 +43346,7 @@
         <v>45818.595625</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43408,7 +43408,7 @@
         <v>45817.88496527778</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43465,7 +43465,7 @@
         <v>45301.67554398148</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43522,7 +43522,7 @@
         <v>45768.65611111111</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43579,7 +43579,7 @@
         <v>44546</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43636,7 +43636,7 @@
         <v>44732.3659837963</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43693,7 +43693,7 @@
         <v>45743.40881944444</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43750,7 +43750,7 @@
         <v>45224.60075231481</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43812,7 +43812,7 @@
         <v>45646.38200231481</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43869,7 +43869,7 @@
         <v>45820.33930555556</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43926,7 +43926,7 @@
         <v>44377</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43983,7 +43983,7 @@
         <v>44790.49040509259</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44040,7 +44040,7 @@
         <v>45820.03518518519</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44097,7 +44097,7 @@
         <v>45820.03976851852</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44154,7 +44154,7 @@
         <v>45820.33708333333</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44211,7 +44211,7 @@
         <v>45820.34128472222</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>45323.53744212963</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44325,7 +44325,7 @@
         <v>45819.61060185185</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44382,7 +44382,7 @@
         <v>45533.55362268518</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44439,7 +44439,7 @@
         <v>44988</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44496,7 +44496,7 @@
         <v>45764.44931712963</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44558,7 +44558,7 @@
         <v>45763.59436342592</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44615,7 +44615,7 @@
         <v>45355.54138888889</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44672,7 +44672,7 @@
         <v>45361.87975694444</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44729,7 +44729,7 @@
         <v>45330</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44786,7 +44786,7 @@
         <v>45330</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44843,7 +44843,7 @@
         <v>44270.38002314815</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44905,7 +44905,7 @@
         <v>44839.4528125</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44962,7 +44962,7 @@
         <v>45217.47834490741</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45019,7 +45019,7 @@
         <v>45121</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45076,7 +45076,7 @@
         <v>44502</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45133,7 +45133,7 @@
         <v>44578.32717592592</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45190,7 +45190,7 @@
         <v>44897</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45247,7 +45247,7 @@
         <v>45825.5796875</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45304,7 +45304,7 @@
         <v>45747.43196759259</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45361,7 +45361,7 @@
         <v>45825.58672453704</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45418,7 +45418,7 @@
         <v>45867.51630787037</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45475,7 +45475,7 @@
         <v>45867.56320601852</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45532,7 +45532,7 @@
         <v>45867.63094907408</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45589,7 +45589,7 @@
         <v>45867.50792824074</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45646,7 +45646,7 @@
         <v>45867.68625</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45703,7 +45703,7 @@
         <v>45867.69346064814</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45760,7 +45760,7 @@
         <v>45091.67936342592</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45817,7 +45817,7 @@
         <v>45259.51916666667</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45879,7 +45879,7 @@
         <v>45259.52020833334</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45941,7 +45941,7 @@
         <v>45734.62017361111</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45998,7 +45998,7 @@
         <v>45867.64663194444</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46055,7 +46055,7 @@
         <v>45825.57805555555</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46112,7 +46112,7 @@
         <v>45825.50280092593</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46169,7 +46169,7 @@
         <v>45825.57680555555</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46226,7 +46226,7 @@
         <v>45826.66646990741</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46283,7 +46283,7 @@
         <v>45698.53336805556</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46340,7 +46340,7 @@
         <v>44418</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46397,7 +46397,7 @@
         <v>45827</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46454,7 +46454,7 @@
         <v>45870.52111111111</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46511,7 +46511,7 @@
         <v>45870.51708333333</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46568,7 +46568,7 @@
         <v>45870.52005787037</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46625,7 +46625,7 @@
         <v>45870.52142361111</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46682,7 +46682,7 @@
         <v>45870.51958333333</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46739,7 +46739,7 @@
         <v>45869.62276620371</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46796,7 +46796,7 @@
         <v>45749.56196759259</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46858,7 +46858,7 @@
         <v>45827</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46915,7 +46915,7 @@
         <v>45349.54434027777</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46972,7 +46972,7 @@
         <v>45345.83557870371</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47029,7 +47029,7 @@
         <v>45831</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47086,7 +47086,7 @@
         <v>45832.46649305556</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47143,7 +47143,7 @@
         <v>45732.75637731481</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47200,7 +47200,7 @@
         <v>45732.76936342593</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47257,7 +47257,7 @@
         <v>45090.89653935185</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47314,7 +47314,7 @@
         <v>45090.89880787037</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47371,7 +47371,7 @@
         <v>44599</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47428,7 +47428,7 @@
         <v>45201</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47485,7 +47485,7 @@
         <v>45674.71810185185</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47542,7 +47542,7 @@
         <v>45588.66457175926</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47599,7 +47599,7 @@
         <v>45275.41833333333</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47656,7 +47656,7 @@
         <v>44495</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47713,7 +47713,7 @@
         <v>45874.57109953704</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47770,7 +47770,7 @@
         <v>45832.34540509259</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47827,7 +47827,7 @@
         <v>45832.46146990741</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47884,7 +47884,7 @@
         <v>44848.59133101852</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47941,7 +47941,7 @@
         <v>45440.28329861111</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47998,7 +47998,7 @@
         <v>44790.45876157407</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48055,7 +48055,7 @@
         <v>44861</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48112,7 +48112,7 @@
         <v>44879.62173611111</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48169,7 +48169,7 @@
         <v>45833.64563657407</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48226,7 +48226,7 @@
         <v>45833.64814814815</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48283,7 +48283,7 @@
         <v>45147</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48340,7 +48340,7 @@
         <v>45875.47454861111</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48397,7 +48397,7 @@
         <v>44987.54104166666</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48454,7 +48454,7 @@
         <v>45875.45716435185</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48511,7 +48511,7 @@
         <v>44060</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48568,7 +48568,7 @@
         <v>45834.64667824074</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48630,7 +48630,7 @@
         <v>45761.44584490741</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48687,7 +48687,7 @@
         <v>45875.42716435185</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48744,7 +48744,7 @@
         <v>45709.62280092593</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48801,7 +48801,7 @@
         <v>45834.65040509259</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48863,7 +48863,7 @@
         <v>45834.65197916667</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48925,7 +48925,7 @@
         <v>45833.64237268519</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48982,7 +48982,7 @@
         <v>45128.37305555555</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49039,7 +49039,7 @@
         <v>45481.56722222222</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49096,7 +49096,7 @@
         <v>44900.57393518519</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49153,7 +49153,7 @@
         <v>45394.66887731481</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49210,7 +49210,7 @@
         <v>44857.65989583333</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49267,7 +49267,7 @@
         <v>44585.50431712963</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49324,7 +49324,7 @@
         <v>44992.34151620371</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49386,7 +49386,7 @@
         <v>44542.90072916666</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>44453.56578703703</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49500,7 +49500,7 @@
         <v>44431</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49557,7 +49557,7 @@
         <v>44566</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49614,7 +49614,7 @@
         <v>45743.41148148148</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49671,7 +49671,7 @@
         <v>45261.44914351852</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49728,7 +49728,7 @@
         <v>45048.59699074074</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49785,7 +49785,7 @@
         <v>45503.5658912037</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49842,7 +49842,7 @@
         <v>44596</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49899,7 +49899,7 @@
         <v>45568.36879629629</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49956,7 +49956,7 @@
         <v>44077</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50013,7 +50013,7 @@
         <v>44952.35775462963</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50070,7 +50070,7 @@
         <v>45093.62777777778</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50132,7 +50132,7 @@
         <v>45215.5959375</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50189,7 +50189,7 @@
         <v>44992.62498842592</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50246,7 +50246,7 @@
         <v>44967.44255787037</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>44600</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50360,7 +50360,7 @@
         <v>45187.60813657408</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50417,7 +50417,7 @@
         <v>44237</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50474,7 +50474,7 @@
         <v>44452</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50531,7 +50531,7 @@
         <v>45009.4671875</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50588,7 +50588,7 @@
         <v>45705.74418981482</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50645,7 +50645,7 @@
         <v>44410</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50702,7 +50702,7 @@
         <v>45111</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50759,7 +50759,7 @@
         <v>44909</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50816,7 +50816,7 @@
         <v>45637.66542824074</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>44310</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50930,7 +50930,7 @@
         <v>45041.63380787037</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50987,7 +50987,7 @@
         <v>44961</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51044,7 +51044,7 @@
         <v>44916.55414351852</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51101,7 +51101,7 @@
         <v>45722.56422453704</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51158,7 +51158,7 @@
         <v>45300.3794212963</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51215,7 +51215,7 @@
         <v>45245.36174768519</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51272,7 +51272,7 @@
         <v>44061</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51329,7 +51329,7 @@
         <v>44999.36081018519</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51386,7 +51386,7 @@
         <v>45495</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51443,7 +51443,7 @@
         <v>45128.9325</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51500,7 +51500,7 @@
         <v>45128.93540509259</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51557,7 +51557,7 @@
         <v>45320.89128472222</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51614,7 +51614,7 @@
         <v>44613</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51671,7 +51671,7 @@
         <v>44992</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51728,7 +51728,7 @@
         <v>45028</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51785,7 +51785,7 @@
         <v>45453.36854166666</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51842,7 +51842,7 @@
         <v>45211.55472222222</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51904,7 +51904,7 @@
         <v>45639.56185185185</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51961,7 +51961,7 @@
         <v>44540</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52018,7 +52018,7 @@
         <v>45174.31395833333</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52075,7 +52075,7 @@
         <v>45446.36865740741</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52137,7 +52137,7 @@
         <v>44981.64725694444</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>

--- a/Översikt VIMMERBY.xlsx
+++ b/Översikt VIMMERBY.xlsx
@@ -567,7 +567,7 @@
         <v>44811</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
         <v>44811</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44811</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44811</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>45314</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>45738.79180555556</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>44939</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>45301.67922453704</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>45755</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45377.54726851852</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>45748</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>45678.64175925926</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>45821</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>45121.60543981481</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>44245</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>44811</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>45628</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>45742</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>45020</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>44424</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>44426.64793981481</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44386</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>45786.52827546297</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>45008.60878472222</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>44943</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>45760.34877314815</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>45072</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>45048</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>44371</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>44403</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>45399.71412037037</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>45125</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>45104</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>45667</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>45574.42767361111</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>44082</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>45649</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>45821</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>45825.58484953704</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>44236</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>45713</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>45168</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>45168</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>44075</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>45224</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>45077</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>44377.61104166666</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>44064</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>44068</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>44083</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>44102</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>44130</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         <v>44287.33261574074</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>44281.79269675926</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>44270.67071759259</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         <v>44210</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>44490.38613425926</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>44481.47483796296</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>44447</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>44350</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>44375.39033564815</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>44614</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>44215</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>44670</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>44670</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         <v>44070.39203703704</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>44063</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>44307</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>44350</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>44105</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>44225</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>44327.47658564815</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>44070</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>44509</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>44406</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
         <v>44230.58883101852</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>44480</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>44063</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>44238</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>44585.51829861111</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>44824.53434027778</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>44418</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>44785.40800925926</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>44578.47597222222</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>44516.59703703703</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>44862</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>44826.68010416667</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>44603</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>44588</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>44404.87505787037</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>44483.58295138889</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>44354</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>44542.8859375</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>44512.70245370371</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>44494</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>44790</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>44090</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         <v>44221.39408564815</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>44261</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>44530.38055555556</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
         <v>44588</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>44588</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>44790</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>44790.47628472222</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
         <v>44175.3815625</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         <v>44175.40881944444</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>44062</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8286,7 +8286,7 @@
         <v>44312</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>44475</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>44385</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>44124.59795138889</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>44237.8550925926</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8571,7 +8571,7 @@
         <v>44410.71038194445</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         <v>44279.33400462963</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         <v>44175</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         <v>44670</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>44365</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>44169</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         <v>44273</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>44301.36048611111</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>44271.37226851852</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>44729.28226851852</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>44340.54472222222</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>44340</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>44774</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>44061</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         <v>44733</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>44733</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>44063</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>44154</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>44371.62743055556</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>44386.40783564815</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         <v>44480</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>44245</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>44070.40998842593</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9887,7 +9887,7 @@
         <v>44337</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         <v>44102</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>44463.29439814815</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>44588</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         <v>44117</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>44789</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>44377</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10286,7 +10286,7 @@
         <v>44379</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
         <v>44508</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>44091</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>44634.69703703704</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10524,7 +10524,7 @@
         <v>44480</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>44340.58002314815</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>44769.45422453704</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10695,7 +10695,7 @@
         <v>44092</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10752,7 +10752,7 @@
         <v>44085</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>44612.86762731482</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>44142</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>44383</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>44476</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>44305.40046296296</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
         <v>44418</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11151,7 +11151,7 @@
         <v>44447</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         <v>44517</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
         <v>44854</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11327,7 +11327,7 @@
         <v>44819</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11384,7 +11384,7 @@
         <v>44824</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11441,7 +11441,7 @@
         <v>44369</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11498,7 +11498,7 @@
         <v>44742</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11555,7 +11555,7 @@
         <v>44832.67608796297</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         <v>44451.8375</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>44823</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
         <v>44621</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>44270</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
         <v>44217.79856481482</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         <v>44341</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11954,7 +11954,7 @@
         <v>44070</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12011,7 +12011,7 @@
         <v>44608</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>44447.34237268518</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12125,7 +12125,7 @@
         <v>44172</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12182,7 +12182,7 @@
         <v>44384</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12239,7 +12239,7 @@
         <v>44790.48503472222</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12296,7 +12296,7 @@
         <v>44854.59157407407</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>44294</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>44116</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>44620</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>44876.48346064815</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>44733.43092592592</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12638,7 +12638,7 @@
         <v>44480</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>44089.78633101852</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         <v>44609</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>44284.42348379629</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>44088</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>44203</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>44088</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>44525.63913194444</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>44421</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>44186</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>44279.64934027778</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13270,7 +13270,7 @@
         <v>44662</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>44095</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>44273</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>44070</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13503,7 +13503,7 @@
         <v>44266.7240625</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13565,7 +13565,7 @@
         <v>44278.63479166666</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>44270.49743055556</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>44564</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>44375.38789351852</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>44386</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>44427</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>44612.86554398148</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>44466.34726851852</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>44866.81100694444</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         <v>44379</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>44470.44232638889</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>44284.44574074074</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>44722.48768518519</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14326,7 +14326,7 @@
         <v>44776</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>44634</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>44636</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>44608.50458333334</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>44817</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         <v>44817.57988425926</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>44851.95016203704</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>44060</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>44294</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>44294</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         <v>44676.85248842592</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>44292</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>44604</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
         <v>45483.82834490741</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15129,7 +15129,7 @@
         <v>45090.38012731481</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>44644</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>44305</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15300,7 +15300,7 @@
         <v>45196</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15357,7 +15357,7 @@
         <v>44607</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>44949</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>45411.47335648148</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>45121.58699074074</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>45569.44684027778</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>45377.40043981482</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>45698.51711805556</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>45211.43555555555</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15823,7 +15823,7 @@
         <v>45391.41310185185</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
         <v>45086.63194444445</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15937,7 +15937,7 @@
         <v>45097.40524305555</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>45086.63334490741</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>45100.4062962963</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>45086</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>45232</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16227,7 +16227,7 @@
         <v>45425.57538194444</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>45525.41762731481</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>45565.40657407408</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>44720.53898148148</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>44243</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         <v>45090</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16569,7 +16569,7 @@
         <v>45728.54832175926</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16626,7 +16626,7 @@
         <v>45749.60487268519</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>45245.5735300926</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16745,7 +16745,7 @@
         <v>44539</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>45450.51092592593</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>45257.67958333333</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>45018</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         <v>45607.56773148148</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17030,7 +17030,7 @@
         <v>44553</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17087,7 +17087,7 @@
         <v>45301.67736111111</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>44895.62296296296</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>45513.55840277778</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>45513.56527777778</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>44466.34962962963</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17372,7 +17372,7 @@
         <v>45110.4184375</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         <v>44964.5115162037</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>45105</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>44278.54855324074</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>45415.47848379629</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         <v>45308.61152777778</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>45299.47513888889</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>45391.41976851852</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17828,7 +17828,7 @@
         <v>45111.48787037037</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>44377.49684027778</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         <v>45539.66027777778</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18004,7 +18004,7 @@
         <v>44833.60123842592</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18061,7 +18061,7 @@
         <v>44867</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18118,7 +18118,7 @@
         <v>45215.59743055556</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>44789</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
         <v>45481.58048611111</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18289,7 +18289,7 @@
         <v>45096.45247685185</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18346,7 +18346,7 @@
         <v>45111.48395833333</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>45588.65545138889</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18460,7 +18460,7 @@
         <v>44967.45122685185</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18517,7 +18517,7 @@
         <v>45581.57016203704</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18574,7 +18574,7 @@
         <v>45481.55984953704</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18631,7 +18631,7 @@
         <v>45539.38744212963</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18688,7 +18688,7 @@
         <v>45784.74996527778</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18745,7 +18745,7 @@
         <v>45539.65212962963</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18802,7 +18802,7 @@
         <v>45463</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>45630.47564814815</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>45000.47998842593</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18973,7 +18973,7 @@
         <v>45552.36759259259</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19030,7 +19030,7 @@
         <v>45098.30535879629</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19087,7 +19087,7 @@
         <v>45786.52931712963</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19144,7 +19144,7 @@
         <v>45786.52996527778</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>45113.56574074074</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>45747.42633101852</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19315,7 +19315,7 @@
         <v>45747.42958333333</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>45726.44471064815</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>44788</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>45581.57958333333</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19543,7 +19543,7 @@
         <v>45548</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19600,7 +19600,7 @@
         <v>45786.52878472222</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19657,7 +19657,7 @@
         <v>45020</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19714,7 +19714,7 @@
         <v>45569.44295138889</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19771,7 +19771,7 @@
         <v>45415.48979166667</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19828,7 +19828,7 @@
         <v>45009</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19885,7 +19885,7 @@
         <v>45790.44976851852</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19942,7 +19942,7 @@
         <v>45726.62721064815</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         <v>45698.69016203703</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20056,7 +20056,7 @@
         <v>45111.48225694444</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20113,7 +20113,7 @@
         <v>45111.48636574074</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>45621.46103009259</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>45114.58148148148</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
         <v>45460.62172453704</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20341,7 +20341,7 @@
         <v>45533.61996527778</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20403,7 +20403,7 @@
         <v>45791.89865740741</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20460,7 +20460,7 @@
         <v>44852</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20517,7 +20517,7 @@
         <v>45384.66917824074</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>45632.44886574074</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20631,7 +20631,7 @@
         <v>45741.37270833334</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20688,7 +20688,7 @@
         <v>45552.36484953704</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>45271.66576388889</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20802,7 +20802,7 @@
         <v>45796</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20859,7 +20859,7 @@
         <v>45114.55136574074</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>44992</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20978,7 +20978,7 @@
         <v>45582.41200231481</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21035,7 +21035,7 @@
         <v>44585.51060185185</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>45572.48293981481</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21149,7 +21149,7 @@
         <v>45001.43854166667</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21206,7 +21206,7 @@
         <v>45182.78834490741</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21263,7 +21263,7 @@
         <v>45377</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21320,7 +21320,7 @@
         <v>45603.74959490741</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21377,7 +21377,7 @@
         <v>45671.46746527778</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>45722.56731481481</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>45527.68784722222</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>44579.62225694444</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21605,7 +21605,7 @@
         <v>45574.49298611111</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21662,7 +21662,7 @@
         <v>45715.44159722222</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21719,7 +21719,7 @@
         <v>44992.4255787037</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21776,7 +21776,7 @@
         <v>44643</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21833,7 +21833,7 @@
         <v>45845.49414351852</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
         <v>45635.66409722222</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21947,7 +21947,7 @@
         <v>45845.43803240741</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
         <v>45328.38755787037</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22061,7 +22061,7 @@
         <v>45713.92412037037</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22118,7 +22118,7 @@
         <v>45401.53033564815</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22175,7 +22175,7 @@
         <v>45804.6953587963</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22237,7 +22237,7 @@
         <v>45804.708125</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22299,7 +22299,7 @@
         <v>45804.39141203704</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>45845.42015046296</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22413,7 +22413,7 @@
         <v>45071</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22470,7 +22470,7 @@
         <v>45804.67065972222</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22527,7 +22527,7 @@
         <v>45804.44519675926</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22584,7 +22584,7 @@
         <v>45805.39247685186</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22641,7 +22641,7 @@
         <v>45257.70313657408</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22698,7 +22698,7 @@
         <v>44795</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22755,7 +22755,7 @@
         <v>45168.89298611111</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22812,7 +22812,7 @@
         <v>44392</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22874,7 +22874,7 @@
         <v>45266.32614583334</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22931,7 +22931,7 @@
         <v>45805</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22988,7 +22988,7 @@
         <v>45052</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23045,7 +23045,7 @@
         <v>45317.40372685185</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23107,7 +23107,7 @@
         <v>44064</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>45309.59487268519</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23221,7 +23221,7 @@
         <v>45359.44837962963</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>44488.35878472222</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>44467.83386574074</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>45482.52887731481</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23449,7 +23449,7 @@
         <v>45371.36359953704</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23506,7 +23506,7 @@
         <v>45371.45865740741</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23563,7 +23563,7 @@
         <v>45359.45038194444</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23620,7 +23620,7 @@
         <v>45847.91280092593</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23677,7 +23677,7 @@
         <v>44861.52505787037</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23734,7 +23734,7 @@
         <v>45533.54429398148</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23791,7 +23791,7 @@
         <v>45533.60232638889</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>45533.60770833334</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23915,7 +23915,7 @@
         <v>45805.52983796296</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
         <v>45755.64450231481</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24029,7 +24029,7 @@
         <v>45446.36774305555</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24091,7 +24091,7 @@
         <v>45623.95947916667</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24148,7 +24148,7 @@
         <v>44635</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24205,7 +24205,7 @@
         <v>45147.67096064815</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24262,7 +24262,7 @@
         <v>45147.67172453704</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24319,7 +24319,7 @@
         <v>44063</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24376,7 +24376,7 @@
         <v>44595.583125</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24433,7 +24433,7 @@
         <v>45211.52642361111</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24490,7 +24490,7 @@
         <v>45211.541875</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24547,7 +24547,7 @@
         <v>45650.37370370371</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24604,7 +24604,7 @@
         <v>45195.58452546296</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>45351.6062962963</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24718,7 +24718,7 @@
         <v>45526.3865625</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24780,7 +24780,7 @@
         <v>45243.84869212963</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24837,7 +24837,7 @@
         <v>45208</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24894,7 +24894,7 @@
         <v>45729.36868055556</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24951,7 +24951,7 @@
         <v>45148</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>45148</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25065,7 +25065,7 @@
         <v>45163.41376157408</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25122,7 +25122,7 @@
         <v>45434.56291666667</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25184,7 +25184,7 @@
         <v>45810.00048611111</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25241,7 +25241,7 @@
         <v>44083</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25298,7 +25298,7 @@
         <v>44949</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25355,7 +25355,7 @@
         <v>45079.87827546296</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25412,7 +25412,7 @@
         <v>45254.62489583333</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>45171.96248842592</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25531,7 +25531,7 @@
         <v>45113.43921296296</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>45030.71012731481</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>44510.52157407408</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25702,7 +25702,7 @@
         <v>44984</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>44598</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25816,7 +25816,7 @@
         <v>44938</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
         <v>45483.82479166667</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25935,7 +25935,7 @@
         <v>45498</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25992,7 +25992,7 @@
         <v>45853.87112268519</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26049,7 +26049,7 @@
         <v>44879</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26106,7 +26106,7 @@
         <v>45811.45460648148</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26163,7 +26163,7 @@
         <v>45811.66133101852</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26220,7 +26220,7 @@
         <v>44825.4336574074</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>45853.87599537037</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26334,7 +26334,7 @@
         <v>45853.88070601852</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26391,7 +26391,7 @@
         <v>45811.65975694444</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26448,7 +26448,7 @@
         <v>45482.54108796296</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26505,7 +26505,7 @@
         <v>45128</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>45196.57247685185</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26619,7 +26619,7 @@
         <v>45236</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26676,7 +26676,7 @@
         <v>44663</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26733,7 +26733,7 @@
         <v>45187</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26790,7 +26790,7 @@
         <v>45814.3865625</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26847,7 +26847,7 @@
         <v>45485.45778935185</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26904,7 +26904,7 @@
         <v>45187.42854166667</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26961,7 +26961,7 @@
         <v>45618.56787037037</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27018,7 +27018,7 @@
         <v>45814.38221064815</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27075,7 +27075,7 @@
         <v>45467.74417824074</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27132,7 +27132,7 @@
         <v>45086</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27189,7 +27189,7 @@
         <v>44159</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>45707.3793287037</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>45736.50743055555</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27360,7 +27360,7 @@
         <v>44918.50106481482</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27417,7 +27417,7 @@
         <v>44172</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27474,7 +27474,7 @@
         <v>45632.37459490741</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27531,7 +27531,7 @@
         <v>45378.32185185186</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27588,7 +27588,7 @@
         <v>45498.673125</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27645,7 +27645,7 @@
         <v>44893</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27702,7 +27702,7 @@
         <v>45275.32266203704</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27759,7 +27759,7 @@
         <v>45540.50098379629</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27816,7 +27816,7 @@
         <v>45858.60641203704</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27873,7 +27873,7 @@
         <v>45818.59261574074</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         <v>45818.5862037037</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27997,7 +27997,7 @@
         <v>45818.58993055556</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28059,7 +28059,7 @@
         <v>45858.66019675926</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28116,7 +28116,7 @@
         <v>44127</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28173,7 +28173,7 @@
         <v>44630</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28230,7 +28230,7 @@
         <v>44893</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28287,7 +28287,7 @@
         <v>45818.58769675926</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>45818.595625</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>45817.88496527778</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28468,7 +28468,7 @@
         <v>45699.45671296296</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>45308.59001157407</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28582,7 +28582,7 @@
         <v>45699.44291666667</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28639,7 +28639,7 @@
         <v>44994.40635416667</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28696,7 +28696,7 @@
         <v>45174</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28753,7 +28753,7 @@
         <v>45574.35809027778</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28810,7 +28810,7 @@
         <v>45559.38876157408</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28867,7 +28867,7 @@
         <v>44587</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28924,7 +28924,7 @@
         <v>45820.33930555556</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28981,7 +28981,7 @@
         <v>45722.48634259259</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29038,7 +29038,7 @@
         <v>45820.03518518519</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29095,7 +29095,7 @@
         <v>45820.03976851852</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29152,7 +29152,7 @@
         <v>45820.33708333333</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29209,7 +29209,7 @@
         <v>45820.34128472222</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29266,7 +29266,7 @@
         <v>45819.61060185185</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29323,7 +29323,7 @@
         <v>45719.84378472222</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29380,7 +29380,7 @@
         <v>45761.4437962963</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29437,7 +29437,7 @@
         <v>45299.62576388889</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29494,7 +29494,7 @@
         <v>44935</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29551,7 +29551,7 @@
         <v>44603</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29608,7 +29608,7 @@
         <v>44999.86172453704</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29665,7 +29665,7 @@
         <v>45700.68289351852</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29722,7 +29722,7 @@
         <v>44999.8625</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29779,7 +29779,7 @@
         <v>45825.5796875</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29836,7 +29836,7 @@
         <v>45825.58672453704</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29893,7 +29893,7 @@
         <v>45867.51630787037</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29950,7 +29950,7 @@
         <v>45867.56320601852</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30007,7 +30007,7 @@
         <v>45867.63094907408</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30064,7 +30064,7 @@
         <v>45867.50792824074</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30121,7 +30121,7 @@
         <v>45867.68625</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30178,7 +30178,7 @@
         <v>45867.69346064814</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30235,7 +30235,7 @@
         <v>44964.50894675926</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30292,7 +30292,7 @@
         <v>45517.8162037037</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30349,7 +30349,7 @@
         <v>45518.40657407408</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30406,7 +30406,7 @@
         <v>44638.55256944444</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30463,7 +30463,7 @@
         <v>45623.9525462963</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30520,7 +30520,7 @@
         <v>45867.64663194444</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30577,7 +30577,7 @@
         <v>45825.57805555555</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30634,7 +30634,7 @@
         <v>45825.50280092593</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30691,7 +30691,7 @@
         <v>44790.49523148148</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30748,7 +30748,7 @@
         <v>45260.4716550926</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30805,7 +30805,7 @@
         <v>45825.57680555555</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30862,7 +30862,7 @@
         <v>44820</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30919,7 +30919,7 @@
         <v>45666</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30976,7 +30976,7 @@
         <v>45826.66646990741</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>44693.62822916666</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31095,7 +31095,7 @@
         <v>45769</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31152,7 +31152,7 @@
         <v>45827</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31209,7 +31209,7 @@
         <v>45870.52111111111</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>45001.59209490741</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31323,7 +31323,7 @@
         <v>44587.48847222222</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>45245.63574074074</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31437,7 +31437,7 @@
         <v>45280.66769675926</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>44956</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31556,7 +31556,7 @@
         <v>45870.51708333333</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31613,7 +31613,7 @@
         <v>45870.52005787037</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31670,7 +31670,7 @@
         <v>45870.52142361111</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31727,7 +31727,7 @@
         <v>45317</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31789,7 +31789,7 @@
         <v>44918</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31846,7 +31846,7 @@
         <v>44959.66407407408</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31903,7 +31903,7 @@
         <v>45870.51958333333</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31960,7 +31960,7 @@
         <v>45219.69356481481</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32017,7 +32017,7 @@
         <v>45869.62276620371</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>45827</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32131,7 +32131,7 @@
         <v>44966</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>44564.62598379629</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32245,7 +32245,7 @@
         <v>45379</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>45225.60192129629</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32359,7 +32359,7 @@
         <v>45495</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32416,7 +32416,7 @@
         <v>44600</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32473,7 +32473,7 @@
         <v>45237.63225694445</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32530,7 +32530,7 @@
         <v>45237.64408564815</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32587,7 +32587,7 @@
         <v>45301.67554398148</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32644,7 +32644,7 @@
         <v>45768.65611111111</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32701,7 +32701,7 @@
         <v>45831</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32758,7 +32758,7 @@
         <v>45026.82216435186</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>44910.54231481482</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32872,7 +32872,7 @@
         <v>44732.3659837963</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32929,7 +32929,7 @@
         <v>45567.42011574074</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32986,7 +32986,7 @@
         <v>45554.62944444444</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33043,7 +33043,7 @@
         <v>45874.57109953704</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33100,7 +33100,7 @@
         <v>45832.34540509259</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33157,7 +33157,7 @@
         <v>45832.46146990741</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33214,7 +33214,7 @@
         <v>44790.49040509259</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33271,7 +33271,7 @@
         <v>45323.53744212963</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33328,7 +33328,7 @@
         <v>45533.55362268518</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33385,7 +33385,7 @@
         <v>45763.59436342592</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33442,7 +33442,7 @@
         <v>45355.54138888889</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33499,7 +33499,7 @@
         <v>45361.87975694444</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33556,7 +33556,7 @@
         <v>45330</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33613,7 +33613,7 @@
         <v>45330</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33670,7 +33670,7 @@
         <v>45833.64563657407</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33727,7 +33727,7 @@
         <v>45833.64814814815</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>44839.4528125</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33841,7 +33841,7 @@
         <v>45875.47454861111</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33898,7 +33898,7 @@
         <v>45875.45716435185</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>45217.47834490741</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34012,7 +34012,7 @@
         <v>45567</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>45834.64667824074</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>44578.32717592592</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34188,7 +34188,7 @@
         <v>45875.42716435185</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34245,7 +34245,7 @@
         <v>44897</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34302,7 +34302,7 @@
         <v>45709.62280092593</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34359,7 +34359,7 @@
         <v>45747.43196759259</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34416,7 +34416,7 @@
         <v>45834.65040509259</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>45834.65197916667</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34540,7 +34540,7 @@
         <v>45833.64237268519</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34597,7 +34597,7 @@
         <v>45835.36229166666</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>45091.67936342592</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>45259.51916666667</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34778,7 +34778,7 @@
         <v>45259.52020833334</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34840,7 +34840,7 @@
         <v>45734.62017361111</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>45835.4924537037</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>45145</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35011,7 +35011,7 @@
         <v>45349.54434027777</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35068,7 +35068,7 @@
         <v>45835.48862268519</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35125,7 +35125,7 @@
         <v>45880.38380787037</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35182,7 +35182,7 @@
         <v>45345.83557870371</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35239,7 +35239,7 @@
         <v>44599</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35296,7 +35296,7 @@
         <v>45201</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35353,7 +35353,7 @@
         <v>45880.51413194444</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35415,7 +35415,7 @@
         <v>45674.71810185185</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35472,7 +35472,7 @@
         <v>45588.66457175926</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35529,7 +35529,7 @@
         <v>45275.41833333333</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35586,7 +35586,7 @@
         <v>45880.51550925926</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35648,7 +35648,7 @@
         <v>45837.77701388889</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35705,7 +35705,7 @@
         <v>45835.48267361111</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35762,7 +35762,7 @@
         <v>45835.48445601852</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35819,7 +35819,7 @@
         <v>45835.45099537037</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35876,7 +35876,7 @@
         <v>44495</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35933,7 +35933,7 @@
         <v>45837.77916666667</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35990,7 +35990,7 @@
         <v>45835.44709490741</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36047,7 +36047,7 @@
         <v>45835.44732638889</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36104,7 +36104,7 @@
         <v>44848.59133101852</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36161,7 +36161,7 @@
         <v>45440.28329861111</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36218,7 +36218,7 @@
         <v>45632.72635416667</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36275,7 +36275,7 @@
         <v>45881</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36332,7 +36332,7 @@
         <v>44790.45876157407</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36389,7 +36389,7 @@
         <v>44475</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36446,7 +36446,7 @@
         <v>44861</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36503,7 +36503,7 @@
         <v>45840.59474537037</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>45840.59853009259</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36617,7 +36617,7 @@
         <v>45202.4209837963</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36674,7 +36674,7 @@
         <v>44879.62173611111</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>45147</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36788,7 +36788,7 @@
         <v>45832.46649305556</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36845,7 +36845,7 @@
         <v>44987.54104166666</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36902,7 +36902,7 @@
         <v>44060</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36959,7 +36959,7 @@
         <v>45881.59877314815</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>45761.44584490741</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37073,7 +37073,7 @@
         <v>45884.50613425926</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37135,7 +37135,7 @@
         <v>45841.70569444444</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37192,7 +37192,7 @@
         <v>45841.70868055556</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>44943.62954861111</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37306,7 +37306,7 @@
         <v>44944.73487268519</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37363,7 +37363,7 @@
         <v>45761.35990740741</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>45761.4566550926</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37477,7 +37477,7 @@
         <v>45128.37305555555</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37534,7 +37534,7 @@
         <v>45481.56722222222</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37591,7 +37591,7 @@
         <v>44900.57393518519</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37648,7 +37648,7 @@
         <v>45841.7072337963</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37705,7 +37705,7 @@
         <v>45394.50028935185</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37762,7 +37762,7 @@
         <v>45394.66887731481</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37819,7 +37819,7 @@
         <v>45581.58418981481</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37876,7 +37876,7 @@
         <v>44867</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37933,7 +37933,7 @@
         <v>45581.57333333333</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37990,7 +37990,7 @@
         <v>45533.63056712963</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>45884.50331018519</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38114,7 +38114,7 @@
         <v>45588.67070601852</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38171,7 +38171,7 @@
         <v>44857.65989583333</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38228,7 +38228,7 @@
         <v>44585.50431712963</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38285,7 +38285,7 @@
         <v>44992.34151620371</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         <v>44542.90072916666</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38404,7 +38404,7 @@
         <v>44784.42528935185</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38461,7 +38461,7 @@
         <v>44453.56578703703</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38518,7 +38518,7 @@
         <v>45176.72427083334</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38575,7 +38575,7 @@
         <v>44431</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38632,7 +38632,7 @@
         <v>45569.45017361111</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38689,7 +38689,7 @@
         <v>44566</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38746,7 +38746,7 @@
         <v>44999.35858796296</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>45713.45311342592</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>45743.41148148148</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38917,7 +38917,7 @@
         <v>45170</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>45261.44914351852</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>45735.58024305556</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>44746.38834490741</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39145,7 +39145,7 @@
         <v>45048.59699074074</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>45503.5658912037</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39259,7 +39259,7 @@
         <v>45622</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>45562.46342592593</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39373,7 +39373,7 @@
         <v>44596</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>45434.55831018519</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39492,7 +39492,7 @@
         <v>45434.56398148148</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39554,7 +39554,7 @@
         <v>45568.36879629629</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39611,7 +39611,7 @@
         <v>44077</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39668,7 +39668,7 @@
         <v>45075.43059027778</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39725,7 +39725,7 @@
         <v>44952.35775462963</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39782,7 +39782,7 @@
         <v>44784.62724537037</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39839,7 +39839,7 @@
         <v>45093.62777777778</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39901,7 +39901,7 @@
         <v>45215.5959375</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39958,7 +39958,7 @@
         <v>45343.68038194445</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40015,7 +40015,7 @@
         <v>44270.39765046296</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40077,7 +40077,7 @@
         <v>44992.62498842592</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40134,7 +40134,7 @@
         <v>45121.61318287037</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40196,7 +40196,7 @@
         <v>45617.47570601852</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40253,7 +40253,7 @@
         <v>44981.58834490741</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40310,7 +40310,7 @@
         <v>44967.44255787037</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40367,7 +40367,7 @@
         <v>44600</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40424,7 +40424,7 @@
         <v>45567</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40481,7 +40481,7 @@
         <v>44994.42113425926</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40538,7 +40538,7 @@
         <v>45187.60813657408</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>44958.61047453704</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>44237</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40709,7 +40709,7 @@
         <v>44965</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>45334.78826388889</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40823,7 +40823,7 @@
         <v>44452</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40880,7 +40880,7 @@
         <v>45009.4671875</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40937,7 +40937,7 @@
         <v>45705.74418981482</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40994,7 +40994,7 @@
         <v>44973.43075231482</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41051,7 +41051,7 @@
         <v>44410</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41108,7 +41108,7 @@
         <v>45111</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41165,7 +41165,7 @@
         <v>44340</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41222,7 +41222,7 @@
         <v>44909</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41279,7 +41279,7 @@
         <v>45637.66542824074</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41336,7 +41336,7 @@
         <v>44977</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41393,7 +41393,7 @@
         <v>44964.44356481481</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41450,7 +41450,7 @@
         <v>45610.59094907407</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41507,7 +41507,7 @@
         <v>44310</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41564,7 +41564,7 @@
         <v>44894.49538194444</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41621,7 +41621,7 @@
         <v>44992</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41678,7 +41678,7 @@
         <v>45041.63380787037</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41735,7 +41735,7 @@
         <v>45020</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41792,7 +41792,7 @@
         <v>44961</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41849,7 +41849,7 @@
         <v>44916.55414351852</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41906,7 +41906,7 @@
         <v>45114.49505787037</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41963,7 +41963,7 @@
         <v>45722.56422453704</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42020,7 +42020,7 @@
         <v>45041</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42077,7 +42077,7 @@
         <v>45300.3794212963</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42134,7 +42134,7 @@
         <v>45245.36174768519</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42191,7 +42191,7 @@
         <v>45632.36706018518</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42248,7 +42248,7 @@
         <v>44745.84396990741</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42305,7 +42305,7 @@
         <v>44061</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42362,7 +42362,7 @@
         <v>44999.36081018519</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42419,7 +42419,7 @@
         <v>45163.63621527778</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42481,7 +42481,7 @@
         <v>45615.48927083334</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>45495</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42595,7 +42595,7 @@
         <v>45128.9325</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42652,7 +42652,7 @@
         <v>45128.93540509259</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42709,7 +42709,7 @@
         <v>45320.89128472222</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42766,7 +42766,7 @@
         <v>45635.66695601852</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42823,7 +42823,7 @@
         <v>45568.30189814815</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42880,7 +42880,7 @@
         <v>45033.76043981482</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42937,7 +42937,7 @@
         <v>45698.7259837963</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42994,7 +42994,7 @@
         <v>45699.45392361111</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43051,7 +43051,7 @@
         <v>45154.49831018518</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43108,7 +43108,7 @@
         <v>44613</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43165,7 +43165,7 @@
         <v>45630.35827546296</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43222,7 +43222,7 @@
         <v>44176</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43279,7 +43279,7 @@
         <v>44992</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43336,7 +43336,7 @@
         <v>45189</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43393,7 +43393,7 @@
         <v>45658.80232638889</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43450,7 +43450,7 @@
         <v>45658.80827546296</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43507,7 +43507,7 @@
         <v>45063.49936342592</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43564,7 +43564,7 @@
         <v>44769.45805555556</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43621,7 +43621,7 @@
         <v>45028</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43678,7 +43678,7 @@
         <v>45453.36854166666</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43735,7 +43735,7 @@
         <v>44546</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43792,7 +43792,7 @@
         <v>45743.40881944444</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43849,7 +43849,7 @@
         <v>45211.55472222222</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43911,7 +43911,7 @@
         <v>45224.60075231481</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>45646.38200231481</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
         <v>45639.56185185185</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>44377</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>44988</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44201,7 +44201,7 @@
         <v>45764.44931712963</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44263,7 +44263,7 @@
         <v>44540</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44320,7 +44320,7 @@
         <v>45174.31395833333</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44377,7 +44377,7 @@
         <v>44270.38002314815</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44439,7 +44439,7 @@
         <v>45446.36865740741</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44501,7 +44501,7 @@
         <v>44981.64725694444</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44558,7 +44558,7 @@
         <v>45121</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44615,7 +44615,7 @@
         <v>44502</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44672,7 +44672,7 @@
         <v>45138</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44729,7 +44729,7 @@
         <v>45698.53336805556</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44786,7 +44786,7 @@
         <v>44418</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44843,7 +44843,7 @@
         <v>44895.46524305556</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44900,7 +44900,7 @@
         <v>45674.74094907408</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44957,7 +44957,7 @@
         <v>45700.68672453704</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45014,7 +45014,7 @@
         <v>45163</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45071,7 +45071,7 @@
         <v>45749.56196759259</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45133,7 +45133,7 @@
         <v>45453.36067129629</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45190,7 +45190,7 @@
         <v>44963.44769675926</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45247,7 +45247,7 @@
         <v>44944.71386574074</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45304,7 +45304,7 @@
         <v>44944.72100694444</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45361,7 +45361,7 @@
         <v>45698.53725694444</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45418,7 +45418,7 @@
         <v>45732.75637731481</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45475,7 +45475,7 @@
         <v>45732.76936342593</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45532,7 +45532,7 @@
         <v>45090.89653935185</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45589,7 +45589,7 @@
         <v>45090.89880787037</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45646,7 +45646,7 @@
         <v>45250.5278587963</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45703,7 +45703,7 @@
         <v>44803.59118055556</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45760,7 +45760,7 @@
         <v>45201.39996527778</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45817,7 +45817,7 @@
         <v>44991.30547453704</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>44991</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>45153.32778935185</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45988,7 +45988,7 @@
         <v>45761.39600694444</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46045,7 +46045,7 @@
         <v>45113.41633101852</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46102,7 +46102,7 @@
         <v>45238.4328587963</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46159,7 +46159,7 @@
         <v>45106</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46216,7 +46216,7 @@
         <v>45106.2610300926</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46273,7 +46273,7 @@
         <v>45699.60055555555</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46330,7 +46330,7 @@
         <v>45063.508125</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46387,7 +46387,7 @@
         <v>45219.40528935185</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46444,7 +46444,7 @@
         <v>45747.39189814815</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46501,7 +46501,7 @@
         <v>45735.56751157407</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46558,7 +46558,7 @@
         <v>44440</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46615,7 +46615,7 @@
         <v>45658.78774305555</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46672,7 +46672,7 @@
         <v>45630.45069444444</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46729,7 +46729,7 @@
         <v>45754.33641203704</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46786,7 +46786,7 @@
         <v>44302</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46843,7 +46843,7 @@
         <v>45224</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46900,7 +46900,7 @@
         <v>45224.64659722222</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46962,7 +46962,7 @@
         <v>45114.47895833333</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47019,7 +47019,7 @@
         <v>45482.49870370371</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47076,7 +47076,7 @@
         <v>45482.54844907407</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47133,7 +47133,7 @@
         <v>45533.38870370371</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47190,7 +47190,7 @@
         <v>45121.5965162037</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47252,7 +47252,7 @@
         <v>45121.59954861111</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47314,7 +47314,7 @@
         <v>45121.6096875</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47376,7 +47376,7 @@
         <v>45558.44914351852</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47433,7 +47433,7 @@
         <v>45732.79925925926</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47490,7 +47490,7 @@
         <v>45111.30824074074</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47547,7 +47547,7 @@
         <v>44984</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47604,7 +47604,7 @@
         <v>45624.60141203704</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47661,7 +47661,7 @@
         <v>45434.55471064815</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47723,7 +47723,7 @@
         <v>44312</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47780,7 +47780,7 @@
         <v>44431.84840277778</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47837,7 +47837,7 @@
         <v>44910.41346064815</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47894,7 +47894,7 @@
         <v>44910</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47951,7 +47951,7 @@
         <v>44984.45895833334</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48008,7 +48008,7 @@
         <v>44984</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48065,7 +48065,7 @@
         <v>45698.52806712963</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48122,7 +48122,7 @@
         <v>44598.7384837963</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48179,7 +48179,7 @@
         <v>44931</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48241,7 +48241,7 @@
         <v>45027.59450231482</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48303,7 +48303,7 @@
         <v>45112.33599537037</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48360,7 +48360,7 @@
         <v>44111</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48417,7 +48417,7 @@
         <v>44440.60415509259</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48474,7 +48474,7 @@
         <v>45350.53306712963</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48531,7 +48531,7 @@
         <v>45660</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48588,7 +48588,7 @@
         <v>44258</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48645,7 +48645,7 @@
         <v>45029</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48702,7 +48702,7 @@
         <v>45369.62780092593</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48759,7 +48759,7 @@
         <v>44943.57309027778</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48816,7 +48816,7 @@
         <v>45554.63225694445</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48873,7 +48873,7 @@
         <v>45722.48915509259</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48930,7 +48930,7 @@
         <v>45635.4874537037</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48987,7 +48987,7 @@
         <v>45545.49508101852</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49044,7 +49044,7 @@
         <v>44451</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49101,7 +49101,7 @@
         <v>45569.47494212963</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>45346.67184027778</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49215,7 +49215,7 @@
         <v>44966</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49272,7 +49272,7 @@
         <v>45070.3665625</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>45070</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49386,7 +49386,7 @@
         <v>45054.6750462963</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>45215.60199074074</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49500,7 +49500,7 @@
         <v>45720.44217592593</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49557,7 +49557,7 @@
         <v>44991.89657407408</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49614,7 +49614,7 @@
         <v>44903.33363425926</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49671,7 +49671,7 @@
         <v>44994.46908564815</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49728,7 +49728,7 @@
         <v>45149.60917824074</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49785,7 +49785,7 @@
         <v>45169</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49842,7 +49842,7 @@
         <v>44578.62943287037</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49899,7 +49899,7 @@
         <v>45278</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>45456.59289351852</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50018,7 +50018,7 @@
         <v>45002</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50075,7 +50075,7 @@
         <v>44867</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50132,7 +50132,7 @@
         <v>44879.55940972222</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50189,7 +50189,7 @@
         <v>45174.40454861111</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50246,7 +50246,7 @@
         <v>44903</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>45533.56108796296</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50360,7 +50360,7 @@
         <v>45533.58302083334</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50422,7 +50422,7 @@
         <v>44896</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50479,7 +50479,7 @@
         <v>44890</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50536,7 +50536,7 @@
         <v>45705.73300925926</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50593,7 +50593,7 @@
         <v>44965.4815162037</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50650,7 +50650,7 @@
         <v>44588.37998842593</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50707,7 +50707,7 @@
         <v>44588</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50764,7 +50764,7 @@
         <v>44175.39748842592</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50821,7 +50821,7 @@
         <v>44875.27736111111</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50878,7 +50878,7 @@
         <v>45171.77335648148</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50935,7 +50935,7 @@
         <v>45361.90282407407</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50992,7 +50992,7 @@
         <v>45224.6515162037</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51054,7 +51054,7 @@
         <v>45475.49018518518</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51111,7 +51111,7 @@
         <v>45061</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51173,7 +51173,7 @@
         <v>44754</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51230,7 +51230,7 @@
         <v>45106.25025462963</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51287,7 +51287,7 @@
         <v>44510.60921296296</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51349,7 +51349,7 @@
         <v>45100.85270833333</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51406,7 +51406,7 @@
         <v>45301</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51463,7 +51463,7 @@
         <v>45301.68237268519</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51520,7 +51520,7 @@
         <v>45475.48303240741</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51577,7 +51577,7 @@
         <v>45415.57682870371</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51634,7 +51634,7 @@
         <v>44517</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51691,7 +51691,7 @@
         <v>45124</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51748,7 +51748,7 @@
         <v>45108.703125</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51805,7 +51805,7 @@
         <v>45446.36482638889</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51867,7 +51867,7 @@
         <v>45759.38987268518</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51924,7 +51924,7 @@
         <v>45755.44333333334</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51981,7 +51981,7 @@
         <v>45530.33202546297</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52038,7 +52038,7 @@
         <v>45110.4275</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52095,7 +52095,7 @@
         <v>45667.39670138889</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52152,7 +52152,7 @@
         <v>45128.58414351852</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         <v>44588</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>

--- a/Översikt VIMMERBY.xlsx
+++ b/Översikt VIMMERBY.xlsx
@@ -567,7 +567,7 @@
         <v>44811</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
         <v>44811</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44811</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44811</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>45314</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>45738.79180555556</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>44939</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>45301.67922453704</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>45755</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45377.54726851852</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>45748</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>45678.64175925926</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>45821</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>45121.60543981481</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>44245</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>44811</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>45628</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>45742</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>45020</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>44424</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>44426.64793981481</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44386</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>45786.52827546297</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>45008.60878472222</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>44943</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>45760.34877314815</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>45072</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>45048</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>44371</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>44403</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>45399.71412037037</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>45125</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>45104</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>45667</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>45574.42767361111</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>44082</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>45649</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>45821</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>45825.58484953704</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>44236</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>45713</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>45168</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>45168</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>44075</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>45224</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>45077</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>44377.61104166666</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>44064</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>44068</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>44083</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>44102</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>44130</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         <v>44287.33261574074</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>44281.79269675926</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>44270.67071759259</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         <v>44210</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>44490.38613425926</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>44481.47483796296</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>44447</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>44350</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>44375.39033564815</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>44614</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>44215</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>44670</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>44670</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         <v>44070.39203703704</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>44063</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>44307</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>44350</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>44105</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>44225</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>44327.47658564815</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>44070</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>44509</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>44406</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
         <v>44230.58883101852</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>44480</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>44063</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>44238</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>44585.51829861111</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>44824.53434027778</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>44418</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>44785.40800925926</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>44578.47597222222</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>44516.59703703703</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>44862</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>44826.68010416667</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>44603</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>44588</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>44404.87505787037</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>44483.58295138889</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>44354</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>44542.8859375</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>44512.70245370371</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>44494</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>44790</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>44090</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         <v>44221.39408564815</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>44261</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>44530.38055555556</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
         <v>44588</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>44588</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>44790</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>44790.47628472222</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
         <v>44175.3815625</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         <v>44175.40881944444</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>44062</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8286,7 +8286,7 @@
         <v>44312</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>44475</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>44385</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>44124.59795138889</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>44237.8550925926</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8571,7 +8571,7 @@
         <v>44410.71038194445</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         <v>44279.33400462963</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         <v>44175</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         <v>44670</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>44365</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>44169</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         <v>44273</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>44301.36048611111</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>44271.37226851852</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>44729.28226851852</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>44340.54472222222</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>44340</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>44774</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>44061</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         <v>44733</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>44733</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>44063</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>44154</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>44371.62743055556</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>44386.40783564815</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         <v>44480</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>44245</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>44070.40998842593</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9887,7 +9887,7 @@
         <v>44337</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         <v>44102</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>44463.29439814815</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>44588</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         <v>44117</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>44789</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>44377</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10286,7 +10286,7 @@
         <v>44379</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
         <v>44508</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>44091</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>44634.69703703704</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10524,7 +10524,7 @@
         <v>44480</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>44340.58002314815</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>44769.45422453704</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10695,7 +10695,7 @@
         <v>44092</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10752,7 +10752,7 @@
         <v>44085</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>44612.86762731482</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>44142</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>44383</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>44476</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>44305.40046296296</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
         <v>44418</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11151,7 +11151,7 @@
         <v>44447</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         <v>44517</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
         <v>44854</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11327,7 +11327,7 @@
         <v>44819</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11384,7 +11384,7 @@
         <v>44824</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11441,7 +11441,7 @@
         <v>44369</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11498,7 +11498,7 @@
         <v>44742</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11555,7 +11555,7 @@
         <v>44832.67608796297</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         <v>44451.8375</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>44823</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
         <v>44621</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>44270</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
         <v>44217.79856481482</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         <v>44341</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11954,7 +11954,7 @@
         <v>44070</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12011,7 +12011,7 @@
         <v>44608</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>44447.34237268518</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12125,7 +12125,7 @@
         <v>44172</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12182,7 +12182,7 @@
         <v>44384</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12239,7 +12239,7 @@
         <v>44790.48503472222</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12296,7 +12296,7 @@
         <v>44854.59157407407</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>44294</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>44116</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>44620</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>44876.48346064815</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>44733.43092592592</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12638,7 +12638,7 @@
         <v>44480</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>44089.78633101852</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         <v>44609</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>44284.42348379629</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>44088</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>44203</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>44088</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>44525.63913194444</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>44421</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>44186</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>44279.64934027778</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13270,7 +13270,7 @@
         <v>44662</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>44095</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>44273</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>44070</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13503,7 +13503,7 @@
         <v>44266.7240625</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13565,7 +13565,7 @@
         <v>44278.63479166666</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>44270.49743055556</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>44564</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>44375.38789351852</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>44386</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>44427</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>44612.86554398148</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>44466.34726851852</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>44866.81100694444</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         <v>44379</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>44470.44232638889</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>44284.44574074074</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>44722.48768518519</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14326,7 +14326,7 @@
         <v>44776</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>44634</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>44636</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>44608.50458333334</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>44817</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         <v>44817.57988425926</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>44851.95016203704</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>44060</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>44294</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>44294</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         <v>44676.85248842592</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>44292</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>44604</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
         <v>45483.82834490741</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15129,7 +15129,7 @@
         <v>45090.38012731481</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>44644</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>44305</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15300,7 +15300,7 @@
         <v>45196</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15357,7 +15357,7 @@
         <v>44607</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>44949</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>45411.47335648148</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>45121.58699074074</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>45569.44684027778</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>45377.40043981482</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>45698.51711805556</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>45211.43555555555</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15823,7 +15823,7 @@
         <v>45391.41310185185</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
         <v>45086.63194444445</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15937,7 +15937,7 @@
         <v>45097.40524305555</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>45086.63334490741</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>45100.4062962963</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>45086</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>45232</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16227,7 +16227,7 @@
         <v>45425.57538194444</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>45525.41762731481</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>45565.40657407408</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>44720.53898148148</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>44243</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         <v>45090</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16569,7 +16569,7 @@
         <v>45728.54832175926</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16626,7 +16626,7 @@
         <v>45749.60487268519</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>45245.5735300926</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16745,7 +16745,7 @@
         <v>44539</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>45450.51092592593</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>45257.67958333333</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>45018</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         <v>45607.56773148148</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17030,7 +17030,7 @@
         <v>44553</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17087,7 +17087,7 @@
         <v>45301.67736111111</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>44895.62296296296</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>45513.55840277778</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>45513.56527777778</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>44466.34962962963</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17372,7 +17372,7 @@
         <v>45110.4184375</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         <v>44964.5115162037</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>45105</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>44278.54855324074</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>45415.47848379629</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         <v>45308.61152777778</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>45299.47513888889</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>45391.41976851852</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17828,7 +17828,7 @@
         <v>45111.48787037037</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>44377.49684027778</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         <v>45539.66027777778</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18004,7 +18004,7 @@
         <v>44833.60123842592</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18061,7 +18061,7 @@
         <v>44867</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18118,7 +18118,7 @@
         <v>45215.59743055556</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>44789</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
         <v>45481.58048611111</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18289,7 +18289,7 @@
         <v>45096.45247685185</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18346,7 +18346,7 @@
         <v>45111.48395833333</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>45588.65545138889</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18460,7 +18460,7 @@
         <v>44967.45122685185</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18517,7 +18517,7 @@
         <v>45581.57016203704</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18574,7 +18574,7 @@
         <v>45481.55984953704</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18631,7 +18631,7 @@
         <v>45539.38744212963</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18688,7 +18688,7 @@
         <v>45784.74996527778</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18745,7 +18745,7 @@
         <v>45539.65212962963</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18802,7 +18802,7 @@
         <v>45463</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>45630.47564814815</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>45000.47998842593</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18973,7 +18973,7 @@
         <v>45552.36759259259</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19030,7 +19030,7 @@
         <v>45098.30535879629</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19087,7 +19087,7 @@
         <v>45786.52931712963</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19144,7 +19144,7 @@
         <v>45786.52996527778</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>45113.56574074074</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>45747.42633101852</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19315,7 +19315,7 @@
         <v>45747.42958333333</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>45726.44471064815</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>44788</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>45581.57958333333</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19543,7 +19543,7 @@
         <v>45548</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19600,7 +19600,7 @@
         <v>45786.52878472222</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19657,7 +19657,7 @@
         <v>45020</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19714,7 +19714,7 @@
         <v>45569.44295138889</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19771,7 +19771,7 @@
         <v>45415.48979166667</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19828,7 +19828,7 @@
         <v>45009</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19885,7 +19885,7 @@
         <v>45790.44976851852</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19942,7 +19942,7 @@
         <v>45726.62721064815</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         <v>45698.69016203703</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20056,7 +20056,7 @@
         <v>45111.48225694444</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20113,7 +20113,7 @@
         <v>45111.48636574074</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>45621.46103009259</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>45114.58148148148</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
         <v>45460.62172453704</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20341,7 +20341,7 @@
         <v>45533.61996527778</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20403,7 +20403,7 @@
         <v>45791.89865740741</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20460,7 +20460,7 @@
         <v>44852</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20517,7 +20517,7 @@
         <v>45384.66917824074</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>45632.44886574074</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20631,7 +20631,7 @@
         <v>45741.37270833334</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20688,7 +20688,7 @@
         <v>45552.36484953704</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>45271.66576388889</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20802,7 +20802,7 @@
         <v>45796</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20859,7 +20859,7 @@
         <v>45114.55136574074</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>44992</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20978,7 +20978,7 @@
         <v>45582.41200231481</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21035,7 +21035,7 @@
         <v>44585.51060185185</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>45572.48293981481</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21149,7 +21149,7 @@
         <v>45001.43854166667</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21206,7 +21206,7 @@
         <v>45182.78834490741</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21263,7 +21263,7 @@
         <v>45377</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21320,7 +21320,7 @@
         <v>45603.74959490741</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21377,7 +21377,7 @@
         <v>45671.46746527778</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>45722.56731481481</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>45527.68784722222</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>44579.62225694444</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21605,7 +21605,7 @@
         <v>45574.49298611111</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21662,7 +21662,7 @@
         <v>45715.44159722222</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21719,7 +21719,7 @@
         <v>44992.4255787037</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21776,7 +21776,7 @@
         <v>44643</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21833,7 +21833,7 @@
         <v>45845.49414351852</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
         <v>45635.66409722222</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21947,7 +21947,7 @@
         <v>45845.43803240741</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
         <v>45328.38755787037</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22061,7 +22061,7 @@
         <v>45713.92412037037</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22118,7 +22118,7 @@
         <v>45401.53033564815</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22175,7 +22175,7 @@
         <v>45804.6953587963</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22237,7 +22237,7 @@
         <v>45804.708125</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22299,7 +22299,7 @@
         <v>45804.39141203704</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>45845.42015046296</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22413,7 +22413,7 @@
         <v>45071</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22470,7 +22470,7 @@
         <v>45804.67065972222</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22527,7 +22527,7 @@
         <v>45804.44519675926</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22584,7 +22584,7 @@
         <v>45805.39247685186</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22641,7 +22641,7 @@
         <v>45257.70313657408</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22698,7 +22698,7 @@
         <v>44795</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22755,7 +22755,7 @@
         <v>45168.89298611111</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22812,7 +22812,7 @@
         <v>44392</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22874,7 +22874,7 @@
         <v>45266.32614583334</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22931,7 +22931,7 @@
         <v>45805</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22988,7 +22988,7 @@
         <v>45052</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23045,7 +23045,7 @@
         <v>45317.40372685185</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23107,7 +23107,7 @@
         <v>44064</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>45309.59487268519</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23221,7 +23221,7 @@
         <v>45359.44837962963</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>44488.35878472222</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>44467.83386574074</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>45482.52887731481</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23449,7 +23449,7 @@
         <v>45371.36359953704</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23506,7 +23506,7 @@
         <v>45371.45865740741</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23563,7 +23563,7 @@
         <v>45359.45038194444</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23620,7 +23620,7 @@
         <v>45847.91280092593</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23677,7 +23677,7 @@
         <v>44861.52505787037</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23734,7 +23734,7 @@
         <v>45533.54429398148</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23791,7 +23791,7 @@
         <v>45533.60232638889</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>45533.60770833334</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23915,7 +23915,7 @@
         <v>45805.52983796296</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
         <v>45755.64450231481</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24029,7 +24029,7 @@
         <v>45446.36774305555</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24091,7 +24091,7 @@
         <v>45623.95947916667</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24148,7 +24148,7 @@
         <v>44635</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24205,7 +24205,7 @@
         <v>45147.67096064815</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24262,7 +24262,7 @@
         <v>45147.67172453704</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24319,7 +24319,7 @@
         <v>44063</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24376,7 +24376,7 @@
         <v>44595.583125</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24433,7 +24433,7 @@
         <v>45211.52642361111</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24490,7 +24490,7 @@
         <v>45211.541875</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24547,7 +24547,7 @@
         <v>45650.37370370371</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24604,7 +24604,7 @@
         <v>45195.58452546296</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>45351.6062962963</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24718,7 +24718,7 @@
         <v>45526.3865625</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24780,7 +24780,7 @@
         <v>45243.84869212963</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24837,7 +24837,7 @@
         <v>45208</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24894,7 +24894,7 @@
         <v>45729.36868055556</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24951,7 +24951,7 @@
         <v>45148</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>45148</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25065,7 +25065,7 @@
         <v>45163.41376157408</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25122,7 +25122,7 @@
         <v>45434.56291666667</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25184,7 +25184,7 @@
         <v>45810.00048611111</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25241,7 +25241,7 @@
         <v>44083</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25298,7 +25298,7 @@
         <v>44949</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25355,7 +25355,7 @@
         <v>45079.87827546296</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25412,7 +25412,7 @@
         <v>45254.62489583333</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>45171.96248842592</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25531,7 +25531,7 @@
         <v>45113.43921296296</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>45030.71012731481</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>44510.52157407408</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25702,7 +25702,7 @@
         <v>44984</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>44598</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25816,7 +25816,7 @@
         <v>44938</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
         <v>45483.82479166667</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25935,7 +25935,7 @@
         <v>45498</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25992,7 +25992,7 @@
         <v>45853.87112268519</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26049,7 +26049,7 @@
         <v>44879</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26106,7 +26106,7 @@
         <v>45811.45460648148</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26163,7 +26163,7 @@
         <v>45811.66133101852</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26220,7 +26220,7 @@
         <v>44825.4336574074</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>45853.87599537037</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26334,7 +26334,7 @@
         <v>45853.88070601852</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26391,7 +26391,7 @@
         <v>45811.65975694444</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26448,7 +26448,7 @@
         <v>45482.54108796296</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26505,7 +26505,7 @@
         <v>45128</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>45196.57247685185</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26619,7 +26619,7 @@
         <v>45236</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26676,7 +26676,7 @@
         <v>44663</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26733,7 +26733,7 @@
         <v>45187</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26790,7 +26790,7 @@
         <v>45814.3865625</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26847,7 +26847,7 @@
         <v>45485.45778935185</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26904,7 +26904,7 @@
         <v>45187.42854166667</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26961,7 +26961,7 @@
         <v>45618.56787037037</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27018,7 +27018,7 @@
         <v>45814.38221064815</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27075,7 +27075,7 @@
         <v>45467.74417824074</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27132,7 +27132,7 @@
         <v>45086</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27189,7 +27189,7 @@
         <v>44159</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>45707.3793287037</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>45736.50743055555</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27360,7 +27360,7 @@
         <v>44918.50106481482</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27417,7 +27417,7 @@
         <v>44172</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27474,7 +27474,7 @@
         <v>45632.37459490741</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27531,7 +27531,7 @@
         <v>45378.32185185186</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27588,7 +27588,7 @@
         <v>45498.673125</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27645,7 +27645,7 @@
         <v>44893</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27702,7 +27702,7 @@
         <v>45275.32266203704</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27759,7 +27759,7 @@
         <v>45540.50098379629</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27816,7 +27816,7 @@
         <v>45858.60641203704</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27873,7 +27873,7 @@
         <v>45818.59261574074</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         <v>45818.5862037037</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27997,7 +27997,7 @@
         <v>45818.58993055556</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28059,7 +28059,7 @@
         <v>45858.66019675926</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28116,7 +28116,7 @@
         <v>44127</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28173,7 +28173,7 @@
         <v>44630</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28230,7 +28230,7 @@
         <v>44893</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28287,7 +28287,7 @@
         <v>45818.58769675926</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>45818.595625</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>45817.88496527778</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28468,7 +28468,7 @@
         <v>45699.45671296296</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>45308.59001157407</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28582,7 +28582,7 @@
         <v>45699.44291666667</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28639,7 +28639,7 @@
         <v>44994.40635416667</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28696,7 +28696,7 @@
         <v>45174</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28753,7 +28753,7 @@
         <v>45574.35809027778</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28810,7 +28810,7 @@
         <v>45559.38876157408</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28867,7 +28867,7 @@
         <v>44587</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28924,7 +28924,7 @@
         <v>45820.33930555556</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28981,7 +28981,7 @@
         <v>45722.48634259259</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29038,7 +29038,7 @@
         <v>45820.03518518519</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29095,7 +29095,7 @@
         <v>45820.03976851852</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29152,7 +29152,7 @@
         <v>45820.33708333333</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29209,7 +29209,7 @@
         <v>45820.34128472222</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29266,7 +29266,7 @@
         <v>45819.61060185185</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29323,7 +29323,7 @@
         <v>45719.84378472222</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29380,7 +29380,7 @@
         <v>45761.4437962963</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29437,7 +29437,7 @@
         <v>45299.62576388889</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29494,7 +29494,7 @@
         <v>44935</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29551,7 +29551,7 @@
         <v>44603</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29608,7 +29608,7 @@
         <v>44999.86172453704</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29665,7 +29665,7 @@
         <v>45700.68289351852</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29722,7 +29722,7 @@
         <v>44999.8625</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29779,7 +29779,7 @@
         <v>45825.5796875</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29836,7 +29836,7 @@
         <v>45825.58672453704</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29893,7 +29893,7 @@
         <v>45867.51630787037</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29950,7 +29950,7 @@
         <v>45867.56320601852</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30007,7 +30007,7 @@
         <v>45867.63094907408</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30064,7 +30064,7 @@
         <v>45867.50792824074</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30121,7 +30121,7 @@
         <v>45867.68625</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30178,7 +30178,7 @@
         <v>45867.69346064814</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30235,7 +30235,7 @@
         <v>44964.50894675926</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30292,7 +30292,7 @@
         <v>45517.8162037037</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30349,7 +30349,7 @@
         <v>45518.40657407408</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30406,7 +30406,7 @@
         <v>44638.55256944444</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30463,7 +30463,7 @@
         <v>45623.9525462963</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30520,7 +30520,7 @@
         <v>45867.64663194444</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30577,7 +30577,7 @@
         <v>45825.57805555555</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30634,7 +30634,7 @@
         <v>45825.50280092593</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30691,7 +30691,7 @@
         <v>44790.49523148148</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30748,7 +30748,7 @@
         <v>45260.4716550926</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30805,7 +30805,7 @@
         <v>45825.57680555555</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30862,7 +30862,7 @@
         <v>44820</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30919,7 +30919,7 @@
         <v>45666</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30976,7 +30976,7 @@
         <v>45826.66646990741</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>44693.62822916666</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31095,7 +31095,7 @@
         <v>45769</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31152,7 +31152,7 @@
         <v>45827</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31209,7 +31209,7 @@
         <v>45870.52111111111</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>45001.59209490741</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31323,7 +31323,7 @@
         <v>44587.48847222222</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>45245.63574074074</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31437,7 +31437,7 @@
         <v>45280.66769675926</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>44956</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31556,7 +31556,7 @@
         <v>45870.51708333333</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31613,7 +31613,7 @@
         <v>45870.52005787037</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31670,7 +31670,7 @@
         <v>45870.52142361111</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31727,7 +31727,7 @@
         <v>45317</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31789,7 +31789,7 @@
         <v>44918</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31846,7 +31846,7 @@
         <v>44959.66407407408</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31903,7 +31903,7 @@
         <v>45870.51958333333</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31960,7 +31960,7 @@
         <v>45219.69356481481</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32017,7 +32017,7 @@
         <v>45869.62276620371</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>45827</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32131,7 +32131,7 @@
         <v>44966</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>44564.62598379629</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32245,7 +32245,7 @@
         <v>45379</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>45225.60192129629</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32359,7 +32359,7 @@
         <v>45495</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32416,7 +32416,7 @@
         <v>44600</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32473,7 +32473,7 @@
         <v>45237.63225694445</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32530,7 +32530,7 @@
         <v>45237.64408564815</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32587,7 +32587,7 @@
         <v>45301.67554398148</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32644,7 +32644,7 @@
         <v>45768.65611111111</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32701,7 +32701,7 @@
         <v>45831</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32758,7 +32758,7 @@
         <v>45026.82216435186</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>44910.54231481482</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32872,7 +32872,7 @@
         <v>44732.3659837963</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32929,7 +32929,7 @@
         <v>45567.42011574074</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32986,7 +32986,7 @@
         <v>45554.62944444444</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33043,7 +33043,7 @@
         <v>45874.57109953704</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33100,7 +33100,7 @@
         <v>45832.34540509259</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33157,7 +33157,7 @@
         <v>45832.46146990741</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33214,7 +33214,7 @@
         <v>44790.49040509259</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33271,7 +33271,7 @@
         <v>45323.53744212963</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33328,7 +33328,7 @@
         <v>45533.55362268518</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33385,7 +33385,7 @@
         <v>45763.59436342592</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33442,7 +33442,7 @@
         <v>45355.54138888889</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33499,7 +33499,7 @@
         <v>45361.87975694444</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33556,7 +33556,7 @@
         <v>45330</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33613,7 +33613,7 @@
         <v>45330</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33670,7 +33670,7 @@
         <v>45833.64563657407</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33727,7 +33727,7 @@
         <v>45833.64814814815</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>44839.4528125</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33841,7 +33841,7 @@
         <v>45875.47454861111</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33898,7 +33898,7 @@
         <v>45875.45716435185</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>45217.47834490741</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34012,7 +34012,7 @@
         <v>45567</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>45834.64667824074</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>44578.32717592592</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34188,7 +34188,7 @@
         <v>45875.42716435185</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34245,7 +34245,7 @@
         <v>44897</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34302,7 +34302,7 @@
         <v>45709.62280092593</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34359,7 +34359,7 @@
         <v>45747.43196759259</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34416,7 +34416,7 @@
         <v>45834.65040509259</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>45834.65197916667</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34540,7 +34540,7 @@
         <v>45833.64237268519</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34597,7 +34597,7 @@
         <v>45835.36229166666</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>45091.67936342592</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>45259.51916666667</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34778,7 +34778,7 @@
         <v>45259.52020833334</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34840,7 +34840,7 @@
         <v>45734.62017361111</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>45835.4924537037</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>45145</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35011,7 +35011,7 @@
         <v>45349.54434027777</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35068,7 +35068,7 @@
         <v>45835.48862268519</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35125,7 +35125,7 @@
         <v>45880.38380787037</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35182,7 +35182,7 @@
         <v>45345.83557870371</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35239,7 +35239,7 @@
         <v>44599</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35296,7 +35296,7 @@
         <v>45201</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35353,7 +35353,7 @@
         <v>45880.51413194444</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35415,7 +35415,7 @@
         <v>45674.71810185185</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35472,7 +35472,7 @@
         <v>45588.66457175926</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35529,7 +35529,7 @@
         <v>45275.41833333333</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35586,7 +35586,7 @@
         <v>45880.51550925926</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35648,7 +35648,7 @@
         <v>45837.77701388889</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35705,7 +35705,7 @@
         <v>45835.48267361111</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35762,7 +35762,7 @@
         <v>45835.48445601852</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35819,7 +35819,7 @@
         <v>45835.45099537037</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35876,7 +35876,7 @@
         <v>44495</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35933,7 +35933,7 @@
         <v>45837.77916666667</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35990,7 +35990,7 @@
         <v>45835.44709490741</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36047,7 +36047,7 @@
         <v>45835.44732638889</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36104,7 +36104,7 @@
         <v>44848.59133101852</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36161,7 +36161,7 @@
         <v>45440.28329861111</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36218,7 +36218,7 @@
         <v>45632.72635416667</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36275,7 +36275,7 @@
         <v>45881</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36332,7 +36332,7 @@
         <v>44790.45876157407</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36389,7 +36389,7 @@
         <v>44475</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36446,7 +36446,7 @@
         <v>44861</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36503,7 +36503,7 @@
         <v>45840.59474537037</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>45840.59853009259</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36617,7 +36617,7 @@
         <v>45202.4209837963</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36674,7 +36674,7 @@
         <v>44879.62173611111</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>45147</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36788,7 +36788,7 @@
         <v>45832.46649305556</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36845,7 +36845,7 @@
         <v>44987.54104166666</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36902,7 +36902,7 @@
         <v>44060</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36959,7 +36959,7 @@
         <v>45881.59877314815</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>45761.44584490741</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37073,7 +37073,7 @@
         <v>45884.50613425926</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37135,7 +37135,7 @@
         <v>45841.70569444444</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37192,7 +37192,7 @@
         <v>45841.70868055556</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>44943.62954861111</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37306,7 +37306,7 @@
         <v>44944.73487268519</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37363,7 +37363,7 @@
         <v>45761.35990740741</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>45761.4566550926</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37477,7 +37477,7 @@
         <v>45128.37305555555</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37534,7 +37534,7 @@
         <v>45481.56722222222</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37591,7 +37591,7 @@
         <v>44900.57393518519</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37648,7 +37648,7 @@
         <v>45841.7072337963</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37705,7 +37705,7 @@
         <v>45394.50028935185</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37762,7 +37762,7 @@
         <v>45394.66887731481</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37819,7 +37819,7 @@
         <v>45581.58418981481</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37876,7 +37876,7 @@
         <v>44867</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37933,7 +37933,7 @@
         <v>45581.57333333333</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37990,7 +37990,7 @@
         <v>45533.63056712963</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>45884.50331018519</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38114,7 +38114,7 @@
         <v>45588.67070601852</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38171,7 +38171,7 @@
         <v>44857.65989583333</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38228,7 +38228,7 @@
         <v>44585.50431712963</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38285,7 +38285,7 @@
         <v>44992.34151620371</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         <v>44542.90072916666</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38404,7 +38404,7 @@
         <v>44784.42528935185</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38461,7 +38461,7 @@
         <v>44453.56578703703</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38518,7 +38518,7 @@
         <v>45176.72427083334</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38575,7 +38575,7 @@
         <v>44431</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38632,7 +38632,7 @@
         <v>45569.45017361111</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38689,7 +38689,7 @@
         <v>44566</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38746,7 +38746,7 @@
         <v>44999.35858796296</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>45713.45311342592</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>45743.41148148148</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38917,7 +38917,7 @@
         <v>45170</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>45261.44914351852</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>45735.58024305556</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>44746.38834490741</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39145,7 +39145,7 @@
         <v>45048.59699074074</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>45503.5658912037</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39259,7 +39259,7 @@
         <v>45622</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>45562.46342592593</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39373,7 +39373,7 @@
         <v>44596</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>45434.55831018519</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39492,7 +39492,7 @@
         <v>45434.56398148148</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39554,7 +39554,7 @@
         <v>45568.36879629629</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39611,7 +39611,7 @@
         <v>44077</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39668,7 +39668,7 @@
         <v>45075.43059027778</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39725,7 +39725,7 @@
         <v>44952.35775462963</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39782,7 +39782,7 @@
         <v>44784.62724537037</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39839,7 +39839,7 @@
         <v>45093.62777777778</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39901,7 +39901,7 @@
         <v>45215.5959375</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39958,7 +39958,7 @@
         <v>45343.68038194445</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40015,7 +40015,7 @@
         <v>44270.39765046296</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40077,7 +40077,7 @@
         <v>44992.62498842592</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40134,7 +40134,7 @@
         <v>45121.61318287037</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40196,7 +40196,7 @@
         <v>45617.47570601852</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40253,7 +40253,7 @@
         <v>44981.58834490741</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40310,7 +40310,7 @@
         <v>44967.44255787037</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40367,7 +40367,7 @@
         <v>44600</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40424,7 +40424,7 @@
         <v>45567</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40481,7 +40481,7 @@
         <v>44994.42113425926</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40538,7 +40538,7 @@
         <v>45187.60813657408</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>44958.61047453704</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>44237</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40709,7 +40709,7 @@
         <v>44965</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>45334.78826388889</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40823,7 +40823,7 @@
         <v>44452</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40880,7 +40880,7 @@
         <v>45009.4671875</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40937,7 +40937,7 @@
         <v>45705.74418981482</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40994,7 +40994,7 @@
         <v>44973.43075231482</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41051,7 +41051,7 @@
         <v>44410</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41108,7 +41108,7 @@
         <v>45111</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41165,7 +41165,7 @@
         <v>44340</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41222,7 +41222,7 @@
         <v>44909</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41279,7 +41279,7 @@
         <v>45637.66542824074</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41336,7 +41336,7 @@
         <v>44977</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41393,7 +41393,7 @@
         <v>44964.44356481481</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41450,7 +41450,7 @@
         <v>45610.59094907407</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41507,7 +41507,7 @@
         <v>44310</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41564,7 +41564,7 @@
         <v>44894.49538194444</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41621,7 +41621,7 @@
         <v>44992</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41678,7 +41678,7 @@
         <v>45041.63380787037</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41735,7 +41735,7 @@
         <v>45020</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41792,7 +41792,7 @@
         <v>44961</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41849,7 +41849,7 @@
         <v>44916.55414351852</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41906,7 +41906,7 @@
         <v>45114.49505787037</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41963,7 +41963,7 @@
         <v>45722.56422453704</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42020,7 +42020,7 @@
         <v>45041</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42077,7 +42077,7 @@
         <v>45300.3794212963</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42134,7 +42134,7 @@
         <v>45245.36174768519</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42191,7 +42191,7 @@
         <v>45632.36706018518</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42248,7 +42248,7 @@
         <v>44745.84396990741</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42305,7 +42305,7 @@
         <v>44061</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42362,7 +42362,7 @@
         <v>44999.36081018519</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42419,7 +42419,7 @@
         <v>45163.63621527778</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42481,7 +42481,7 @@
         <v>45615.48927083334</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>45495</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42595,7 +42595,7 @@
         <v>45128.9325</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42652,7 +42652,7 @@
         <v>45128.93540509259</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42709,7 +42709,7 @@
         <v>45320.89128472222</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42766,7 +42766,7 @@
         <v>45635.66695601852</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42823,7 +42823,7 @@
         <v>45568.30189814815</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42880,7 +42880,7 @@
         <v>45033.76043981482</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42937,7 +42937,7 @@
         <v>45698.7259837963</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42994,7 +42994,7 @@
         <v>45699.45392361111</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43051,7 +43051,7 @@
         <v>45154.49831018518</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43108,7 +43108,7 @@
         <v>44613</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43165,7 +43165,7 @@
         <v>45630.35827546296</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43222,7 +43222,7 @@
         <v>44176</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43279,7 +43279,7 @@
         <v>44992</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43336,7 +43336,7 @@
         <v>45189</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43393,7 +43393,7 @@
         <v>45658.80232638889</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43450,7 +43450,7 @@
         <v>45658.80827546296</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43507,7 +43507,7 @@
         <v>45063.49936342592</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43564,7 +43564,7 @@
         <v>44769.45805555556</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43621,7 +43621,7 @@
         <v>45028</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43678,7 +43678,7 @@
         <v>45453.36854166666</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43735,7 +43735,7 @@
         <v>44546</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43792,7 +43792,7 @@
         <v>45743.40881944444</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43849,7 +43849,7 @@
         <v>45211.55472222222</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43911,7 +43911,7 @@
         <v>45224.60075231481</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>45646.38200231481</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
         <v>45639.56185185185</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>44377</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>44988</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44201,7 +44201,7 @@
         <v>45764.44931712963</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44263,7 +44263,7 @@
         <v>44540</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44320,7 +44320,7 @@
         <v>45174.31395833333</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44377,7 +44377,7 @@
         <v>44270.38002314815</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44439,7 +44439,7 @@
         <v>45446.36865740741</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44501,7 +44501,7 @@
         <v>44981.64725694444</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44558,7 +44558,7 @@
         <v>45121</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44615,7 +44615,7 @@
         <v>44502</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44672,7 +44672,7 @@
         <v>45138</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44729,7 +44729,7 @@
         <v>45698.53336805556</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44786,7 +44786,7 @@
         <v>44418</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44843,7 +44843,7 @@
         <v>44895.46524305556</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44900,7 +44900,7 @@
         <v>45674.74094907408</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44957,7 +44957,7 @@
         <v>45700.68672453704</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45014,7 +45014,7 @@
         <v>45163</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45071,7 +45071,7 @@
         <v>45749.56196759259</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45133,7 +45133,7 @@
         <v>45453.36067129629</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45190,7 +45190,7 @@
         <v>44963.44769675926</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45247,7 +45247,7 @@
         <v>44944.71386574074</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45304,7 +45304,7 @@
         <v>44944.72100694444</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45361,7 +45361,7 @@
         <v>45698.53725694444</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45418,7 +45418,7 @@
         <v>45732.75637731481</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45475,7 +45475,7 @@
         <v>45732.76936342593</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45532,7 +45532,7 @@
         <v>45090.89653935185</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45589,7 +45589,7 @@
         <v>45090.89880787037</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45646,7 +45646,7 @@
         <v>45250.5278587963</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45703,7 +45703,7 @@
         <v>44803.59118055556</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45760,7 +45760,7 @@
         <v>45201.39996527778</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45817,7 +45817,7 @@
         <v>44991.30547453704</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>44991</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>45153.32778935185</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45988,7 +45988,7 @@
         <v>45761.39600694444</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46045,7 +46045,7 @@
         <v>45113.41633101852</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46102,7 +46102,7 @@
         <v>45238.4328587963</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46159,7 +46159,7 @@
         <v>45106</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46216,7 +46216,7 @@
         <v>45106.2610300926</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46273,7 +46273,7 @@
         <v>45699.60055555555</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46330,7 +46330,7 @@
         <v>45063.508125</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46387,7 +46387,7 @@
         <v>45219.40528935185</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46444,7 +46444,7 @@
         <v>45747.39189814815</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46501,7 +46501,7 @@
         <v>45735.56751157407</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46558,7 +46558,7 @@
         <v>44440</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46615,7 +46615,7 @@
         <v>45658.78774305555</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46672,7 +46672,7 @@
         <v>45630.45069444444</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46729,7 +46729,7 @@
         <v>45754.33641203704</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46786,7 +46786,7 @@
         <v>44302</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46843,7 +46843,7 @@
         <v>45224</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46900,7 +46900,7 @@
         <v>45224.64659722222</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46962,7 +46962,7 @@
         <v>45114.47895833333</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47019,7 +47019,7 @@
         <v>45482.49870370371</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47076,7 +47076,7 @@
         <v>45482.54844907407</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47133,7 +47133,7 @@
         <v>45533.38870370371</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47190,7 +47190,7 @@
         <v>45121.5965162037</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47252,7 +47252,7 @@
         <v>45121.59954861111</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47314,7 +47314,7 @@
         <v>45121.6096875</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47376,7 +47376,7 @@
         <v>45558.44914351852</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47433,7 +47433,7 @@
         <v>45732.79925925926</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47490,7 +47490,7 @@
         <v>45111.30824074074</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47547,7 +47547,7 @@
         <v>44984</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47604,7 +47604,7 @@
         <v>45624.60141203704</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47661,7 +47661,7 @@
         <v>45434.55471064815</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47723,7 +47723,7 @@
         <v>44312</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47780,7 +47780,7 @@
         <v>44431.84840277778</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47837,7 +47837,7 @@
         <v>44910.41346064815</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47894,7 +47894,7 @@
         <v>44910</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47951,7 +47951,7 @@
         <v>44984.45895833334</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48008,7 +48008,7 @@
         <v>44984</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48065,7 +48065,7 @@
         <v>45698.52806712963</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48122,7 +48122,7 @@
         <v>44598.7384837963</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48179,7 +48179,7 @@
         <v>44931</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48241,7 +48241,7 @@
         <v>45027.59450231482</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48303,7 +48303,7 @@
         <v>45112.33599537037</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48360,7 +48360,7 @@
         <v>44111</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48417,7 +48417,7 @@
         <v>44440.60415509259</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48474,7 +48474,7 @@
         <v>45350.53306712963</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48531,7 +48531,7 @@
         <v>45660</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48588,7 +48588,7 @@
         <v>44258</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48645,7 +48645,7 @@
         <v>45029</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48702,7 +48702,7 @@
         <v>45369.62780092593</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48759,7 +48759,7 @@
         <v>44943.57309027778</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48816,7 +48816,7 @@
         <v>45554.63225694445</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48873,7 +48873,7 @@
         <v>45722.48915509259</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48930,7 +48930,7 @@
         <v>45635.4874537037</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48987,7 +48987,7 @@
         <v>45545.49508101852</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49044,7 +49044,7 @@
         <v>44451</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49101,7 +49101,7 @@
         <v>45569.47494212963</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>45346.67184027778</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49215,7 +49215,7 @@
         <v>44966</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49272,7 +49272,7 @@
         <v>45070.3665625</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>45070</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49386,7 +49386,7 @@
         <v>45054.6750462963</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>45215.60199074074</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49500,7 +49500,7 @@
         <v>45720.44217592593</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49557,7 +49557,7 @@
         <v>44991.89657407408</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49614,7 +49614,7 @@
         <v>44903.33363425926</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49671,7 +49671,7 @@
         <v>44994.46908564815</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49728,7 +49728,7 @@
         <v>45149.60917824074</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49785,7 +49785,7 @@
         <v>45169</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49842,7 +49842,7 @@
         <v>44578.62943287037</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49899,7 +49899,7 @@
         <v>45278</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>45456.59289351852</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50018,7 +50018,7 @@
         <v>45002</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50075,7 +50075,7 @@
         <v>44867</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50132,7 +50132,7 @@
         <v>44879.55940972222</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50189,7 +50189,7 @@
         <v>45174.40454861111</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50246,7 +50246,7 @@
         <v>44903</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>45533.56108796296</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50360,7 +50360,7 @@
         <v>45533.58302083334</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50422,7 +50422,7 @@
         <v>44896</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50479,7 +50479,7 @@
         <v>44890</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50536,7 +50536,7 @@
         <v>45705.73300925926</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50593,7 +50593,7 @@
         <v>44965.4815162037</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50650,7 +50650,7 @@
         <v>44588.37998842593</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50707,7 +50707,7 @@
         <v>44588</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50764,7 +50764,7 @@
         <v>44175.39748842592</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50821,7 +50821,7 @@
         <v>44875.27736111111</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50878,7 +50878,7 @@
         <v>45171.77335648148</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50935,7 +50935,7 @@
         <v>45361.90282407407</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50992,7 +50992,7 @@
         <v>45224.6515162037</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51054,7 +51054,7 @@
         <v>45475.49018518518</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51111,7 +51111,7 @@
         <v>45061</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51173,7 +51173,7 @@
         <v>44754</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51230,7 +51230,7 @@
         <v>45106.25025462963</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51287,7 +51287,7 @@
         <v>44510.60921296296</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51349,7 +51349,7 @@
         <v>45100.85270833333</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51406,7 +51406,7 @@
         <v>45301</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51463,7 +51463,7 @@
         <v>45301.68237268519</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51520,7 +51520,7 @@
         <v>45475.48303240741</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51577,7 +51577,7 @@
         <v>45415.57682870371</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51634,7 +51634,7 @@
         <v>44517</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51691,7 +51691,7 @@
         <v>45124</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51748,7 +51748,7 @@
         <v>45108.703125</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51805,7 +51805,7 @@
         <v>45446.36482638889</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51867,7 +51867,7 @@
         <v>45759.38987268518</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51924,7 +51924,7 @@
         <v>45755.44333333334</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51981,7 +51981,7 @@
         <v>45530.33202546297</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52038,7 +52038,7 @@
         <v>45110.4275</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52095,7 +52095,7 @@
         <v>45667.39670138889</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52152,7 +52152,7 @@
         <v>45128.58414351852</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         <v>44588</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>

--- a/Översikt VIMMERBY.xlsx
+++ b/Översikt VIMMERBY.xlsx
@@ -567,7 +567,7 @@
         <v>44811</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
         <v>44811</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44811</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44811</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>45314</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>44939</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>45377.54726851852</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>45301.67922453704</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>45755</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45748</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>45121.60543981481</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>45678.64175925926</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>45821</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>44245</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>44811</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>45628</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>45020</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>45742</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>44424</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>44426.64793981481</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>44386</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>45760.34877314815</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>45048</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>44943</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>45786.52827546297</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>45072</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>45008.60878472222</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>44371</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>45713</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>45399.71412037037</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>44082</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>44236</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>45104</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>44075</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>45224</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>45168</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>45168</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>45667</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>44403</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>44377.61104166666</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>45821</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>45649</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>45825.58484953704</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>45077</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>45574.42767361111</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>45125</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>44068</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         <v>44083</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>44130</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>44102</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>44281.79269675926</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>44270.67071759259</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>44287.33261574074</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>44210</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>44481.47483796296</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>44490.38613425926</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>44447</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>44350</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>44614</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>44375.39033564815</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>44215</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         <v>44070.39203703704</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>44670</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>44670</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>44307</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>44350</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>44105</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         <v>44225</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         <v>44070</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6078,7 +6078,7 @@
         <v>44327.47658564815</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>44509</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6192,7 +6192,7 @@
         <v>44406</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>44230.58883101852</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         <v>44480</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>44238</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>44585.51829861111</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>44824.53434027778</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>44418</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>44785.40800925926</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         <v>44862</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>44578.47597222222</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>44516.59703703703</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         <v>44603</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>44588</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>44826.68010416667</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>44483.58295138889</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         <v>44542.8859375</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>44404.87505787037</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         <v>44494</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7218,7 +7218,7 @@
         <v>44354</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>44512.70245370371</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>44090</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
         <v>44221.39408564815</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>44790</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>44261</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>44530.38055555556</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         <v>44588</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>44588</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>44790</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>44790.47628472222</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>44175.3815625</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>44175.40881944444</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>44312</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>44475</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>44385</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>44237.8550925926</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>44124.59795138889</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>44410.71038194445</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         <v>44279.33400462963</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>44175</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>44670</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8472,7 +8472,7 @@
         <v>44365</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>44169</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
         <v>44273</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>44301.36048611111</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>44729.28226851852</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>44271.37226851852</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>44340.54472222222</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>44340</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>44774</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>44733</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>44733</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>44154</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>44371.62743055556</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>44386.40783564815</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
         <v>44480</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>44245</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>44070.40998842593</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>44337</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9503,7 +9503,7 @@
         <v>44102</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>44463.29439814815</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>44588</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>44117</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>44789</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>44377</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9845,7 +9845,7 @@
         <v>44379</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>44508</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>44294</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>44294</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>44676.85248842592</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>44604</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>44091</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10254,7 +10254,7 @@
         <v>44305</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>44634.69703703704</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         <v>44851.95016203704</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>44480</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>44769.45422453704</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
         <v>44340.58002314815</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10596,7 +10596,7 @@
         <v>44085</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         <v>44142</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>44092</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>44612.86762731482</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>44644</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>44305.40046296296</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>44447</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         <v>44383</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>44476</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>44517</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>44418</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>44854</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>44824</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11342,7 +11342,7 @@
         <v>44369</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>44742</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>44832.67608796297</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>44819</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>44217.79856481482</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11627,7 +11627,7 @@
         <v>44451.8375</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11684,7 +11684,7 @@
         <v>44823</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
         <v>44621</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>44172</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11855,7 +11855,7 @@
         <v>44384</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11912,7 +11912,7 @@
         <v>44790.48503472222</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>44854.59157407407</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>44270</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>44341</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>44070</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12197,7 +12197,7 @@
         <v>44608</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
         <v>44876.48346064815</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12311,7 +12311,7 @@
         <v>44733.43092592592</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>44620</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         <v>44447.34237268518</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12482,7 +12482,7 @@
         <v>44294</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>44116</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12596,7 +12596,7 @@
         <v>44609</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12653,7 +12653,7 @@
         <v>44203</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12710,7 +12710,7 @@
         <v>44284.42348379629</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>44088</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>44088</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12881,7 +12881,7 @@
         <v>44421</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12938,7 +12938,7 @@
         <v>44186</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12995,7 +12995,7 @@
         <v>44273</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13052,7 +13052,7 @@
         <v>44070</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13109,7 +13109,7 @@
         <v>44266.7240625</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13171,7 +13171,7 @@
         <v>44278.63479166666</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>44480</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>44270.49743055556</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>44089.78633101852</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>44612.86554398148</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
         <v>44466.34726851852</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13523,7 +13523,7 @@
         <v>44866.81100694444</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>44470.44232638889</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13642,7 +13642,7 @@
         <v>44375.38789351852</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13699,7 +13699,7 @@
         <v>44776</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13756,7 +13756,7 @@
         <v>44634</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13813,7 +13813,7 @@
         <v>44525.63913194444</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13870,7 +13870,7 @@
         <v>44722.48768518519</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13927,7 +13927,7 @@
         <v>44279.64934027778</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         <v>44386</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         <v>44608.50458333334</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14103,7 +14103,7 @@
         <v>44817</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14160,7 +14160,7 @@
         <v>44662</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>44095</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>44427</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>44292</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>44588.37998842593</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>44588</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         <v>45545.49508101852</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>44564</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>45361.87975694444</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>45632.72635416667</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         <v>45113.56574074074</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>44896</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>44540</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>44916.55414351852</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>44379</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>44284.44574074074</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15087,7 +15087,7 @@
         <v>45699.44291666667</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>45111.48395833333</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15201,7 +15201,7 @@
         <v>45114.49505787037</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15258,7 +15258,7 @@
         <v>44176</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
         <v>45111.48225694444</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>45111.48636574074</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>44636</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15486,7 +15486,7 @@
         <v>45098.30535879629</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15543,7 +15543,7 @@
         <v>45149.60917824074</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>45482.52887731481</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>44817.57988425926</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>44879.62173611111</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>44994.40635416667</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>44175.39748842592</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>45033.76043981482</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>45196.57247685185</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>45667.39670138889</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>45705.73300925926</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>45154.49831018518</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>45700.68672453704</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16227,7 +16227,7 @@
         <v>45722.48634259259</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>45481.56722222222</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>44603</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>45453.36854166666</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>44992.34151620371</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>45147.67172453704</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>44502</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>44959.66407407408</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>45378.32185185186</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16745,7 +16745,7 @@
         <v>45726.44471064815</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>45114.55136574074</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>45624.60141203704</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>45617.47570601852</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         <v>45171.77335648148</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17030,7 +17030,7 @@
         <v>45698.53336805556</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17087,7 +17087,7 @@
         <v>45377.40043981482</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>45219.69356481481</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>45411.47335648148</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>44607</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>45211.55472222222</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>45113.43921296296</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>44991.89657407408</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>44879.55940972222</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17548,7 +17548,7 @@
         <v>45764.44931712963</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>45054.6750462963</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>44967.45122685185</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>44903</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>44977</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>44991.30547453704</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>44991</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>45498.673125</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>44963.44769675926</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>45720.44217592593</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>44909</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>44825.4336574074</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>45215.60199074074</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>45747.43196759259</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>45533.55362268518</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>45747.42633101852</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>45747.42958333333</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>45699.60055555555</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>44784.62724537037</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>45754.33641203704</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>45415.57682870371</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>45187.42854166667</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>45735.56751157407</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18864,7 +18864,7 @@
         <v>45048.59699074074</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         <v>44475</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         <v>44981.58834490741</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>44839.4528125</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19092,7 +19092,7 @@
         <v>45761.44584490741</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>45728.54832175926</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>44693.62822916666</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19268,7 +19268,7 @@
         <v>44875.27736111111</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19325,7 +19325,7 @@
         <v>45533.54429398148</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>44973.43075231482</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>45261.44914351852</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19496,7 +19496,7 @@
         <v>44910.54231481482</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19553,7 +19553,7 @@
         <v>45106.2610300926</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>45705.74418981482</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>45301.68237268519</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>45722.48915509259</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19781,7 +19781,7 @@
         <v>45346.67184027778</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>45732.79925925926</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19895,7 +19895,7 @@
         <v>45106</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19952,7 +19952,7 @@
         <v>45743.41148148148</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20009,7 +20009,7 @@
         <v>45147.67096064815</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20066,7 +20066,7 @@
         <v>45569.44684027778</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20123,7 +20123,7 @@
         <v>45610.59094907407</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20180,7 +20180,7 @@
         <v>45148</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20237,7 +20237,7 @@
         <v>45361.90282407407</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20294,7 +20294,7 @@
         <v>44952.35775462963</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20351,7 +20351,7 @@
         <v>45243.84869212963</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20408,7 +20408,7 @@
         <v>44643</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20465,7 +20465,7 @@
         <v>45548</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20522,7 +20522,7 @@
         <v>44992</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20579,7 +20579,7 @@
         <v>45052</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20636,7 +20636,7 @@
         <v>45394.50028935185</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>45761.35990740741</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20750,7 +20750,7 @@
         <v>44964.44356481481</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>45138</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20864,7 +20864,7 @@
         <v>45238.4328587963</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20921,7 +20921,7 @@
         <v>45394.66887731481</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20978,7 +20978,7 @@
         <v>45299.62576388889</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21035,7 +21035,7 @@
         <v>44893</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>45623.9525462963</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21149,7 +21149,7 @@
         <v>45658.80232638889</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21206,7 +21206,7 @@
         <v>45658.80827546296</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21263,7 +21263,7 @@
         <v>45572.48293981481</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21320,7 +21320,7 @@
         <v>45147</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21377,7 +21377,7 @@
         <v>45453.36067129629</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>45020</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>45317</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>45384.66917824074</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>45734.62017361111</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         <v>44992.62498842592</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21724,7 +21724,7 @@
         <v>44302</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21781,7 +21781,7 @@
         <v>45588.66457175926</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21838,7 +21838,7 @@
         <v>45169</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21895,7 +21895,7 @@
         <v>45698.51711805556</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21952,7 +21952,7 @@
         <v>45513.55840277778</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22009,7 +22009,7 @@
         <v>45513.56527777778</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22066,7 +22066,7 @@
         <v>44867</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22123,7 +22123,7 @@
         <v>44564.62598379629</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22180,7 +22180,7 @@
         <v>45552.36759259259</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22237,7 +22237,7 @@
         <v>45607.56773148148</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22294,7 +22294,7 @@
         <v>45674.71810185185</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>44111</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22408,7 +22408,7 @@
         <v>45637.66542824074</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22465,7 +22465,7 @@
         <v>44745.84396990741</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22522,7 +22522,7 @@
         <v>45030.71012731481</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22579,7 +22579,7 @@
         <v>45639.56185185185</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22636,7 +22636,7 @@
         <v>45630.45069444444</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22693,7 +22693,7 @@
         <v>45153.32778935185</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>45635.66695601852</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22807,7 +22807,7 @@
         <v>45434.55831018519</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22869,7 +22869,7 @@
         <v>45434.56398148148</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22931,7 +22931,7 @@
         <v>45533.56108796296</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22988,7 +22988,7 @@
         <v>45533.58302083334</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>45345.83557870371</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23107,7 +23107,7 @@
         <v>45211.541875</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>45124</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23221,7 +23221,7 @@
         <v>44890</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>44278.54855324074</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>45224.64659722222</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>45278</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23459,7 +23459,7 @@
         <v>45761.39600694444</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23516,7 +23516,7 @@
         <v>45029</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23573,7 +23573,7 @@
         <v>44720.53898148148</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23630,7 +23630,7 @@
         <v>45588.65545138889</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>45539.38744212963</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>45699.45671296296</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>45086</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23858,7 +23858,7 @@
         <v>45128</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23915,7 +23915,7 @@
         <v>45121.5965162037</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23977,7 +23977,7 @@
         <v>45121.59954861111</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24039,7 +24039,7 @@
         <v>45121.6096875</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>44635</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         <v>44966</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24215,7 +24215,7 @@
         <v>45482.49870370371</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24272,7 +24272,7 @@
         <v>44243</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24329,7 +24329,7 @@
         <v>45237.63225694445</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24386,7 +24386,7 @@
         <v>45237.64408564815</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24443,7 +24443,7 @@
         <v>45533.63056712963</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24505,7 +24505,7 @@
         <v>44431</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24562,7 +24562,7 @@
         <v>45343.68038194445</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
         <v>45581.57958333333</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>45071</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24733,7 +24733,7 @@
         <v>45539.65212962963</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24790,7 +24790,7 @@
         <v>45763.59436342592</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24847,7 +24847,7 @@
         <v>44410</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24904,7 +24904,7 @@
         <v>45301.67554398148</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24961,7 +24961,7 @@
         <v>45301.67736111111</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25018,7 +25018,7 @@
         <v>45769</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25075,7 +25075,7 @@
         <v>45097.40524305555</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25137,7 +25137,7 @@
         <v>44546</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25194,7 +25194,7 @@
         <v>45481.58048611111</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25251,7 +25251,7 @@
         <v>45768.65611111111</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
         <v>45111.48787037037</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25365,7 +25365,7 @@
         <v>45391.41976851852</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25422,7 +25422,7 @@
         <v>44931</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>44377</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>45369.62780092593</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25598,7 +25598,7 @@
         <v>44377.49684027778</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>44965.4815162037</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25717,7 +25717,7 @@
         <v>45328.38755787037</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25774,7 +25774,7 @@
         <v>45558.44914351852</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>45309.59487268519</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>44861</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>45300.3794212963</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26002,7 +26002,7 @@
         <v>45526.3865625</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26064,7 +26064,7 @@
         <v>45755.64450231481</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26121,7 +26121,7 @@
         <v>45254.62489583333</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26183,7 +26183,7 @@
         <v>45350.53306712963</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26240,7 +26240,7 @@
         <v>45518.40657407408</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>45063.49936342592</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26354,7 +26354,7 @@
         <v>45741.37270833334</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26411,7 +26411,7 @@
         <v>45784.74996527778</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>44237</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26525,7 +26525,7 @@
         <v>45622</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>45574.35809027778</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26639,7 +26639,7 @@
         <v>45533.61996527778</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>45485.45778935185</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>44588</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>45582.41200231481</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26872,7 +26872,7 @@
         <v>45786.52931712963</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>45786.52996527778</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>45786.52878472222</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>45145</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>45463</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>45187.60813657408</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>45736.50743055555</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>44833.60123842592</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27328,7 +27328,7 @@
         <v>44981.64725694444</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27385,7 +27385,7 @@
         <v>44270.39765046296</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>45163.41376157408</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27504,7 +27504,7 @@
         <v>45630.47564814815</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27561,7 +27561,7 @@
         <v>45108.703125</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27618,7 +27618,7 @@
         <v>44510.52157407408</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27675,7 +27675,7 @@
         <v>44553</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27732,7 +27732,7 @@
         <v>44897</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27789,7 +27789,7 @@
         <v>45498</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27846,7 +27846,7 @@
         <v>45698.69016203703</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>45726.62721064815</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>44418</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28017,7 +28017,7 @@
         <v>45009.4671875</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28074,7 +28074,7 @@
         <v>45217.47834490741</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
         <v>44566</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28188,7 +28188,7 @@
         <v>44488.35878472222</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28245,7 +28245,7 @@
         <v>44918</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28302,7 +28302,7 @@
         <v>44992</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28359,7 +28359,7 @@
         <v>45450.51092592593</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28416,7 +28416,7 @@
         <v>45163</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
         <v>44988</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28530,7 +28530,7 @@
         <v>45275.41833333333</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>45168.89298611111</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>44999.86172453704</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>44999.8625</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>45148</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>45187</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>44453.56578703703</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>44754</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28986,7 +28986,7 @@
         <v>45791.89865740741</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29043,7 +29043,7 @@
         <v>45552.36484953704</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>45460.62172453704</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>45581.57016203704</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29214,7 +29214,7 @@
         <v>45581.58418981481</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29271,7 +29271,7 @@
         <v>45495</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29328,7 +29328,7 @@
         <v>45618.56787037037</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>45699.45392361111</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>44769.45805555556</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>45128.58414351852</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29556,7 +29556,7 @@
         <v>44127</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29613,7 +29613,7 @@
         <v>45259.51916666667</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29675,7 +29675,7 @@
         <v>45259.52020833334</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>45171.96248842592</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29794,7 +29794,7 @@
         <v>45562.46342592593</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>45796</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29908,7 +29908,7 @@
         <v>45650.37370370371</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29965,7 +29965,7 @@
         <v>45749.56196759259</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30027,7 +30027,7 @@
         <v>45086</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30084,7 +30084,7 @@
         <v>44613</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30141,7 +30141,7 @@
         <v>45128.37305555555</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30198,7 +30198,7 @@
         <v>45189</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30255,7 +30255,7 @@
         <v>44517</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30312,7 +30312,7 @@
         <v>45540.50098379629</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30369,7 +30369,7 @@
         <v>45533.38870370371</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
         <v>44992</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30488,7 +30488,7 @@
         <v>45658.78774305555</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30545,7 +30545,7 @@
         <v>45121.61318287037</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30607,7 +30607,7 @@
         <v>45275.32266203704</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>44746.38834490741</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30721,7 +30721,7 @@
         <v>45527.68784722222</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30778,7 +30778,7 @@
         <v>44598</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30835,7 +30835,7 @@
         <v>45603.74959490741</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30892,7 +30892,7 @@
         <v>45079.87827546296</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30949,7 +30949,7 @@
         <v>45425.57538194444</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31006,7 +31006,7 @@
         <v>45475.48303240741</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31063,7 +31063,7 @@
         <v>45735.58024305556</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31120,7 +31120,7 @@
         <v>44579.62225694444</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31177,7 +31177,7 @@
         <v>44495</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31234,7 +31234,7 @@
         <v>45090.89653935185</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31291,7 +31291,7 @@
         <v>45090.89880787037</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31348,7 +31348,7 @@
         <v>45232</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31405,7 +31405,7 @@
         <v>44638.55256944444</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31462,7 +31462,7 @@
         <v>44600</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31519,7 +31519,7 @@
         <v>45041.63380787037</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31576,7 +31576,7 @@
         <v>45002</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31633,7 +31633,7 @@
         <v>45715.44159722222</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31690,7 +31690,7 @@
         <v>44992.4255787037</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31747,7 +31747,7 @@
         <v>45482.54844907407</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31804,7 +31804,7 @@
         <v>44867</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31861,7 +31861,7 @@
         <v>44451</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31918,7 +31918,7 @@
         <v>45236</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31975,7 +31975,7 @@
         <v>45574.49298611111</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32032,7 +32032,7 @@
         <v>45121</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32089,7 +32089,7 @@
         <v>44967.44255787037</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32146,7 +32146,7 @@
         <v>44903.33363425926</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32203,7 +32203,7 @@
         <v>45401.53033564815</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32260,7 +32260,7 @@
         <v>45245.5735300926</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32317,7 +32317,7 @@
         <v>45415.47848379629</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>45635.66409722222</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32431,7 +32431,7 @@
         <v>45174.31395833333</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32488,7 +32488,7 @@
         <v>45621.46103009259</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32545,7 +32545,7 @@
         <v>44943.57309027778</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32602,7 +32602,7 @@
         <v>45804.39141203704</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32659,7 +32659,7 @@
         <v>45804.67065972222</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32716,7 +32716,7 @@
         <v>45804.6953587963</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32778,7 +32778,7 @@
         <v>44861.52505787037</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32835,7 +32835,7 @@
         <v>45308.61152777778</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32892,7 +32892,7 @@
         <v>45804.708125</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32954,7 +32954,7 @@
         <v>45317.40372685185</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33016,7 +33016,7 @@
         <v>44857.65989583333</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33073,7 +33073,7 @@
         <v>44077</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33130,7 +33130,7 @@
         <v>45805.39247685186</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33187,7 +33187,7 @@
         <v>44965</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33244,7 +33244,7 @@
         <v>45063.508125</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33301,7 +33301,7 @@
         <v>44895.62296296296</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33358,7 +33358,7 @@
         <v>44452</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33415,7 +33415,7 @@
         <v>45359.44837962963</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33472,7 +33472,7 @@
         <v>45805.52983796296</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33529,7 +33529,7 @@
         <v>45009</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33586,7 +33586,7 @@
         <v>45379</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33643,7 +33643,7 @@
         <v>45804.44519675926</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33700,7 +33700,7 @@
         <v>45805</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33757,7 +33757,7 @@
         <v>45719.84378472222</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33814,7 +33814,7 @@
         <v>44944.71386574074</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33871,7 +33871,7 @@
         <v>44944.72100694444</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33928,7 +33928,7 @@
         <v>45467.74417824074</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33985,7 +33985,7 @@
         <v>45446.36482638889</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>44820</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34104,7 +34104,7 @@
         <v>44312</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34161,7 +34161,7 @@
         <v>45853.87112268519</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34218,7 +34218,7 @@
         <v>45215.5959375</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34275,7 +34275,7 @@
         <v>45215.59743055556</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34332,7 +34332,7 @@
         <v>45351.6062962963</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34389,7 +34389,7 @@
         <v>45000.47998842593</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34446,7 +34446,7 @@
         <v>45853.88070601852</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34503,7 +34503,7 @@
         <v>45440.28329861111</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34560,7 +34560,7 @@
         <v>45495</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34617,7 +34617,7 @@
         <v>45554.63225694445</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         <v>45257.67958333333</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>45674.74094907408</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>44595.583125</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>44999.35858796296</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34902,7 +34902,7 @@
         <v>45810.00048611111</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34959,7 +34959,7 @@
         <v>45301</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35016,7 +35016,7 @@
         <v>44789</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35073,7 +35073,7 @@
         <v>45539.66027777778</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35130,7 +35130,7 @@
         <v>45565.40657407408</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35187,7 +35187,7 @@
         <v>45482.54108796296</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35244,7 +35244,7 @@
         <v>45195.58452546296</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35301,7 +35301,7 @@
         <v>45026.82216435186</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35358,7 +35358,7 @@
         <v>44958.61047453704</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35415,7 +35415,7 @@
         <v>45219.40528935185</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35472,7 +35472,7 @@
         <v>45853.87599537037</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35529,7 +35529,7 @@
         <v>45266.32614583334</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35586,7 +35586,7 @@
         <v>44663</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35643,7 +35643,7 @@
         <v>45567</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35700,7 +35700,7 @@
         <v>45623.95947916667</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>45041</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35814,7 +35814,7 @@
         <v>44440</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35871,7 +35871,7 @@
         <v>45434.55471064815</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35933,7 +35933,7 @@
         <v>45434.56291666667</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35995,7 +35995,7 @@
         <v>45554.62944444444</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36052,7 +36052,7 @@
         <v>44083</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36109,7 +36109,7 @@
         <v>45632.37459490741</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36166,7 +36166,7 @@
         <v>45201.39996527778</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36223,7 +36223,7 @@
         <v>44803.59118055556</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36280,7 +36280,7 @@
         <v>45567.42011574074</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36337,7 +36337,7 @@
         <v>45086.63334490741</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36394,7 +36394,7 @@
         <v>44587.48847222222</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36451,7 +36451,7 @@
         <v>45110.4275</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36508,7 +36508,7 @@
         <v>45858.60641203704</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36565,7 +36565,7 @@
         <v>45814.38221064815</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36622,7 +36622,7 @@
         <v>45503.5658912037</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36679,7 +36679,7 @@
         <v>44599</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36736,7 +36736,7 @@
         <v>44956</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36798,7 +36798,7 @@
         <v>44270.38002314815</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36860,7 +36860,7 @@
         <v>45814.3865625</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36917,7 +36917,7 @@
         <v>44944.73487268519</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36974,7 +36974,7 @@
         <v>44596</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37031,7 +37031,7 @@
         <v>45330</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37088,7 +37088,7 @@
         <v>45330</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37145,7 +37145,7 @@
         <v>45858.66019675926</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37202,7 +37202,7 @@
         <v>45818.58993055556</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37264,7 +37264,7 @@
         <v>45113.41633101852</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37321,7 +37321,7 @@
         <v>45818.58769675926</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37383,7 +37383,7 @@
         <v>45818.595625</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37445,7 +37445,7 @@
         <v>45818.59261574074</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37507,7 +37507,7 @@
         <v>45666</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37564,7 +37564,7 @@
         <v>45818.5862037037</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37626,7 +37626,7 @@
         <v>45817.88496527778</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37683,7 +37683,7 @@
         <v>45250.5278587963</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37740,7 +37740,7 @@
         <v>45070</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37797,7 +37797,7 @@
         <v>45225.60192129629</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37854,7 +37854,7 @@
         <v>44918.50106481482</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37911,7 +37911,7 @@
         <v>45819.61060185185</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37968,7 +37968,7 @@
         <v>45700.68289351852</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38025,7 +38025,7 @@
         <v>44539</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38082,7 +38082,7 @@
         <v>45299.47513888889</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38139,7 +38139,7 @@
         <v>45027.59450231482</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38201,7 +38201,7 @@
         <v>45820.33708333333</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38258,7 +38258,7 @@
         <v>45820.34128472222</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38315,7 +38315,7 @@
         <v>44910</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38372,7 +38372,7 @@
         <v>45224.6515162037</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38434,7 +38434,7 @@
         <v>45377</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38491,7 +38491,7 @@
         <v>45106.25025462963</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38548,7 +38548,7 @@
         <v>45114.47895833333</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38605,7 +38605,7 @@
         <v>45820.33930555556</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38662,7 +38662,7 @@
         <v>44598.7384837963</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38719,7 +38719,7 @@
         <v>45825.57805555555</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38776,7 +38776,7 @@
         <v>45867.64663194444</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38833,7 +38833,7 @@
         <v>45867.69346064814</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38890,7 +38890,7 @@
         <v>45867.50792824074</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38947,7 +38947,7 @@
         <v>44848.59133101852</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39004,7 +39004,7 @@
         <v>45867.63094907408</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39061,7 +39061,7 @@
         <v>45825.58672453704</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39118,7 +39118,7 @@
         <v>45867.56320601852</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>45867.68625</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>45825.50280092593</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>45825.5796875</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39346,7 +39346,7 @@
         <v>45559.38876157408</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39403,7 +39403,7 @@
         <v>45224</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39460,7 +39460,7 @@
         <v>45349.54434027777</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39517,7 +39517,7 @@
         <v>45867.51630787037</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39574,7 +39574,7 @@
         <v>45334.78826388889</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39631,7 +39631,7 @@
         <v>45825.57680555555</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39688,7 +39688,7 @@
         <v>45415.48979166667</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39745,7 +39745,7 @@
         <v>45114.58148148148</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39802,7 +39802,7 @@
         <v>44600</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39859,7 +39859,7 @@
         <v>45581.57333333333</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39916,7 +39916,7 @@
         <v>44542.90072916666</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39973,7 +39973,7 @@
         <v>45359.45038194444</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40030,7 +40030,7 @@
         <v>44895.46524305556</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40087,7 +40087,7 @@
         <v>44587</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>45827</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40201,7 +40201,7 @@
         <v>45569.45017361111</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40258,7 +40258,7 @@
         <v>45569.47494212963</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40315,7 +40315,7 @@
         <v>45827</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>45588.67070601852</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40429,7 +40429,7 @@
         <v>45749.60487268519</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40491,7 +40491,7 @@
         <v>45355.54138888889</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40548,7 +40548,7 @@
         <v>45869.62276620371</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40605,7 +40605,7 @@
         <v>44984.45895833334</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40662,7 +40662,7 @@
         <v>44949</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40719,7 +40719,7 @@
         <v>45660</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>45446.36865740741</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40838,7 +40838,7 @@
         <v>45245.63574074074</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>45090</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40952,7 +40952,7 @@
         <v>44467.83386574074</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41009,7 +41009,7 @@
         <v>45870.51958333333</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41066,7 +41066,7 @@
         <v>45870.51708333333</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41123,7 +41123,7 @@
         <v>45870.52005787037</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41180,7 +41180,7 @@
         <v>45870.52142361111</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41237,7 +41237,7 @@
         <v>45831</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41294,7 +41294,7 @@
         <v>45732.75637731481</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41351,7 +41351,7 @@
         <v>45732.76936342593</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41408,7 +41408,7 @@
         <v>44340</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41465,7 +41465,7 @@
         <v>45707.3793287037</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41522,7 +41522,7 @@
         <v>45870.52111111111</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41579,7 +41579,7 @@
         <v>45875.42716435185</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41636,7 +41636,7 @@
         <v>45874.57109953704</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41693,7 +41693,7 @@
         <v>44790.49040509259</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41750,7 +41750,7 @@
         <v>44784.42528935185</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41807,7 +41807,7 @@
         <v>45875.47454861111</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41864,7 +41864,7 @@
         <v>45833.64563657407</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41921,7 +41921,7 @@
         <v>45833.64814814815</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41978,7 +41978,7 @@
         <v>45832.46146990741</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42035,7 +42035,7 @@
         <v>44578.32717592592</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42092,7 +42092,7 @@
         <v>45833.64237268519</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42149,7 +42149,7 @@
         <v>44935</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42206,7 +42206,7 @@
         <v>44852</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42263,7 +42263,7 @@
         <v>45875.45716435185</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42320,7 +42320,7 @@
         <v>45100.85270833333</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42377,7 +42377,7 @@
         <v>45525.41762731481</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42434,7 +42434,7 @@
         <v>45832.34540509259</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42491,7 +42491,7 @@
         <v>44964.5115162037</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42548,7 +42548,7 @@
         <v>45517.8162037037</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42605,7 +42605,7 @@
         <v>45834.65040509259</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42667,7 +42667,7 @@
         <v>44578.62943287037</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42724,7 +42724,7 @@
         <v>45709.62280092593</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42781,7 +42781,7 @@
         <v>45835.44709490741</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42838,7 +42838,7 @@
         <v>44994.46908564815</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42895,7 +42895,7 @@
         <v>44900.57393518519</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42952,7 +42952,7 @@
         <v>45835.48267361111</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43009,7 +43009,7 @@
         <v>45835.48445601852</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43066,7 +43066,7 @@
         <v>45835.48862268519</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43123,7 +43123,7 @@
         <v>44440.60415509259</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43180,7 +43180,7 @@
         <v>45201</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43237,7 +43237,7 @@
         <v>45121.58699074074</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43299,7 +43299,7 @@
         <v>44966</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43356,7 +43356,7 @@
         <v>45834.64667824074</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43418,7 +43418,7 @@
         <v>45835.44732638889</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43475,7 +43475,7 @@
         <v>45211.52642361111</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43532,7 +43532,7 @@
         <v>45323.53744212963</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43589,7 +43589,7 @@
         <v>45075.43059027778</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43646,7 +43646,7 @@
         <v>44630</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43703,7 +43703,7 @@
         <v>45308.59001157407</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43760,7 +43760,7 @@
         <v>45111.30824074074</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>45371.45865740741</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43874,7 +43874,7 @@
         <v>45100.4062962963</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43931,7 +43931,7 @@
         <v>45086.63194444445</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43988,7 +43988,7 @@
         <v>45196</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44045,7 +44045,7 @@
         <v>44795</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44102,7 +44102,7 @@
         <v>45835.36229166666</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44164,7 +44164,7 @@
         <v>45835.45099537037</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44221,7 +44221,7 @@
         <v>45280.66769675926</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44278,7 +44278,7 @@
         <v>45835.4924537037</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44335,7 +44335,7 @@
         <v>45834.65197916667</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44397,7 +44397,7 @@
         <v>45112.33599537037</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44454,7 +44454,7 @@
         <v>45111</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44511,7 +44511,7 @@
         <v>45320.89128472222</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44568,7 +44568,7 @@
         <v>44987.54104166666</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44625,7 +44625,7 @@
         <v>45202.4209837963</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44682,7 +44682,7 @@
         <v>45632.36706018518</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44739,7 +44739,7 @@
         <v>45632.44886574074</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44796,7 +44796,7 @@
         <v>45245.36174768519</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44853,7 +44853,7 @@
         <v>44585.50431712963</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44910,7 +44910,7 @@
         <v>45208</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44967,7 +44967,7 @@
         <v>45001.43854166667</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45024,7 +45024,7 @@
         <v>44585.51060185185</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45081,7 +45081,7 @@
         <v>45260.4716550926</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45138,7 +45138,7 @@
         <v>45880.51413194444</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45200,7 +45200,7 @@
         <v>45881</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45257,7 +45257,7 @@
         <v>45880.51550925926</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45319,7 +45319,7 @@
         <v>44943.62954861111</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45376,7 +45376,7 @@
         <v>45170</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45433,7 +45433,7 @@
         <v>45881.59877314815</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45490,7 +45490,7 @@
         <v>45837.77916666667</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45547,7 +45547,7 @@
         <v>45371.36359953704</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45604,7 +45604,7 @@
         <v>45837.77701388889</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45661,7 +45661,7 @@
         <v>45880.38380787037</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45718,7 +45718,7 @@
         <v>45840.59474537037</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45775,7 +45775,7 @@
         <v>45840.59853009259</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45832,7 +45832,7 @@
         <v>45841.70569444444</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45889,7 +45889,7 @@
         <v>45841.70868055556</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45946,7 +45946,7 @@
         <v>44938</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46008,7 +46008,7 @@
         <v>45832.46649305556</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46065,7 +46065,7 @@
         <v>44949</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46127,7 +46127,7 @@
         <v>45841.7072337963</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46184,7 +46184,7 @@
         <v>44867</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46241,7 +46241,7 @@
         <v>44732.3659837963</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46298,7 +46298,7 @@
         <v>45635.4874537037</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46355,7 +46355,7 @@
         <v>45483.82479166667</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>45020</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46469,7 +46469,7 @@
         <v>45568.30189814815</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46526,7 +46526,7 @@
         <v>45568.36879629629</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46583,7 +46583,7 @@
         <v>45811.45460648148</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46640,7 +46640,7 @@
         <v>44159</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46697,7 +46697,7 @@
         <v>44894.49538194444</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46754,7 +46754,7 @@
         <v>45884.50331018519</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46816,7 +46816,7 @@
         <v>44172</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46873,7 +46873,7 @@
         <v>45713.92412037037</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46930,7 +46930,7 @@
         <v>45845.42015046296</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46987,7 +46987,7 @@
         <v>45446.36774305555</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47049,7 +47049,7 @@
         <v>45615.48927083334</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47106,7 +47106,7 @@
         <v>45845.43803240741</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47163,7 +47163,7 @@
         <v>45845.49414351852</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47220,7 +47220,7 @@
         <v>44790.45876157407</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47277,7 +47277,7 @@
         <v>44790.49523148148</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47334,7 +47334,7 @@
         <v>45820.03976851852</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47391,7 +47391,7 @@
         <v>45884.50613425926</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47453,7 +47453,7 @@
         <v>45729.36868055556</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47510,7 +47510,7 @@
         <v>45887.68759259259</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47567,7 +47567,7 @@
         <v>45211.43555555555</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47624,7 +47624,7 @@
         <v>44893</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47681,7 +47681,7 @@
         <v>45174.40454861111</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47738,7 +47738,7 @@
         <v>44984</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47795,7 +47795,7 @@
         <v>44984</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47852,7 +47852,7 @@
         <v>45018</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47909,7 +47909,7 @@
         <v>45713.45311342592</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47966,7 +47966,7 @@
         <v>44994.42113425926</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48023,7 +48023,7 @@
         <v>45176.72427083334</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48080,7 +48080,7 @@
         <v>45759.38987268518</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48137,7 +48137,7 @@
         <v>45105</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48194,7 +48194,7 @@
         <v>44788</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48251,7 +48251,7 @@
         <v>45847.91280092593</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48308,7 +48308,7 @@
         <v>45891.50525462963</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48365,7 +48365,7 @@
         <v>45891.50986111111</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48422,7 +48422,7 @@
         <v>44258</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>45061</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48541,7 +48541,7 @@
         <v>45070.3665625</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48598,7 +48598,7 @@
         <v>45891</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48655,7 +48655,7 @@
         <v>45028</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48712,7 +48712,7 @@
         <v>44310</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48769,7 +48769,7 @@
         <v>45096.45247685185</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48826,7 +48826,7 @@
         <v>45391.41310185185</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48883,7 +48883,7 @@
         <v>45698.53725694444</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48940,7 +48940,7 @@
         <v>45163.63621527778</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49002,7 +49002,7 @@
         <v>45891</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49059,7 +49059,7 @@
         <v>45456.59289351852</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49116,7 +49116,7 @@
         <v>45891.50216435185</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49173,7 +49173,7 @@
         <v>45481.55984953704</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49230,7 +49230,7 @@
         <v>45093.62777777778</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49292,7 +49292,7 @@
         <v>45630.35827546296</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49349,7 +49349,7 @@
         <v>44964.50894675926</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49406,7 +49406,7 @@
         <v>45257.70313657408</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49463,7 +49463,7 @@
         <v>44431.84840277778</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49520,7 +49520,7 @@
         <v>45671.46746527778</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49577,7 +49577,7 @@
         <v>45755.44333333334</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49634,7 +49634,7 @@
         <v>45110.4184375</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49691,7 +49691,7 @@
         <v>45533.60232638889</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49753,7 +49753,7 @@
         <v>45533.60770833334</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49815,7 +49815,7 @@
         <v>45001.59209490741</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49872,7 +49872,7 @@
         <v>45569.44295138889</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49929,7 +49929,7 @@
         <v>44879</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49986,7 +49986,7 @@
         <v>45182.78834490741</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50043,7 +50043,7 @@
         <v>45475.49018518518</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50100,7 +50100,7 @@
         <v>44510.60921296296</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50162,7 +50162,7 @@
         <v>45761.4437962963</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50219,7 +50219,7 @@
         <v>44961</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50276,7 +50276,7 @@
         <v>45128.9325</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50333,7 +50333,7 @@
         <v>45128.93540509259</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50390,7 +50390,7 @@
         <v>44999.36081018519</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50447,7 +50447,7 @@
         <v>44984</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50504,7 +50504,7 @@
         <v>45567</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50561,7 +50561,7 @@
         <v>45090.38012731481</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50618,7 +50618,7 @@
         <v>44466.34962962963</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50675,7 +50675,7 @@
         <v>45530.33202546297</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50732,7 +50732,7 @@
         <v>45174</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50789,7 +50789,7 @@
         <v>45091.67936342592</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50846,7 +50846,7 @@
         <v>44910.41346064815</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50903,7 +50903,7 @@
         <v>45483.82834490741</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50960,7 +50960,7 @@
         <v>45698.52806712963</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51017,7 +51017,7 @@
         <v>45271.66576388889</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51074,7 +51074,7 @@
         <v>45224.60075231481</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51136,7 +51136,7 @@
         <v>45646.38200231481</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51193,7 +51193,7 @@
         <v>44392</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>

--- a/Översikt VIMMERBY.xlsx
+++ b/Översikt VIMMERBY.xlsx
@@ -567,7 +567,7 @@
         <v>44811</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
         <v>44811</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44811</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44811</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>45314</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>44939</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>45377.54726851852</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>45301.67922453704</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>45755</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45748</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>45121.60543981481</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>45678.64175925926</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>45821</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>44245</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>44811</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>45628</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>45020</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>45742</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>44424</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>44426.64793981481</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>44386</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>45760.34877314815</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>45048</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>44943</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>45786.52827546297</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>45072</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>45008.60878472222</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>44371</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>45713</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>45399.71412037037</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>44082</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>44236</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>45104</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>44075</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>45224</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>45168</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>45168</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>45667</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>44403</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>44377.61104166666</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>45821</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>45649</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>45825.58484953704</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>45077</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>45574.42767361111</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>45125</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>44068</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         <v>44083</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>44130</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>44102</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>44281.79269675926</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>44270.67071759259</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>44287.33261574074</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>44210</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>44481.47483796296</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>44490.38613425926</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>44447</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>44350</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>44614</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>44375.39033564815</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>44215</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         <v>44070.39203703704</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>44670</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>44670</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>44307</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>44350</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>44105</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         <v>44225</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         <v>44070</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6078,7 +6078,7 @@
         <v>44327.47658564815</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>44509</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6192,7 +6192,7 @@
         <v>44406</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>44230.58883101852</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         <v>44480</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>44238</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>44585.51829861111</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>44824.53434027778</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>44418</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>44785.40800925926</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         <v>44862</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>44578.47597222222</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>44516.59703703703</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         <v>44603</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>44588</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>44826.68010416667</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>44483.58295138889</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         <v>44542.8859375</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>44404.87505787037</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         <v>44494</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7218,7 +7218,7 @@
         <v>44354</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>44512.70245370371</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>44090</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
         <v>44221.39408564815</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>44790</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>44261</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>44530.38055555556</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         <v>44588</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>44588</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>44790</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>44790.47628472222</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>44175.3815625</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>44175.40881944444</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>44312</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>44475</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>44385</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>44237.8550925926</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>44124.59795138889</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>44410.71038194445</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         <v>44279.33400462963</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>44175</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>44670</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8472,7 +8472,7 @@
         <v>44365</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>44169</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
         <v>44273</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>44301.36048611111</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>44729.28226851852</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>44271.37226851852</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>44340.54472222222</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>44340</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>44774</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>44733</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>44733</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>44154</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>44371.62743055556</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>44386.40783564815</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
         <v>44480</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>44245</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>44070.40998842593</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>44337</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9503,7 +9503,7 @@
         <v>44102</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>44463.29439814815</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>44588</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>44117</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>44789</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>44377</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9845,7 +9845,7 @@
         <v>44379</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>44508</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>44294</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>44294</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>44676.85248842592</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>44604</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>44091</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10254,7 +10254,7 @@
         <v>44305</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>44634.69703703704</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         <v>44851.95016203704</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>44480</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>44769.45422453704</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
         <v>44340.58002314815</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10596,7 +10596,7 @@
         <v>44085</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         <v>44142</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>44092</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>44612.86762731482</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>44644</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>44305.40046296296</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>44447</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         <v>44383</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>44476</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>44517</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>44418</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>44854</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>44824</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11342,7 +11342,7 @@
         <v>44369</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>44742</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>44832.67608796297</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>44819</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>44217.79856481482</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11627,7 +11627,7 @@
         <v>44451.8375</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11684,7 +11684,7 @@
         <v>44823</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
         <v>44621</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>44172</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11855,7 +11855,7 @@
         <v>44384</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11912,7 +11912,7 @@
         <v>44790.48503472222</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>44854.59157407407</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>44270</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>44341</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>44070</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12197,7 +12197,7 @@
         <v>44608</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
         <v>44876.48346064815</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12311,7 +12311,7 @@
         <v>44733.43092592592</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>44620</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         <v>44447.34237268518</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12482,7 +12482,7 @@
         <v>44294</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>44116</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12596,7 +12596,7 @@
         <v>44609</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12653,7 +12653,7 @@
         <v>44203</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12710,7 +12710,7 @@
         <v>44284.42348379629</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>44088</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>44088</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12881,7 +12881,7 @@
         <v>44421</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12938,7 +12938,7 @@
         <v>44186</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12995,7 +12995,7 @@
         <v>44273</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13052,7 +13052,7 @@
         <v>44070</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13109,7 +13109,7 @@
         <v>44266.7240625</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13171,7 +13171,7 @@
         <v>44278.63479166666</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>44480</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>44270.49743055556</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>44089.78633101852</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>44612.86554398148</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
         <v>44466.34726851852</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13523,7 +13523,7 @@
         <v>44866.81100694444</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>44470.44232638889</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13642,7 +13642,7 @@
         <v>44375.38789351852</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13699,7 +13699,7 @@
         <v>44776</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13756,7 +13756,7 @@
         <v>44634</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13813,7 +13813,7 @@
         <v>44525.63913194444</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13870,7 +13870,7 @@
         <v>44722.48768518519</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13927,7 +13927,7 @@
         <v>44279.64934027778</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         <v>44386</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         <v>44608.50458333334</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14103,7 +14103,7 @@
         <v>44817</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14160,7 +14160,7 @@
         <v>44662</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>44095</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>44427</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>44292</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>44588.37998842593</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>44588</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         <v>45545.49508101852</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>44564</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>45361.87975694444</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>45632.72635416667</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         <v>45113.56574074074</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>44896</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>44540</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>44916.55414351852</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>44379</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>44284.44574074074</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15087,7 +15087,7 @@
         <v>45699.44291666667</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>45111.48395833333</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15201,7 +15201,7 @@
         <v>45114.49505787037</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15258,7 +15258,7 @@
         <v>44176</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
         <v>45111.48225694444</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>45111.48636574074</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>44636</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15486,7 +15486,7 @@
         <v>45098.30535879629</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15543,7 +15543,7 @@
         <v>45149.60917824074</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>45482.52887731481</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>44817.57988425926</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>44879.62173611111</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>44994.40635416667</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>44175.39748842592</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>45033.76043981482</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>45196.57247685185</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>45667.39670138889</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>45705.73300925926</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>45154.49831018518</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>45700.68672453704</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16227,7 +16227,7 @@
         <v>45722.48634259259</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>45481.56722222222</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>44603</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>45453.36854166666</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>44992.34151620371</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>45147.67172453704</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>44502</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>44959.66407407408</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>45378.32185185186</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16745,7 +16745,7 @@
         <v>45726.44471064815</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>45114.55136574074</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>45624.60141203704</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>45617.47570601852</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         <v>45171.77335648148</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17030,7 +17030,7 @@
         <v>45698.53336805556</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17087,7 +17087,7 @@
         <v>45377.40043981482</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>45219.69356481481</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>45411.47335648148</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>44607</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>45211.55472222222</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>45113.43921296296</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>44991.89657407408</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>44879.55940972222</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17548,7 +17548,7 @@
         <v>45764.44931712963</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>45054.6750462963</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>44967.45122685185</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>44903</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>44977</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>44991.30547453704</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>44991</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>45498.673125</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>44963.44769675926</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>45720.44217592593</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>44909</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>44825.4336574074</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>45215.60199074074</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>45747.43196759259</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>45533.55362268518</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>45747.42633101852</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>45747.42958333333</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>45699.60055555555</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>44784.62724537037</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>45754.33641203704</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>45415.57682870371</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>45187.42854166667</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>45735.56751157407</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18864,7 +18864,7 @@
         <v>45048.59699074074</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         <v>44475</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         <v>44981.58834490741</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>44839.4528125</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19092,7 +19092,7 @@
         <v>45761.44584490741</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>45728.54832175926</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>44693.62822916666</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19268,7 +19268,7 @@
         <v>44875.27736111111</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19325,7 +19325,7 @@
         <v>45533.54429398148</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>44973.43075231482</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>45261.44914351852</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19496,7 +19496,7 @@
         <v>44910.54231481482</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19553,7 +19553,7 @@
         <v>45106.2610300926</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>45705.74418981482</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>45301.68237268519</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>45722.48915509259</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19781,7 +19781,7 @@
         <v>45346.67184027778</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>45732.79925925926</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19895,7 +19895,7 @@
         <v>45106</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19952,7 +19952,7 @@
         <v>45743.41148148148</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20009,7 +20009,7 @@
         <v>45147.67096064815</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20066,7 +20066,7 @@
         <v>45569.44684027778</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20123,7 +20123,7 @@
         <v>45610.59094907407</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20180,7 +20180,7 @@
         <v>45148</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20237,7 +20237,7 @@
         <v>45361.90282407407</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20294,7 +20294,7 @@
         <v>44952.35775462963</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20351,7 +20351,7 @@
         <v>45243.84869212963</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20408,7 +20408,7 @@
         <v>44643</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20465,7 +20465,7 @@
         <v>45548</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20522,7 +20522,7 @@
         <v>44992</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20579,7 +20579,7 @@
         <v>45052</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20636,7 +20636,7 @@
         <v>45394.50028935185</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>45761.35990740741</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20750,7 +20750,7 @@
         <v>44964.44356481481</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>45138</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20864,7 +20864,7 @@
         <v>45238.4328587963</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20921,7 +20921,7 @@
         <v>45394.66887731481</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20978,7 +20978,7 @@
         <v>45299.62576388889</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21035,7 +21035,7 @@
         <v>44893</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>45623.9525462963</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21149,7 +21149,7 @@
         <v>45658.80232638889</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21206,7 +21206,7 @@
         <v>45658.80827546296</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21263,7 +21263,7 @@
         <v>45572.48293981481</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21320,7 +21320,7 @@
         <v>45147</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21377,7 +21377,7 @@
         <v>45453.36067129629</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>45020</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>45317</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>45384.66917824074</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>45734.62017361111</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         <v>44992.62498842592</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21724,7 +21724,7 @@
         <v>44302</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21781,7 +21781,7 @@
         <v>45588.66457175926</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21838,7 +21838,7 @@
         <v>45169</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21895,7 +21895,7 @@
         <v>45698.51711805556</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21952,7 +21952,7 @@
         <v>45513.55840277778</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22009,7 +22009,7 @@
         <v>45513.56527777778</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22066,7 +22066,7 @@
         <v>44867</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22123,7 +22123,7 @@
         <v>44564.62598379629</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22180,7 +22180,7 @@
         <v>45552.36759259259</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22237,7 +22237,7 @@
         <v>45607.56773148148</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22294,7 +22294,7 @@
         <v>45674.71810185185</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>44111</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22408,7 +22408,7 @@
         <v>45637.66542824074</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22465,7 +22465,7 @@
         <v>44745.84396990741</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22522,7 +22522,7 @@
         <v>45030.71012731481</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22579,7 +22579,7 @@
         <v>45639.56185185185</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22636,7 +22636,7 @@
         <v>45630.45069444444</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22693,7 +22693,7 @@
         <v>45153.32778935185</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>45635.66695601852</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22807,7 +22807,7 @@
         <v>45434.55831018519</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22869,7 +22869,7 @@
         <v>45434.56398148148</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22931,7 +22931,7 @@
         <v>45533.56108796296</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22988,7 +22988,7 @@
         <v>45533.58302083334</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>45345.83557870371</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23107,7 +23107,7 @@
         <v>45211.541875</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>45124</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23221,7 +23221,7 @@
         <v>44890</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>44278.54855324074</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>45224.64659722222</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>45278</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23459,7 +23459,7 @@
         <v>45761.39600694444</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23516,7 +23516,7 @@
         <v>45029</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23573,7 +23573,7 @@
         <v>44720.53898148148</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23630,7 +23630,7 @@
         <v>45588.65545138889</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>45539.38744212963</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>45699.45671296296</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>45086</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23858,7 +23858,7 @@
         <v>45128</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23915,7 +23915,7 @@
         <v>45121.5965162037</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23977,7 +23977,7 @@
         <v>45121.59954861111</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24039,7 +24039,7 @@
         <v>45121.6096875</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>44635</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         <v>44966</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24215,7 +24215,7 @@
         <v>45482.49870370371</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24272,7 +24272,7 @@
         <v>44243</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24329,7 +24329,7 @@
         <v>45237.63225694445</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24386,7 +24386,7 @@
         <v>45237.64408564815</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24443,7 +24443,7 @@
         <v>45533.63056712963</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24505,7 +24505,7 @@
         <v>44431</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24562,7 +24562,7 @@
         <v>45343.68038194445</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
         <v>45581.57958333333</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>45071</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24733,7 +24733,7 @@
         <v>45539.65212962963</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24790,7 +24790,7 @@
         <v>45763.59436342592</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24847,7 +24847,7 @@
         <v>44410</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24904,7 +24904,7 @@
         <v>45301.67554398148</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24961,7 +24961,7 @@
         <v>45301.67736111111</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25018,7 +25018,7 @@
         <v>45769</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25075,7 +25075,7 @@
         <v>45097.40524305555</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25137,7 +25137,7 @@
         <v>44546</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25194,7 +25194,7 @@
         <v>45481.58048611111</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25251,7 +25251,7 @@
         <v>45768.65611111111</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
         <v>45111.48787037037</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25365,7 +25365,7 @@
         <v>45391.41976851852</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25422,7 +25422,7 @@
         <v>44931</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>44377</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>45369.62780092593</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25598,7 +25598,7 @@
         <v>44377.49684027778</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>44965.4815162037</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25717,7 +25717,7 @@
         <v>45328.38755787037</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25774,7 +25774,7 @@
         <v>45558.44914351852</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>45309.59487268519</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>44861</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>45300.3794212963</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26002,7 +26002,7 @@
         <v>45526.3865625</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26064,7 +26064,7 @@
         <v>45755.64450231481</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26121,7 +26121,7 @@
         <v>45254.62489583333</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26183,7 +26183,7 @@
         <v>45350.53306712963</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26240,7 +26240,7 @@
         <v>45518.40657407408</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>45063.49936342592</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26354,7 +26354,7 @@
         <v>45741.37270833334</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26411,7 +26411,7 @@
         <v>45784.74996527778</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>44237</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26525,7 +26525,7 @@
         <v>45622</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>45574.35809027778</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26639,7 +26639,7 @@
         <v>45533.61996527778</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>45485.45778935185</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>44588</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>45582.41200231481</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26872,7 +26872,7 @@
         <v>45786.52931712963</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>45786.52996527778</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>45786.52878472222</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>45145</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>45463</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>45187.60813657408</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>45736.50743055555</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>44833.60123842592</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27328,7 +27328,7 @@
         <v>44981.64725694444</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27385,7 +27385,7 @@
         <v>44270.39765046296</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>45163.41376157408</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27504,7 +27504,7 @@
         <v>45630.47564814815</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27561,7 +27561,7 @@
         <v>45108.703125</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27618,7 +27618,7 @@
         <v>44510.52157407408</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27675,7 +27675,7 @@
         <v>44553</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27732,7 +27732,7 @@
         <v>44897</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27789,7 +27789,7 @@
         <v>45498</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27846,7 +27846,7 @@
         <v>45698.69016203703</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>45726.62721064815</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>44418</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28017,7 +28017,7 @@
         <v>45009.4671875</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28074,7 +28074,7 @@
         <v>45217.47834490741</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
         <v>44566</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28188,7 +28188,7 @@
         <v>44488.35878472222</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28245,7 +28245,7 @@
         <v>44918</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28302,7 +28302,7 @@
         <v>44992</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28359,7 +28359,7 @@
         <v>45450.51092592593</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28416,7 +28416,7 @@
         <v>45163</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
         <v>44988</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28530,7 +28530,7 @@
         <v>45275.41833333333</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>45168.89298611111</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>44999.86172453704</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>44999.8625</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>45148</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>45187</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>44453.56578703703</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>44754</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28986,7 +28986,7 @@
         <v>45791.89865740741</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29043,7 +29043,7 @@
         <v>45552.36484953704</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>45460.62172453704</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>45581.57016203704</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29214,7 +29214,7 @@
         <v>45581.58418981481</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29271,7 +29271,7 @@
         <v>45495</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29328,7 +29328,7 @@
         <v>45618.56787037037</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>45699.45392361111</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>44769.45805555556</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>45128.58414351852</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29556,7 +29556,7 @@
         <v>44127</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29613,7 +29613,7 @@
         <v>45259.51916666667</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29675,7 +29675,7 @@
         <v>45259.52020833334</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>45171.96248842592</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29794,7 +29794,7 @@
         <v>45562.46342592593</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>45796</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29908,7 +29908,7 @@
         <v>45650.37370370371</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29965,7 +29965,7 @@
         <v>45749.56196759259</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30027,7 +30027,7 @@
         <v>45086</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30084,7 +30084,7 @@
         <v>44613</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30141,7 +30141,7 @@
         <v>45128.37305555555</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30198,7 +30198,7 @@
         <v>45189</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30255,7 +30255,7 @@
         <v>44517</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30312,7 +30312,7 @@
         <v>45540.50098379629</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30369,7 +30369,7 @@
         <v>45533.38870370371</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
         <v>44992</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30488,7 +30488,7 @@
         <v>45658.78774305555</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30545,7 +30545,7 @@
         <v>45121.61318287037</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30607,7 +30607,7 @@
         <v>45275.32266203704</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>44746.38834490741</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30721,7 +30721,7 @@
         <v>45527.68784722222</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30778,7 +30778,7 @@
         <v>44598</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30835,7 +30835,7 @@
         <v>45603.74959490741</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30892,7 +30892,7 @@
         <v>45079.87827546296</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30949,7 +30949,7 @@
         <v>45425.57538194444</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31006,7 +31006,7 @@
         <v>45475.48303240741</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31063,7 +31063,7 @@
         <v>45735.58024305556</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31120,7 +31120,7 @@
         <v>44579.62225694444</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31177,7 +31177,7 @@
         <v>44495</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31234,7 +31234,7 @@
         <v>45090.89653935185</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31291,7 +31291,7 @@
         <v>45090.89880787037</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31348,7 +31348,7 @@
         <v>45232</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31405,7 +31405,7 @@
         <v>44638.55256944444</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31462,7 +31462,7 @@
         <v>44600</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31519,7 +31519,7 @@
         <v>45041.63380787037</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31576,7 +31576,7 @@
         <v>45002</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31633,7 +31633,7 @@
         <v>45715.44159722222</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31690,7 +31690,7 @@
         <v>44992.4255787037</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31747,7 +31747,7 @@
         <v>45482.54844907407</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31804,7 +31804,7 @@
         <v>44867</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31861,7 +31861,7 @@
         <v>44451</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31918,7 +31918,7 @@
         <v>45236</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31975,7 +31975,7 @@
         <v>45574.49298611111</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32032,7 +32032,7 @@
         <v>45121</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32089,7 +32089,7 @@
         <v>44967.44255787037</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32146,7 +32146,7 @@
         <v>44903.33363425926</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32203,7 +32203,7 @@
         <v>45401.53033564815</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32260,7 +32260,7 @@
         <v>45245.5735300926</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32317,7 +32317,7 @@
         <v>45415.47848379629</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>45635.66409722222</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32431,7 +32431,7 @@
         <v>45174.31395833333</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32488,7 +32488,7 @@
         <v>45621.46103009259</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32545,7 +32545,7 @@
         <v>44943.57309027778</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32602,7 +32602,7 @@
         <v>45804.39141203704</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32659,7 +32659,7 @@
         <v>45804.67065972222</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32716,7 +32716,7 @@
         <v>45804.6953587963</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32778,7 +32778,7 @@
         <v>44861.52505787037</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32835,7 +32835,7 @@
         <v>45308.61152777778</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32892,7 +32892,7 @@
         <v>45804.708125</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32954,7 +32954,7 @@
         <v>45317.40372685185</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33016,7 +33016,7 @@
         <v>44857.65989583333</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33073,7 +33073,7 @@
         <v>44077</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33130,7 +33130,7 @@
         <v>45805.39247685186</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33187,7 +33187,7 @@
         <v>44965</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33244,7 +33244,7 @@
         <v>45063.508125</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33301,7 +33301,7 @@
         <v>44895.62296296296</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33358,7 +33358,7 @@
         <v>44452</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33415,7 +33415,7 @@
         <v>45359.44837962963</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33472,7 +33472,7 @@
         <v>45805.52983796296</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33529,7 +33529,7 @@
         <v>45009</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33586,7 +33586,7 @@
         <v>45379</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33643,7 +33643,7 @@
         <v>45804.44519675926</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33700,7 +33700,7 @@
         <v>45805</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33757,7 +33757,7 @@
         <v>45719.84378472222</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33814,7 +33814,7 @@
         <v>44944.71386574074</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33871,7 +33871,7 @@
         <v>44944.72100694444</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33928,7 +33928,7 @@
         <v>45467.74417824074</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33985,7 +33985,7 @@
         <v>45446.36482638889</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>44820</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34104,7 +34104,7 @@
         <v>44312</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34161,7 +34161,7 @@
         <v>45853.87112268519</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34218,7 +34218,7 @@
         <v>45215.5959375</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34275,7 +34275,7 @@
         <v>45215.59743055556</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34332,7 +34332,7 @@
         <v>45351.6062962963</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34389,7 +34389,7 @@
         <v>45000.47998842593</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34446,7 +34446,7 @@
         <v>45853.88070601852</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34503,7 +34503,7 @@
         <v>45440.28329861111</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34560,7 +34560,7 @@
         <v>45495</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34617,7 +34617,7 @@
         <v>45554.63225694445</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         <v>45257.67958333333</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>45674.74094907408</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>44595.583125</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>44999.35858796296</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34902,7 +34902,7 @@
         <v>45810.00048611111</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34959,7 +34959,7 @@
         <v>45301</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35016,7 +35016,7 @@
         <v>44789</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35073,7 +35073,7 @@
         <v>45539.66027777778</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35130,7 +35130,7 @@
         <v>45565.40657407408</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35187,7 +35187,7 @@
         <v>45482.54108796296</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35244,7 +35244,7 @@
         <v>45195.58452546296</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35301,7 +35301,7 @@
         <v>45026.82216435186</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35358,7 +35358,7 @@
         <v>44958.61047453704</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35415,7 +35415,7 @@
         <v>45219.40528935185</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35472,7 +35472,7 @@
         <v>45853.87599537037</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35529,7 +35529,7 @@
         <v>45266.32614583334</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35586,7 +35586,7 @@
         <v>44663</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35643,7 +35643,7 @@
         <v>45567</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35700,7 +35700,7 @@
         <v>45623.95947916667</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>45041</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35814,7 +35814,7 @@
         <v>44440</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35871,7 +35871,7 @@
         <v>45434.55471064815</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35933,7 +35933,7 @@
         <v>45434.56291666667</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35995,7 +35995,7 @@
         <v>45554.62944444444</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36052,7 +36052,7 @@
         <v>44083</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36109,7 +36109,7 @@
         <v>45632.37459490741</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36166,7 +36166,7 @@
         <v>45201.39996527778</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36223,7 +36223,7 @@
         <v>44803.59118055556</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36280,7 +36280,7 @@
         <v>45567.42011574074</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36337,7 +36337,7 @@
         <v>45086.63334490741</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36394,7 +36394,7 @@
         <v>44587.48847222222</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36451,7 +36451,7 @@
         <v>45110.4275</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36508,7 +36508,7 @@
         <v>45858.60641203704</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36565,7 +36565,7 @@
         <v>45814.38221064815</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36622,7 +36622,7 @@
         <v>45503.5658912037</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36679,7 +36679,7 @@
         <v>44599</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36736,7 +36736,7 @@
         <v>44956</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36798,7 +36798,7 @@
         <v>44270.38002314815</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36860,7 +36860,7 @@
         <v>45814.3865625</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36917,7 +36917,7 @@
         <v>44944.73487268519</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36974,7 +36974,7 @@
         <v>44596</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37031,7 +37031,7 @@
         <v>45330</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37088,7 +37088,7 @@
         <v>45330</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37145,7 +37145,7 @@
         <v>45858.66019675926</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37202,7 +37202,7 @@
         <v>45818.58993055556</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37264,7 +37264,7 @@
         <v>45113.41633101852</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37321,7 +37321,7 @@
         <v>45818.58769675926</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37383,7 +37383,7 @@
         <v>45818.595625</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37445,7 +37445,7 @@
         <v>45818.59261574074</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37507,7 +37507,7 @@
         <v>45666</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37564,7 +37564,7 @@
         <v>45818.5862037037</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37626,7 +37626,7 @@
         <v>45817.88496527778</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37683,7 +37683,7 @@
         <v>45250.5278587963</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37740,7 +37740,7 @@
         <v>45070</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37797,7 +37797,7 @@
         <v>45225.60192129629</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37854,7 +37854,7 @@
         <v>44918.50106481482</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37911,7 +37911,7 @@
         <v>45819.61060185185</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37968,7 +37968,7 @@
         <v>45700.68289351852</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38025,7 +38025,7 @@
         <v>44539</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38082,7 +38082,7 @@
         <v>45299.47513888889</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38139,7 +38139,7 @@
         <v>45027.59450231482</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38201,7 +38201,7 @@
         <v>45820.33708333333</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38258,7 +38258,7 @@
         <v>45820.34128472222</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38315,7 +38315,7 @@
         <v>44910</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38372,7 +38372,7 @@
         <v>45224.6515162037</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38434,7 +38434,7 @@
         <v>45377</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38491,7 +38491,7 @@
         <v>45106.25025462963</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38548,7 +38548,7 @@
         <v>45114.47895833333</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38605,7 +38605,7 @@
         <v>45820.33930555556</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38662,7 +38662,7 @@
         <v>44598.7384837963</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38719,7 +38719,7 @@
         <v>45825.57805555555</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38776,7 +38776,7 @@
         <v>45867.64663194444</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38833,7 +38833,7 @@
         <v>45867.69346064814</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38890,7 +38890,7 @@
         <v>45867.50792824074</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38947,7 +38947,7 @@
         <v>44848.59133101852</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39004,7 +39004,7 @@
         <v>45867.63094907408</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39061,7 +39061,7 @@
         <v>45825.58672453704</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39118,7 +39118,7 @@
         <v>45867.56320601852</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>45867.68625</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>45825.50280092593</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>45825.5796875</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39346,7 +39346,7 @@
         <v>45559.38876157408</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39403,7 +39403,7 @@
         <v>45224</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39460,7 +39460,7 @@
         <v>45349.54434027777</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39517,7 +39517,7 @@
         <v>45867.51630787037</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39574,7 +39574,7 @@
         <v>45334.78826388889</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39631,7 +39631,7 @@
         <v>45825.57680555555</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39688,7 +39688,7 @@
         <v>45415.48979166667</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39745,7 +39745,7 @@
         <v>45114.58148148148</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39802,7 +39802,7 @@
         <v>44600</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39859,7 +39859,7 @@
         <v>45581.57333333333</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39916,7 +39916,7 @@
         <v>44542.90072916666</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39973,7 +39973,7 @@
         <v>45359.45038194444</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40030,7 +40030,7 @@
         <v>44895.46524305556</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40087,7 +40087,7 @@
         <v>44587</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>45827</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40201,7 +40201,7 @@
         <v>45569.45017361111</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40258,7 +40258,7 @@
         <v>45569.47494212963</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40315,7 +40315,7 @@
         <v>45827</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>45588.67070601852</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40429,7 +40429,7 @@
         <v>45749.60487268519</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40491,7 +40491,7 @@
         <v>45355.54138888889</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40548,7 +40548,7 @@
         <v>45869.62276620371</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40605,7 +40605,7 @@
         <v>44984.45895833334</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40662,7 +40662,7 @@
         <v>44949</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40719,7 +40719,7 @@
         <v>45660</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>45446.36865740741</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40838,7 +40838,7 @@
         <v>45245.63574074074</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>45090</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40952,7 +40952,7 @@
         <v>44467.83386574074</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41009,7 +41009,7 @@
         <v>45870.51958333333</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41066,7 +41066,7 @@
         <v>45870.51708333333</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41123,7 +41123,7 @@
         <v>45870.52005787037</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41180,7 +41180,7 @@
         <v>45870.52142361111</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41237,7 +41237,7 @@
         <v>45831</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41294,7 +41294,7 @@
         <v>45732.75637731481</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41351,7 +41351,7 @@
         <v>45732.76936342593</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41408,7 +41408,7 @@
         <v>44340</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41465,7 +41465,7 @@
         <v>45707.3793287037</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41522,7 +41522,7 @@
         <v>45870.52111111111</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41579,7 +41579,7 @@
         <v>45875.42716435185</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41636,7 +41636,7 @@
         <v>45874.57109953704</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41693,7 +41693,7 @@
         <v>44790.49040509259</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41750,7 +41750,7 @@
         <v>44784.42528935185</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41807,7 +41807,7 @@
         <v>45875.47454861111</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41864,7 +41864,7 @@
         <v>45833.64563657407</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41921,7 +41921,7 @@
         <v>45833.64814814815</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41978,7 +41978,7 @@
         <v>45832.46146990741</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42035,7 +42035,7 @@
         <v>44578.32717592592</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42092,7 +42092,7 @@
         <v>45833.64237268519</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42149,7 +42149,7 @@
         <v>44935</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42206,7 +42206,7 @@
         <v>44852</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42263,7 +42263,7 @@
         <v>45875.45716435185</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42320,7 +42320,7 @@
         <v>45100.85270833333</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42377,7 +42377,7 @@
         <v>45525.41762731481</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42434,7 +42434,7 @@
         <v>45832.34540509259</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42491,7 +42491,7 @@
         <v>44964.5115162037</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42548,7 +42548,7 @@
         <v>45517.8162037037</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42605,7 +42605,7 @@
         <v>45834.65040509259</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42667,7 +42667,7 @@
         <v>44578.62943287037</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42724,7 +42724,7 @@
         <v>45709.62280092593</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42781,7 +42781,7 @@
         <v>45835.44709490741</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42838,7 +42838,7 @@
         <v>44994.46908564815</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42895,7 +42895,7 @@
         <v>44900.57393518519</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42952,7 +42952,7 @@
         <v>45835.48267361111</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43009,7 +43009,7 @@
         <v>45835.48445601852</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43066,7 +43066,7 @@
         <v>45835.48862268519</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43123,7 +43123,7 @@
         <v>44440.60415509259</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43180,7 +43180,7 @@
         <v>45201</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43237,7 +43237,7 @@
         <v>45121.58699074074</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43299,7 +43299,7 @@
         <v>44966</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43356,7 +43356,7 @@
         <v>45834.64667824074</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43418,7 +43418,7 @@
         <v>45835.44732638889</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43475,7 +43475,7 @@
         <v>45211.52642361111</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43532,7 +43532,7 @@
         <v>45323.53744212963</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43589,7 +43589,7 @@
         <v>45075.43059027778</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43646,7 +43646,7 @@
         <v>44630</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43703,7 +43703,7 @@
         <v>45308.59001157407</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43760,7 +43760,7 @@
         <v>45111.30824074074</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>45371.45865740741</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43874,7 +43874,7 @@
         <v>45100.4062962963</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43931,7 +43931,7 @@
         <v>45086.63194444445</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43988,7 +43988,7 @@
         <v>45196</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44045,7 +44045,7 @@
         <v>44795</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44102,7 +44102,7 @@
         <v>45835.36229166666</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44164,7 +44164,7 @@
         <v>45835.45099537037</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44221,7 +44221,7 @@
         <v>45280.66769675926</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44278,7 +44278,7 @@
         <v>45835.4924537037</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44335,7 +44335,7 @@
         <v>45834.65197916667</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44397,7 +44397,7 @@
         <v>45112.33599537037</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44454,7 +44454,7 @@
         <v>45111</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44511,7 +44511,7 @@
         <v>45320.89128472222</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44568,7 +44568,7 @@
         <v>44987.54104166666</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44625,7 +44625,7 @@
         <v>45202.4209837963</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44682,7 +44682,7 @@
         <v>45632.36706018518</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44739,7 +44739,7 @@
         <v>45632.44886574074</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44796,7 +44796,7 @@
         <v>45245.36174768519</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44853,7 +44853,7 @@
         <v>44585.50431712963</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44910,7 +44910,7 @@
         <v>45208</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44967,7 +44967,7 @@
         <v>45001.43854166667</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45024,7 +45024,7 @@
         <v>44585.51060185185</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45081,7 +45081,7 @@
         <v>45260.4716550926</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45138,7 +45138,7 @@
         <v>45880.51413194444</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45200,7 +45200,7 @@
         <v>45881</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45257,7 +45257,7 @@
         <v>45880.51550925926</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45319,7 +45319,7 @@
         <v>44943.62954861111</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45376,7 +45376,7 @@
         <v>45170</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45433,7 +45433,7 @@
         <v>45881.59877314815</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45490,7 +45490,7 @@
         <v>45837.77916666667</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45547,7 +45547,7 @@
         <v>45371.36359953704</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45604,7 +45604,7 @@
         <v>45837.77701388889</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45661,7 +45661,7 @@
         <v>45880.38380787037</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45718,7 +45718,7 @@
         <v>45840.59474537037</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45775,7 +45775,7 @@
         <v>45840.59853009259</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45832,7 +45832,7 @@
         <v>45841.70569444444</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45889,7 +45889,7 @@
         <v>45841.70868055556</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45946,7 +45946,7 @@
         <v>44938</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46008,7 +46008,7 @@
         <v>45832.46649305556</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46065,7 +46065,7 @@
         <v>44949</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46127,7 +46127,7 @@
         <v>45841.7072337963</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46184,7 +46184,7 @@
         <v>44867</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46241,7 +46241,7 @@
         <v>44732.3659837963</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46298,7 +46298,7 @@
         <v>45635.4874537037</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46355,7 +46355,7 @@
         <v>45483.82479166667</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>45020</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46469,7 +46469,7 @@
         <v>45568.30189814815</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46526,7 +46526,7 @@
         <v>45568.36879629629</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46583,7 +46583,7 @@
         <v>45811.45460648148</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46640,7 +46640,7 @@
         <v>44159</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46697,7 +46697,7 @@
         <v>44894.49538194444</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46754,7 +46754,7 @@
         <v>45884.50331018519</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46816,7 +46816,7 @@
         <v>44172</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46873,7 +46873,7 @@
         <v>45713.92412037037</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46930,7 +46930,7 @@
         <v>45845.42015046296</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46987,7 +46987,7 @@
         <v>45446.36774305555</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47049,7 +47049,7 @@
         <v>45615.48927083334</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47106,7 +47106,7 @@
         <v>45845.43803240741</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47163,7 +47163,7 @@
         <v>45845.49414351852</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47220,7 +47220,7 @@
         <v>44790.45876157407</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47277,7 +47277,7 @@
         <v>44790.49523148148</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47334,7 +47334,7 @@
         <v>45820.03976851852</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47391,7 +47391,7 @@
         <v>45884.50613425926</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47453,7 +47453,7 @@
         <v>45729.36868055556</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47510,7 +47510,7 @@
         <v>45887.68759259259</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47567,7 +47567,7 @@
         <v>45211.43555555555</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47624,7 +47624,7 @@
         <v>44893</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47681,7 +47681,7 @@
         <v>45174.40454861111</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47738,7 +47738,7 @@
         <v>44984</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47795,7 +47795,7 @@
         <v>44984</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47852,7 +47852,7 @@
         <v>45018</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47909,7 +47909,7 @@
         <v>45713.45311342592</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47966,7 +47966,7 @@
         <v>44994.42113425926</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48023,7 +48023,7 @@
         <v>45176.72427083334</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48080,7 +48080,7 @@
         <v>45759.38987268518</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48137,7 +48137,7 @@
         <v>45105</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48194,7 +48194,7 @@
         <v>44788</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48251,7 +48251,7 @@
         <v>45847.91280092593</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48308,7 +48308,7 @@
         <v>45891.50525462963</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48365,7 +48365,7 @@
         <v>45891.50986111111</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48422,7 +48422,7 @@
         <v>44258</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>45061</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48541,7 +48541,7 @@
         <v>45070.3665625</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48598,7 +48598,7 @@
         <v>45891</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48655,7 +48655,7 @@
         <v>45028</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48712,7 +48712,7 @@
         <v>44310</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48769,7 +48769,7 @@
         <v>45096.45247685185</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48826,7 +48826,7 @@
         <v>45391.41310185185</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48883,7 +48883,7 @@
         <v>45698.53725694444</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48940,7 +48940,7 @@
         <v>45163.63621527778</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49002,7 +49002,7 @@
         <v>45891</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49059,7 +49059,7 @@
         <v>45456.59289351852</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49116,7 +49116,7 @@
         <v>45891.50216435185</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49173,7 +49173,7 @@
         <v>45481.55984953704</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49230,7 +49230,7 @@
         <v>45093.62777777778</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49292,7 +49292,7 @@
         <v>45630.35827546296</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49349,7 +49349,7 @@
         <v>44964.50894675926</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49406,7 +49406,7 @@
         <v>45257.70313657408</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49463,7 +49463,7 @@
         <v>44431.84840277778</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49520,7 +49520,7 @@
         <v>45671.46746527778</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49577,7 +49577,7 @@
         <v>45755.44333333334</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49634,7 +49634,7 @@
         <v>45110.4184375</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49691,7 +49691,7 @@
         <v>45533.60232638889</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49753,7 +49753,7 @@
         <v>45533.60770833334</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49815,7 +49815,7 @@
         <v>45001.59209490741</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49872,7 +49872,7 @@
         <v>45569.44295138889</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49929,7 +49929,7 @@
         <v>44879</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49986,7 +49986,7 @@
         <v>45182.78834490741</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50043,7 +50043,7 @@
         <v>45475.49018518518</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50100,7 +50100,7 @@
         <v>44510.60921296296</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50162,7 +50162,7 @@
         <v>45761.4437962963</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50219,7 +50219,7 @@
         <v>44961</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50276,7 +50276,7 @@
         <v>45128.9325</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50333,7 +50333,7 @@
         <v>45128.93540509259</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50390,7 +50390,7 @@
         <v>44999.36081018519</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50447,7 +50447,7 @@
         <v>44984</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50504,7 +50504,7 @@
         <v>45567</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50561,7 +50561,7 @@
         <v>45090.38012731481</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50618,7 +50618,7 @@
         <v>44466.34962962963</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50675,7 +50675,7 @@
         <v>45530.33202546297</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50732,7 +50732,7 @@
         <v>45174</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50789,7 +50789,7 @@
         <v>45091.67936342592</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50846,7 +50846,7 @@
         <v>44910.41346064815</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50903,7 +50903,7 @@
         <v>45483.82834490741</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50960,7 +50960,7 @@
         <v>45698.52806712963</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51017,7 +51017,7 @@
         <v>45271.66576388889</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51074,7 +51074,7 @@
         <v>45224.60075231481</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51136,7 +51136,7 @@
         <v>45646.38200231481</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51193,7 +51193,7 @@
         <v>44392</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>

--- a/Översikt VIMMERBY.xlsx
+++ b/Översikt VIMMERBY.xlsx
@@ -567,7 +567,7 @@
         <v>44811</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
         <v>44811</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44811</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44811</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>45314</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>44939</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>45301.67922453704</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>45755</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>45377.54726851852</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45121.60543981481</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>45678.64175925926</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>45748</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>44245</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>44811</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>45628</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>45742</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>45020</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>44424</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>44426.64793981481</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>44386</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>45786.52827546297</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>45008.60878472222</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>44943</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>45760.34877314815</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>45072</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>45048</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>44371</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>44403</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>45399.71412037037</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>45125</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>44082</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>45667</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>45104</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>45574.42767361111</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>45649</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>45821</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>45168</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>45168</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>44236</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>45713</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>45077</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>44075</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>45224</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>44377.61104166666</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         <v>44083</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
         <v>44102</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         <v>44130</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>44281.79269675926</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>44270.67071759259</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>44287.33261574074</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>44210</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>44490.38613425926</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         <v>44447</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
         <v>44481.47483796296</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>44350</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>44375.39033564815</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>44614</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>44215</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>44670</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>44670</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>44307</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         <v>44350</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>44105</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>44225</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>44327.47658564815</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>44509</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>44406</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>44230.58883101852</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         <v>44480</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
         <v>44238</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44585.51829861111</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>44824.53434027778</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>44418</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>44785.40800925926</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>44578.47597222222</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>44516.59703703703</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>44862</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>44603</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>44588</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>44404.87505787037</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>44826.68010416667</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>44494</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>44483.58295138889</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>44354</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>44542.8859375</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>44512.70245370371</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>44090</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>44790</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>44221.39408564815</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         <v>44261</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>44530.38055555556</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>44588</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>44588</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>44790</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>44790.47628472222</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>44175.3815625</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>44175.40881944444</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         <v>44475</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>44312</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>44385</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>44124.59795138889</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>44237.8550925926</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>44410.71038194445</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>44279.33400462963</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>44175</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>44670</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>44365</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         <v>44169</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>44301.36048611111</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         <v>44273</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         <v>44729.28226851852</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
         <v>44271.37226851852</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>44340.54472222222</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>44340</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>44774</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>44733</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>44733</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>44154</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         <v>44371.62743055556</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>44386.40783564815</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>44480</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>44245</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         <v>44337</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>44102</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         <v>44463.29439814815</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9208,7 +9208,7 @@
         <v>44588</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         <v>44789</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>44117</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         <v>44377</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         <v>44379</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         <v>44508</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>44091</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>44634.69703703704</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>44480</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>44769.45422453704</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>44340.58002314815</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9845,7 +9845,7 @@
         <v>44085</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         <v>44092</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         <v>44612.86762731482</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
         <v>44383</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10073,7 +10073,7 @@
         <v>44142</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>44644</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>44476</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         <v>44305.40046296296</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>44418</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>44447</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         <v>44517</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>44854</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>44819</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
         <v>44824</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>44369</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         <v>44742</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>44832.67608796297</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
         <v>44451.8375</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         <v>44823</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10933,7 +10933,7 @@
         <v>44270</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10990,7 +10990,7 @@
         <v>44341</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11047,7 +11047,7 @@
         <v>44608</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11104,7 +11104,7 @@
         <v>44217.79856481482</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>44447.34237268518</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>44384</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11275,7 +11275,7 @@
         <v>44790.48503472222</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>44854.59157407407</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>44621</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11446,7 +11446,7 @@
         <v>44294</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11503,7 +11503,7 @@
         <v>44116</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>44620</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>44172</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
         <v>44480</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>44876.48346064815</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>44733.43092592592</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11845,7 +11845,7 @@
         <v>44089.78633101852</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11902,7 +11902,7 @@
         <v>44203</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>44525.63913194444</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         <v>44609</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>44279.64934027778</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>44266.7240625</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12197,7 +12197,7 @@
         <v>44284.42348379629</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
         <v>44088</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12311,7 +12311,7 @@
         <v>44662</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>44088</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         <v>44270.49743055556</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>44095</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         <v>44421</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>44186</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
         <v>44273</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12720,7 +12720,7 @@
         <v>44564</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>44278.63479166666</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12839,7 +12839,7 @@
         <v>44375.38789351852</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>44386</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12953,7 +12953,7 @@
         <v>44722.48768518519</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>44427</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>44612.86554398148</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>44466.34726851852</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>44379</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>44866.81100694444</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13305,7 +13305,7 @@
         <v>44284.44574074074</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>44470.44232638889</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>44776</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13476,7 +13476,7 @@
         <v>44634</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>44636</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>44608.50458333334</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>44817.57988425926</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>44817</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>44851.95016203704</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13818,7 +13818,7 @@
         <v>44294</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         <v>44294</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13932,7 +13932,7 @@
         <v>44676.85248842592</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         <v>44292</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14051,7 +14051,7 @@
         <v>44466.34962962963</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14108,7 +14108,7 @@
         <v>45105</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>44278.54855324074</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>45196</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>44604</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>45483.82834490741</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>45090.38012731481</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>44607</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14507,7 +14507,7 @@
         <v>44377.49684027778</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>44949</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14631,7 +14631,7 @@
         <v>44833.60123842592</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14688,7 +14688,7 @@
         <v>44305</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
         <v>45215.59743055556</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>44789</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>45121.58699074074</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14921,7 +14921,7 @@
         <v>45569.44684027778</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>45391.41310185185</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15035,7 +15035,7 @@
         <v>45411.47335648148</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15092,7 +15092,7 @@
         <v>45086.63194444445</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15149,7 +15149,7 @@
         <v>45086.63334490741</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>45232</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>45525.41762731481</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15320,7 +15320,7 @@
         <v>45377.40043981482</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15377,7 +15377,7 @@
         <v>45698.51711805556</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>45565.40657407408</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         <v>45211.43555555555</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15548,7 +15548,7 @@
         <v>45086</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>45728.54832175926</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>45097.40524305555</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>45100.4062962963</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>45257.67958333333</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>44720.53898148148</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
         <v>44243</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15952,7 +15952,7 @@
         <v>45018</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         <v>45607.56773148148</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>45425.57538194444</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>45301.67736111111</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         <v>45513.55840277778</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16237,7 +16237,7 @@
         <v>45513.56527777778</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>45110.4184375</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>45415.47848379629</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16408,7 +16408,7 @@
         <v>45090</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>44539</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16522,7 +16522,7 @@
         <v>45749.60487268519</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
         <v>45391.41976851852</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         <v>45245.5735300926</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>45111.48787037037</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>45450.51092592593</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>44553</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>45481.58048611111</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>44964.5115162037</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
         <v>44895.62296296296</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>45308.61152777778</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         <v>45299.47513888889</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>44867</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>45096.45247685185</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>45539.66027777778</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>45111.48395833333</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>45784.74996527778</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>45588.65545138889</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>44967.45122685185</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>44852</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>45384.66917824074</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>45463</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>45630.47564814815</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>45114.55136574074</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>44992</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17900,7 +17900,7 @@
         <v>45581.57016203704</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>45257.70313657408</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>44392</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         <v>45481.55984953704</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18133,7 +18133,7 @@
         <v>45266.32614583334</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>45539.38744212963</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>45317.40372685185</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
         <v>45309.59487268519</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18366,7 +18366,7 @@
         <v>45786.52931712963</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>45786.52996527778</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>45359.44837962963</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18537,7 +18537,7 @@
         <v>44488.35878472222</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>44467.83386574074</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>45482.52887731481</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>45371.36359953704</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         <v>45539.65212962963</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
         <v>45371.45865740741</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18879,7 +18879,7 @@
         <v>45359.45038194444</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>44861.52505787037</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>45533.54429398148</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>45533.60232638889</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>45533.60770833334</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19174,7 +19174,7 @@
         <v>45446.36774305555</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>45147.67096064815</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>45147.67172453704</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19350,7 +19350,7 @@
         <v>45786.52878472222</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19407,7 +19407,7 @@
         <v>45000.47998842593</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>45552.36759259259</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19521,7 +19521,7 @@
         <v>45098.30535879629</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>45113.56574074074</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19635,7 +19635,7 @@
         <v>45747.42633101852</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>45747.42958333333</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>45726.44471064815</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19806,7 +19806,7 @@
         <v>45726.62721064815</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>45698.69016203703</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19920,7 +19920,7 @@
         <v>45526.3865625</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19982,7 +19982,7 @@
         <v>44788</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20039,7 +20039,7 @@
         <v>45243.84869212963</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20096,7 +20096,7 @@
         <v>45581.57958333333</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20153,7 +20153,7 @@
         <v>45548</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20210,7 +20210,7 @@
         <v>45020</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20267,7 +20267,7 @@
         <v>45569.44295138889</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20324,7 +20324,7 @@
         <v>45415.48979166667</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>45009</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20438,7 +20438,7 @@
         <v>45791.89865740741</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20495,7 +20495,7 @@
         <v>45111.48225694444</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>45111.48636574074</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>45621.46103009259</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>45114.58148148148</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>45460.62172453704</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>45533.61996527778</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20842,7 +20842,7 @@
         <v>44083</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20899,7 +20899,7 @@
         <v>44949</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         <v>45171.96248842592</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21013,7 +21013,7 @@
         <v>45632.44886574074</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21070,7 +21070,7 @@
         <v>45030.71012731481</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>45741.37270833334</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21184,7 +21184,7 @@
         <v>45796</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21241,7 +21241,7 @@
         <v>44510.52157407408</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>44984</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21355,7 +21355,7 @@
         <v>44598</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21412,7 +21412,7 @@
         <v>44938</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>45483.82479166667</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21531,7 +21531,7 @@
         <v>45498</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21588,7 +21588,7 @@
         <v>45552.36484953704</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>44879</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>45271.66576388889</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         <v>45482.54108796296</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>45582.41200231481</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21873,7 +21873,7 @@
         <v>45603.74959490741</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>45485.45778935185</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21987,7 +21987,7 @@
         <v>44585.51060185185</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22044,7 +22044,7 @@
         <v>45572.48293981481</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22101,7 +22101,7 @@
         <v>45618.56787037037</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
         <v>45001.43854166667</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22215,7 +22215,7 @@
         <v>45467.74417824074</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>45086</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22329,7 +22329,7 @@
         <v>44159</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22386,7 +22386,7 @@
         <v>45182.78834490741</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22443,7 +22443,7 @@
         <v>45527.68784722222</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22500,7 +22500,7 @@
         <v>44918.50106481482</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22557,7 +22557,7 @@
         <v>45574.49298611111</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22614,7 +22614,7 @@
         <v>45715.44159722222</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>45632.37459490741</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22728,7 +22728,7 @@
         <v>45378.32185185186</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
         <v>45498.673125</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22842,7 +22842,7 @@
         <v>44893</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
         <v>45275.32266203704</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22956,7 +22956,7 @@
         <v>44992.4255787037</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23013,7 +23013,7 @@
         <v>45540.50098379629</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
         <v>45377</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23127,7 +23127,7 @@
         <v>45635.66409722222</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>45401.53033564815</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23241,7 +23241,7 @@
         <v>44127</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23298,7 +23298,7 @@
         <v>45804.6953587963</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23360,7 +23360,7 @@
         <v>45804.708125</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23422,7 +23422,7 @@
         <v>45804.39141203704</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23479,7 +23479,7 @@
         <v>44630</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23536,7 +23536,7 @@
         <v>44893</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23593,7 +23593,7 @@
         <v>45671.46746527778</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23650,7 +23650,7 @@
         <v>45804.67065972222</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23707,7 +23707,7 @@
         <v>45804.44519675926</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23764,7 +23764,7 @@
         <v>45699.45671296296</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>44994.40635416667</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23878,7 +23878,7 @@
         <v>45805.39247685186</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23935,7 +23935,7 @@
         <v>44579.62225694444</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23992,7 +23992,7 @@
         <v>45574.35809027778</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24049,7 +24049,7 @@
         <v>45559.38876157408</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24106,7 +24106,7 @@
         <v>45805</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24163,7 +24163,7 @@
         <v>44587</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24220,7 +24220,7 @@
         <v>45805.52983796296</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24277,7 +24277,7 @@
         <v>44935</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24334,7 +24334,7 @@
         <v>44643</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24391,7 +24391,7 @@
         <v>44603</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24448,7 +24448,7 @@
         <v>44999.86172453704</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24505,7 +24505,7 @@
         <v>44999.8625</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24562,7 +24562,7 @@
         <v>45328.38755787037</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
         <v>45713.92412037037</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>44964.50894675926</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24733,7 +24733,7 @@
         <v>45071</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24790,7 +24790,7 @@
         <v>44795</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24847,7 +24847,7 @@
         <v>45517.8162037037</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24904,7 +24904,7 @@
         <v>45168.89298611111</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24961,7 +24961,7 @@
         <v>45518.40657407408</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25018,7 +25018,7 @@
         <v>44638.55256944444</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25075,7 +25075,7 @@
         <v>45052</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25132,7 +25132,7 @@
         <v>45666</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25189,7 +25189,7 @@
         <v>45001.59209490741</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25246,7 +25246,7 @@
         <v>44587.48847222222</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25303,7 +25303,7 @@
         <v>44918</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25360,7 +25360,7 @@
         <v>44959.66407407408</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25417,7 +25417,7 @@
         <v>45814.3865625</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>45814.38221064815</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25531,7 +25531,7 @@
         <v>45755.64450231481</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>44966</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>45623.95947916667</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25702,7 +25702,7 @@
         <v>44564.62598379629</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>44635</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25816,7 +25816,7 @@
         <v>45858.60641203704</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25873,7 +25873,7 @@
         <v>45495</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25930,7 +25930,7 @@
         <v>45818.59261574074</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25992,7 +25992,7 @@
         <v>44600</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26049,7 +26049,7 @@
         <v>45818.5862037037</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>45818.58993055556</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26173,7 +26173,7 @@
         <v>45858.66019675926</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26230,7 +26230,7 @@
         <v>45026.82216435186</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26287,7 +26287,7 @@
         <v>44595.583125</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>44910.54231481482</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>45567.42011574074</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26458,7 +26458,7 @@
         <v>45554.62944444444</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>45818.58769675926</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26577,7 +26577,7 @@
         <v>45818.595625</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26639,7 +26639,7 @@
         <v>45211.52642361111</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26696,7 +26696,7 @@
         <v>45211.541875</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>45650.37370370371</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26810,7 +26810,7 @@
         <v>45567</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         <v>45195.58452546296</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26924,7 +26924,7 @@
         <v>45820.33930555556</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>45351.6062962963</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27038,7 +27038,7 @@
         <v>45145</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>45820.33708333333</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>45820.34128472222</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27209,7 +27209,7 @@
         <v>45819.61060185185</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27266,7 +27266,7 @@
         <v>45208</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27323,7 +27323,7 @@
         <v>45729.36868055556</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27380,7 +27380,7 @@
         <v>45632.72635416667</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>45148</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27494,7 +27494,7 @@
         <v>45148</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27551,7 +27551,7 @@
         <v>45163.41376157408</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27608,7 +27608,7 @@
         <v>44475</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27665,7 +27665,7 @@
         <v>45825.5796875</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27722,7 +27722,7 @@
         <v>45825.58672453704</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27779,7 +27779,7 @@
         <v>45434.56291666667</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27841,7 +27841,7 @@
         <v>45867.51630787037</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>45867.56320601852</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27955,7 +27955,7 @@
         <v>45867.63094907408</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28012,7 +28012,7 @@
         <v>45867.50792824074</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28069,7 +28069,7 @@
         <v>45867.68625</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>45867.69346064814</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>45202.4209837963</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>45079.87827546296</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>45867.64663194444</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28354,7 +28354,7 @@
         <v>45825.57805555555</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>45825.57680555555</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28468,7 +28468,7 @@
         <v>44943.62954861111</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>44944.73487268519</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28582,7 +28582,7 @@
         <v>45761.35990740741</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28639,7 +28639,7 @@
         <v>45827</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28696,7 +28696,7 @@
         <v>45870.52111111111</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28753,7 +28753,7 @@
         <v>45254.62489583333</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>45113.43921296296</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>45870.51708333333</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>45870.52005787037</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28986,7 +28986,7 @@
         <v>45870.52142361111</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29043,7 +29043,7 @@
         <v>45870.51958333333</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>45394.50028935185</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>45869.62276620371</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29214,7 +29214,7 @@
         <v>45827</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29271,7 +29271,7 @@
         <v>45581.58418981481</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29328,7 +29328,7 @@
         <v>44867</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>45581.57333333333</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>45533.63056712963</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29504,7 +29504,7 @@
         <v>45588.67070601852</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29561,7 +29561,7 @@
         <v>44784.42528935185</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29618,7 +29618,7 @@
         <v>45831</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29675,7 +29675,7 @@
         <v>44825.4336574074</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29732,7 +29732,7 @@
         <v>45176.72427083334</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29789,7 +29789,7 @@
         <v>45874.57109953704</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29846,7 +29846,7 @@
         <v>45832.34540509259</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29903,7 +29903,7 @@
         <v>45569.45017361111</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>45832.46146990741</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30017,7 +30017,7 @@
         <v>44999.35858796296</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>45128</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30131,7 +30131,7 @@
         <v>45196.57247685185</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30188,7 +30188,7 @@
         <v>45713.45311342592</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30245,7 +30245,7 @@
         <v>45833.64563657407</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30302,7 +30302,7 @@
         <v>45833.64814814815</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30359,7 +30359,7 @@
         <v>45170</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30416,7 +30416,7 @@
         <v>45735.58024305556</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30473,7 +30473,7 @@
         <v>45236</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30530,7 +30530,7 @@
         <v>44746.38834490741</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30587,7 +30587,7 @@
         <v>44663</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30644,7 +30644,7 @@
         <v>45875.47454861111</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30701,7 +30701,7 @@
         <v>45875.45716435185</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30758,7 +30758,7 @@
         <v>45187</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
         <v>45187.42854166667</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30872,7 +30872,7 @@
         <v>45707.3793287037</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30929,7 +30929,7 @@
         <v>45622</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30986,7 +30986,7 @@
         <v>45736.50743055555</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31043,7 +31043,7 @@
         <v>44172</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31100,7 +31100,7 @@
         <v>45562.46342592593</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31157,7 +31157,7 @@
         <v>45834.64667824074</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31219,7 +31219,7 @@
         <v>45434.55831018519</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31281,7 +31281,7 @@
         <v>45434.56398148148</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31343,7 +31343,7 @@
         <v>45075.43059027778</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31400,7 +31400,7 @@
         <v>44784.62724537037</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>45875.42716435185</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>45308.59001157407</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>45699.44291666667</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31628,7 +31628,7 @@
         <v>45174</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31685,7 +31685,7 @@
         <v>45709.62280092593</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31742,7 +31742,7 @@
         <v>45343.68038194445</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31799,7 +31799,7 @@
         <v>45834.65040509259</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31861,7 +31861,7 @@
         <v>45834.65197916667</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31923,7 +31923,7 @@
         <v>44270.39765046296</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31985,7 +31985,7 @@
         <v>45833.64237268519</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32042,7 +32042,7 @@
         <v>45835.36229166666</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32104,7 +32104,7 @@
         <v>45835.4924537037</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32161,7 +32161,7 @@
         <v>45121.61318287037</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32223,7 +32223,7 @@
         <v>45835.48862268519</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32280,7 +32280,7 @@
         <v>45880.38380787037</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32337,7 +32337,7 @@
         <v>45722.48634259259</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32394,7 +32394,7 @@
         <v>45617.47570601852</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32451,7 +32451,7 @@
         <v>45880.51413194444</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32513,7 +32513,7 @@
         <v>45880.51550925926</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32575,7 +32575,7 @@
         <v>45837.77701388889</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32632,7 +32632,7 @@
         <v>45835.48267361111</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32689,7 +32689,7 @@
         <v>45835.48445601852</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32746,7 +32746,7 @@
         <v>45719.84378472222</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32803,7 +32803,7 @@
         <v>45835.45099537037</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>45837.77916666667</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32917,7 +32917,7 @@
         <v>44981.58834490741</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32974,7 +32974,7 @@
         <v>45835.44709490741</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33031,7 +33031,7 @@
         <v>45761.4437962963</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33088,7 +33088,7 @@
         <v>45835.44732638889</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33145,7 +33145,7 @@
         <v>45299.62576388889</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33202,7 +33202,7 @@
         <v>45881</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33259,7 +33259,7 @@
         <v>45700.68289351852</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33316,7 +33316,7 @@
         <v>45567</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33373,7 +33373,7 @@
         <v>44994.42113425926</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33430,7 +33430,7 @@
         <v>45840.59474537037</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33487,7 +33487,7 @@
         <v>45840.59853009259</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33544,7 +33544,7 @@
         <v>44958.61047453704</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33601,7 +33601,7 @@
         <v>45623.9525462963</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33658,7 +33658,7 @@
         <v>44790.49523148148</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33715,7 +33715,7 @@
         <v>45260.4716550926</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33772,7 +33772,7 @@
         <v>45832.46649305556</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33829,7 +33829,7 @@
         <v>44820</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33886,7 +33886,7 @@
         <v>45881.59877314815</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33943,7 +33943,7 @@
         <v>45884.50613425926</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34005,7 +34005,7 @@
         <v>44693.62822916666</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34067,7 +34067,7 @@
         <v>45769</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34124,7 +34124,7 @@
         <v>45245.63574074074</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34181,7 +34181,7 @@
         <v>45280.66769675926</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34238,7 +34238,7 @@
         <v>44956</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34300,7 +34300,7 @@
         <v>45317</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>45219.69356481481</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34419,7 +34419,7 @@
         <v>45379</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>45225.60192129629</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34533,7 +34533,7 @@
         <v>45841.70569444444</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34590,7 +34590,7 @@
         <v>45841.70868055556</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34647,7 +34647,7 @@
         <v>44965</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34704,7 +34704,7 @@
         <v>45237.63225694445</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34761,7 +34761,7 @@
         <v>45237.64408564815</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34818,7 +34818,7 @@
         <v>45334.78826388889</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34875,7 +34875,7 @@
         <v>45768.65611111111</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34932,7 +34932,7 @@
         <v>44973.43075231482</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34989,7 +34989,7 @@
         <v>45841.7072337963</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35046,7 +35046,7 @@
         <v>44340</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35103,7 +35103,7 @@
         <v>44732.3659837963</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35160,7 +35160,7 @@
         <v>45884.50331018519</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35222,7 +35222,7 @@
         <v>45820.03976851852</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35279,7 +35279,7 @@
         <v>44977</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35336,7 +35336,7 @@
         <v>44790.49040509259</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35393,7 +35393,7 @@
         <v>44964.44356481481</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35450,7 +35450,7 @@
         <v>45887.68759259259</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35507,7 +35507,7 @@
         <v>45323.53744212963</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35564,7 +35564,7 @@
         <v>45533.55362268518</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35621,7 +35621,7 @@
         <v>45610.59094907407</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35678,7 +35678,7 @@
         <v>45763.59436342592</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35735,7 +35735,7 @@
         <v>45355.54138888889</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35792,7 +35792,7 @@
         <v>45361.87975694444</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35849,7 +35849,7 @@
         <v>45330</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35906,7 +35906,7 @@
         <v>45330</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>45845.42015046296</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>45845.43803240741</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36077,7 +36077,7 @@
         <v>44894.49538194444</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36134,7 +36134,7 @@
         <v>44992</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36191,7 +36191,7 @@
         <v>45845.49414351852</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36248,7 +36248,7 @@
         <v>44839.4528125</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36305,7 +36305,7 @@
         <v>45020</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36362,7 +36362,7 @@
         <v>45217.47834490741</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36419,7 +36419,7 @@
         <v>45811.45460648148</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36476,7 +36476,7 @@
         <v>45114.49505787037</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36533,7 +36533,7 @@
         <v>44578.32717592592</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36590,7 +36590,7 @@
         <v>45041</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36647,7 +36647,7 @@
         <v>44897</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36704,7 +36704,7 @@
         <v>45747.43196759259</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36761,7 +36761,7 @@
         <v>45632.36706018518</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36818,7 +36818,7 @@
         <v>45847.91280092593</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>44745.84396990741</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36932,7 +36932,7 @@
         <v>45163.63621527778</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36994,7 +36994,7 @@
         <v>45091.67936342592</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37051,7 +37051,7 @@
         <v>45259.51916666667</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37113,7 +37113,7 @@
         <v>45259.52020833334</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37175,7 +37175,7 @@
         <v>45734.62017361111</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37232,7 +37232,7 @@
         <v>45615.48927083334</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37289,7 +37289,7 @@
         <v>45891</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37346,7 +37346,7 @@
         <v>45349.54434027777</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37403,7 +37403,7 @@
         <v>45891.50525462963</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37460,7 +37460,7 @@
         <v>45891.50986111111</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37517,7 +37517,7 @@
         <v>45345.83557870371</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37574,7 +37574,7 @@
         <v>44599</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37631,7 +37631,7 @@
         <v>45201</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37688,7 +37688,7 @@
         <v>45891.50216435185</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37745,7 +37745,7 @@
         <v>45674.71810185185</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37802,7 +37802,7 @@
         <v>45588.66457175926</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37859,7 +37859,7 @@
         <v>45275.41833333333</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37916,7 +37916,7 @@
         <v>45635.66695601852</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37973,7 +37973,7 @@
         <v>45568.30189814815</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38030,7 +38030,7 @@
         <v>45033.76043981482</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38087,7 +38087,7 @@
         <v>44495</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38144,7 +38144,7 @@
         <v>45853.87112268519</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38201,7 +38201,7 @@
         <v>45699.45392361111</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38258,7 +38258,7 @@
         <v>45154.49831018518</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38315,7 +38315,7 @@
         <v>44848.59133101852</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38372,7 +38372,7 @@
         <v>45440.28329861111</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38429,7 +38429,7 @@
         <v>45853.87599537037</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38486,7 +38486,7 @@
         <v>45853.88070601852</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38543,7 +38543,7 @@
         <v>45630.35827546296</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38600,7 +38600,7 @@
         <v>45896.86820601852</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38657,7 +38657,7 @@
         <v>45755.44333333334</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38714,7 +38714,7 @@
         <v>44790.45876157407</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38771,7 +38771,7 @@
         <v>45891</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38828,7 +38828,7 @@
         <v>44176</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38885,7 +38885,7 @@
         <v>44861</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38942,7 +38942,7 @@
         <v>44879.62173611111</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>45147</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39056,7 +39056,7 @@
         <v>45189</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39113,7 +39113,7 @@
         <v>44987.54104166666</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>45658.80232638889</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39227,7 +39227,7 @@
         <v>45658.80827546296</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39284,7 +39284,7 @@
         <v>45897.63520833333</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39341,7 +39341,7 @@
         <v>45063.49936342592</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39398,7 +39398,7 @@
         <v>45897.88836805556</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39455,7 +39455,7 @@
         <v>45761.44584490741</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39512,7 +39512,7 @@
         <v>44769.45805555556</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39569,7 +39569,7 @@
         <v>45897.64208333333</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>45898.58861111111</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39683,7 +39683,7 @@
         <v>45897.89737268518</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39740,7 +39740,7 @@
         <v>45897.88706018519</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39797,7 +39797,7 @@
         <v>44546</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39854,7 +39854,7 @@
         <v>45224.60075231481</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39916,7 +39916,7 @@
         <v>45646.38200231481</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39973,7 +39973,7 @@
         <v>45128.37305555555</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40030,7 +40030,7 @@
         <v>44377</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40087,7 +40087,7 @@
         <v>45481.56722222222</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>44900.57393518519</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40201,7 +40201,7 @@
         <v>45394.66887731481</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40258,7 +40258,7 @@
         <v>44988</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40315,7 +40315,7 @@
         <v>45764.44931712963</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40377,7 +40377,7 @@
         <v>44270.38002314815</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40439,7 +40439,7 @@
         <v>45121</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40496,7 +40496,7 @@
         <v>44502</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40553,7 +40553,7 @@
         <v>44857.65989583333</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40610,7 +40610,7 @@
         <v>44585.50431712963</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40667,7 +40667,7 @@
         <v>44992.34151620371</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         <v>44542.90072916666</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40786,7 +40786,7 @@
         <v>45698.53336805556</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40843,7 +40843,7 @@
         <v>44418</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40900,7 +40900,7 @@
         <v>44453.56578703703</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40957,7 +40957,7 @@
         <v>44431</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41014,7 +41014,7 @@
         <v>44566</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41071,7 +41071,7 @@
         <v>45749.56196759259</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41133,7 +41133,7 @@
         <v>45743.41148148148</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41190,7 +41190,7 @@
         <v>45261.44914351852</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41247,7 +41247,7 @@
         <v>45048.59699074074</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41304,7 +41304,7 @@
         <v>45732.76936342593</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41361,7 +41361,7 @@
         <v>45090.89653935185</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41418,7 +41418,7 @@
         <v>45090.89880787037</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41475,7 +41475,7 @@
         <v>45503.5658912037</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41532,7 +41532,7 @@
         <v>45201.39996527778</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41589,7 +41589,7 @@
         <v>44991.30547453704</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41646,7 +41646,7 @@
         <v>44991</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41703,7 +41703,7 @@
         <v>45113.41633101852</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41760,7 +41760,7 @@
         <v>45238.4328587963</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41817,7 +41817,7 @@
         <v>44596</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41874,7 +41874,7 @@
         <v>45063.508125</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41931,7 +41931,7 @@
         <v>45219.40528935185</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41988,7 +41988,7 @@
         <v>45568.36879629629</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42045,7 +42045,7 @@
         <v>44077</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42102,7 +42102,7 @@
         <v>44952.35775462963</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42159,7 +42159,7 @@
         <v>45735.56751157407</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42216,7 +42216,7 @@
         <v>44440</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42273,7 +42273,7 @@
         <v>45093.62777777778</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42335,7 +42335,7 @@
         <v>45215.5959375</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42392,7 +42392,7 @@
         <v>45754.33641203704</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42449,7 +42449,7 @@
         <v>44992.62498842592</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42506,7 +42506,7 @@
         <v>45114.47895833333</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42563,7 +42563,7 @@
         <v>45482.49870370371</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42620,7 +42620,7 @@
         <v>45482.54844907407</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42677,7 +42677,7 @@
         <v>45533.38870370371</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42734,7 +42734,7 @@
         <v>45732.79925925926</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42791,7 +42791,7 @@
         <v>45111.30824074074</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42848,7 +42848,7 @@
         <v>44967.44255787037</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42905,7 +42905,7 @@
         <v>44600</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42962,7 +42962,7 @@
         <v>44431.84840277778</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43019,7 +43019,7 @@
         <v>44910.41346064815</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43076,7 +43076,7 @@
         <v>44910</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43133,7 +43133,7 @@
         <v>45187.60813657408</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>44237</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43247,7 +43247,7 @@
         <v>44598.7384837963</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43304,7 +43304,7 @@
         <v>44931</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43366,7 +43366,7 @@
         <v>45027.59450231482</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43428,7 +43428,7 @@
         <v>45112.33599537037</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43485,7 +43485,7 @@
         <v>44452</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43542,7 +43542,7 @@
         <v>44111</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43599,7 +43599,7 @@
         <v>44440.60415509259</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43656,7 +43656,7 @@
         <v>45009.4671875</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43713,7 +43713,7 @@
         <v>45705.74418981482</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43770,7 +43770,7 @@
         <v>45029</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43827,7 +43827,7 @@
         <v>44943.57309027778</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43884,7 +43884,7 @@
         <v>44410</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43941,7 +43941,7 @@
         <v>45111</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43998,7 +43998,7 @@
         <v>44451</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44055,7 +44055,7 @@
         <v>44909</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44112,7 +44112,7 @@
         <v>45346.67184027778</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44169,7 +44169,7 @@
         <v>45637.66542824074</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44226,7 +44226,7 @@
         <v>44966</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44283,7 +44283,7 @@
         <v>45054.6750462963</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44340,7 +44340,7 @@
         <v>44903.33363425926</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44397,7 +44397,7 @@
         <v>44310</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44454,7 +44454,7 @@
         <v>45041.63380787037</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44511,7 +44511,7 @@
         <v>44961</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44568,7 +44568,7 @@
         <v>44578.62943287037</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44625,7 +44625,7 @@
         <v>44916.55414351852</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44682,7 +44682,7 @@
         <v>44867</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44739,7 +44739,7 @@
         <v>44879.55940972222</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44796,7 +44796,7 @@
         <v>45300.3794212963</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44853,7 +44853,7 @@
         <v>44903</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44910,7 +44910,7 @@
         <v>45245.36174768519</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44967,7 +44967,7 @@
         <v>44896</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45024,7 +45024,7 @@
         <v>44890</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45081,7 +45081,7 @@
         <v>44588.37998842593</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45138,7 +45138,7 @@
         <v>44588</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45195,7 +45195,7 @@
         <v>44999.36081018519</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45252,7 +45252,7 @@
         <v>44175.39748842592</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45309,7 +45309,7 @@
         <v>45495</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45366,7 +45366,7 @@
         <v>45361.90282407407</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45423,7 +45423,7 @@
         <v>45224.6515162037</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45485,7 +45485,7 @@
         <v>45128.9325</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45542,7 +45542,7 @@
         <v>45128.93540509259</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45599,7 +45599,7 @@
         <v>45320.89128472222</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45656,7 +45656,7 @@
         <v>44754</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45713,7 +45713,7 @@
         <v>45106.25025462963</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45770,7 +45770,7 @@
         <v>45100.85270833333</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45827,7 +45827,7 @@
         <v>45415.57682870371</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45884,7 +45884,7 @@
         <v>44517</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45941,7 +45941,7 @@
         <v>45108.703125</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45998,7 +45998,7 @@
         <v>45110.4275</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46055,7 +46055,7 @@
         <v>44613</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46112,7 +46112,7 @@
         <v>44992</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46169,7 +46169,7 @@
         <v>45028</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46226,7 +46226,7 @@
         <v>45453.36854166666</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46283,7 +46283,7 @@
         <v>45211.55472222222</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46345,7 +46345,7 @@
         <v>45639.56185185185</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46402,7 +46402,7 @@
         <v>44540</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46459,7 +46459,7 @@
         <v>45174.31395833333</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46516,7 +46516,7 @@
         <v>45446.36865740741</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46578,7 +46578,7 @@
         <v>44981.64725694444</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46635,7 +46635,7 @@
         <v>45138</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46692,7 +46692,7 @@
         <v>44895.46524305556</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>45674.74094907408</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46806,7 +46806,7 @@
         <v>45700.68672453704</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46863,7 +46863,7 @@
         <v>45163</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46920,7 +46920,7 @@
         <v>45453.36067129629</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46977,7 +46977,7 @@
         <v>44963.44769675926</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47034,7 +47034,7 @@
         <v>44944.71386574074</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47091,7 +47091,7 @@
         <v>44944.72100694444</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47148,7 +47148,7 @@
         <v>45698.53725694444</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47205,7 +47205,7 @@
         <v>45250.5278587963</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47262,7 +47262,7 @@
         <v>44803.59118055556</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47319,7 +47319,7 @@
         <v>45153.32778935185</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47376,7 +47376,7 @@
         <v>45761.39600694444</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47433,7 +47433,7 @@
         <v>45106</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47490,7 +47490,7 @@
         <v>45106.2610300926</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47547,7 +47547,7 @@
         <v>45699.60055555555</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47604,7 +47604,7 @@
         <v>45658.78774305555</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47661,7 +47661,7 @@
         <v>45630.45069444444</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47718,7 +47718,7 @@
         <v>44302</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47775,7 +47775,7 @@
         <v>45224</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47832,7 +47832,7 @@
         <v>45224.64659722222</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47894,7 +47894,7 @@
         <v>45121.5965162037</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47956,7 +47956,7 @@
         <v>45121.59954861111</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48018,7 +48018,7 @@
         <v>45121.6096875</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48080,7 +48080,7 @@
         <v>45558.44914351852</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48137,7 +48137,7 @@
         <v>44984</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48194,7 +48194,7 @@
         <v>45624.60141203704</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48251,7 +48251,7 @@
         <v>45434.55471064815</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48313,7 +48313,7 @@
         <v>44312</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48370,7 +48370,7 @@
         <v>44984.45895833334</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48427,7 +48427,7 @@
         <v>44984</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48484,7 +48484,7 @@
         <v>45698.52806712963</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48541,7 +48541,7 @@
         <v>45350.53306712963</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48598,7 +48598,7 @@
         <v>45660</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48655,7 +48655,7 @@
         <v>44258</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48712,7 +48712,7 @@
         <v>45369.62780092593</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48769,7 +48769,7 @@
         <v>45554.63225694445</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48826,7 +48826,7 @@
         <v>45722.48915509259</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48883,7 +48883,7 @@
         <v>45635.4874537037</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48940,7 +48940,7 @@
         <v>45545.49508101852</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48997,7 +48997,7 @@
         <v>45569.47494212963</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49054,7 +49054,7 @@
         <v>45070.3665625</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49111,7 +49111,7 @@
         <v>45070</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49168,7 +49168,7 @@
         <v>45215.60199074074</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49225,7 +49225,7 @@
         <v>45720.44217592593</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49282,7 +49282,7 @@
         <v>44991.89657407408</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49339,7 +49339,7 @@
         <v>44994.46908564815</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49396,7 +49396,7 @@
         <v>45149.60917824074</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49453,7 +49453,7 @@
         <v>45169</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49510,7 +49510,7 @@
         <v>45278</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49572,7 +49572,7 @@
         <v>45456.59289351852</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49629,7 +49629,7 @@
         <v>45002</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49686,7 +49686,7 @@
         <v>45174.40454861111</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49743,7 +49743,7 @@
         <v>45533.56108796296</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49800,7 +49800,7 @@
         <v>45533.58302083334</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49862,7 +49862,7 @@
         <v>45705.73300925926</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49919,7 +49919,7 @@
         <v>44965.4815162037</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49976,7 +49976,7 @@
         <v>44875.27736111111</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50033,7 +50033,7 @@
         <v>45171.77335648148</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50090,7 +50090,7 @@
         <v>45475.49018518518</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50147,7 +50147,7 @@
         <v>45061</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50209,7 +50209,7 @@
         <v>44510.60921296296</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50271,7 +50271,7 @@
         <v>45301</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50328,7 +50328,7 @@
         <v>45301.68237268519</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50385,7 +50385,7 @@
         <v>45475.48303240741</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50442,7 +50442,7 @@
         <v>45124</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50499,7 +50499,7 @@
         <v>45446.36482638889</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50561,7 +50561,7 @@
         <v>45759.38987268518</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50618,7 +50618,7 @@
         <v>45530.33202546297</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50675,7 +50675,7 @@
         <v>45667.39670138889</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50732,7 +50732,7 @@
         <v>45128.58414351852</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50789,7 +50789,7 @@
         <v>44588</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>

--- a/Översikt VIMMERBY.xlsx
+++ b/Översikt VIMMERBY.xlsx
@@ -567,7 +567,7 @@
         <v>44811</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
         <v>44811</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44811</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44811</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>45314</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>44939</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>45301.67922453704</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>45755</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>45377.54726851852</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45748</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>45121.60543981481</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>45678.64175925926</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>44245</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>44811</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>45020</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>45742</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>45628</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>44424</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>44426.64793981481</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>44386</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>45786.52827546297</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>44943</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>45072</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>45896.86820601852</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>45008.60878472222</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>45760.34877314815</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>45048</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>44371</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>45713</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>45104</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>45224</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>45667</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>45168</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>45168</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>45821</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>44403</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>45649</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>44377.61104166666</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>45077</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>45574.42767361111</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         <v>45125</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>44082</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>44236</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>45399.71412037037</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>44083</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>44102</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>44130</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>44287.33261574074</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>44210</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>44281.79269675926</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         <v>44270.67071759259</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>44490.38613425926</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>44447</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>44481.47483796296</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>44350</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>44375.39033564815</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>44614</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>44215</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>44670</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>44670</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>44307</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>44350</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>44105</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>44225</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>44327.47658564815</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>44406</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>44509</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>44480</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>44230.58883101852</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>44238</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>44585.51829861111</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>44824.53434027778</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>44418</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>44785.40800925926</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>44578.47597222222</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         <v>44516.59703703703</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>44862</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44603</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>44588</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>44826.68010416667</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>44404.87505787037</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>44483.58295138889</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>44494</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>44542.8859375</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         <v>44354</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>44512.70245370371</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>44090</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         <v>44221.39408564815</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>44790</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>44261</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>44530.38055555556</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>44588</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         <v>44588</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         <v>44790</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>44790.47628472222</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>44175.3815625</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>44175.40881944444</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>44312</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>44475</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>44385</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>44237.8550925926</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>44124.59795138889</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>44410.71038194445</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>44279.33400462963</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>44175</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>44670</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>44365</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>44169</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>44273</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         <v>44301.36048611111</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>44729.28226851852</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>44271.37226851852</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8472,7 +8472,7 @@
         <v>44340.54472222222</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>44340</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>44774</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>44733</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>44733</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
         <v>44154</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>44371.62743055556</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8871,7 +8871,7 @@
         <v>44386.40783564815</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8928,7 +8928,7 @@
         <v>44480</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         <v>44245</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>44337</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9099,7 +9099,7 @@
         <v>44102</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>44463.29439814815</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         <v>44588</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>44789</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>44117</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>44377</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>44379</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9503,7 +9503,7 @@
         <v>44508</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>44091</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9622,7 +9622,7 @@
         <v>44634.69703703704</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>44480</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         <v>44769.45422453704</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
         <v>44092</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         <v>44085</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>44612.86762731482</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>44383</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>44142</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>44340.58002314815</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10135,7 +10135,7 @@
         <v>44476</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10192,7 +10192,7 @@
         <v>44305.40046296296</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>44447</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>44517</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         <v>44418</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>44854</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>44824</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
         <v>44369</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10596,7 +10596,7 @@
         <v>44819</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         <v>44742</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>44832.67608796297</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>44270</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>44341</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>44451.8375</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>44823</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>44608</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>44447.34237268518</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11109,7 +11109,7 @@
         <v>44294</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11166,7 +11166,7 @@
         <v>44116</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11223,7 +11223,7 @@
         <v>44384</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>44790.48503472222</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         <v>44854.59157407407</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>44621</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>44480</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         <v>44620</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>44217.79856481482</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>44172</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>44876.48346064815</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
         <v>44733.43092592592</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>44203</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11850,7 +11850,7 @@
         <v>44609</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>44266.7240625</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>44284.42348379629</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>44088</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>44088</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>44270.49743055556</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>44421</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>44186</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12316,7 +12316,7 @@
         <v>44273</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>44278.63479166666</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>44722.48768518519</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>44089.78633101852</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         <v>44375.38789351852</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>44525.63913194444</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
         <v>44612.86554398148</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12720,7 +12720,7 @@
         <v>44279.64934027778</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>44662</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12839,7 +12839,7 @@
         <v>44466.34726851852</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>44866.81100694444</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>44095</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>44386</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13077,7 +13077,7 @@
         <v>44470.44232638889</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13134,7 +13134,7 @@
         <v>44776</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13191,7 +13191,7 @@
         <v>44634</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13248,7 +13248,7 @@
         <v>44427</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13305,7 +13305,7 @@
         <v>44564</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>44608.50458333334</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>44817</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13476,7 +13476,7 @@
         <v>44903</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>44991.30547453704</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>44991</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>44379</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>44284.44574074074</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>44292</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>44636</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>44817.57988425926</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>44294</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13999,7 +13999,7 @@
         <v>44294</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>44851.95016203704</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>44588.37998842593</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>44588</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>44676.85248842592</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14284,7 +14284,7 @@
         <v>44644</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>45735.56751157407</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>45632.72635416667</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>44604</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         <v>45048.59699074074</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>44305</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>44981.58834490741</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>45637.66542824074</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         <v>45728.54832175926</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>44693.62822916666</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>45639.56185185185</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14916,7 +14916,7 @@
         <v>45153.32778935185</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14973,7 +14973,7 @@
         <v>44431</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>45071</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15087,7 +15087,7 @@
         <v>45763.59436342592</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>44410</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15201,7 +15201,7 @@
         <v>45769</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15258,7 +15258,7 @@
         <v>45481.58048611111</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
         <v>45635.66695601852</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>45111.48787037037</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>45391.41976851852</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15486,7 +15486,7 @@
         <v>45261.44914351852</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15543,7 +15543,7 @@
         <v>44910.54231481482</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>45211.541875</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>44890</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>44278.54855324074</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>45346.67184027778</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>45732.79925925926</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>45278</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>45147.67096064815</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>45610.59094907407</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>45029</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>44992</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>45052</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>45588.65545138889</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>45699.45671296296</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>45111.48395833333</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>45086</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16460,7 +16460,7 @@
         <v>45128</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>45121.5965162037</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
         <v>45121.59954861111</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         <v>45121.6096875</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16703,7 +16703,7 @@
         <v>45394.66887731481</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>45299.62576388889</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>45784.74996527778</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>45623.9525462963</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16931,7 +16931,7 @@
         <v>44635</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16988,7 +16988,7 @@
         <v>45453.36067129629</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>45020</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>44992.62498842592</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17159,7 +17159,7 @@
         <v>44302</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         <v>45588.66457175926</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17273,7 +17273,7 @@
         <v>44994.40635416667</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
         <v>44175.39748842592</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>45033.76043981482</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17444,7 +17444,7 @@
         <v>44564.62598379629</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>45552.36759259259</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>45196.57247685185</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>45607.56773148148</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17672,7 +17672,7 @@
         <v>45674.71810185185</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>45343.68038194445</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
         <v>45581.57958333333</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17843,7 +17843,7 @@
         <v>45539.65212962963</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17900,7 +17900,7 @@
         <v>45114.55136574074</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>45301.67736111111</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>44546</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>45030.71012731481</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>45786.52931712963</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>45786.52996527778</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>45786.52878472222</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>45768.65611111111</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>44377</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>45463</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>45369.62780092593</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>45624.60141203704</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18584,7 +18584,7 @@
         <v>44377.49684027778</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>45526.3865625</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>45755.64450231481</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         <v>45630.47564814815</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
         <v>45617.47570601852</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18879,7 +18879,7 @@
         <v>45411.47335648148</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>45518.40657407408</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>44607</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>45434.55831018519</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>45434.56398148148</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19174,7 +19174,7 @@
         <v>45698.69016203703</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19231,7 +19231,7 @@
         <v>45345.83557870371</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19288,7 +19288,7 @@
         <v>45726.62721064815</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19345,7 +19345,7 @@
         <v>45224.64659722222</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19407,7 +19407,7 @@
         <v>44991.89657407408</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>45741.37270833334</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19521,7 +19521,7 @@
         <v>44879.55940972222</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>45764.44931712963</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>45054.6750462963</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19697,7 +19697,7 @@
         <v>45761.39600694444</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19754,7 +19754,7 @@
         <v>44720.53898148148</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19811,7 +19811,7 @@
         <v>45539.38744212963</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>44237</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19925,7 +19925,7 @@
         <v>45622</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19982,7 +19982,7 @@
         <v>45574.35809027778</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20039,7 +20039,7 @@
         <v>45533.61996527778</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20101,7 +20101,7 @@
         <v>44588</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20158,7 +20158,7 @@
         <v>44966</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20215,7 +20215,7 @@
         <v>45482.49870370371</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20272,7 +20272,7 @@
         <v>44243</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20329,7 +20329,7 @@
         <v>45237.63225694445</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20386,7 +20386,7 @@
         <v>45237.64408564815</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>45533.63056712963</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20505,7 +20505,7 @@
         <v>45582.41200231481</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20562,7 +20562,7 @@
         <v>45791.89865740741</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         <v>45097.40524305555</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20681,7 +20681,7 @@
         <v>45736.50743055555</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20738,7 +20738,7 @@
         <v>44931</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20800,7 +20800,7 @@
         <v>44833.60123842592</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20857,7 +20857,7 @@
         <v>44270.39765046296</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20919,7 +20919,7 @@
         <v>44897</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>44965.4815162037</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21033,7 +21033,7 @@
         <v>45328.38755787037</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21090,7 +21090,7 @@
         <v>45498</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>45558.44914351852</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21204,7 +21204,7 @@
         <v>45309.59487268519</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21261,7 +21261,7 @@
         <v>45796</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>44861</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21375,7 +21375,7 @@
         <v>45009.4671875</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21432,7 +21432,7 @@
         <v>45300.3794212963</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21489,7 +21489,7 @@
         <v>44992</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21546,7 +21546,7 @@
         <v>45254.62489583333</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21608,7 +21608,7 @@
         <v>45350.53306712963</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21665,7 +21665,7 @@
         <v>45063.49936342592</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21722,7 +21722,7 @@
         <v>44999.86172453704</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21779,7 +21779,7 @@
         <v>44999.8625</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         <v>45148</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>44453.56578703703</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>45485.45778935185</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22007,7 +22007,7 @@
         <v>45527.68784722222</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>45581.57016203704</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>45581.58418981481</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22178,7 +22178,7 @@
         <v>45145</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>45495</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>45618.56787037037</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22349,7 +22349,7 @@
         <v>45699.45392361111</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22406,7 +22406,7 @@
         <v>45187.60813657408</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22463,7 +22463,7 @@
         <v>45603.74959490741</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22520,7 +22520,7 @@
         <v>45715.44159722222</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         <v>44127</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22634,7 +22634,7 @@
         <v>45259.51916666667</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22696,7 +22696,7 @@
         <v>45259.52020833334</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22758,7 +22758,7 @@
         <v>44992.4255787037</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22815,7 +22815,7 @@
         <v>45562.46342592593</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22872,7 +22872,7 @@
         <v>44981.64725694444</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22929,7 +22929,7 @@
         <v>45163.41376157408</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22986,7 +22986,7 @@
         <v>45749.56196759259</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23048,7 +23048,7 @@
         <v>45108.703125</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>45086</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23162,7 +23162,7 @@
         <v>44510.52157407408</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23219,7 +23219,7 @@
         <v>44553</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23276,7 +23276,7 @@
         <v>45574.49298611111</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23333,7 +23333,7 @@
         <v>44517</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23390,7 +23390,7 @@
         <v>45533.38870370371</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23447,7 +23447,7 @@
         <v>44992</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23509,7 +23509,7 @@
         <v>45401.53033564815</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23566,7 +23566,7 @@
         <v>44418</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23623,7 +23623,7 @@
         <v>45658.78774305555</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>45121.61318287037</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
         <v>45275.32266203704</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>45217.47834490741</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23856,7 +23856,7 @@
         <v>44566</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23913,7 +23913,7 @@
         <v>44488.35878472222</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23970,7 +23970,7 @@
         <v>44918</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24027,7 +24027,7 @@
         <v>44746.38834490741</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>45450.51092592593</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>44598</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>45163</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>44988</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>45275.41833333333</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24369,7 +24369,7 @@
         <v>45635.66409722222</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24426,7 +24426,7 @@
         <v>45168.89298611111</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24483,7 +24483,7 @@
         <v>45079.87827546296</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24540,7 +24540,7 @@
         <v>45187</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24597,7 +24597,7 @@
         <v>44754</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24654,7 +24654,7 @@
         <v>45804.39141203704</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
         <v>45804.67065972222</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24768,7 +24768,7 @@
         <v>45804.6953587963</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24830,7 +24830,7 @@
         <v>44579.62225694444</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24887,7 +24887,7 @@
         <v>45552.36484953704</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24944,7 +24944,7 @@
         <v>45460.62172453704</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25001,7 +25001,7 @@
         <v>44495</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25058,7 +25058,7 @@
         <v>45090.89653935185</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25115,7 +25115,7 @@
         <v>45090.89880787037</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25172,7 +25172,7 @@
         <v>44638.55256944444</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25229,7 +25229,7 @@
         <v>44600</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25286,7 +25286,7 @@
         <v>45804.708125</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25348,7 +25348,7 @@
         <v>44769.45805555556</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25405,7 +25405,7 @@
         <v>45128.58414351852</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25462,7 +25462,7 @@
         <v>45805.39247685186</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         <v>45171.96248842592</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25576,7 +25576,7 @@
         <v>45805.52983796296</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25633,7 +25633,7 @@
         <v>45650.37370370371</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25690,7 +25690,7 @@
         <v>45804.44519675926</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25747,7 +25747,7 @@
         <v>45805</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25804,7 +25804,7 @@
         <v>44451</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25861,7 +25861,7 @@
         <v>44613</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25918,7 +25918,7 @@
         <v>45128.37305555555</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25975,7 +25975,7 @@
         <v>45189</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26032,7 +26032,7 @@
         <v>45540.50098379629</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26089,7 +26089,7 @@
         <v>45245.5735300926</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>45415.47848379629</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26203,7 +26203,7 @@
         <v>45621.46103009259</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26260,7 +26260,7 @@
         <v>44861.52505787037</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26317,7 +26317,7 @@
         <v>45308.61152777778</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26374,7 +26374,7 @@
         <v>45425.57538194444</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26431,7 +26431,7 @@
         <v>45063.508125</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26488,7 +26488,7 @@
         <v>44895.62296296296</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26545,7 +26545,7 @@
         <v>44452</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26602,7 +26602,7 @@
         <v>45009</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26659,7 +26659,7 @@
         <v>45379</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26716,7 +26716,7 @@
         <v>45719.84378472222</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26773,7 +26773,7 @@
         <v>45475.48303240741</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26830,7 +26830,7 @@
         <v>45735.58024305556</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26887,7 +26887,7 @@
         <v>44820</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         <v>45232</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>45215.5959375</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>45215.59743055556</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         <v>45351.6062962963</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27172,7 +27172,7 @@
         <v>45041.63380787037</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27229,7 +27229,7 @@
         <v>45674.74094907408</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27286,7 +27286,7 @@
         <v>45539.66027777778</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27343,7 +27343,7 @@
         <v>45002</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27400,7 +27400,7 @@
         <v>45565.40657407408</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27457,7 +27457,7 @@
         <v>45814.38221064815</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>45814.3865625</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>45482.54108796296</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27628,7 +27628,7 @@
         <v>45195.58452546296</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>45818.58993055556</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27747,7 +27747,7 @@
         <v>45818.58769675926</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27809,7 +27809,7 @@
         <v>45818.595625</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27871,7 +27871,7 @@
         <v>45026.82216435186</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27928,7 +27928,7 @@
         <v>45818.59261574074</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27990,7 +27990,7 @@
         <v>45482.54844907407</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28047,7 +28047,7 @@
         <v>45818.5862037037</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28109,7 +28109,7 @@
         <v>44867</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28166,7 +28166,7 @@
         <v>45266.32614583334</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28223,7 +28223,7 @@
         <v>45819.61060185185</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28280,7 +28280,7 @@
         <v>45236</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28337,7 +28337,7 @@
         <v>45121</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28394,7 +28394,7 @@
         <v>44967.44255787037</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28451,7 +28451,7 @@
         <v>44903.33363425926</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28508,7 +28508,7 @@
         <v>45174.31395833333</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28565,7 +28565,7 @@
         <v>44943.57309027778</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28622,7 +28622,7 @@
         <v>45820.33708333333</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28679,7 +28679,7 @@
         <v>45820.34128472222</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28736,7 +28736,7 @@
         <v>45820.33930555556</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28793,7 +28793,7 @@
         <v>44440</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28850,7 +28850,7 @@
         <v>45825.57805555555</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28907,7 +28907,7 @@
         <v>45867.64663194444</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28964,7 +28964,7 @@
         <v>45554.62944444444</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29021,7 +29021,7 @@
         <v>44083</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         <v>45632.37459490741</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29135,7 +29135,7 @@
         <v>45867.69346064814</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29192,7 +29192,7 @@
         <v>45867.50792824074</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29249,7 +29249,7 @@
         <v>45867.63094907408</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29306,7 +29306,7 @@
         <v>45825.58672453704</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29363,7 +29363,7 @@
         <v>45867.56320601852</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29420,7 +29420,7 @@
         <v>45867.68625</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29477,7 +29477,7 @@
         <v>44803.59118055556</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29534,7 +29534,7 @@
         <v>45825.5796875</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29591,7 +29591,7 @@
         <v>45567.42011574074</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29648,7 +29648,7 @@
         <v>45867.51630787037</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29705,7 +29705,7 @@
         <v>45825.57680555555</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29762,7 +29762,7 @@
         <v>45827</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29819,7 +29819,7 @@
         <v>45827</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29876,7 +29876,7 @@
         <v>45869.62276620371</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29933,7 +29933,7 @@
         <v>45317.40372685185</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29995,7 +29995,7 @@
         <v>44857.65989583333</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30052,7 +30052,7 @@
         <v>45870.51958333333</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30109,7 +30109,7 @@
         <v>45870.51708333333</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30166,7 +30166,7 @@
         <v>45870.52005787037</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30223,7 +30223,7 @@
         <v>45870.52142361111</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
         <v>45831</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30337,7 +30337,7 @@
         <v>44587.48847222222</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30394,7 +30394,7 @@
         <v>45870.52111111111</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30451,7 +30451,7 @@
         <v>45875.42716435185</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30508,7 +30508,7 @@
         <v>44965</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30565,7 +30565,7 @@
         <v>45874.57109953704</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30622,7 +30622,7 @@
         <v>45359.44837962963</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30679,7 +30679,7 @@
         <v>45875.47454861111</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30736,7 +30736,7 @@
         <v>45833.64563657407</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30793,7 +30793,7 @@
         <v>45833.64814814815</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30850,7 +30850,7 @@
         <v>44944.71386574074</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30907,7 +30907,7 @@
         <v>44944.72100694444</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30964,7 +30964,7 @@
         <v>45832.46146990741</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>45833.64237268519</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31078,7 +31078,7 @@
         <v>45875.45716435185</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31135,7 +31135,7 @@
         <v>45110.4275</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31192,7 +31192,7 @@
         <v>45832.34540509259</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31249,7 +31249,7 @@
         <v>45467.74417824074</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31306,7 +31306,7 @@
         <v>45834.65040509259</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31368,7 +31368,7 @@
         <v>45709.62280092593</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31425,7 +31425,7 @@
         <v>45835.44709490741</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31482,7 +31482,7 @@
         <v>45835.48267361111</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31539,7 +31539,7 @@
         <v>45835.48445601852</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31596,7 +31596,7 @@
         <v>45835.48862268519</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31653,7 +31653,7 @@
         <v>45446.36482638889</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31715,7 +31715,7 @@
         <v>45834.64667824074</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31777,7 +31777,7 @@
         <v>45835.44732638889</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31834,7 +31834,7 @@
         <v>44312</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31891,7 +31891,7 @@
         <v>45835.36229166666</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31953,7 +31953,7 @@
         <v>45835.45099537037</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32010,7 +32010,7 @@
         <v>45835.4924537037</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32067,7 +32067,7 @@
         <v>45834.65197916667</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32129,7 +32129,7 @@
         <v>45000.47998842593</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32186,7 +32186,7 @@
         <v>45503.5658912037</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32243,7 +32243,7 @@
         <v>45880.51413194444</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32305,7 +32305,7 @@
         <v>45881</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32362,7 +32362,7 @@
         <v>45880.51550925926</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32424,7 +32424,7 @@
         <v>45881.59877314815</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32481,7 +32481,7 @@
         <v>45837.77916666667</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32538,7 +32538,7 @@
         <v>45837.77701388889</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32595,7 +32595,7 @@
         <v>45880.38380787037</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32652,7 +32652,7 @@
         <v>45840.59474537037</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32709,7 +32709,7 @@
         <v>45840.59853009259</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32766,7 +32766,7 @@
         <v>45841.70569444444</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32823,7 +32823,7 @@
         <v>45841.70868055556</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32880,7 +32880,7 @@
         <v>45832.46649305556</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32937,7 +32937,7 @@
         <v>45440.28329861111</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32994,7 +32994,7 @@
         <v>45841.7072337963</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33051,7 +33051,7 @@
         <v>45495</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33108,7 +33108,7 @@
         <v>45811.45460648148</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33165,7 +33165,7 @@
         <v>45554.63225694445</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33222,7 +33222,7 @@
         <v>44956</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33284,7 +33284,7 @@
         <v>44270.38002314815</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33346,7 +33346,7 @@
         <v>45884.50331018519</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33408,7 +33408,7 @@
         <v>45845.42015046296</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33465,7 +33465,7 @@
         <v>45845.43803240741</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33522,7 +33522,7 @@
         <v>45845.49414351852</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33579,7 +33579,7 @@
         <v>45820.03976851852</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33636,7 +33636,7 @@
         <v>44596</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33693,7 +33693,7 @@
         <v>45257.67958333333</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33750,7 +33750,7 @@
         <v>45884.50613425926</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33812,7 +33812,7 @@
         <v>45887.68759259259</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33869,7 +33869,7 @@
         <v>45113.41633101852</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33926,7 +33926,7 @@
         <v>45666</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33983,7 +33983,7 @@
         <v>44595.583125</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34040,7 +34040,7 @@
         <v>44918.50106481482</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34097,7 +34097,7 @@
         <v>44999.35858796296</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34154,7 +34154,7 @@
         <v>45847.91280092593</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34211,7 +34211,7 @@
         <v>45891.50525462963</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34268,7 +34268,7 @@
         <v>45891.50986111111</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34325,7 +34325,7 @@
         <v>45301</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34382,7 +34382,7 @@
         <v>45891</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34439,7 +34439,7 @@
         <v>45891.50216435185</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34496,7 +34496,7 @@
         <v>45027.59450231482</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34558,7 +34558,7 @@
         <v>44789</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34615,7 +34615,7 @@
         <v>45224.6515162037</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34677,7 +34677,7 @@
         <v>45891</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34734,7 +34734,7 @@
         <v>45897.64208333333</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34791,7 +34791,7 @@
         <v>45897.89737268518</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34848,7 +34848,7 @@
         <v>45377</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34905,7 +34905,7 @@
         <v>45853.87112268519</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34962,7 +34962,7 @@
         <v>45853.87599537037</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>45853.88070601852</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35076,7 +35076,7 @@
         <v>45106.25025462963</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35133,7 +35133,7 @@
         <v>45897.88836805556</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35190,7 +35190,7 @@
         <v>45897.88706018519</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35247,7 +35247,7 @@
         <v>45897.63520833333</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35304,7 +35304,7 @@
         <v>45755.44333333334</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35361,7 +35361,7 @@
         <v>45858.60641203704</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35418,7 +35418,7 @@
         <v>45901.63219907408</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35475,7 +35475,7 @@
         <v>45901.6327662037</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35532,7 +35532,7 @@
         <v>45858.66019675926</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35589,7 +35589,7 @@
         <v>45898.58861111111</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35646,7 +35646,7 @@
         <v>45114.47895833333</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35703,7 +35703,7 @@
         <v>44958.61047453704</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35760,7 +35760,7 @@
         <v>45902.47164351852</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35817,7 +35817,7 @@
         <v>45219.40528935185</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35874,7 +35874,7 @@
         <v>45903.38800925926</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35931,7 +35931,7 @@
         <v>44663</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35988,7 +35988,7 @@
         <v>45567</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36045,7 +36045,7 @@
         <v>45623.95947916667</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36102,7 +36102,7 @@
         <v>45349.54434027777</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36159,7 +36159,7 @@
         <v>45041</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36216,7 +36216,7 @@
         <v>45334.78826388889</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36273,7 +36273,7 @@
         <v>45114.58148148148</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36330,7 +36330,7 @@
         <v>44600</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36387,7 +36387,7 @@
         <v>45581.57333333333</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36444,7 +36444,7 @@
         <v>45434.55471064815</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36506,7 +36506,7 @@
         <v>45434.56291666667</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36568,7 +36568,7 @@
         <v>45359.45038194444</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36625,7 +36625,7 @@
         <v>45201.39996527778</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36682,7 +36682,7 @@
         <v>44895.46524305556</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36739,7 +36739,7 @@
         <v>44587</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36796,7 +36796,7 @@
         <v>45086.63334490741</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36853,7 +36853,7 @@
         <v>45569.45017361111</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36910,7 +36910,7 @@
         <v>45569.47494212963</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36967,7 +36967,7 @@
         <v>45588.67070601852</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37024,7 +37024,7 @@
         <v>45355.54138888889</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37081,7 +37081,7 @@
         <v>44949</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37138,7 +37138,7 @@
         <v>45660</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37195,7 +37195,7 @@
         <v>44599</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37252,7 +37252,7 @@
         <v>45090</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37309,7 +37309,7 @@
         <v>44467.83386574074</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37366,7 +37366,7 @@
         <v>44340</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37423,7 +37423,7 @@
         <v>44944.73487268519</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37480,7 +37480,7 @@
         <v>45330</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>45330</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37594,7 +37594,7 @@
         <v>44790.49040509259</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37651,7 +37651,7 @@
         <v>44784.42528935185</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37708,7 +37708,7 @@
         <v>45250.5278587963</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37765,7 +37765,7 @@
         <v>45070</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37822,7 +37822,7 @@
         <v>45225.60192129629</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37879,7 +37879,7 @@
         <v>44935</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37936,7 +37936,7 @@
         <v>44852</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37993,7 +37993,7 @@
         <v>45700.68289351852</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38050,7 +38050,7 @@
         <v>44539</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38107,7 +38107,7 @@
         <v>45100.85270833333</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38164,7 +38164,7 @@
         <v>45517.8162037037</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38221,7 +38221,7 @@
         <v>45299.47513888889</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38278,7 +38278,7 @@
         <v>44578.62943287037</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38335,7 +38335,7 @@
         <v>44994.46908564815</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38392,7 +38392,7 @@
         <v>44910</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38449,7 +38449,7 @@
         <v>44900.57393518519</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38506,7 +38506,7 @@
         <v>44440.60415509259</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38563,7 +38563,7 @@
         <v>45201</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38620,7 +38620,7 @@
         <v>44598.7384837963</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38677,7 +38677,7 @@
         <v>44966</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38734,7 +38734,7 @@
         <v>44848.59133101852</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38791,7 +38791,7 @@
         <v>45323.53744212963</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38848,7 +38848,7 @@
         <v>45308.59001157407</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38905,7 +38905,7 @@
         <v>45559.38876157408</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38962,7 +38962,7 @@
         <v>45111.30824074074</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39019,7 +39019,7 @@
         <v>45224</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39076,7 +39076,7 @@
         <v>45086.63194444445</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39133,7 +39133,7 @@
         <v>45196</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39190,7 +39190,7 @@
         <v>45415.48979166667</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39247,7 +39247,7 @@
         <v>44542.90072916666</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39304,7 +39304,7 @@
         <v>45749.60487268519</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39366,7 +39366,7 @@
         <v>44984.45895833334</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39423,7 +39423,7 @@
         <v>45446.36865740741</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39485,7 +39485,7 @@
         <v>45245.63574074074</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39542,7 +39542,7 @@
         <v>45732.76936342593</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39599,7 +39599,7 @@
         <v>45707.3793287037</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39656,7 +39656,7 @@
         <v>44578.32717592592</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39713,7 +39713,7 @@
         <v>45525.41762731481</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39770,7 +39770,7 @@
         <v>44964.5115162037</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39827,7 +39827,7 @@
         <v>45320.89128472222</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39884,7 +39884,7 @@
         <v>44987.54104166666</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39941,7 +39941,7 @@
         <v>45121.58699074074</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40003,7 +40003,7 @@
         <v>45208</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40060,7 +40060,7 @@
         <v>45001.43854166667</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40117,7 +40117,7 @@
         <v>45211.52642361111</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40174,7 +40174,7 @@
         <v>44585.51060185185</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40231,7 +40231,7 @@
         <v>45260.4716550926</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40288,7 +40288,7 @@
         <v>44943.62954861111</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40345,7 +40345,7 @@
         <v>45075.43059027778</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40402,7 +40402,7 @@
         <v>44630</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40459,7 +40459,7 @@
         <v>45371.36359953704</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40516,7 +40516,7 @@
         <v>45371.45865740741</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40573,7 +40573,7 @@
         <v>45100.4062962963</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40630,7 +40630,7 @@
         <v>44938</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40692,7 +40692,7 @@
         <v>44795</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40749,7 +40749,7 @@
         <v>44949</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40811,7 +40811,7 @@
         <v>45280.66769675926</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40868,7 +40868,7 @@
         <v>45112.33599537037</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40925,7 +40925,7 @@
         <v>45111</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40982,7 +40982,7 @@
         <v>45020</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41039,7 +41039,7 @@
         <v>45568.30189814815</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41096,7 +41096,7 @@
         <v>45568.36879629629</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41153,7 +41153,7 @@
         <v>44159</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41210,7 +41210,7 @@
         <v>45202.4209837963</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41267,7 +41267,7 @@
         <v>45632.36706018518</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41324,7 +41324,7 @@
         <v>45632.44886574074</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41381,7 +41381,7 @@
         <v>44894.49538194444</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41438,7 +41438,7 @@
         <v>45245.36174768519</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41495,7 +41495,7 @@
         <v>44585.50431712963</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41552,7 +41552,7 @@
         <v>44172</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41609,7 +41609,7 @@
         <v>44790.45876157407</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41666,7 +41666,7 @@
         <v>44790.49523148148</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41723,7 +41723,7 @@
         <v>45170</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41780,7 +41780,7 @@
         <v>45211.43555555555</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41837,7 +41837,7 @@
         <v>44893</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41894,7 +41894,7 @@
         <v>45174.40454861111</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41951,7 +41951,7 @@
         <v>45713.45311342592</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42008,7 +42008,7 @@
         <v>44867</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42065,7 +42065,7 @@
         <v>44732.3659837963</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42122,7 +42122,7 @@
         <v>45635.4874537037</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42179,7 +42179,7 @@
         <v>44994.42113425926</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42236,7 +42236,7 @@
         <v>45483.82479166667</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42293,7 +42293,7 @@
         <v>45176.72427083334</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42350,7 +42350,7 @@
         <v>45759.38987268518</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42407,7 +42407,7 @@
         <v>45713.92412037037</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42464,7 +42464,7 @@
         <v>45446.36774305555</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42526,7 +42526,7 @@
         <v>45615.48927083334</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42583,7 +42583,7 @@
         <v>45061</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42645,7 +42645,7 @@
         <v>44310</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42702,7 +42702,7 @@
         <v>45096.45247685185</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42759,7 +42759,7 @@
         <v>45391.41310185185</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42816,7 +42816,7 @@
         <v>45163.63621527778</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42878,7 +42878,7 @@
         <v>45729.36868055556</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42935,7 +42935,7 @@
         <v>45093.62777777778</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42997,7 +42997,7 @@
         <v>45630.35827546296</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43054,7 +43054,7 @@
         <v>44431.84840277778</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43111,7 +43111,7 @@
         <v>45671.46746527778</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43168,7 +43168,7 @@
         <v>44984</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>44984</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43282,7 +43282,7 @@
         <v>45110.4184375</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43339,7 +43339,7 @@
         <v>45018</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43396,7 +43396,7 @@
         <v>45182.78834490741</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43453,7 +43453,7 @@
         <v>45761.4437962963</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43510,7 +43510,7 @@
         <v>45128.9325</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43567,7 +43567,7 @@
         <v>45128.93540509259</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43624,7 +43624,7 @@
         <v>44999.36081018519</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43681,7 +43681,7 @@
         <v>45567</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43738,7 +43738,7 @@
         <v>45105</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43795,7 +43795,7 @@
         <v>44788</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43852,7 +43852,7 @@
         <v>44258</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43909,7 +43909,7 @@
         <v>44466.34962962963</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43966,7 +43966,7 @@
         <v>45070.3665625</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44023,7 +44023,7 @@
         <v>45028</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44080,7 +44080,7 @@
         <v>45698.53725694444</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44137,7 +44137,7 @@
         <v>45456.59289351852</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44194,7 +44194,7 @@
         <v>45481.55984953704</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44251,7 +44251,7 @@
         <v>45530.33202546297</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44308,7 +44308,7 @@
         <v>44964.50894675926</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44365,7 +44365,7 @@
         <v>45257.70313657408</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44422,7 +44422,7 @@
         <v>45533.60232638889</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44484,7 +44484,7 @@
         <v>45533.60770833334</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44546,7 +44546,7 @@
         <v>45001.59209490741</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44603,7 +44603,7 @@
         <v>45569.44295138889</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44660,7 +44660,7 @@
         <v>44910.41346064815</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44717,7 +44717,7 @@
         <v>45483.82834490741</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44774,7 +44774,7 @@
         <v>44879</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44831,7 +44831,7 @@
         <v>45698.52806712963</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44888,7 +44888,7 @@
         <v>45271.66576388889</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44945,7 +44945,7 @@
         <v>45224.60075231481</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45007,7 +45007,7 @@
         <v>45113.56574074074</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45064,7 +45064,7 @@
         <v>45475.49018518518</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45121,7 +45121,7 @@
         <v>44540</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45178,7 +45178,7 @@
         <v>44510.60921296296</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45240,7 +45240,7 @@
         <v>44916.55414351852</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45297,7 +45297,7 @@
         <v>44961</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45354,7 +45354,7 @@
         <v>44984</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45411,7 +45411,7 @@
         <v>45090.38012731481</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45468,7 +45468,7 @@
         <v>45149.60917824074</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45525,7 +45525,7 @@
         <v>45482.52887731481</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45582,7 +45582,7 @@
         <v>44879.62173611111</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45639,7 +45639,7 @@
         <v>45174</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45696,7 +45696,7 @@
         <v>45705.73300925926</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45753,7 +45753,7 @@
         <v>45091.67936342592</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45810,7 +45810,7 @@
         <v>45700.68672453704</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45867,7 +45867,7 @@
         <v>45646.38200231481</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45924,7 +45924,7 @@
         <v>44603</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45981,7 +45981,7 @@
         <v>45147.67172453704</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46038,7 +46038,7 @@
         <v>44959.66407407408</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46095,7 +46095,7 @@
         <v>45171.77335648148</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46152,7 +46152,7 @@
         <v>45698.53336805556</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46209,7 +46209,7 @@
         <v>44392</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46271,7 +46271,7 @@
         <v>45113.43921296296</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46328,7 +46328,7 @@
         <v>44967.45122685185</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46385,7 +46385,7 @@
         <v>45545.49508101852</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46442,7 +46442,7 @@
         <v>45361.87975694444</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46499,7 +46499,7 @@
         <v>44896</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>44963.44769675926</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46613,7 +46613,7 @@
         <v>45720.44217592593</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46670,7 +46670,7 @@
         <v>45699.44291666667</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46727,7 +46727,7 @@
         <v>45114.49505787037</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46784,7 +46784,7 @@
         <v>44909</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46841,7 +46841,7 @@
         <v>44176</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46898,7 +46898,7 @@
         <v>45111.48225694444</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46955,7 +46955,7 @@
         <v>45111.48636574074</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47012,7 +47012,7 @@
         <v>45747.43196759259</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47069,7 +47069,7 @@
         <v>45747.42633101852</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47126,7 +47126,7 @@
         <v>45747.42958333333</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47183,7 +47183,7 @@
         <v>45098.30535879629</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47240,7 +47240,7 @@
         <v>45699.60055555555</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47297,7 +47297,7 @@
         <v>44784.62724537037</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47354,7 +47354,7 @@
         <v>45667.39670138889</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47411,7 +47411,7 @@
         <v>45154.49831018518</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47468,7 +47468,7 @@
         <v>45722.48634259259</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47525,7 +47525,7 @@
         <v>45481.56722222222</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47582,7 +47582,7 @@
         <v>45453.36854166666</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47639,7 +47639,7 @@
         <v>44992.34151620371</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47701,7 +47701,7 @@
         <v>44502</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47758,7 +47758,7 @@
         <v>45378.32185185186</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47815,7 +47815,7 @@
         <v>45243.84869212963</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47872,7 +47872,7 @@
         <v>44643</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47929,7 +47929,7 @@
         <v>45726.44471064815</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47986,7 +47986,7 @@
         <v>45377.40043981482</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48043,7 +48043,7 @@
         <v>45219.69356481481</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48100,7 +48100,7 @@
         <v>45211.55472222222</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48162,7 +48162,7 @@
         <v>45761.35990740741</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48219,7 +48219,7 @@
         <v>44964.44356481481</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48276,7 +48276,7 @@
         <v>45238.4328587963</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48333,7 +48333,7 @@
         <v>44977</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48390,7 +48390,7 @@
         <v>45498.673125</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48447,7 +48447,7 @@
         <v>44893</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48504,7 +48504,7 @@
         <v>45658.80232638889</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48561,7 +48561,7 @@
         <v>45658.80827546296</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48618,7 +48618,7 @@
         <v>45572.48293981481</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48675,7 +48675,7 @@
         <v>45147</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48732,7 +48732,7 @@
         <v>44825.4336574074</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48789,7 +48789,7 @@
         <v>45215.60199074074</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48846,7 +48846,7 @@
         <v>45533.55362268518</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48903,7 +48903,7 @@
         <v>45754.33641203704</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48960,7 +48960,7 @@
         <v>45415.57682870371</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49017,7 +49017,7 @@
         <v>45187.42854166667</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49074,7 +49074,7 @@
         <v>45169</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49131,7 +49131,7 @@
         <v>44867</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49188,7 +49188,7 @@
         <v>44475</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49245,7 +49245,7 @@
         <v>44111</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49302,7 +49302,7 @@
         <v>44839.4528125</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49359,7 +49359,7 @@
         <v>44745.84396990741</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49416,7 +49416,7 @@
         <v>44875.27736111111</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49473,7 +49473,7 @@
         <v>45533.54429398148</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49530,7 +49530,7 @@
         <v>45630.45069444444</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49587,7 +49587,7 @@
         <v>44973.43075231482</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49644,7 +49644,7 @@
         <v>45106.2610300926</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49701,7 +49701,7 @@
         <v>45705.74418981482</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49758,7 +49758,7 @@
         <v>45301.68237268519</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49815,7 +49815,7 @@
         <v>45533.56108796296</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49872,7 +49872,7 @@
         <v>45533.58302083334</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49934,7 +49934,7 @@
         <v>45124</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49991,7 +49991,7 @@
         <v>45722.48915509259</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50048,7 +50048,7 @@
         <v>45106</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50105,7 +50105,7 @@
         <v>45743.41148148148</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50162,7 +50162,7 @@
         <v>45569.44684027778</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50219,7 +50219,7 @@
         <v>45148</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50276,7 +50276,7 @@
         <v>45361.90282407407</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50333,7 +50333,7 @@
         <v>44952.35775462963</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50390,7 +50390,7 @@
         <v>45548</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50447,7 +50447,7 @@
         <v>45394.50028935185</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50504,7 +50504,7 @@
         <v>45138</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50561,7 +50561,7 @@
         <v>45317</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50623,7 +50623,7 @@
         <v>45384.66917824074</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50680,7 +50680,7 @@
         <v>45734.62017361111</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50737,7 +50737,7 @@
         <v>45698.51711805556</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50794,7 +50794,7 @@
         <v>45513.55840277778</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50851,7 +50851,7 @@
         <v>45513.56527777778</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>

--- a/Översikt VIMMERBY.xlsx
+++ b/Översikt VIMMERBY.xlsx
@@ -567,7 +567,7 @@
         <v>44811</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
         <v>44811</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44811</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44811</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>45314</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>44939</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>45301.67922453704</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>45755</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>45377.54726851852</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45748</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>45121.60543981481</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>45678.64175925926</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>44245</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>44811</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>45628</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>45742</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>45020</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>44424</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>44426.64793981481</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>44386</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>45786.52827546297</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>45008.60878472222</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>44943</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>45760.34877314815</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>45880.51413194444</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>45072</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>45048</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>45896.86820601852</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>45908</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>44371</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>44403</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>45399.71412037037</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>45125</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>45104</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>45574.42767361111</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>45667</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>45649</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>45821</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>45168</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>45168</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>44236</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>45713</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>45884.50331018519</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>45077</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>45224</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>44377.61104166666</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>44102</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>44130</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>44281.79269675926</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>44270.67071759259</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>44287.33261574074</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>44210</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>44481.47483796296</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>44490.38613425926</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>44447</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>44375.39033564815</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
         <v>44350</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5403,7 +5403,7 @@
         <v>44614</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>44215</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>44670</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         <v>44670</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>44307</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>44350</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5745,7 +5745,7 @@
         <v>44105</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         <v>44225</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>44327.47658564815</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         <v>44509</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>44230.58883101852</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>44480</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         <v>44238</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
         <v>44406</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         <v>44585.51829861111</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>44824.53434027778</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>44418</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>44785.40800925926</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>44826.68010416667</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         <v>44862</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>44578.47597222222</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>44516.59703703703</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>44603</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>44588</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>44404.87505787037</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>44483.58295138889</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>44494</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>44542.8859375</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>44354</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>44512.70245370371</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>44090</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>44790</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>44261</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>44530.38055555556</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>44221.39408564815</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>44588</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>44588</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>44790</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>44790.47628472222</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>44175.3815625</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>44175.40881944444</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>44312</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>44475</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>44385</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>44124.59795138889</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>44237.8550925926</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>44410.71038194445</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8087,7 +8087,7 @@
         <v>44279.33400462963</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>44175</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         <v>44670</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>44365</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>44169</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>44273</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>44301.36048611111</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>44729.28226851852</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>44271.37226851852</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>44340.54472222222</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>44340</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>44774</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>44733</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>44733</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>44371.62743055556</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>44386.40783564815</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>44480</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>44154</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>44245</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>44337</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>44102</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>44463.29439814815</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9346,7 +9346,7 @@
         <v>44588</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>44117</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>44789</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>44377</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>44379</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>44508</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         <v>44091</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>44634.69703703704</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>44480</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>44769.45422453704</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>44340.58002314815</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9983,7 +9983,7 @@
         <v>44644</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10040,7 +10040,7 @@
         <v>44383</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>44092</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10154,7 +10154,7 @@
         <v>44612.86762731482</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>44476</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10268,7 +10268,7 @@
         <v>44418</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>44517</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10382,7 +10382,7 @@
         <v>44854</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         <v>44819</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         <v>44832.67608796297</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         <v>44142</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10610,7 +10610,7 @@
         <v>44305.40046296296</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         <v>44451.8375</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         <v>44823</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>44447</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>44621</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>44172</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>44270</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11014,7 +11014,7 @@
         <v>44341</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11071,7 +11071,7 @@
         <v>44608</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11128,7 +11128,7 @@
         <v>44447.34237268518</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         <v>44384</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>44294</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>44876.48346064815</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>44733.43092592592</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>44790.48503472222</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>44116</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>44854.59157407407</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>44824</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>44369</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>44742</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11755,7 +11755,7 @@
         <v>44620</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11812,7 +11812,7 @@
         <v>44609</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>44480</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
         <v>44284.42348379629</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>44088</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>44088</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12097,7 +12097,7 @@
         <v>44421</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>44186</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
         <v>44089.78633101852</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>44273</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>44203</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>44278.63479166666</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>44266.7240625</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>44525.63913194444</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>44612.86554398148</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>44270.49743055556</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12682,7 +12682,7 @@
         <v>44466.34726851852</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>44866.81100694444</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>44279.64934027778</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
         <v>44662</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12920,7 +12920,7 @@
         <v>44095</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>44470.44232638889</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
         <v>44776</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>44634</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13153,7 +13153,7 @@
         <v>44722.48768518519</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13210,7 +13210,7 @@
         <v>44564</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>44608.50458333334</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13324,7 +13324,7 @@
         <v>44817</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13381,7 +13381,7 @@
         <v>44379</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>44292</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>44284.44574074074</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13562,7 +13562,7 @@
         <v>45483.82834490741</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13619,7 +13619,7 @@
         <v>44636</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13676,7 +13676,7 @@
         <v>44217.79856481482</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13733,7 +13733,7 @@
         <v>45090.38012731481</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>44466.34962962963</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13847,7 +13847,7 @@
         <v>45105</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>44278.54855324074</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13961,7 +13961,7 @@
         <v>44377.49684027778</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14023,7 +14023,7 @@
         <v>44833.60123842592</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>45215.59743055556</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14137,7 +14137,7 @@
         <v>44817.57988425926</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>44789</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14251,7 +14251,7 @@
         <v>44294</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         <v>44294</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14365,7 +14365,7 @@
         <v>44676.85248842592</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14422,7 +14422,7 @@
         <v>45411.47335648148</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14479,7 +14479,7 @@
         <v>44604</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14536,7 +14536,7 @@
         <v>45377.40043981482</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14593,7 +14593,7 @@
         <v>45698.51711805556</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
         <v>45211.43555555555</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14707,7 +14707,7 @@
         <v>44305</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>45097.40524305555</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>45100.4062962963</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14883,7 +14883,7 @@
         <v>45425.57538194444</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14940,7 +14940,7 @@
         <v>45196</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>44607</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>44949</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15116,7 +15116,7 @@
         <v>45121.58699074074</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15178,7 +15178,7 @@
         <v>45569.44684027778</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15235,7 +15235,7 @@
         <v>45090</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         <v>45749.60487268519</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         <v>45232</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>45245.5735300926</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15468,7 +15468,7 @@
         <v>45525.41762731481</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15525,7 +15525,7 @@
         <v>45391.41310185185</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15582,7 +15582,7 @@
         <v>45450.51092592593</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15639,7 +15639,7 @@
         <v>45086.63194444445</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15696,7 +15696,7 @@
         <v>45086.63334490741</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         <v>45565.40657407408</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>45086</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
         <v>45728.54832175926</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15924,7 +15924,7 @@
         <v>45257.67958333333</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>45018</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>45607.56773148148</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>44720.53898148148</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>44243</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16209,7 +16209,7 @@
         <v>45301.67736111111</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16266,7 +16266,7 @@
         <v>45513.55840277778</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16323,7 +16323,7 @@
         <v>45513.56527777778</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16380,7 +16380,7 @@
         <v>45110.4184375</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>44895.62296296296</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>45415.47848379629</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>44539</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>45308.61152777778</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16665,7 +16665,7 @@
         <v>45299.47513888889</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16722,7 +16722,7 @@
         <v>45391.41976851852</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>45111.48787037037</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
         <v>44553</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>45539.66027777778</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>44964.5115162037</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17007,7 +17007,7 @@
         <v>45481.58048611111</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>44867</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>45096.45247685185</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>45111.48395833333</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>44852</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>45384.66917824074</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17349,7 +17349,7 @@
         <v>45588.65545138889</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17406,7 +17406,7 @@
         <v>44967.45122685185</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17463,7 +17463,7 @@
         <v>45784.74996527778</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17520,7 +17520,7 @@
         <v>45581.57016203704</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17577,7 +17577,7 @@
         <v>45114.55136574074</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>44992</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17696,7 +17696,7 @@
         <v>45463</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>45481.55984953704</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17810,7 +17810,7 @@
         <v>45630.47564814815</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>45257.70313657408</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17924,7 +17924,7 @@
         <v>45539.38744212963</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         <v>44392</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>45539.65212962963</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18100,7 +18100,7 @@
         <v>45266.32614583334</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>45317.40372685185</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18219,7 +18219,7 @@
         <v>45309.59487268519</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18276,7 +18276,7 @@
         <v>45359.44837962963</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         <v>44488.35878472222</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
         <v>44467.83386574074</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18447,7 +18447,7 @@
         <v>45482.52887731481</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>45371.36359953704</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18561,7 +18561,7 @@
         <v>45371.45865740741</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18618,7 +18618,7 @@
         <v>45000.47998842593</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>45359.45038194444</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18732,7 +18732,7 @@
         <v>45786.52996527778</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18789,7 +18789,7 @@
         <v>45552.36759259259</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18846,7 +18846,7 @@
         <v>45098.30535879629</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         <v>44861.52505787037</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>45533.54429398148</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19017,7 +19017,7 @@
         <v>45533.60232638889</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
         <v>45533.60770833334</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19141,7 +19141,7 @@
         <v>45113.56574074074</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19198,7 +19198,7 @@
         <v>45446.36774305555</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19260,7 +19260,7 @@
         <v>45747.42633101852</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19317,7 +19317,7 @@
         <v>45747.42958333333</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19374,7 +19374,7 @@
         <v>45726.44471064815</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19431,7 +19431,7 @@
         <v>45786.52878472222</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         <v>45147.67096064815</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19545,7 +19545,7 @@
         <v>45147.67172453704</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19602,7 +19602,7 @@
         <v>44788</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>45581.57958333333</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>45548</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>45020</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19830,7 +19830,7 @@
         <v>45569.44295138889</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19887,7 +19887,7 @@
         <v>45415.48979166667</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19944,7 +19944,7 @@
         <v>45009</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20001,7 +20001,7 @@
         <v>44375.38789351852</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>45726.62721064815</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20115,7 +20115,7 @@
         <v>45698.69016203703</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20172,7 +20172,7 @@
         <v>44386</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>45111.48225694444</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20286,7 +20286,7 @@
         <v>45111.48636574074</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20343,7 +20343,7 @@
         <v>45526.3865625</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
         <v>45621.46103009259</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>45114.58148148148</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>45243.84869212963</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20576,7 +20576,7 @@
         <v>45460.62172453704</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20633,7 +20633,7 @@
         <v>44427</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         <v>45533.61996527778</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>45791.89865740741</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20809,7 +20809,7 @@
         <v>45632.44886574074</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20866,7 +20866,7 @@
         <v>44949</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20923,7 +20923,7 @@
         <v>45741.37270833334</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20980,7 +20980,7 @@
         <v>45552.36484953704</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>45171.96248842592</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21094,7 +21094,7 @@
         <v>45030.71012731481</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21151,7 +21151,7 @@
         <v>45271.66576388889</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21208,7 +21208,7 @@
         <v>44510.52157407408</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21265,7 +21265,7 @@
         <v>44984</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>44598</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>44938</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21441,7 +21441,7 @@
         <v>45483.82479166667</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
         <v>45498</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21555,7 +21555,7 @@
         <v>45796</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21612,7 +21612,7 @@
         <v>44879</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21669,7 +21669,7 @@
         <v>45582.41200231481</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21726,7 +21726,7 @@
         <v>44585.51060185185</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21783,7 +21783,7 @@
         <v>45572.48293981481</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>45001.43854166667</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21897,7 +21897,7 @@
         <v>45182.78834490741</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21954,7 +21954,7 @@
         <v>45482.54108796296</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22011,7 +22011,7 @@
         <v>45377</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>45485.45778935185</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22125,7 +22125,7 @@
         <v>45671.46746527778</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22182,7 +22182,7 @@
         <v>45618.56787037037</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22239,7 +22239,7 @@
         <v>45467.74417824074</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22296,7 +22296,7 @@
         <v>45086</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22353,7 +22353,7 @@
         <v>44159</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22410,7 +22410,7 @@
         <v>45603.74959490741</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22467,7 +22467,7 @@
         <v>44579.62225694444</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22524,7 +22524,7 @@
         <v>44918.50106481482</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>45632.37459490741</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>45378.32185185186</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>45498.673125</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22752,7 +22752,7 @@
         <v>44893</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22809,7 +22809,7 @@
         <v>45527.68784722222</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22866,7 +22866,7 @@
         <v>44643</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22923,7 +22923,7 @@
         <v>45275.32266203704</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22980,7 +22980,7 @@
         <v>45574.49298611111</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23037,7 +23037,7 @@
         <v>45540.50098379629</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23094,7 +23094,7 @@
         <v>45715.44159722222</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>45328.38755787037</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23208,7 +23208,7 @@
         <v>45713.92412037037</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23265,7 +23265,7 @@
         <v>44851.95016203704</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23322,7 +23322,7 @@
         <v>44992.4255787037</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23379,7 +23379,7 @@
         <v>45071</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23436,7 +23436,7 @@
         <v>45635.66409722222</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23493,7 +23493,7 @@
         <v>45401.53033564815</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23550,7 +23550,7 @@
         <v>44127</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23607,7 +23607,7 @@
         <v>45804.6953587963</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23669,7 +23669,7 @@
         <v>45804.708125</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>45804.39141203704</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23788,7 +23788,7 @@
         <v>45804.67065972222</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23845,7 +23845,7 @@
         <v>44630</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>45804.44519675926</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>44893</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24016,7 +24016,7 @@
         <v>44795</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24073,7 +24073,7 @@
         <v>45168.89298611111</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24130,7 +24130,7 @@
         <v>45805.39247685186</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24187,7 +24187,7 @@
         <v>45699.45671296296</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24244,7 +24244,7 @@
         <v>45052</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24301,7 +24301,7 @@
         <v>44994.40635416667</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24358,7 +24358,7 @@
         <v>45574.35809027778</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24415,7 +24415,7 @@
         <v>45805</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24472,7 +24472,7 @@
         <v>45559.38876157408</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24529,7 +24529,7 @@
         <v>44587</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24586,7 +24586,7 @@
         <v>45755.64450231481</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>45623.95947916667</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24700,7 +24700,7 @@
         <v>45805.52983796296</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24757,7 +24757,7 @@
         <v>44635</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24814,7 +24814,7 @@
         <v>44935</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24871,7 +24871,7 @@
         <v>44603</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24928,7 +24928,7 @@
         <v>44999.86172453704</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>44999.8625</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25042,7 +25042,7 @@
         <v>44595.583125</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25099,7 +25099,7 @@
         <v>44964.50894675926</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25156,7 +25156,7 @@
         <v>45517.8162037037</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>45518.40657407408</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25270,7 +25270,7 @@
         <v>44638.55256944444</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25327,7 +25327,7 @@
         <v>45211.52642361111</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25384,7 +25384,7 @@
         <v>45211.541875</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25441,7 +25441,7 @@
         <v>45650.37370370371</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25498,7 +25498,7 @@
         <v>45666</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25555,7 +25555,7 @@
         <v>45195.58452546296</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25612,7 +25612,7 @@
         <v>45351.6062962963</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25669,7 +25669,7 @@
         <v>45001.59209490741</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25726,7 +25726,7 @@
         <v>44587.48847222222</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25783,7 +25783,7 @@
         <v>45208</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25840,7 +25840,7 @@
         <v>45729.36868055556</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25897,7 +25897,7 @@
         <v>44918</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25954,7 +25954,7 @@
         <v>44959.66407407408</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26011,7 +26011,7 @@
         <v>44966</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>44564.62598379629</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26125,7 +26125,7 @@
         <v>45148</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26182,7 +26182,7 @@
         <v>45148</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26239,7 +26239,7 @@
         <v>45495</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26296,7 +26296,7 @@
         <v>45163.41376157408</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>44600</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>45434.56291666667</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>45026.82216435186</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>45079.87827546296</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>45814.3865625</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
         <v>45814.38221064815</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26700,7 +26700,7 @@
         <v>44910.54231481482</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26757,7 +26757,7 @@
         <v>45567.42011574074</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
         <v>45554.62944444444</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>45254.62489583333</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26933,7 +26933,7 @@
         <v>45818.59261574074</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26995,7 +26995,7 @@
         <v>45113.43921296296</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27052,7 +27052,7 @@
         <v>45818.5862037037</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27114,7 +27114,7 @@
         <v>45818.58993055556</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27176,7 +27176,7 @@
         <v>45818.58769675926</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27238,7 +27238,7 @@
         <v>45818.595625</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27300,7 +27300,7 @@
         <v>45567</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27357,7 +27357,7 @@
         <v>44825.4336574074</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27414,7 +27414,7 @@
         <v>45145</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27471,7 +27471,7 @@
         <v>45128</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27528,7 +27528,7 @@
         <v>45196.57247685185</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         <v>45820.33930555556</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27642,7 +27642,7 @@
         <v>45820.33708333333</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27699,7 +27699,7 @@
         <v>45820.34128472222</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27756,7 +27756,7 @@
         <v>45819.61060185185</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27813,7 +27813,7 @@
         <v>45236</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>44663</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27927,7 +27927,7 @@
         <v>45632.72635416667</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27984,7 +27984,7 @@
         <v>45187</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28041,7 +28041,7 @@
         <v>45187.42854166667</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28098,7 +28098,7 @@
         <v>45707.3793287037</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28155,7 +28155,7 @@
         <v>45736.50743055555</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>44172</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28269,7 +28269,7 @@
         <v>44475</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>45202.4209837963</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28383,7 +28383,7 @@
         <v>45825.5796875</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>45825.58672453704</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>45308.59001157407</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28554,7 +28554,7 @@
         <v>45699.44291666667</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28611,7 +28611,7 @@
         <v>45825.57805555555</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28668,7 +28668,7 @@
         <v>45825.57680555555</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28725,7 +28725,7 @@
         <v>45174</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28782,7 +28782,7 @@
         <v>44943.62954861111</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>44944.73487268519</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28896,7 +28896,7 @@
         <v>45827</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28953,7 +28953,7 @@
         <v>45761.35990740741</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29010,7 +29010,7 @@
         <v>45722.48634259259</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29067,7 +29067,7 @@
         <v>45827</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29124,7 +29124,7 @@
         <v>45719.84378472222</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29181,7 +29181,7 @@
         <v>45394.50028935185</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29238,7 +29238,7 @@
         <v>45831</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>45761.4437962963</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29352,7 +29352,7 @@
         <v>45581.58418981481</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>44867</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>45581.57333333333</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29523,7 +29523,7 @@
         <v>45299.62576388889</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29580,7 +29580,7 @@
         <v>45533.63056712963</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>45588.67070601852</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>45700.68289351852</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>45874.57109953704</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>45832.34540509259</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44784.42528935185</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>45832.46146990741</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>45623.9525462963</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>44790.49523148148</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>45260.4716550926</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30155,7 +30155,7 @@
         <v>45833.64563657407</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>45833.64814814815</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>44820</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>45176.72427083334</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>44693.62822916666</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30445,7 +30445,7 @@
         <v>45875.47454861111</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30502,7 +30502,7 @@
         <v>45875.45716435185</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30559,7 +30559,7 @@
         <v>45834.64667824074</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30621,7 +30621,7 @@
         <v>45569.45017361111</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30678,7 +30678,7 @@
         <v>45245.63574074074</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30735,7 +30735,7 @@
         <v>45280.66769675926</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30792,7 +30792,7 @@
         <v>44956</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30854,7 +30854,7 @@
         <v>45875.42716435185</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30911,7 +30911,7 @@
         <v>45317</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30973,7 +30973,7 @@
         <v>45709.62280092593</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31030,7 +31030,7 @@
         <v>44999.35858796296</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31087,7 +31087,7 @@
         <v>45834.65040509259</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31149,7 +31149,7 @@
         <v>45834.65197916667</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31211,7 +31211,7 @@
         <v>45713.45311342592</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31268,7 +31268,7 @@
         <v>45219.69356481481</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31325,7 +31325,7 @@
         <v>45833.64237268519</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31382,7 +31382,7 @@
         <v>45170</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31439,7 +31439,7 @@
         <v>45735.58024305556</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31496,7 +31496,7 @@
         <v>45835.36229166666</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31558,7 +31558,7 @@
         <v>44746.38834490741</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31615,7 +31615,7 @@
         <v>45379</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31672,7 +31672,7 @@
         <v>45622</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31729,7 +31729,7 @@
         <v>45562.46342592593</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31786,7 +31786,7 @@
         <v>45835.4924537037</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31843,7 +31843,7 @@
         <v>45225.60192129629</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31900,7 +31900,7 @@
         <v>45434.55831018519</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31962,7 +31962,7 @@
         <v>45434.56398148148</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32024,7 +32024,7 @@
         <v>45075.43059027778</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32081,7 +32081,7 @@
         <v>44784.62724537037</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32138,7 +32138,7 @@
         <v>45343.68038194445</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32195,7 +32195,7 @@
         <v>45237.63225694445</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32252,7 +32252,7 @@
         <v>45237.64408564815</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32309,7 +32309,7 @@
         <v>44270.39765046296</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>45121.61318287037</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32433,7 +32433,7 @@
         <v>45835.48862268519</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>45880.38380787037</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32547,7 +32547,7 @@
         <v>45768.65611111111</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32604,7 +32604,7 @@
         <v>45880.51550925926</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32666,7 +32666,7 @@
         <v>45837.77701388889</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>45617.47570601852</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32780,7 +32780,7 @@
         <v>44732.3659837963</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32837,7 +32837,7 @@
         <v>45835.48267361111</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>45835.48445601852</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32951,7 +32951,7 @@
         <v>45835.45099537037</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33008,7 +33008,7 @@
         <v>45837.77916666667</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33065,7 +33065,7 @@
         <v>44981.58834490741</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>45835.44709490741</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33179,7 +33179,7 @@
         <v>45835.44732638889</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>45567</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>44994.42113425926</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         <v>44790.49040509259</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>45323.53744212963</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>45533.55362268518</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>44958.61047453704</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33578,7 +33578,7 @@
         <v>44965</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33635,7 +33635,7 @@
         <v>45763.59436342592</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>45355.54138888889</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>45334.78826388889</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33806,7 +33806,7 @@
         <v>45361.87975694444</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33863,7 +33863,7 @@
         <v>45330</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33920,7 +33920,7 @@
         <v>45330</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33977,7 +33977,7 @@
         <v>44973.43075231482</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34034,7 +34034,7 @@
         <v>44839.4528125</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34091,7 +34091,7 @@
         <v>44340</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34148,7 +34148,7 @@
         <v>45217.47834490741</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34205,7 +34205,7 @@
         <v>45881</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34262,7 +34262,7 @@
         <v>44578.32717592592</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34319,7 +34319,7 @@
         <v>44897</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34376,7 +34376,7 @@
         <v>44977</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34433,7 +34433,7 @@
         <v>45747.43196759259</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34490,7 +34490,7 @@
         <v>44964.44356481481</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34547,7 +34547,7 @@
         <v>45840.59474537037</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34604,7 +34604,7 @@
         <v>45840.59853009259</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34661,7 +34661,7 @@
         <v>45610.59094907407</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34718,7 +34718,7 @@
         <v>44894.49538194444</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34775,7 +34775,7 @@
         <v>44992</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34832,7 +34832,7 @@
         <v>45091.67936342592</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34889,7 +34889,7 @@
         <v>45259.51916666667</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34951,7 +34951,7 @@
         <v>45259.52020833334</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>45734.62017361111</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35070,7 +35070,7 @@
         <v>45020</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35127,7 +35127,7 @@
         <v>45114.49505787037</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35184,7 +35184,7 @@
         <v>45041</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35241,7 +35241,7 @@
         <v>45632.36706018518</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35298,7 +35298,7 @@
         <v>45832.46649305556</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35355,7 +35355,7 @@
         <v>44745.84396990741</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35412,7 +35412,7 @@
         <v>45163.63621527778</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35474,7 +35474,7 @@
         <v>45615.48927083334</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>45349.54434027777</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>45345.83557870371</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>45635.66695601852</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35702,7 +35702,7 @@
         <v>45568.30189814815</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35759,7 +35759,7 @@
         <v>45033.76043981482</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35816,7 +35816,7 @@
         <v>44599</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35873,7 +35873,7 @@
         <v>45699.45392361111</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35930,7 +35930,7 @@
         <v>45154.49831018518</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35987,7 +35987,7 @@
         <v>45201</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36044,7 +36044,7 @@
         <v>45630.35827546296</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>45674.71810185185</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36158,7 +36158,7 @@
         <v>45588.66457175926</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36215,7 +36215,7 @@
         <v>45275.41833333333</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>44176</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36329,7 +36329,7 @@
         <v>45881.59877314815</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36386,7 +36386,7 @@
         <v>45884.50613425926</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36448,7 +36448,7 @@
         <v>45189</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36505,7 +36505,7 @@
         <v>45658.80232638889</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36562,7 +36562,7 @@
         <v>45658.80827546296</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36619,7 +36619,7 @@
         <v>45063.49936342592</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36676,7 +36676,7 @@
         <v>45841.70569444444</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36733,7 +36733,7 @@
         <v>45841.70868055556</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36790,7 +36790,7 @@
         <v>44495</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>44769.45805555556</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>44848.59133101852</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36961,7 +36961,7 @@
         <v>45440.28329861111</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37018,7 +37018,7 @@
         <v>44546</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37075,7 +37075,7 @@
         <v>45224.60075231481</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37137,7 +37137,7 @@
         <v>45646.38200231481</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>44377</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37251,7 +37251,7 @@
         <v>44988</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37308,7 +37308,7 @@
         <v>45764.44931712963</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37370,7 +37370,7 @@
         <v>44790.45876157407</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37427,7 +37427,7 @@
         <v>44270.38002314815</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37489,7 +37489,7 @@
         <v>45121</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37546,7 +37546,7 @@
         <v>44502</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37603,7 +37603,7 @@
         <v>44861</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37660,7 +37660,7 @@
         <v>44879.62173611111</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37717,7 +37717,7 @@
         <v>45147</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37774,7 +37774,7 @@
         <v>44987.54104166666</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37831,7 +37831,7 @@
         <v>45698.53336805556</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37888,7 +37888,7 @@
         <v>44418</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37945,7 +37945,7 @@
         <v>45841.7072337963</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38002,7 +38002,7 @@
         <v>45749.56196759259</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38064,7 +38064,7 @@
         <v>45732.76936342593</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38121,7 +38121,7 @@
         <v>45090.89653935185</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38178,7 +38178,7 @@
         <v>45090.89880787037</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38235,7 +38235,7 @@
         <v>45201.39996527778</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38292,7 +38292,7 @@
         <v>44991.30547453704</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38349,7 +38349,7 @@
         <v>44991</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38406,7 +38406,7 @@
         <v>45113.41633101852</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38463,7 +38463,7 @@
         <v>45238.4328587963</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38520,7 +38520,7 @@
         <v>45063.508125</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38577,7 +38577,7 @@
         <v>45219.40528935185</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38634,7 +38634,7 @@
         <v>45735.56751157407</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38691,7 +38691,7 @@
         <v>44440</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38748,7 +38748,7 @@
         <v>45754.33641203704</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38805,7 +38805,7 @@
         <v>45114.47895833333</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38862,7 +38862,7 @@
         <v>45482.49870370371</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38919,7 +38919,7 @@
         <v>45482.54844907407</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38976,7 +38976,7 @@
         <v>45533.38870370371</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39033,7 +39033,7 @@
         <v>45732.79925925926</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39090,7 +39090,7 @@
         <v>45111.30824074074</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39147,7 +39147,7 @@
         <v>44431.84840277778</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39204,7 +39204,7 @@
         <v>44910.41346064815</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39261,7 +39261,7 @@
         <v>44910</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39318,7 +39318,7 @@
         <v>44598.7384837963</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39375,7 +39375,7 @@
         <v>44931</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39437,7 +39437,7 @@
         <v>45027.59450231482</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39499,7 +39499,7 @@
         <v>45112.33599537037</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39556,7 +39556,7 @@
         <v>44111</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39613,7 +39613,7 @@
         <v>44440.60415509259</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>45029</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>45128.37305555555</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39784,7 +39784,7 @@
         <v>44943.57309027778</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>45481.56722222222</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39898,7 +39898,7 @@
         <v>44900.57393518519</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>44451</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40012,7 +40012,7 @@
         <v>45394.66887731481</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40069,7 +40069,7 @@
         <v>45346.67184027778</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40126,7 +40126,7 @@
         <v>44966</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40183,7 +40183,7 @@
         <v>45054.6750462963</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40240,7 +40240,7 @@
         <v>45820.03976851852</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40297,7 +40297,7 @@
         <v>44903.33363425926</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40354,7 +40354,7 @@
         <v>44857.65989583333</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>44585.50431712963</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40468,7 +40468,7 @@
         <v>44578.62943287037</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40525,7 +40525,7 @@
         <v>45887.68759259259</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40582,7 +40582,7 @@
         <v>44992.34151620371</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40644,7 +40644,7 @@
         <v>44542.90072916666</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40701,7 +40701,7 @@
         <v>44867</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>44879.55940972222</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40815,7 +40815,7 @@
         <v>44903</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40872,7 +40872,7 @@
         <v>44896</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40929,7 +40929,7 @@
         <v>44890</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40986,7 +40986,7 @@
         <v>44453.56578703703</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41043,7 +41043,7 @@
         <v>44588.37998842593</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41100,7 +41100,7 @@
         <v>44588</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41157,7 +41157,7 @@
         <v>45845.42015046296</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41214,7 +41214,7 @@
         <v>45845.43803240741</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41271,7 +41271,7 @@
         <v>44175.39748842592</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41328,7 +41328,7 @@
         <v>44431</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41385,7 +41385,7 @@
         <v>45845.49414351852</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41442,7 +41442,7 @@
         <v>44566</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41499,7 +41499,7 @@
         <v>45361.90282407407</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>45224.6515162037</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41618,7 +41618,7 @@
         <v>45811.45460648148</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>44754</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41732,7 +41732,7 @@
         <v>45106.25025462963</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41789,7 +41789,7 @@
         <v>45743.41148148148</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41846,7 +41846,7 @@
         <v>45100.85270833333</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41903,7 +41903,7 @@
         <v>45261.44914351852</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41960,7 +41960,7 @@
         <v>45415.57682870371</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42017,7 +42017,7 @@
         <v>45048.59699074074</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42074,7 +42074,7 @@
         <v>45503.5658912037</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42131,7 +42131,7 @@
         <v>45847.91280092593</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42188,7 +42188,7 @@
         <v>44517</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42245,7 +42245,7 @@
         <v>45108.703125</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42302,7 +42302,7 @@
         <v>44596</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42359,7 +42359,7 @@
         <v>45110.4275</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42416,7 +42416,7 @@
         <v>44952.35775462963</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42473,7 +42473,7 @@
         <v>45891</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42530,7 +42530,7 @@
         <v>45891.50525462963</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42587,7 +42587,7 @@
         <v>45891.50986111111</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42644,7 +42644,7 @@
         <v>45093.62777777778</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42706,7 +42706,7 @@
         <v>45215.5959375</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42763,7 +42763,7 @@
         <v>44992.62498842592</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42820,7 +42820,7 @@
         <v>45891.50216435185</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42877,7 +42877,7 @@
         <v>45853.87112268519</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42934,7 +42934,7 @@
         <v>45853.87599537037</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42991,7 +42991,7 @@
         <v>45853.88070601852</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43048,7 +43048,7 @@
         <v>44967.44255787037</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43105,7 +43105,7 @@
         <v>45755.44333333334</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43162,7 +43162,7 @@
         <v>44600</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43219,7 +43219,7 @@
         <v>45891</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43276,7 +43276,7 @@
         <v>45187.60813657408</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43333,7 +43333,7 @@
         <v>44237</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43390,7 +43390,7 @@
         <v>45897.63520833333</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43447,7 +43447,7 @@
         <v>45897.88836805556</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43504,7 +43504,7 @@
         <v>45897.64208333333</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43561,7 +43561,7 @@
         <v>44452</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43618,7 +43618,7 @@
         <v>45009.4671875</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43675,7 +43675,7 @@
         <v>45705.74418981482</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43732,7 +43732,7 @@
         <v>44410</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43789,7 +43789,7 @@
         <v>45111</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43846,7 +43846,7 @@
         <v>45898.58861111111</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43903,7 +43903,7 @@
         <v>45897.89737268518</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43960,7 +43960,7 @@
         <v>45897.88706018519</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44017,7 +44017,7 @@
         <v>44909</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44074,7 +44074,7 @@
         <v>45637.66542824074</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44131,7 +44131,7 @@
         <v>45901.63219907408</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44188,7 +44188,7 @@
         <v>45901.6327662037</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44245,7 +44245,7 @@
         <v>45858.66019675926</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44302,7 +44302,7 @@
         <v>45858.60641203704</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44359,7 +44359,7 @@
         <v>44310</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44416,7 +44416,7 @@
         <v>45902.47164351852</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44473,7 +44473,7 @@
         <v>45041.63380787037</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44530,7 +44530,7 @@
         <v>44961</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44587,7 +44587,7 @@
         <v>44916.55414351852</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44644,7 +44644,7 @@
         <v>45903.38800925926</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44701,7 +44701,7 @@
         <v>45300.3794212963</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44758,7 +44758,7 @@
         <v>45245.36174768519</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44815,7 +44815,7 @@
         <v>44999.36081018519</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44872,7 +44872,7 @@
         <v>45495</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44929,7 +44929,7 @@
         <v>45128.9325</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44986,7 +44986,7 @@
         <v>45128.93540509259</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45043,7 +45043,7 @@
         <v>45908.57716435185</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45100,7 +45100,7 @@
         <v>45320.89128472222</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45157,7 +45157,7 @@
         <v>45769</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45214,7 +45214,7 @@
         <v>45867.63094907408</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45271,7 +45271,7 @@
         <v>45867.69346064814</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45328,7 +45328,7 @@
         <v>44613</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>45867.50792824074</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45442,7 +45442,7 @@
         <v>45867.51630787037</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>45867.68625</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45556,7 +45556,7 @@
         <v>45867.56320601852</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45613,7 +45613,7 @@
         <v>45867.64663194444</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45670,7 +45670,7 @@
         <v>44992</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45727,7 +45727,7 @@
         <v>45908</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45784,7 +45784,7 @@
         <v>45869.62276620371</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45841,7 +45841,7 @@
         <v>45908</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45898,7 +45898,7 @@
         <v>45911.47138888889</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45955,7 +45955,7 @@
         <v>45028</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46012,7 +46012,7 @@
         <v>45870.51708333333</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46069,7 +46069,7 @@
         <v>45870.52111111111</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46126,7 +46126,7 @@
         <v>45453.36854166666</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46183,7 +46183,7 @@
         <v>45911.67798611111</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46240,7 +46240,7 @@
         <v>45845</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46297,7 +46297,7 @@
         <v>45870.51958333333</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46354,7 +46354,7 @@
         <v>45870.52005787037</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46411,7 +46411,7 @@
         <v>45870.52142361111</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46468,7 +46468,7 @@
         <v>45211.55472222222</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46530,7 +46530,7 @@
         <v>45639.56185185185</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46587,7 +46587,7 @@
         <v>44540</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46644,7 +46644,7 @@
         <v>45174.31395833333</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46701,7 +46701,7 @@
         <v>45446.36865740741</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46763,7 +46763,7 @@
         <v>44981.64725694444</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46820,7 +46820,7 @@
         <v>45138</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46877,7 +46877,7 @@
         <v>44895.46524305556</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46934,7 +46934,7 @@
         <v>45674.74094907408</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46991,7 +46991,7 @@
         <v>45700.68672453704</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47048,7 +47048,7 @@
         <v>45163</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47105,7 +47105,7 @@
         <v>45453.36067129629</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47162,7 +47162,7 @@
         <v>44963.44769675926</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47219,7 +47219,7 @@
         <v>44944.71386574074</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47276,7 +47276,7 @@
         <v>44944.72100694444</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47333,7 +47333,7 @@
         <v>45698.53725694444</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47390,7 +47390,7 @@
         <v>45250.5278587963</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>44803.59118055556</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47504,7 +47504,7 @@
         <v>45153.32778935185</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47561,7 +47561,7 @@
         <v>45761.39600694444</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47618,7 +47618,7 @@
         <v>45106</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47675,7 +47675,7 @@
         <v>45106.2610300926</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47732,7 +47732,7 @@
         <v>45699.60055555555</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47789,7 +47789,7 @@
         <v>45658.78774305555</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45630.45069444444</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47903,7 +47903,7 @@
         <v>44302</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47960,7 +47960,7 @@
         <v>45224</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48017,7 +48017,7 @@
         <v>45224.64659722222</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48079,7 +48079,7 @@
         <v>45121.5965162037</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48141,7 +48141,7 @@
         <v>45121.59954861111</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48203,7 +48203,7 @@
         <v>45121.6096875</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>45558.44914351852</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48322,7 +48322,7 @@
         <v>44984</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48379,7 +48379,7 @@
         <v>45624.60141203704</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48436,7 +48436,7 @@
         <v>45434.55471064815</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48498,7 +48498,7 @@
         <v>44312</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48555,7 +48555,7 @@
         <v>44984.45895833334</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48612,7 +48612,7 @@
         <v>44984</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48669,7 +48669,7 @@
         <v>45698.52806712963</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48726,7 +48726,7 @@
         <v>45350.53306712963</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48783,7 +48783,7 @@
         <v>45660</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48840,7 +48840,7 @@
         <v>44258</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>45369.62780092593</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>45554.63225694445</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>45722.48915509259</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49068,7 +49068,7 @@
         <v>45635.4874537037</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49125,7 +49125,7 @@
         <v>45545.49508101852</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49182,7 +49182,7 @@
         <v>45569.47494212963</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49239,7 +49239,7 @@
         <v>45070.3665625</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49296,7 +49296,7 @@
         <v>45070</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49353,7 +49353,7 @@
         <v>45215.60199074074</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49410,7 +49410,7 @@
         <v>45720.44217592593</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49467,7 +49467,7 @@
         <v>44991.89657407408</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49524,7 +49524,7 @@
         <v>44994.46908564815</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49581,7 +49581,7 @@
         <v>45149.60917824074</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49638,7 +49638,7 @@
         <v>45169</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49695,7 +49695,7 @@
         <v>45278</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49757,7 +49757,7 @@
         <v>45456.59289351852</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49814,7 +49814,7 @@
         <v>45002</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49871,7 +49871,7 @@
         <v>45174.40454861111</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49928,7 +49928,7 @@
         <v>45533.56108796296</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49985,7 +49985,7 @@
         <v>45533.58302083334</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50047,7 +50047,7 @@
         <v>45705.73300925926</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50104,7 +50104,7 @@
         <v>44965.4815162037</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50161,7 +50161,7 @@
         <v>44875.27736111111</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50218,7 +50218,7 @@
         <v>45171.77335648148</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50275,7 +50275,7 @@
         <v>45475.49018518518</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50332,7 +50332,7 @@
         <v>45061</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50394,7 +50394,7 @@
         <v>44510.60921296296</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50456,7 +50456,7 @@
         <v>45301</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50513,7 +50513,7 @@
         <v>45301.68237268519</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50570,7 +50570,7 @@
         <v>45475.48303240741</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50627,7 +50627,7 @@
         <v>45124</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50684,7 +50684,7 @@
         <v>45446.36482638889</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50746,7 +50746,7 @@
         <v>45759.38987268518</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50803,7 +50803,7 @@
         <v>45530.33202546297</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50860,7 +50860,7 @@
         <v>45128.58414351852</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50917,7 +50917,7 @@
         <v>44588</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>

--- a/Översikt VIMMERBY.xlsx
+++ b/Översikt VIMMERBY.xlsx
@@ -567,7 +567,7 @@
         <v>44811</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
         <v>44811</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44811</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44811</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>45314</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>44939</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>45301.67922453704</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>45755</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>45377.54726851852</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45748</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>45121.60543981481</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>45678.64175925926</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>44245</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>44811</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>45628</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>45742</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>45020</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>44424</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>44426.64793981481</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>44386</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>45786.52827546297</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>45008.60878472222</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>44943</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>45760.34877314815</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>45880.51413194444</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>45072</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>45048</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>45896.86820601852</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>45908</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>44371</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>44403</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>45399.71412037037</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>45125</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>45104</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>45574.42767361111</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>45667</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>45649</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>45821</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>45168</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>45168</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>44236</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>45713</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>45884.50331018519</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>45077</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>45224</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>44377.61104166666</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>44102</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>44130</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>44281.79269675926</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>44270.67071759259</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>44287.33261574074</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>44210</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>44481.47483796296</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>44490.38613425926</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>44447</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>44375.39033564815</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
         <v>44350</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5403,7 +5403,7 @@
         <v>44614</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>44215</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>44670</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         <v>44670</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>44307</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>44350</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5745,7 +5745,7 @@
         <v>44105</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         <v>44225</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>44327.47658564815</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         <v>44509</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>44230.58883101852</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>44480</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         <v>44238</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
         <v>44406</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         <v>44585.51829861111</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>44824.53434027778</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>44418</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>44785.40800925926</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>44826.68010416667</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         <v>44862</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>44578.47597222222</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>44516.59703703703</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>44603</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>44588</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>44404.87505787037</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>44483.58295138889</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>44494</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>44542.8859375</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>44354</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>44512.70245370371</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>44090</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>44790</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>44261</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>44530.38055555556</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>44221.39408564815</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>44588</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>44588</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>44790</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>44790.47628472222</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>44175.3815625</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>44175.40881944444</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>44312</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>44475</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>44385</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>44124.59795138889</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>44237.8550925926</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>44410.71038194445</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8087,7 +8087,7 @@
         <v>44279.33400462963</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>44175</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         <v>44670</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>44365</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>44169</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>44273</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>44301.36048611111</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>44729.28226851852</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>44271.37226851852</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>44340.54472222222</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>44340</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>44774</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>44733</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>44733</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>44371.62743055556</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>44386.40783564815</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>44480</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>44154</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>44245</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>44337</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>44102</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>44463.29439814815</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9346,7 +9346,7 @@
         <v>44588</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>44117</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>44789</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>44377</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>44379</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>44508</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         <v>44091</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>44634.69703703704</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>44480</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>44769.45422453704</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>44340.58002314815</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9983,7 +9983,7 @@
         <v>44644</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10040,7 +10040,7 @@
         <v>44383</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>44092</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10154,7 +10154,7 @@
         <v>44612.86762731482</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>44476</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10268,7 +10268,7 @@
         <v>44418</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>44517</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10382,7 +10382,7 @@
         <v>44854</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         <v>44819</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         <v>44832.67608796297</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         <v>44142</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10610,7 +10610,7 @@
         <v>44305.40046296296</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         <v>44451.8375</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         <v>44823</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>44447</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>44621</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>44172</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>44270</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11014,7 +11014,7 @@
         <v>44341</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11071,7 +11071,7 @@
         <v>44608</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11128,7 +11128,7 @@
         <v>44447.34237268518</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         <v>44384</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>44294</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>44876.48346064815</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>44733.43092592592</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>44790.48503472222</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>44116</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>44854.59157407407</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>44824</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>44369</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>44742</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11755,7 +11755,7 @@
         <v>44620</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11812,7 +11812,7 @@
         <v>44609</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>44480</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
         <v>44284.42348379629</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>44088</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>44088</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12097,7 +12097,7 @@
         <v>44421</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>44186</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
         <v>44089.78633101852</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>44273</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>44203</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>44278.63479166666</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>44266.7240625</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>44525.63913194444</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>44612.86554398148</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>44270.49743055556</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12682,7 +12682,7 @@
         <v>44466.34726851852</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>44866.81100694444</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>44279.64934027778</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
         <v>44662</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12920,7 +12920,7 @@
         <v>44095</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>44470.44232638889</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
         <v>44776</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>44634</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13153,7 +13153,7 @@
         <v>44722.48768518519</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13210,7 +13210,7 @@
         <v>44564</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>44608.50458333334</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13324,7 +13324,7 @@
         <v>44817</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13381,7 +13381,7 @@
         <v>44379</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>44292</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>44284.44574074074</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13562,7 +13562,7 @@
         <v>45483.82834490741</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13619,7 +13619,7 @@
         <v>44636</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13676,7 +13676,7 @@
         <v>44217.79856481482</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13733,7 +13733,7 @@
         <v>45090.38012731481</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>44466.34962962963</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13847,7 +13847,7 @@
         <v>45105</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>44278.54855324074</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13961,7 +13961,7 @@
         <v>44377.49684027778</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14023,7 +14023,7 @@
         <v>44833.60123842592</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>45215.59743055556</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14137,7 +14137,7 @@
         <v>44817.57988425926</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>44789</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14251,7 +14251,7 @@
         <v>44294</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         <v>44294</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14365,7 +14365,7 @@
         <v>44676.85248842592</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14422,7 +14422,7 @@
         <v>45411.47335648148</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14479,7 +14479,7 @@
         <v>44604</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14536,7 +14536,7 @@
         <v>45377.40043981482</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14593,7 +14593,7 @@
         <v>45698.51711805556</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
         <v>45211.43555555555</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14707,7 +14707,7 @@
         <v>44305</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>45097.40524305555</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>45100.4062962963</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14883,7 +14883,7 @@
         <v>45425.57538194444</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14940,7 +14940,7 @@
         <v>45196</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>44607</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>44949</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15116,7 +15116,7 @@
         <v>45121.58699074074</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15178,7 +15178,7 @@
         <v>45569.44684027778</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15235,7 +15235,7 @@
         <v>45090</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         <v>45749.60487268519</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         <v>45232</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>45245.5735300926</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15468,7 +15468,7 @@
         <v>45525.41762731481</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15525,7 +15525,7 @@
         <v>45391.41310185185</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15582,7 +15582,7 @@
         <v>45450.51092592593</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15639,7 +15639,7 @@
         <v>45086.63194444445</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15696,7 +15696,7 @@
         <v>45086.63334490741</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         <v>45565.40657407408</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>45086</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
         <v>45728.54832175926</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15924,7 +15924,7 @@
         <v>45257.67958333333</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>45018</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>45607.56773148148</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>44720.53898148148</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>44243</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16209,7 +16209,7 @@
         <v>45301.67736111111</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16266,7 +16266,7 @@
         <v>45513.55840277778</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16323,7 +16323,7 @@
         <v>45513.56527777778</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16380,7 +16380,7 @@
         <v>45110.4184375</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>44895.62296296296</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>45415.47848379629</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>44539</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>45308.61152777778</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16665,7 +16665,7 @@
         <v>45299.47513888889</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16722,7 +16722,7 @@
         <v>45391.41976851852</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>45111.48787037037</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
         <v>44553</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>45539.66027777778</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>44964.5115162037</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17007,7 +17007,7 @@
         <v>45481.58048611111</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>44867</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>45096.45247685185</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>45111.48395833333</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>44852</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>45384.66917824074</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17349,7 +17349,7 @@
         <v>45588.65545138889</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17406,7 +17406,7 @@
         <v>44967.45122685185</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17463,7 +17463,7 @@
         <v>45784.74996527778</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17520,7 +17520,7 @@
         <v>45581.57016203704</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17577,7 +17577,7 @@
         <v>45114.55136574074</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>44992</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17696,7 +17696,7 @@
         <v>45463</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>45481.55984953704</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17810,7 +17810,7 @@
         <v>45630.47564814815</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>45257.70313657408</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17924,7 +17924,7 @@
         <v>45539.38744212963</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         <v>44392</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>45539.65212962963</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18100,7 +18100,7 @@
         <v>45266.32614583334</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>45317.40372685185</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18219,7 +18219,7 @@
         <v>45309.59487268519</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18276,7 +18276,7 @@
         <v>45359.44837962963</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         <v>44488.35878472222</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
         <v>44467.83386574074</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18447,7 +18447,7 @@
         <v>45482.52887731481</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>45371.36359953704</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18561,7 +18561,7 @@
         <v>45371.45865740741</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18618,7 +18618,7 @@
         <v>45000.47998842593</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>45359.45038194444</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18732,7 +18732,7 @@
         <v>45786.52996527778</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18789,7 +18789,7 @@
         <v>45552.36759259259</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18846,7 +18846,7 @@
         <v>45098.30535879629</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         <v>44861.52505787037</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>45533.54429398148</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19017,7 +19017,7 @@
         <v>45533.60232638889</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
         <v>45533.60770833334</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19141,7 +19141,7 @@
         <v>45113.56574074074</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19198,7 +19198,7 @@
         <v>45446.36774305555</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19260,7 +19260,7 @@
         <v>45747.42633101852</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19317,7 +19317,7 @@
         <v>45747.42958333333</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19374,7 +19374,7 @@
         <v>45726.44471064815</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19431,7 +19431,7 @@
         <v>45786.52878472222</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         <v>45147.67096064815</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19545,7 +19545,7 @@
         <v>45147.67172453704</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19602,7 +19602,7 @@
         <v>44788</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>45581.57958333333</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>45548</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>45020</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19830,7 +19830,7 @@
         <v>45569.44295138889</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19887,7 +19887,7 @@
         <v>45415.48979166667</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19944,7 +19944,7 @@
         <v>45009</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20001,7 +20001,7 @@
         <v>44375.38789351852</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>45726.62721064815</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20115,7 +20115,7 @@
         <v>45698.69016203703</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20172,7 +20172,7 @@
         <v>44386</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>45111.48225694444</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20286,7 +20286,7 @@
         <v>45111.48636574074</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20343,7 +20343,7 @@
         <v>45526.3865625</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
         <v>45621.46103009259</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>45114.58148148148</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>45243.84869212963</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20576,7 +20576,7 @@
         <v>45460.62172453704</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20633,7 +20633,7 @@
         <v>44427</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         <v>45533.61996527778</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>45791.89865740741</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20809,7 +20809,7 @@
         <v>45632.44886574074</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20866,7 +20866,7 @@
         <v>44949</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20923,7 +20923,7 @@
         <v>45741.37270833334</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20980,7 +20980,7 @@
         <v>45552.36484953704</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>45171.96248842592</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21094,7 +21094,7 @@
         <v>45030.71012731481</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21151,7 +21151,7 @@
         <v>45271.66576388889</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21208,7 +21208,7 @@
         <v>44510.52157407408</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21265,7 +21265,7 @@
         <v>44984</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>44598</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>44938</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21441,7 +21441,7 @@
         <v>45483.82479166667</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
         <v>45498</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21555,7 +21555,7 @@
         <v>45796</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21612,7 +21612,7 @@
         <v>44879</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21669,7 +21669,7 @@
         <v>45582.41200231481</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21726,7 +21726,7 @@
         <v>44585.51060185185</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21783,7 +21783,7 @@
         <v>45572.48293981481</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>45001.43854166667</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21897,7 +21897,7 @@
         <v>45182.78834490741</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21954,7 +21954,7 @@
         <v>45482.54108796296</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22011,7 +22011,7 @@
         <v>45377</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>45485.45778935185</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22125,7 +22125,7 @@
         <v>45671.46746527778</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22182,7 +22182,7 @@
         <v>45618.56787037037</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22239,7 +22239,7 @@
         <v>45467.74417824074</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22296,7 +22296,7 @@
         <v>45086</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22353,7 +22353,7 @@
         <v>44159</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22410,7 +22410,7 @@
         <v>45603.74959490741</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22467,7 +22467,7 @@
         <v>44579.62225694444</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22524,7 +22524,7 @@
         <v>44918.50106481482</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>45632.37459490741</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>45378.32185185186</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>45498.673125</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22752,7 +22752,7 @@
         <v>44893</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22809,7 +22809,7 @@
         <v>45527.68784722222</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22866,7 +22866,7 @@
         <v>44643</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22923,7 +22923,7 @@
         <v>45275.32266203704</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22980,7 +22980,7 @@
         <v>45574.49298611111</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23037,7 +23037,7 @@
         <v>45540.50098379629</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23094,7 +23094,7 @@
         <v>45715.44159722222</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>45328.38755787037</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23208,7 +23208,7 @@
         <v>45713.92412037037</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23265,7 +23265,7 @@
         <v>44851.95016203704</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23322,7 +23322,7 @@
         <v>44992.4255787037</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23379,7 +23379,7 @@
         <v>45071</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23436,7 +23436,7 @@
         <v>45635.66409722222</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23493,7 +23493,7 @@
         <v>45401.53033564815</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23550,7 +23550,7 @@
         <v>44127</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23607,7 +23607,7 @@
         <v>45804.6953587963</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23669,7 +23669,7 @@
         <v>45804.708125</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>45804.39141203704</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23788,7 +23788,7 @@
         <v>45804.67065972222</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23845,7 +23845,7 @@
         <v>44630</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>45804.44519675926</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>44893</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24016,7 +24016,7 @@
         <v>44795</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24073,7 +24073,7 @@
         <v>45168.89298611111</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24130,7 +24130,7 @@
         <v>45805.39247685186</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24187,7 +24187,7 @@
         <v>45699.45671296296</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24244,7 +24244,7 @@
         <v>45052</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24301,7 +24301,7 @@
         <v>44994.40635416667</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24358,7 +24358,7 @@
         <v>45574.35809027778</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24415,7 +24415,7 @@
         <v>45805</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24472,7 +24472,7 @@
         <v>45559.38876157408</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24529,7 +24529,7 @@
         <v>44587</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24586,7 +24586,7 @@
         <v>45755.64450231481</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>45623.95947916667</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24700,7 +24700,7 @@
         <v>45805.52983796296</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24757,7 +24757,7 @@
         <v>44635</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24814,7 +24814,7 @@
         <v>44935</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24871,7 +24871,7 @@
         <v>44603</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24928,7 +24928,7 @@
         <v>44999.86172453704</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>44999.8625</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25042,7 +25042,7 @@
         <v>44595.583125</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25099,7 +25099,7 @@
         <v>44964.50894675926</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25156,7 +25156,7 @@
         <v>45517.8162037037</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>45518.40657407408</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25270,7 +25270,7 @@
         <v>44638.55256944444</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25327,7 +25327,7 @@
         <v>45211.52642361111</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25384,7 +25384,7 @@
         <v>45211.541875</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25441,7 +25441,7 @@
         <v>45650.37370370371</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25498,7 +25498,7 @@
         <v>45666</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25555,7 +25555,7 @@
         <v>45195.58452546296</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25612,7 +25612,7 @@
         <v>45351.6062962963</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25669,7 +25669,7 @@
         <v>45001.59209490741</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25726,7 +25726,7 @@
         <v>44587.48847222222</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25783,7 +25783,7 @@
         <v>45208</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25840,7 +25840,7 @@
         <v>45729.36868055556</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25897,7 +25897,7 @@
         <v>44918</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25954,7 +25954,7 @@
         <v>44959.66407407408</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26011,7 +26011,7 @@
         <v>44966</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>44564.62598379629</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26125,7 +26125,7 @@
         <v>45148</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26182,7 +26182,7 @@
         <v>45148</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26239,7 +26239,7 @@
         <v>45495</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26296,7 +26296,7 @@
         <v>45163.41376157408</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>44600</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>45434.56291666667</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>45026.82216435186</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>45079.87827546296</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>45814.3865625</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
         <v>45814.38221064815</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26700,7 +26700,7 @@
         <v>44910.54231481482</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26757,7 +26757,7 @@
         <v>45567.42011574074</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
         <v>45554.62944444444</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>45254.62489583333</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26933,7 +26933,7 @@
         <v>45818.59261574074</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26995,7 +26995,7 @@
         <v>45113.43921296296</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27052,7 +27052,7 @@
         <v>45818.5862037037</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27114,7 +27114,7 @@
         <v>45818.58993055556</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27176,7 +27176,7 @@
         <v>45818.58769675926</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27238,7 +27238,7 @@
         <v>45818.595625</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27300,7 +27300,7 @@
         <v>45567</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27357,7 +27357,7 @@
         <v>44825.4336574074</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27414,7 +27414,7 @@
         <v>45145</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27471,7 +27471,7 @@
         <v>45128</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27528,7 +27528,7 @@
         <v>45196.57247685185</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         <v>45820.33930555556</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27642,7 +27642,7 @@
         <v>45820.33708333333</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27699,7 +27699,7 @@
         <v>45820.34128472222</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27756,7 +27756,7 @@
         <v>45819.61060185185</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27813,7 +27813,7 @@
         <v>45236</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>44663</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27927,7 +27927,7 @@
         <v>45632.72635416667</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27984,7 +27984,7 @@
         <v>45187</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28041,7 +28041,7 @@
         <v>45187.42854166667</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28098,7 +28098,7 @@
         <v>45707.3793287037</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28155,7 +28155,7 @@
         <v>45736.50743055555</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>44172</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28269,7 +28269,7 @@
         <v>44475</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>45202.4209837963</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28383,7 +28383,7 @@
         <v>45825.5796875</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>45825.58672453704</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>45308.59001157407</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28554,7 +28554,7 @@
         <v>45699.44291666667</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28611,7 +28611,7 @@
         <v>45825.57805555555</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28668,7 +28668,7 @@
         <v>45825.57680555555</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28725,7 +28725,7 @@
         <v>45174</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28782,7 +28782,7 @@
         <v>44943.62954861111</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>44944.73487268519</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28896,7 +28896,7 @@
         <v>45827</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28953,7 +28953,7 @@
         <v>45761.35990740741</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29010,7 +29010,7 @@
         <v>45722.48634259259</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29067,7 +29067,7 @@
         <v>45827</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29124,7 +29124,7 @@
         <v>45719.84378472222</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29181,7 +29181,7 @@
         <v>45394.50028935185</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29238,7 +29238,7 @@
         <v>45831</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>45761.4437962963</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29352,7 +29352,7 @@
         <v>45581.58418981481</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>44867</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>45581.57333333333</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29523,7 +29523,7 @@
         <v>45299.62576388889</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29580,7 +29580,7 @@
         <v>45533.63056712963</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>45588.67070601852</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>45700.68289351852</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>45874.57109953704</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>45832.34540509259</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44784.42528935185</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>45832.46146990741</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>45623.9525462963</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>44790.49523148148</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>45260.4716550926</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30155,7 +30155,7 @@
         <v>45833.64563657407</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>45833.64814814815</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>44820</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>45176.72427083334</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>44693.62822916666</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30445,7 +30445,7 @@
         <v>45875.47454861111</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30502,7 +30502,7 @@
         <v>45875.45716435185</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30559,7 +30559,7 @@
         <v>45834.64667824074</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30621,7 +30621,7 @@
         <v>45569.45017361111</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30678,7 +30678,7 @@
         <v>45245.63574074074</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30735,7 +30735,7 @@
         <v>45280.66769675926</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30792,7 +30792,7 @@
         <v>44956</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30854,7 +30854,7 @@
         <v>45875.42716435185</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30911,7 +30911,7 @@
         <v>45317</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30973,7 +30973,7 @@
         <v>45709.62280092593</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31030,7 +31030,7 @@
         <v>44999.35858796296</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31087,7 +31087,7 @@
         <v>45834.65040509259</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31149,7 +31149,7 @@
         <v>45834.65197916667</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31211,7 +31211,7 @@
         <v>45713.45311342592</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31268,7 +31268,7 @@
         <v>45219.69356481481</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31325,7 +31325,7 @@
         <v>45833.64237268519</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31382,7 +31382,7 @@
         <v>45170</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31439,7 +31439,7 @@
         <v>45735.58024305556</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31496,7 +31496,7 @@
         <v>45835.36229166666</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31558,7 +31558,7 @@
         <v>44746.38834490741</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31615,7 +31615,7 @@
         <v>45379</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31672,7 +31672,7 @@
         <v>45622</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31729,7 +31729,7 @@
         <v>45562.46342592593</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31786,7 +31786,7 @@
         <v>45835.4924537037</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31843,7 +31843,7 @@
         <v>45225.60192129629</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31900,7 +31900,7 @@
         <v>45434.55831018519</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31962,7 +31962,7 @@
         <v>45434.56398148148</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32024,7 +32024,7 @@
         <v>45075.43059027778</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32081,7 +32081,7 @@
         <v>44784.62724537037</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32138,7 +32138,7 @@
         <v>45343.68038194445</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32195,7 +32195,7 @@
         <v>45237.63225694445</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32252,7 +32252,7 @@
         <v>45237.64408564815</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32309,7 +32309,7 @@
         <v>44270.39765046296</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>45121.61318287037</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32433,7 +32433,7 @@
         <v>45835.48862268519</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>45880.38380787037</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32547,7 +32547,7 @@
         <v>45768.65611111111</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32604,7 +32604,7 @@
         <v>45880.51550925926</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32666,7 +32666,7 @@
         <v>45837.77701388889</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>45617.47570601852</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32780,7 +32780,7 @@
         <v>44732.3659837963</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32837,7 +32837,7 @@
         <v>45835.48267361111</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>45835.48445601852</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32951,7 +32951,7 @@
         <v>45835.45099537037</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33008,7 +33008,7 @@
         <v>45837.77916666667</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33065,7 +33065,7 @@
         <v>44981.58834490741</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>45835.44709490741</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33179,7 +33179,7 @@
         <v>45835.44732638889</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>45567</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>44994.42113425926</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         <v>44790.49040509259</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>45323.53744212963</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>45533.55362268518</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>44958.61047453704</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33578,7 +33578,7 @@
         <v>44965</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33635,7 +33635,7 @@
         <v>45763.59436342592</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>45355.54138888889</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>45334.78826388889</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33806,7 +33806,7 @@
         <v>45361.87975694444</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33863,7 +33863,7 @@
         <v>45330</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33920,7 +33920,7 @@
         <v>45330</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33977,7 +33977,7 @@
         <v>44973.43075231482</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34034,7 +34034,7 @@
         <v>44839.4528125</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34091,7 +34091,7 @@
         <v>44340</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34148,7 +34148,7 @@
         <v>45217.47834490741</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34205,7 +34205,7 @@
         <v>45881</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34262,7 +34262,7 @@
         <v>44578.32717592592</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34319,7 +34319,7 @@
         <v>44897</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34376,7 +34376,7 @@
         <v>44977</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34433,7 +34433,7 @@
         <v>45747.43196759259</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34490,7 +34490,7 @@
         <v>44964.44356481481</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34547,7 +34547,7 @@
         <v>45840.59474537037</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34604,7 +34604,7 @@
         <v>45840.59853009259</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34661,7 +34661,7 @@
         <v>45610.59094907407</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34718,7 +34718,7 @@
         <v>44894.49538194444</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34775,7 +34775,7 @@
         <v>44992</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34832,7 +34832,7 @@
         <v>45091.67936342592</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34889,7 +34889,7 @@
         <v>45259.51916666667</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34951,7 +34951,7 @@
         <v>45259.52020833334</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>45734.62017361111</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35070,7 +35070,7 @@
         <v>45020</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35127,7 +35127,7 @@
         <v>45114.49505787037</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35184,7 +35184,7 @@
         <v>45041</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35241,7 +35241,7 @@
         <v>45632.36706018518</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35298,7 +35298,7 @@
         <v>45832.46649305556</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35355,7 +35355,7 @@
         <v>44745.84396990741</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35412,7 +35412,7 @@
         <v>45163.63621527778</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35474,7 +35474,7 @@
         <v>45615.48927083334</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>45349.54434027777</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>45345.83557870371</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>45635.66695601852</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35702,7 +35702,7 @@
         <v>45568.30189814815</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35759,7 +35759,7 @@
         <v>45033.76043981482</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35816,7 +35816,7 @@
         <v>44599</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35873,7 +35873,7 @@
         <v>45699.45392361111</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35930,7 +35930,7 @@
         <v>45154.49831018518</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35987,7 +35987,7 @@
         <v>45201</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36044,7 +36044,7 @@
         <v>45630.35827546296</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>45674.71810185185</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36158,7 +36158,7 @@
         <v>45588.66457175926</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36215,7 +36215,7 @@
         <v>45275.41833333333</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>44176</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36329,7 +36329,7 @@
         <v>45881.59877314815</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36386,7 +36386,7 @@
         <v>45884.50613425926</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36448,7 +36448,7 @@
         <v>45189</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36505,7 +36505,7 @@
         <v>45658.80232638889</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36562,7 +36562,7 @@
         <v>45658.80827546296</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36619,7 +36619,7 @@
         <v>45063.49936342592</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36676,7 +36676,7 @@
         <v>45841.70569444444</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36733,7 +36733,7 @@
         <v>45841.70868055556</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36790,7 +36790,7 @@
         <v>44495</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>44769.45805555556</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>44848.59133101852</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36961,7 +36961,7 @@
         <v>45440.28329861111</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37018,7 +37018,7 @@
         <v>44546</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37075,7 +37075,7 @@
         <v>45224.60075231481</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37137,7 +37137,7 @@
         <v>45646.38200231481</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>44377</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37251,7 +37251,7 @@
         <v>44988</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37308,7 +37308,7 @@
         <v>45764.44931712963</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37370,7 +37370,7 @@
         <v>44790.45876157407</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37427,7 +37427,7 @@
         <v>44270.38002314815</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37489,7 +37489,7 @@
         <v>45121</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37546,7 +37546,7 @@
         <v>44502</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37603,7 +37603,7 @@
         <v>44861</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37660,7 +37660,7 @@
         <v>44879.62173611111</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37717,7 +37717,7 @@
         <v>45147</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37774,7 +37774,7 @@
         <v>44987.54104166666</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37831,7 +37831,7 @@
         <v>45698.53336805556</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37888,7 +37888,7 @@
         <v>44418</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37945,7 +37945,7 @@
         <v>45841.7072337963</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38002,7 +38002,7 @@
         <v>45749.56196759259</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38064,7 +38064,7 @@
         <v>45732.76936342593</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38121,7 +38121,7 @@
         <v>45090.89653935185</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38178,7 +38178,7 @@
         <v>45090.89880787037</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38235,7 +38235,7 @@
         <v>45201.39996527778</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38292,7 +38292,7 @@
         <v>44991.30547453704</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38349,7 +38349,7 @@
         <v>44991</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38406,7 +38406,7 @@
         <v>45113.41633101852</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38463,7 +38463,7 @@
         <v>45238.4328587963</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38520,7 +38520,7 @@
         <v>45063.508125</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38577,7 +38577,7 @@
         <v>45219.40528935185</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38634,7 +38634,7 @@
         <v>45735.56751157407</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38691,7 +38691,7 @@
         <v>44440</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38748,7 +38748,7 @@
         <v>45754.33641203704</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38805,7 +38805,7 @@
         <v>45114.47895833333</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38862,7 +38862,7 @@
         <v>45482.49870370371</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38919,7 +38919,7 @@
         <v>45482.54844907407</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38976,7 +38976,7 @@
         <v>45533.38870370371</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39033,7 +39033,7 @@
         <v>45732.79925925926</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39090,7 +39090,7 @@
         <v>45111.30824074074</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39147,7 +39147,7 @@
         <v>44431.84840277778</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39204,7 +39204,7 @@
         <v>44910.41346064815</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39261,7 +39261,7 @@
         <v>44910</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39318,7 +39318,7 @@
         <v>44598.7384837963</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39375,7 +39375,7 @@
         <v>44931</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39437,7 +39437,7 @@
         <v>45027.59450231482</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39499,7 +39499,7 @@
         <v>45112.33599537037</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39556,7 +39556,7 @@
         <v>44111</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39613,7 +39613,7 @@
         <v>44440.60415509259</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>45029</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>45128.37305555555</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39784,7 +39784,7 @@
         <v>44943.57309027778</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>45481.56722222222</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39898,7 +39898,7 @@
         <v>44900.57393518519</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>44451</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40012,7 +40012,7 @@
         <v>45394.66887731481</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40069,7 +40069,7 @@
         <v>45346.67184027778</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40126,7 +40126,7 @@
         <v>44966</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40183,7 +40183,7 @@
         <v>45054.6750462963</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40240,7 +40240,7 @@
         <v>45820.03976851852</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40297,7 +40297,7 @@
         <v>44903.33363425926</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40354,7 +40354,7 @@
         <v>44857.65989583333</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>44585.50431712963</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40468,7 +40468,7 @@
         <v>44578.62943287037</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40525,7 +40525,7 @@
         <v>45887.68759259259</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40582,7 +40582,7 @@
         <v>44992.34151620371</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40644,7 +40644,7 @@
         <v>44542.90072916666</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40701,7 +40701,7 @@
         <v>44867</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>44879.55940972222</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40815,7 +40815,7 @@
         <v>44903</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40872,7 +40872,7 @@
         <v>44896</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40929,7 +40929,7 @@
         <v>44890</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40986,7 +40986,7 @@
         <v>44453.56578703703</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41043,7 +41043,7 @@
         <v>44588.37998842593</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41100,7 +41100,7 @@
         <v>44588</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41157,7 +41157,7 @@
         <v>45845.42015046296</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41214,7 +41214,7 @@
         <v>45845.43803240741</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41271,7 +41271,7 @@
         <v>44175.39748842592</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41328,7 +41328,7 @@
         <v>44431</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41385,7 +41385,7 @@
         <v>45845.49414351852</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41442,7 +41442,7 @@
         <v>44566</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41499,7 +41499,7 @@
         <v>45361.90282407407</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>45224.6515162037</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41618,7 +41618,7 @@
         <v>45811.45460648148</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>44754</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41732,7 +41732,7 @@
         <v>45106.25025462963</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41789,7 +41789,7 @@
         <v>45743.41148148148</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41846,7 +41846,7 @@
         <v>45100.85270833333</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41903,7 +41903,7 @@
         <v>45261.44914351852</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41960,7 +41960,7 @@
         <v>45415.57682870371</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42017,7 +42017,7 @@
         <v>45048.59699074074</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42074,7 +42074,7 @@
         <v>45503.5658912037</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42131,7 +42131,7 @@
         <v>45847.91280092593</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42188,7 +42188,7 @@
         <v>44517</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42245,7 +42245,7 @@
         <v>45108.703125</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42302,7 +42302,7 @@
         <v>44596</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42359,7 +42359,7 @@
         <v>45110.4275</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42416,7 +42416,7 @@
         <v>44952.35775462963</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42473,7 +42473,7 @@
         <v>45891</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42530,7 +42530,7 @@
         <v>45891.50525462963</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42587,7 +42587,7 @@
         <v>45891.50986111111</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42644,7 +42644,7 @@
         <v>45093.62777777778</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42706,7 +42706,7 @@
         <v>45215.5959375</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42763,7 +42763,7 @@
         <v>44992.62498842592</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42820,7 +42820,7 @@
         <v>45891.50216435185</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42877,7 +42877,7 @@
         <v>45853.87112268519</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42934,7 +42934,7 @@
         <v>45853.87599537037</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42991,7 +42991,7 @@
         <v>45853.88070601852</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43048,7 +43048,7 @@
         <v>44967.44255787037</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43105,7 +43105,7 @@
         <v>45755.44333333334</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43162,7 +43162,7 @@
         <v>44600</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43219,7 +43219,7 @@
         <v>45891</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43276,7 +43276,7 @@
         <v>45187.60813657408</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43333,7 +43333,7 @@
         <v>44237</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43390,7 +43390,7 @@
         <v>45897.63520833333</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43447,7 +43447,7 @@
         <v>45897.88836805556</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43504,7 +43504,7 @@
         <v>45897.64208333333</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43561,7 +43561,7 @@
         <v>44452</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43618,7 +43618,7 @@
         <v>45009.4671875</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43675,7 +43675,7 @@
         <v>45705.74418981482</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43732,7 +43732,7 @@
         <v>44410</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43789,7 +43789,7 @@
         <v>45111</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43846,7 +43846,7 @@
         <v>45898.58861111111</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43903,7 +43903,7 @@
         <v>45897.89737268518</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43960,7 +43960,7 @@
         <v>45897.88706018519</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44017,7 +44017,7 @@
         <v>44909</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44074,7 +44074,7 @@
         <v>45637.66542824074</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44131,7 +44131,7 @@
         <v>45901.63219907408</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44188,7 +44188,7 @@
         <v>45901.6327662037</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44245,7 +44245,7 @@
         <v>45858.66019675926</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44302,7 +44302,7 @@
         <v>45858.60641203704</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44359,7 +44359,7 @@
         <v>44310</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44416,7 +44416,7 @@
         <v>45902.47164351852</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44473,7 +44473,7 @@
         <v>45041.63380787037</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44530,7 +44530,7 @@
         <v>44961</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44587,7 +44587,7 @@
         <v>44916.55414351852</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44644,7 +44644,7 @@
         <v>45903.38800925926</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44701,7 +44701,7 @@
         <v>45300.3794212963</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44758,7 +44758,7 @@
         <v>45245.36174768519</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44815,7 +44815,7 @@
         <v>44999.36081018519</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44872,7 +44872,7 @@
         <v>45495</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44929,7 +44929,7 @@
         <v>45128.9325</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44986,7 +44986,7 @@
         <v>45128.93540509259</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45043,7 +45043,7 @@
         <v>45908.57716435185</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45100,7 +45100,7 @@
         <v>45320.89128472222</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45157,7 +45157,7 @@
         <v>45769</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45214,7 +45214,7 @@
         <v>45867.63094907408</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45271,7 +45271,7 @@
         <v>45867.69346064814</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45328,7 +45328,7 @@
         <v>44613</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>45867.50792824074</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45442,7 +45442,7 @@
         <v>45867.51630787037</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>45867.68625</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45556,7 +45556,7 @@
         <v>45867.56320601852</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45613,7 +45613,7 @@
         <v>45867.64663194444</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45670,7 +45670,7 @@
         <v>44992</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45727,7 +45727,7 @@
         <v>45908</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45784,7 +45784,7 @@
         <v>45869.62276620371</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45841,7 +45841,7 @@
         <v>45908</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45898,7 +45898,7 @@
         <v>45911.47138888889</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45955,7 +45955,7 @@
         <v>45028</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46012,7 +46012,7 @@
         <v>45870.51708333333</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46069,7 +46069,7 @@
         <v>45870.52111111111</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46126,7 +46126,7 @@
         <v>45453.36854166666</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46183,7 +46183,7 @@
         <v>45911.67798611111</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46240,7 +46240,7 @@
         <v>45845</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46297,7 +46297,7 @@
         <v>45870.51958333333</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46354,7 +46354,7 @@
         <v>45870.52005787037</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46411,7 +46411,7 @@
         <v>45870.52142361111</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46468,7 +46468,7 @@
         <v>45211.55472222222</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46530,7 +46530,7 @@
         <v>45639.56185185185</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46587,7 +46587,7 @@
         <v>44540</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46644,7 +46644,7 @@
         <v>45174.31395833333</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46701,7 +46701,7 @@
         <v>45446.36865740741</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46763,7 +46763,7 @@
         <v>44981.64725694444</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46820,7 +46820,7 @@
         <v>45138</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46877,7 +46877,7 @@
         <v>44895.46524305556</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46934,7 +46934,7 @@
         <v>45674.74094907408</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46991,7 +46991,7 @@
         <v>45700.68672453704</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47048,7 +47048,7 @@
         <v>45163</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47105,7 +47105,7 @@
         <v>45453.36067129629</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47162,7 +47162,7 @@
         <v>44963.44769675926</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47219,7 +47219,7 @@
         <v>44944.71386574074</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47276,7 +47276,7 @@
         <v>44944.72100694444</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47333,7 +47333,7 @@
         <v>45698.53725694444</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47390,7 +47390,7 @@
         <v>45250.5278587963</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>44803.59118055556</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47504,7 +47504,7 @@
         <v>45153.32778935185</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47561,7 +47561,7 @@
         <v>45761.39600694444</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47618,7 +47618,7 @@
         <v>45106</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47675,7 +47675,7 @@
         <v>45106.2610300926</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47732,7 +47732,7 @@
         <v>45699.60055555555</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47789,7 +47789,7 @@
         <v>45658.78774305555</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45630.45069444444</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47903,7 +47903,7 @@
         <v>44302</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47960,7 +47960,7 @@
         <v>45224</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48017,7 +48017,7 @@
         <v>45224.64659722222</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48079,7 +48079,7 @@
         <v>45121.5965162037</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48141,7 +48141,7 @@
         <v>45121.59954861111</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48203,7 +48203,7 @@
         <v>45121.6096875</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>45558.44914351852</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48322,7 +48322,7 @@
         <v>44984</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48379,7 +48379,7 @@
         <v>45624.60141203704</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48436,7 +48436,7 @@
         <v>45434.55471064815</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48498,7 +48498,7 @@
         <v>44312</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48555,7 +48555,7 @@
         <v>44984.45895833334</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48612,7 +48612,7 @@
         <v>44984</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48669,7 +48669,7 @@
         <v>45698.52806712963</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48726,7 +48726,7 @@
         <v>45350.53306712963</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48783,7 +48783,7 @@
         <v>45660</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48840,7 +48840,7 @@
         <v>44258</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>45369.62780092593</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>45554.63225694445</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>45722.48915509259</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49068,7 +49068,7 @@
         <v>45635.4874537037</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49125,7 +49125,7 @@
         <v>45545.49508101852</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49182,7 +49182,7 @@
         <v>45569.47494212963</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49239,7 +49239,7 @@
         <v>45070.3665625</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49296,7 +49296,7 @@
         <v>45070</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49353,7 +49353,7 @@
         <v>45215.60199074074</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49410,7 +49410,7 @@
         <v>45720.44217592593</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49467,7 +49467,7 @@
         <v>44991.89657407408</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49524,7 +49524,7 @@
         <v>44994.46908564815</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49581,7 +49581,7 @@
         <v>45149.60917824074</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49638,7 +49638,7 @@
         <v>45169</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49695,7 +49695,7 @@
         <v>45278</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49757,7 +49757,7 @@
         <v>45456.59289351852</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49814,7 +49814,7 @@
         <v>45002</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49871,7 +49871,7 @@
         <v>45174.40454861111</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49928,7 +49928,7 @@
         <v>45533.56108796296</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49985,7 +49985,7 @@
         <v>45533.58302083334</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50047,7 +50047,7 @@
         <v>45705.73300925926</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50104,7 +50104,7 @@
         <v>44965.4815162037</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50161,7 +50161,7 @@
         <v>44875.27736111111</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50218,7 +50218,7 @@
         <v>45171.77335648148</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50275,7 +50275,7 @@
         <v>45475.49018518518</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50332,7 +50332,7 @@
         <v>45061</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50394,7 +50394,7 @@
         <v>44510.60921296296</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50456,7 +50456,7 @@
         <v>45301</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50513,7 +50513,7 @@
         <v>45301.68237268519</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50570,7 +50570,7 @@
         <v>45475.48303240741</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50627,7 +50627,7 @@
         <v>45124</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50684,7 +50684,7 @@
         <v>45446.36482638889</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50746,7 +50746,7 @@
         <v>45759.38987268518</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50803,7 +50803,7 @@
         <v>45530.33202546297</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50860,7 +50860,7 @@
         <v>45128.58414351852</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50917,7 +50917,7 @@
         <v>44588</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>

--- a/Översikt VIMMERBY.xlsx
+++ b/Översikt VIMMERBY.xlsx
@@ -567,7 +567,7 @@
         <v>44811</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
         <v>44811</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44811</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44811</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>45314</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>44939</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>45301.67922453704</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>45377.54726851852</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>45755</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45121.60543981481</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>45678.64175925926</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>45748</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>44245</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>44811</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>45020</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>45742</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>45628</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>45880.51413194444</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>44424</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>44426.64793981481</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>44386</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>45786.52827546297</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>44943</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>45072</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>45008.60878472222</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>45896.86820601852</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>45760.34877314815</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         <v>45048</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>45908</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>44371</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>45713</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
         <v>45104</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>45224</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45667</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>44403</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>45821</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>45168</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>45168</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>44377.61104166666</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>45649</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>45077</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>45884.50331018519</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         <v>45574.42767361111</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>45125</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>45399.71412037037</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>44236</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         <v>44102</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>44130</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>44287.33261574074</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>44281.79269675926</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>44270.67071759259</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>44210</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>44481.47483796296</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>44490.38613425926</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>44447</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>44375.39033564815</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>44350</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>44614</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>44215</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>44670</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>44670</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>44307</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>44105</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
         <v>44350</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>44225</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>44327.47658564815</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>44509</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>44406</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>44230.58883101852</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         <v>44480</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>44238</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         <v>44585.51829861111</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>44824.53434027778</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>44418</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>44785.40800925926</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>44578.47597222222</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
         <v>44516.59703703703</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>44826.68010416667</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>44603</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>44588</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6720,7 +6720,7 @@
         <v>44862</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         <v>44404.87505787037</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>44483.58295138889</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         <v>44494</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>44354</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         <v>44542.8859375</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         <v>44512.70245370371</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         <v>44790</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>44221.39408564815</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
         <v>44530.38055555556</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>44261</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7347,7 +7347,7 @@
         <v>44588</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>44588</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         <v>44790</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>44790.47628472222</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7575,7 +7575,7 @@
         <v>44175.3815625</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>44175.40881944444</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         <v>44312</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v>44475</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>44385</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>44124.59795138889</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         <v>44237.8550925926</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>44410.71038194445</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>44279.33400462963</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>44175</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>44670</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>44365</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>44169</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8321,7 +8321,7 @@
         <v>44273</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>44301.36048611111</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>44729.28226851852</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>44271.37226851852</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>44340.54472222222</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>44340</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>44774</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>44733</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>44733</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>44154</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         <v>44371.62743055556</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         <v>44386.40783564815</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>44480</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>44245</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
         <v>44337</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9176,7 +9176,7 @@
         <v>44102</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         <v>44463.29439814815</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9290,7 +9290,7 @@
         <v>44588</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>44117</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>44789</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         <v>44377</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>44379</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>44508</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>44634.69703703704</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         <v>44480</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         <v>44769.45422453704</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>44340.58002314815</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         <v>44142</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>44612.86762731482</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>44383</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>44476</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>44305.40046296296</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>44418</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>44447</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
         <v>44517</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10331,7 +10331,7 @@
         <v>44854</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         <v>44819</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10445,7 +10445,7 @@
         <v>44824</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v>44369</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         <v>44742</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
         <v>44451.8375</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>44823</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>44270</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>44341</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
         <v>44608</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
         <v>44447.34237268518</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10958,7 +10958,7 @@
         <v>44384</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
         <v>44790.48503472222</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         <v>44294</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11129,7 +11129,7 @@
         <v>44217.79856481482</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>44854.59157407407</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>44116</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>44644</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>44620</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>44480</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>44203</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>44525.63913194444</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>44279.64934027778</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>44662</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>44564</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>44266.7240625</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11823,7 +11823,7 @@
         <v>44375.38789351852</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11880,7 +11880,7 @@
         <v>44379</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>44284.44574074074</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         <v>44270.49743055556</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>44386</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>44427</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>44636</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>44817.57988425926</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>44722.48768518519</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>44294</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>44294</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>44676.85248842592</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>44851.95016203704</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>44604</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>44305</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>44431</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>45114.55136574074</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>45624.60141203704</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>45617.47570601852</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12916,7 +12916,7 @@
         <v>45071</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12973,7 +12973,7 @@
         <v>45763.59436342592</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>44410</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>45637.66542824074</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13144,7 +13144,7 @@
         <v>45411.47335648148</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>44607</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>44991.89657407408</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         <v>45639.56185185185</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13372,7 +13372,7 @@
         <v>45481.58048611111</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>45111.48787037037</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>45153.32778935185</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13543,7 +13543,7 @@
         <v>45391.41976851852</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>44879.55940972222</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>45764.44931712963</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>45054.6750462963</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13776,7 +13776,7 @@
         <v>44903</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>44991.30547453704</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>44991</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>45635.66695601852</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>45211.541875</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>44890</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14118,7 +14118,7 @@
         <v>44278.54855324074</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>45278</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>44832.67608796297</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>45029</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14351,7 +14351,7 @@
         <v>45735.56751157407</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14408,7 +14408,7 @@
         <v>45048.59699074074</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14465,7 +14465,7 @@
         <v>45588.65545138889</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>44981.58834490741</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>45699.45671296296</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>45086</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14693,7 +14693,7 @@
         <v>45128</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14750,7 +14750,7 @@
         <v>45728.54832175926</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>44693.62822916666</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
         <v>45121.5965162037</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>45121.59954861111</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>45121.6096875</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15055,7 +15055,7 @@
         <v>44635</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>45261.44914351852</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>44910.54231481482</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>45346.67184027778</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15283,7 +15283,7 @@
         <v>45732.79925925926</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15340,7 +15340,7 @@
         <v>45343.68038194445</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15397,7 +15397,7 @@
         <v>45581.57958333333</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15454,7 +15454,7 @@
         <v>45539.65212962963</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15511,7 +15511,7 @@
         <v>45147.67096064815</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
         <v>45301.67736111111</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15625,7 +15625,7 @@
         <v>45610.59094907407</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>44546</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15739,7 +15739,7 @@
         <v>45768.65611111111</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>44377</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15853,7 +15853,7 @@
         <v>44992</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>45786.52996527778</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15967,7 +15967,7 @@
         <v>45786.52878472222</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16024,7 +16024,7 @@
         <v>45369.62780092593</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16081,7 +16081,7 @@
         <v>45052</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16138,7 +16138,7 @@
         <v>44621</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16195,7 +16195,7 @@
         <v>45463</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16252,7 +16252,7 @@
         <v>44377.49684027778</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16314,7 +16314,7 @@
         <v>45526.3865625</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16376,7 +16376,7 @@
         <v>45755.64450231481</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16433,7 +16433,7 @@
         <v>45518.40657407408</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>44172</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16547,7 +16547,7 @@
         <v>45741.37270833334</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>44237</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>45394.66887731481</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16718,7 +16718,7 @@
         <v>45299.62576388889</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16775,7 +16775,7 @@
         <v>45623.9525462963</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>45453.36067129629</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>45630.47564814815</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16946,7 +16946,7 @@
         <v>45020</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17003,7 +17003,7 @@
         <v>45622</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>45574.35809027778</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>44992.62498842592</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17174,7 +17174,7 @@
         <v>44302</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17231,7 +17231,7 @@
         <v>45588.66457175926</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17288,7 +17288,7 @@
         <v>45533.61996527778</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17350,7 +17350,7 @@
         <v>44588</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17407,7 +17407,7 @@
         <v>44564.62598379629</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>45552.36759259259</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>45698.69016203703</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17578,7 +17578,7 @@
         <v>45582.41200231481</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>45607.56773148148</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17692,7 +17692,7 @@
         <v>45674.71810185185</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17749,7 +17749,7 @@
         <v>45726.62721064815</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17806,7 +17806,7 @@
         <v>44876.48346064815</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
         <v>44733.43092592592</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>45030.71012731481</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         <v>45736.50743055555</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18034,7 +18034,7 @@
         <v>44833.60123842592</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>45434.55831018519</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18153,7 +18153,7 @@
         <v>45434.56398148148</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18215,7 +18215,7 @@
         <v>45345.83557870371</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>44270.39765046296</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18334,7 +18334,7 @@
         <v>45224.64659722222</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
         <v>44897</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>44609</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>45761.39600694444</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>44284.42348379629</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>45498</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18681,7 +18681,7 @@
         <v>44720.53898148148</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>44421</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18795,7 +18795,7 @@
         <v>44186</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18852,7 +18852,7 @@
         <v>45539.38744212963</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>44273</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>45791.89865740741</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19023,7 +19023,7 @@
         <v>45009.4671875</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>44966</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19137,7 +19137,7 @@
         <v>45482.49870370371</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19194,7 +19194,7 @@
         <v>44243</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19251,7 +19251,7 @@
         <v>44278.63479166666</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>45237.63225694445</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>45237.64408564815</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>45533.63056712963</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19489,7 +19489,7 @@
         <v>44992</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19546,7 +19546,7 @@
         <v>44999.86172453704</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>44999.8625</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>45148</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>44453.56578703703</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19774,7 +19774,7 @@
         <v>44612.86554398148</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19831,7 +19831,7 @@
         <v>44466.34726851852</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>45796</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19945,7 +19945,7 @@
         <v>44866.81100694444</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>44470.44232638889</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>45581.57016203704</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>45581.58418981481</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>44776</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>45097.40524305555</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>45495</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>45618.56787037037</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>45699.45392361111</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>44127</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20525,7 +20525,7 @@
         <v>44634</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20582,7 +20582,7 @@
         <v>45259.51916666667</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>45259.52020833334</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20706,7 +20706,7 @@
         <v>45562.46342592593</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20763,7 +20763,7 @@
         <v>44931</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>45749.56196759259</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20887,7 +20887,7 @@
         <v>45086</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>44517</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21001,7 +21001,7 @@
         <v>45533.38870370371</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21058,7 +21058,7 @@
         <v>44992</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>45658.78774305555</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21177,7 +21177,7 @@
         <v>45121.61318287037</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21239,7 +21239,7 @@
         <v>45275.32266203704</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21296,7 +21296,7 @@
         <v>44965.4815162037</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21353,7 +21353,7 @@
         <v>45328.38755787037</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21410,7 +21410,7 @@
         <v>44746.38834490741</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         <v>45558.44914351852</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21524,7 +21524,7 @@
         <v>44598</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21581,7 +21581,7 @@
         <v>45309.59487268519</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21638,7 +21638,7 @@
         <v>44608.50458333334</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21695,7 +21695,7 @@
         <v>44817</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21752,7 +21752,7 @@
         <v>44861</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21809,7 +21809,7 @@
         <v>45300.3794212963</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21866,7 +21866,7 @@
         <v>45527.68784722222</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21923,7 +21923,7 @@
         <v>45254.62489583333</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21985,7 +21985,7 @@
         <v>45350.53306712963</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>45079.87827546296</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
         <v>45063.49936342592</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>45603.74959490741</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22213,7 +22213,7 @@
         <v>44579.62225694444</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22270,7 +22270,7 @@
         <v>45715.44159722222</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22327,7 +22327,7 @@
         <v>44992.4255787037</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22384,7 +22384,7 @@
         <v>44495</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22441,7 +22441,7 @@
         <v>45090.89653935185</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22498,7 +22498,7 @@
         <v>45090.89880787037</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22555,7 +22555,7 @@
         <v>44638.55256944444</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22612,7 +22612,7 @@
         <v>44600</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22669,7 +22669,7 @@
         <v>45485.45778935185</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22726,7 +22726,7 @@
         <v>45574.49298611111</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22783,7 +22783,7 @@
         <v>45401.53033564815</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22840,7 +22840,7 @@
         <v>44451</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22897,7 +22897,7 @@
         <v>44292</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>44588.37998842593</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>44588</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>45145</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>45635.66409722222</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>45187.60813657408</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>45804.39141203704</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>45804.6953587963</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
         <v>45245.5735300926</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23420,7 +23420,7 @@
         <v>45415.47848379629</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23477,7 +23477,7 @@
         <v>45804.708125</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>44981.64725694444</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23596,7 +23596,7 @@
         <v>45163.41376157408</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23653,7 +23653,7 @@
         <v>45632.72635416667</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23710,7 +23710,7 @@
         <v>45805.39247685186</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
         <v>45108.703125</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23824,7 +23824,7 @@
         <v>45621.46103009259</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23881,7 +23881,7 @@
         <v>44510.52157407408</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23938,7 +23938,7 @@
         <v>44553</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23995,7 +23995,7 @@
         <v>45805.52983796296</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24052,7 +24052,7 @@
         <v>45804.44519675926</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24109,7 +24109,7 @@
         <v>45805</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>44861.52505787037</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>45308.61152777778</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24280,7 +24280,7 @@
         <v>44418</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
         <v>45217.47834490741</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24394,7 +24394,7 @@
         <v>44566</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24451,7 +24451,7 @@
         <v>44488.35878472222</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24508,7 +24508,7 @@
         <v>44918</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24565,7 +24565,7 @@
         <v>45063.508125</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24622,7 +24622,7 @@
         <v>44895.62296296296</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24679,7 +24679,7 @@
         <v>44452</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24736,7 +24736,7 @@
         <v>45450.51092592593</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24793,7 +24793,7 @@
         <v>45009</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24850,7 +24850,7 @@
         <v>45379</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24907,7 +24907,7 @@
         <v>45163</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24964,7 +24964,7 @@
         <v>44988</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25021,7 +25021,7 @@
         <v>45275.41833333333</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25078,7 +25078,7 @@
         <v>45168.89298611111</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         <v>45719.84378472222</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25192,7 +25192,7 @@
         <v>45187</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25249,7 +25249,7 @@
         <v>44754</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25306,7 +25306,7 @@
         <v>44820</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25363,7 +25363,7 @@
         <v>45552.36484953704</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>45460.62172453704</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25477,7 +25477,7 @@
         <v>44769.45805555556</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25534,7 +25534,7 @@
         <v>45215.5959375</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25591,7 +25591,7 @@
         <v>45215.59743055556</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25648,7 +25648,7 @@
         <v>45128.58414351852</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25705,7 +25705,7 @@
         <v>45351.6062962963</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25762,7 +25762,7 @@
         <v>45171.96248842592</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25819,7 +25819,7 @@
         <v>45650.37370370371</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25876,7 +25876,7 @@
         <v>44613</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25933,7 +25933,7 @@
         <v>45128.37305555555</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25990,7 +25990,7 @@
         <v>45189</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26047,7 +26047,7 @@
         <v>45674.74094907408</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26104,7 +26104,7 @@
         <v>45540.50098379629</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26161,7 +26161,7 @@
         <v>45539.66027777778</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26218,7 +26218,7 @@
         <v>45565.40657407408</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26275,7 +26275,7 @@
         <v>45425.57538194444</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26332,7 +26332,7 @@
         <v>45482.54108796296</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26389,7 +26389,7 @@
         <v>45814.38221064815</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26446,7 +26446,7 @@
         <v>45814.3865625</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26503,7 +26503,7 @@
         <v>45818.58993055556</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26565,7 +26565,7 @@
         <v>45195.58452546296</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26622,7 +26622,7 @@
         <v>45818.58769675926</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26684,7 +26684,7 @@
         <v>45026.82216435186</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26741,7 +26741,7 @@
         <v>45818.595625</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26803,7 +26803,7 @@
         <v>45818.59261574074</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>45475.48303240741</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         <v>45735.58024305556</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26979,7 +26979,7 @@
         <v>45818.5862037037</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
         <v>45819.61060185185</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>45232</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27155,7 +27155,7 @@
         <v>45266.32614583334</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27212,7 +27212,7 @@
         <v>45041.63380787037</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27269,7 +27269,7 @@
         <v>45111.48395833333</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27326,7 +27326,7 @@
         <v>44994.40635416667</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27383,7 +27383,7 @@
         <v>44440</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27440,7 +27440,7 @@
         <v>44175.39748842592</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27497,7 +27497,7 @@
         <v>45002</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27554,7 +27554,7 @@
         <v>45033.76043981482</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27611,7 +27611,7 @@
         <v>45196.57247685185</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         <v>45554.62944444444</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27725,7 +27725,7 @@
         <v>45482.54844907407</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27782,7 +27782,7 @@
         <v>44867</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27839,7 +27839,7 @@
         <v>45632.37459490741</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>44803.59118055556</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27953,7 +27953,7 @@
         <v>45567.42011574074</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28010,7 +28010,7 @@
         <v>44587.48847222222</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28067,7 +28067,7 @@
         <v>45110.4275</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28124,7 +28124,7 @@
         <v>45820.33708333333</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>45820.34128472222</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28238,7 +28238,7 @@
         <v>45503.5658912037</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28295,7 +28295,7 @@
         <v>44956</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28357,7 +28357,7 @@
         <v>44270.38002314815</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28419,7 +28419,7 @@
         <v>44596</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>45236</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28533,7 +28533,7 @@
         <v>45121</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28590,7 +28590,7 @@
         <v>44967.44255787037</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28647,7 +28647,7 @@
         <v>44903.33363425926</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28704,7 +28704,7 @@
         <v>45174.31395833333</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28761,7 +28761,7 @@
         <v>44943.57309027778</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28818,7 +28818,7 @@
         <v>45113.41633101852</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28875,7 +28875,7 @@
         <v>45666</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28932,7 +28932,7 @@
         <v>45317.40372685185</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28994,7 +28994,7 @@
         <v>44857.65989583333</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29051,7 +29051,7 @@
         <v>44965</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29108,7 +29108,7 @@
         <v>45359.44837962963</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29165,7 +29165,7 @@
         <v>44918.50106481482</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29222,7 +29222,7 @@
         <v>44944.71386574074</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29279,7 +29279,7 @@
         <v>44944.72100694444</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29336,7 +29336,7 @@
         <v>45467.74417824074</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29393,7 +29393,7 @@
         <v>45446.36482638889</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29455,7 +29455,7 @@
         <v>44312</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29512,7 +29512,7 @@
         <v>45000.47998842593</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>45027.59450231482</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29631,7 +29631,7 @@
         <v>45440.28329861111</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29688,7 +29688,7 @@
         <v>45224.6515162037</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29750,7 +29750,7 @@
         <v>45495</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29807,7 +29807,7 @@
         <v>45554.63225694445</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29864,7 +29864,7 @@
         <v>45820.33930555556</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29921,7 +29921,7 @@
         <v>45377</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29978,7 +29978,7 @@
         <v>45257.67958333333</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30035,7 +30035,7 @@
         <v>45106.25025462963</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30092,7 +30092,7 @@
         <v>45114.47895833333</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30149,7 +30149,7 @@
         <v>44595.583125</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30206,7 +30206,7 @@
         <v>44999.35858796296</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30263,7 +30263,7 @@
         <v>45301</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30320,7 +30320,7 @@
         <v>44789</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30377,7 +30377,7 @@
         <v>45349.54434027777</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30434,7 +30434,7 @@
         <v>44958.61047453704</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30491,7 +30491,7 @@
         <v>45334.78826388889</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30548,7 +30548,7 @@
         <v>45219.40528935185</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30605,7 +30605,7 @@
         <v>45114.58148148148</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30662,7 +30662,7 @@
         <v>44600</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30719,7 +30719,7 @@
         <v>45825.57805555555</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30776,7 +30776,7 @@
         <v>45581.57333333333</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30833,7 +30833,7 @@
         <v>44663</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30890,7 +30890,7 @@
         <v>45567</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30947,7 +30947,7 @@
         <v>45623.95947916667</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31004,7 +31004,7 @@
         <v>45041</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31061,7 +31061,7 @@
         <v>45359.45038194444</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31118,7 +31118,7 @@
         <v>44895.46524305556</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31175,7 +31175,7 @@
         <v>44587</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31232,7 +31232,7 @@
         <v>45434.55471064815</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31294,7 +31294,7 @@
         <v>45434.56291666667</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31356,7 +31356,7 @@
         <v>45569.45017361111</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31413,7 +31413,7 @@
         <v>45569.47494212963</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31470,7 +31470,7 @@
         <v>45201.39996527778</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31527,7 +31527,7 @@
         <v>45588.67070601852</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31584,7 +31584,7 @@
         <v>45355.54138888889</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31641,7 +31641,7 @@
         <v>45086.63334490741</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31698,7 +31698,7 @@
         <v>44949</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31755,7 +31755,7 @@
         <v>45660</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31812,7 +31812,7 @@
         <v>45090</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31869,7 +31869,7 @@
         <v>44467.83386574074</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>45825.58672453704</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>44599</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32040,7 +32040,7 @@
         <v>44340</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>44944.73487268519</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32154,7 +32154,7 @@
         <v>45330</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32211,7 +32211,7 @@
         <v>45330</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32268,7 +32268,7 @@
         <v>45250.5278587963</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32325,7 +32325,7 @@
         <v>45070</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32382,7 +32382,7 @@
         <v>45225.60192129629</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32439,7 +32439,7 @@
         <v>44790.49040509259</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32496,7 +32496,7 @@
         <v>45825.5796875</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32553,7 +32553,7 @@
         <v>44784.42528935185</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32610,7 +32610,7 @@
         <v>45700.68289351852</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32667,7 +32667,7 @@
         <v>44539</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32724,7 +32724,7 @@
         <v>44935</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32781,7 +32781,7 @@
         <v>44852</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32838,7 +32838,7 @@
         <v>45100.85270833333</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32895,7 +32895,7 @@
         <v>45299.47513888889</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32952,7 +32952,7 @@
         <v>45517.8162037037</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33009,7 +33009,7 @@
         <v>44910</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33066,7 +33066,7 @@
         <v>44598.7384837963</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33123,7 +33123,7 @@
         <v>44578.62943287037</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33180,7 +33180,7 @@
         <v>44994.46908564815</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33237,7 +33237,7 @@
         <v>44900.57393518519</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33294,7 +33294,7 @@
         <v>44848.59133101852</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33351,7 +33351,7 @@
         <v>44440.60415509259</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33408,7 +33408,7 @@
         <v>45201</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33465,7 +33465,7 @@
         <v>44966</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33522,7 +33522,7 @@
         <v>45559.38876157408</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33579,7 +33579,7 @@
         <v>45224</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33636,7 +33636,7 @@
         <v>45415.48979166667</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33693,7 +33693,7 @@
         <v>44542.90072916666</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33750,7 +33750,7 @@
         <v>45323.53744212963</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33807,7 +33807,7 @@
         <v>45825.57680555555</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33864,7 +33864,7 @@
         <v>45308.59001157407</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33921,7 +33921,7 @@
         <v>45111.30824074074</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33978,7 +33978,7 @@
         <v>45086.63194444445</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34035,7 +34035,7 @@
         <v>45196</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34092,7 +34092,7 @@
         <v>45749.60487268519</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34154,7 +34154,7 @@
         <v>44984.45895833334</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34211,7 +34211,7 @@
         <v>45446.36865740741</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34273,7 +34273,7 @@
         <v>45245.63574074074</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34330,7 +34330,7 @@
         <v>45732.76936342593</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34387,7 +34387,7 @@
         <v>45707.3793287037</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34444,7 +34444,7 @@
         <v>45320.89128472222</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34501,7 +34501,7 @@
         <v>44987.54104166666</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34558,7 +34558,7 @@
         <v>44578.32717592592</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34615,7 +34615,7 @@
         <v>45525.41762731481</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34672,7 +34672,7 @@
         <v>44964.5115162037</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34729,7 +34729,7 @@
         <v>45208</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34786,7 +34786,7 @@
         <v>45001.43854166667</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34843,7 +34843,7 @@
         <v>44585.51060185185</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34900,7 +34900,7 @@
         <v>45260.4716550926</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34957,7 +34957,7 @@
         <v>44943.62954861111</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35014,7 +35014,7 @@
         <v>45827</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35071,7 +35071,7 @@
         <v>45121.58699074074</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35133,7 +35133,7 @@
         <v>45827</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35190,7 +35190,7 @@
         <v>45371.36359953704</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35247,7 +35247,7 @@
         <v>45211.52642361111</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35304,7 +35304,7 @@
         <v>45075.43059027778</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35361,7 +35361,7 @@
         <v>44630</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35418,7 +35418,7 @@
         <v>45831</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35475,7 +35475,7 @@
         <v>44938</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35537,7 +35537,7 @@
         <v>44949</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35599,7 +35599,7 @@
         <v>45371.45865740741</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35656,7 +35656,7 @@
         <v>45100.4062962963</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35713,7 +35713,7 @@
         <v>44795</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35770,7 +35770,7 @@
         <v>45280.66769675926</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35827,7 +35827,7 @@
         <v>45112.33599537037</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35884,7 +35884,7 @@
         <v>45111</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35941,7 +35941,7 @@
         <v>45020</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35998,7 +35998,7 @@
         <v>45568.30189814815</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36055,7 +36055,7 @@
         <v>44159</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36112,7 +36112,7 @@
         <v>44894.49538194444</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36169,7 +36169,7 @@
         <v>45202.4209837963</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36226,7 +36226,7 @@
         <v>45632.36706018518</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36283,7 +36283,7 @@
         <v>44172</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36340,7 +36340,7 @@
         <v>45632.44886574074</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36397,7 +36397,7 @@
         <v>45833.64563657407</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36454,7 +36454,7 @@
         <v>45833.64814814815</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36511,7 +36511,7 @@
         <v>45832.46146990741</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36568,7 +36568,7 @@
         <v>45245.36174768519</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36625,7 +36625,7 @@
         <v>45833.64237268519</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36682,7 +36682,7 @@
         <v>44585.50431712963</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36739,7 +36739,7 @@
         <v>45832.34540509259</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36796,7 +36796,7 @@
         <v>45170</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36853,7 +36853,7 @@
         <v>45834.65040509259</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>44790.45876157407</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36972,7 +36972,7 @@
         <v>44790.49523148148</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37029,7 +37029,7 @@
         <v>45709.62280092593</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37086,7 +37086,7 @@
         <v>45835.44709490741</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37143,7 +37143,7 @@
         <v>45835.48267361111</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37200,7 +37200,7 @@
         <v>45835.48445601852</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37257,7 +37257,7 @@
         <v>45835.48862268519</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37314,7 +37314,7 @@
         <v>45834.64667824074</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37376,7 +37376,7 @@
         <v>45835.44732638889</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37433,7 +37433,7 @@
         <v>45835.36229166666</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37495,7 +37495,7 @@
         <v>45835.45099537037</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37552,7 +37552,7 @@
         <v>45835.4924537037</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37609,7 +37609,7 @@
         <v>45834.65197916667</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37671,7 +37671,7 @@
         <v>45211.43555555555</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37728,7 +37728,7 @@
         <v>44893</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>44867</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37842,7 +37842,7 @@
         <v>44732.3659837963</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>45174.40454861111</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37956,7 +37956,7 @@
         <v>45635.4874537037</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38013,7 +38013,7 @@
         <v>45837.77701388889</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38070,7 +38070,7 @@
         <v>45840.59474537037</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38127,7 +38127,7 @@
         <v>45841.70569444444</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>45841.70868055556</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>45483.82479166667</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38298,7 +38298,7 @@
         <v>45713.45311342592</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>45832.46649305556</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38412,7 +38412,7 @@
         <v>45841.7072337963</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>45713.92412037037</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38526,7 +38526,7 @@
         <v>45446.36774305555</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>45615.48927083334</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38645,7 +38645,7 @@
         <v>45811.45460648148</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>44994.42113425926</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38759,7 +38759,7 @@
         <v>45845.42015046296</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38816,7 +38816,7 @@
         <v>45176.72427083334</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38873,7 +38873,7 @@
         <v>45845.43803240741</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38930,7 +38930,7 @@
         <v>45845.49414351852</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38987,7 +38987,7 @@
         <v>45820.03976851852</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39044,7 +39044,7 @@
         <v>45729.36868055556</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39101,7 +39101,7 @@
         <v>45884.50613425926</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39163,7 +39163,7 @@
         <v>45759.38987268518</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39220,7 +39220,7 @@
         <v>45887.68759259259</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39277,7 +39277,7 @@
         <v>44984</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39334,7 +39334,7 @@
         <v>44984</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39391,7 +39391,7 @@
         <v>45061</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39453,7 +39453,7 @@
         <v>45018</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39510,7 +39510,7 @@
         <v>44310</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39567,7 +39567,7 @@
         <v>45096.45247685185</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39624,7 +39624,7 @@
         <v>45105</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>44788</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39738,7 +39738,7 @@
         <v>45391.41310185185</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39795,7 +39795,7 @@
         <v>44258</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>45163.63621527778</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>45070.3665625</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39971,7 +39971,7 @@
         <v>45028</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40028,7 +40028,7 @@
         <v>45698.53725694444</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40085,7 +40085,7 @@
         <v>45093.62777777778</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40147,7 +40147,7 @@
         <v>45630.35827546296</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40204,7 +40204,7 @@
         <v>45456.59289351852</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40261,7 +40261,7 @@
         <v>44431.84840277778</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40318,7 +40318,7 @@
         <v>45671.46746527778</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40375,7 +40375,7 @@
         <v>45847.91280092593</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40432,7 +40432,7 @@
         <v>45481.55984953704</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40489,7 +40489,7 @@
         <v>45110.4184375</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40546,7 +40546,7 @@
         <v>44964.50894675926</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40603,7 +40603,7 @@
         <v>45257.70313657408</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40660,7 +40660,7 @@
         <v>45891.50525462963</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40717,7 +40717,7 @@
         <v>45891.50986111111</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40774,7 +40774,7 @@
         <v>45533.60232638889</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40836,7 +40836,7 @@
         <v>45533.60770833334</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40898,7 +40898,7 @@
         <v>45001.59209490741</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40955,7 +40955,7 @@
         <v>45569.44295138889</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41012,7 +41012,7 @@
         <v>44879</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41069,7 +41069,7 @@
         <v>45182.78834490741</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41126,7 +41126,7 @@
         <v>45475.49018518518</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41183,7 +41183,7 @@
         <v>44510.60921296296</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41245,7 +41245,7 @@
         <v>45891</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41302,7 +41302,7 @@
         <v>45891.50216435185</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41359,7 +41359,7 @@
         <v>45761.4437962963</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41416,7 +41416,7 @@
         <v>44961</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41473,7 +41473,7 @@
         <v>45128.9325</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41530,7 +41530,7 @@
         <v>45128.93540509259</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41587,7 +41587,7 @@
         <v>44999.36081018519</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41644,7 +41644,7 @@
         <v>45567</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41701,7 +41701,7 @@
         <v>44984</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41758,7 +41758,7 @@
         <v>45090.38012731481</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41815,7 +41815,7 @@
         <v>44466.34962962963</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41872,7 +41872,7 @@
         <v>45174</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41929,7 +41929,7 @@
         <v>45891</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41986,7 +41986,7 @@
         <v>45530.33202546297</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42043,7 +42043,7 @@
         <v>45897.64208333333</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42100,7 +42100,7 @@
         <v>45091.67936342592</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42157,7 +42157,7 @@
         <v>45897.89737268518</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42214,7 +42214,7 @@
         <v>45853.87112268519</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42271,7 +42271,7 @@
         <v>45853.87599537037</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42328,7 +42328,7 @@
         <v>45853.88070601852</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42385,7 +42385,7 @@
         <v>45897.88836805556</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42442,7 +42442,7 @@
         <v>45897.88706018519</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42499,7 +42499,7 @@
         <v>45897.63520833333</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42556,7 +42556,7 @@
         <v>45755.44333333334</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42613,7 +42613,7 @@
         <v>45646.38200231481</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42670,7 +42670,7 @@
         <v>45858.60641203704</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42727,7 +42727,7 @@
         <v>45901.63219907408</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42784,7 +42784,7 @@
         <v>45901.6327662037</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42841,7 +42841,7 @@
         <v>44910.41346064815</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42898,7 +42898,7 @@
         <v>45483.82834490741</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42955,7 +42955,7 @@
         <v>45858.66019675926</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43012,7 +43012,7 @@
         <v>45698.52806712963</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43069,7 +43069,7 @@
         <v>45271.66576388889</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43126,7 +43126,7 @@
         <v>45224.60075231481</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43188,7 +43188,7 @@
         <v>44392</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43250,7 +43250,7 @@
         <v>45898.58861111111</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43307,7 +43307,7 @@
         <v>45113.56574074074</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43364,7 +43364,7 @@
         <v>44540</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43421,7 +43421,7 @@
         <v>44916.55414351852</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43478,7 +43478,7 @@
         <v>45545.49508101852</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43535,7 +43535,7 @@
         <v>45361.87975694444</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43592,7 +43592,7 @@
         <v>44896</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43649,7 +43649,7 @@
         <v>45902.47164351852</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43706,7 +43706,7 @@
         <v>45149.60917824074</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43763,7 +43763,7 @@
         <v>45699.44291666667</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43820,7 +43820,7 @@
         <v>45114.49505787037</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43877,7 +43877,7 @@
         <v>45903.38800925926</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43934,7 +43934,7 @@
         <v>44176</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43991,7 +43991,7 @@
         <v>45111.48225694444</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44048,7 +44048,7 @@
         <v>45482.52887731481</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44105,7 +44105,7 @@
         <v>45111.48636574074</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44162,7 +44162,7 @@
         <v>44879.62173611111</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44219,7 +44219,7 @@
         <v>45098.30535879629</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44276,7 +44276,7 @@
         <v>45154.49831018518</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44333,7 +44333,7 @@
         <v>45705.73300925926</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44390,7 +44390,7 @@
         <v>45722.48634259259</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44447,7 +44447,7 @@
         <v>45867.51630787037</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44504,7 +44504,7 @@
         <v>45867.63094907408</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44561,7 +44561,7 @@
         <v>45481.56722222222</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44618,7 +44618,7 @@
         <v>45867.64663194444</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44675,7 +44675,7 @@
         <v>45453.36854166666</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44732,7 +44732,7 @@
         <v>44992.34151620371</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44794,7 +44794,7 @@
         <v>45700.68672453704</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44851,7 +44851,7 @@
         <v>45867.56320601852</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44908,7 +44908,7 @@
         <v>44502</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44965,7 +44965,7 @@
         <v>45867.68625</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45022,7 +45022,7 @@
         <v>45378.32185185186</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45079,7 +45079,7 @@
         <v>44603</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45136,7 +45136,7 @@
         <v>45908.57716435185</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45193,7 +45193,7 @@
         <v>45726.44471064815</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45250,7 +45250,7 @@
         <v>45867.50792824074</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45307,7 +45307,7 @@
         <v>45147.67172453704</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45364,7 +45364,7 @@
         <v>44959.66407407408</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45421,7 +45421,7 @@
         <v>45769</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45478,7 +45478,7 @@
         <v>45377.40043981482</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45535,7 +45535,7 @@
         <v>45219.69356481481</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45592,7 +45592,7 @@
         <v>45867.69346064814</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45649,7 +45649,7 @@
         <v>45211.55472222222</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45711,7 +45711,7 @@
         <v>45171.77335648148</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45768,7 +45768,7 @@
         <v>45911.67798611111</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45825,7 +45825,7 @@
         <v>45698.53336805556</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45882,7 +45882,7 @@
         <v>45869.62276620371</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45939,7 +45939,7 @@
         <v>44977</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45996,7 +45996,7 @@
         <v>45498.673125</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46053,7 +46053,7 @@
         <v>45113.43921296296</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46110,7 +46110,7 @@
         <v>45911.47138888889</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46167,7 +46167,7 @@
         <v>45908</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46224,7 +46224,7 @@
         <v>44967.45122685185</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46281,7 +46281,7 @@
         <v>44963.44769675926</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46338,7 +46338,7 @@
         <v>45720.44217592593</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46395,7 +46395,7 @@
         <v>44909</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46452,7 +46452,7 @@
         <v>45747.43196759259</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46509,7 +46509,7 @@
         <v>45747.42633101852</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46566,7 +46566,7 @@
         <v>45747.42958333333</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46623,7 +46623,7 @@
         <v>45699.60055555555</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46680,7 +46680,7 @@
         <v>44825.4336574074</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46737,7 +46737,7 @@
         <v>45215.60199074074</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46794,7 +46794,7 @@
         <v>45533.55362268518</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46851,7 +46851,7 @@
         <v>44784.62724537037</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46908,7 +46908,7 @@
         <v>45908</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46965,7 +46965,7 @@
         <v>45754.33641203704</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47022,7 +47022,7 @@
         <v>45415.57682870371</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47079,7 +47079,7 @@
         <v>45187.42854166667</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47136,7 +47136,7 @@
         <v>45845</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47193,7 +47193,7 @@
         <v>45870.51708333333</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47250,7 +47250,7 @@
         <v>45870.52111111111</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47307,7 +47307,7 @@
         <v>44475</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47364,7 +47364,7 @@
         <v>44839.4528125</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47421,7 +47421,7 @@
         <v>45243.84869212963</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47478,7 +47478,7 @@
         <v>44643</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47535,7 +47535,7 @@
         <v>44875.27736111111</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47592,7 +47592,7 @@
         <v>45533.54429398148</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47649,7 +47649,7 @@
         <v>44973.43075231482</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47706,7 +47706,7 @@
         <v>45915.55950231481</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47763,7 +47763,7 @@
         <v>45106.2610300926</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47820,7 +47820,7 @@
         <v>45705.74418981482</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47877,7 +47877,7 @@
         <v>45301.68237268519</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47934,7 +47934,7 @@
         <v>45870.52142361111</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47991,7 +47991,7 @@
         <v>45915.56430555556</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48048,7 +48048,7 @@
         <v>45761.35990740741</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48105,7 +48105,7 @@
         <v>44964.44356481481</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48162,7 +48162,7 @@
         <v>45722.48915509259</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48219,7 +48219,7 @@
         <v>45238.4328587963</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48276,7 +48276,7 @@
         <v>45870.51958333333</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48333,7 +48333,7 @@
         <v>45870.52005787037</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48390,7 +48390,7 @@
         <v>45106</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48447,7 +48447,7 @@
         <v>45743.41148148148</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48504,7 +48504,7 @@
         <v>45569.44684027778</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48561,7 +48561,7 @@
         <v>45148</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48618,7 +48618,7 @@
         <v>45917.67054398148</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48675,7 +48675,7 @@
         <v>44893</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48732,7 +48732,7 @@
         <v>45361.90282407407</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48789,7 +48789,7 @@
         <v>44952.35775462963</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48846,7 +48846,7 @@
         <v>45658.80232638889</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48903,7 +48903,7 @@
         <v>45658.80827546296</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48960,7 +48960,7 @@
         <v>45572.48293981481</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49017,7 +49017,7 @@
         <v>45875.45716435185</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49074,7 +49074,7 @@
         <v>45875.47454861111</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49131,7 +49131,7 @@
         <v>45147</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49188,7 +49188,7 @@
         <v>45548</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49245,7 +49245,7 @@
         <v>45875.42716435185</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49302,7 +49302,7 @@
         <v>45394.50028935185</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49359,7 +49359,7 @@
         <v>45138</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49416,7 +49416,7 @@
         <v>45916.41019675926</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49473,7 +49473,7 @@
         <v>45916.7103587963</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49530,7 +49530,7 @@
         <v>45874.57109953704</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49587,7 +49587,7 @@
         <v>45169</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49644,7 +49644,7 @@
         <v>44867</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49701,7 +49701,7 @@
         <v>45317</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49763,7 +49763,7 @@
         <v>45919.42387731482</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49820,7 +49820,7 @@
         <v>44111</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49877,7 +49877,7 @@
         <v>45384.66917824074</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49934,7 +49934,7 @@
         <v>45734.62017361111</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49991,7 +49991,7 @@
         <v>44745.84396990741</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50048,7 +50048,7 @@
         <v>45698.51711805556</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50105,7 +50105,7 @@
         <v>45513.55840277778</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50162,7 +50162,7 @@
         <v>45513.56527777778</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50219,7 +50219,7 @@
         <v>45630.45069444444</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50276,7 +50276,7 @@
         <v>45880.38380787037</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50333,7 +50333,7 @@
         <v>45921.95611111111</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50390,7 +50390,7 @@
         <v>45533.56108796296</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50447,7 +50447,7 @@
         <v>45533.58302083334</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50509,7 +50509,7 @@
         <v>45124</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50566,7 +50566,7 @@
         <v>45921.96395833333</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50623,7 +50623,7 @@
         <v>45880.51550925926</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50685,7 +50685,7 @@
         <v>45924.57697916667</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50742,7 +50742,7 @@
         <v>45881.59877314815</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50799,7 +50799,7 @@
         <v>45881</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50856,7 +50856,7 @@
         <v>45925.49670138889</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50913,7 +50913,7 @@
         <v>45925.50075231482</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>

--- a/Översikt VIMMERBY.xlsx
+++ b/Översikt VIMMERBY.xlsx
@@ -567,7 +567,7 @@
         <v>44811</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
         <v>44811</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44811</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44811</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>45314</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>44939</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>45377.54726851852</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>45755</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>45301.67922453704</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45121.60543981481</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>45748</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>45678.64175925926</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>44245</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>44811</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>45742</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>45628</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>45880.51413194444</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>45020</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>44424</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>44426.64793981481</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>44386</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>45896.86820601852</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>44943</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>45760.34877314815</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>45908</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>45072</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>45048</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>45786.52827546297</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>45008.60878472222</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>44371</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>44403</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
         <v>45713</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>45168</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45168</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>45884.50331018519</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>45224</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>45926.90006944445</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>44377.61104166666</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v>45077</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>45667</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>45399.71412037037</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>45125</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         <v>45649</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>45821</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>45104</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>45574.42767361111</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>44236</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>44102</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>44130</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>44281.79269675926</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         <v>44270.67071759259</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
         <v>44287.33261574074</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>44210</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>44447</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>44490.38613425926</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>44481.47483796296</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>44350</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>44614</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>44375.39033564815</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         <v>44215</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>44670</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>44670</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>44307</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>44105</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>44350</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>44225</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         <v>44327.47658564815</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
         <v>44406</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44509</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>44230.58883101852</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>44480</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>44238</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>44585.51829861111</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>44824.53434027778</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>44418</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>44785.40800925926</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>44826.68010416667</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>44578.47597222222</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>44516.59703703703</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>44862</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>44603</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>44588</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>44404.87505787037</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>44483.58295138889</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>44494</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>44354</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>44542.8859375</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         <v>44512.70245370371</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>44221.39408564815</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>44790</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>44261</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>44530.38055555556</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>44588</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>44588</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>44790</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         <v>44790.47628472222</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>44175.3815625</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>44175.40881944444</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>44312</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>44475</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>44385</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>44124.59795138889</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>44237.8550925926</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>44410.71038194445</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>44279.33400462963</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>44175</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>44670</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>44365</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         <v>44169</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
         <v>44273</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>44301.36048611111</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>44729.28226851852</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>44271.37226851852</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>44340.54472222222</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>44340</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>44774</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         <v>44733</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>44733</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>44154</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>44371.62743055556</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         <v>44386.40783564815</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>44480</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         <v>44245</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9208,7 +9208,7 @@
         <v>44337</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         <v>44102</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>44463.29439814815</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         <v>44588</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         <v>44117</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
         <v>44789</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>44377</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>44379</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9669,7 +9669,7 @@
         <v>44508</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>44634.69703703704</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>44480</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9845,7 +9845,7 @@
         <v>44769.45422453704</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         <v>44340.58002314815</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         <v>44612.86762731482</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
         <v>44517</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10073,7 +10073,7 @@
         <v>44819</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>44621</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>44217.79856481482</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         <v>44172</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>44451.8375</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>44823</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>44270</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>44876.48346064815</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>44733.43092592592</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>44341</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         <v>44608</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
         <v>44447.34237268518</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>44384</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>44790.48503472222</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10871,7 +10871,7 @@
         <v>44854.59157407407</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10928,7 +10928,7 @@
         <v>44294</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10985,7 +10985,7 @@
         <v>44116</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>44609</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11099,7 +11099,7 @@
         <v>44284.42348379629</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11156,7 +11156,7 @@
         <v>44620</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         <v>44421</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
         <v>44186</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11327,7 +11327,7 @@
         <v>44480</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11384,7 +11384,7 @@
         <v>44273</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11441,7 +11441,7 @@
         <v>44278.63479166666</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11503,7 +11503,7 @@
         <v>44375.38789351852</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>44612.86554398148</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>44466.34726851852</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
         <v>44203</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>44866.81100694444</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>44470.44232638889</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11850,7 +11850,7 @@
         <v>44525.63913194444</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>44776</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11964,7 +11964,7 @@
         <v>44279.64934027778</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>44386</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>44427</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>44662</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12197,7 +12197,7 @@
         <v>44634</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
         <v>44608.50458333334</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12311,7 +12311,7 @@
         <v>44817</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>44266.7240625</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>44292</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>45483.82834490741</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         <v>45090.38012731481</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>44270.49743055556</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12668,7 +12668,7 @@
         <v>44564</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
         <v>44851.95016203704</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>44379</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>44284.44574074074</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>44636</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>44722.48768518519</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>44644</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>44466.34962962963</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>45105</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>44278.54855324074</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>44817.57988425926</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>44377.49684027778</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>44833.60123842592</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>44294</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13476,7 +13476,7 @@
         <v>44294</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>44676.85248842592</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>45215.59743055556</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>44789</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>44604</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>45411.47335648148</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13818,7 +13818,7 @@
         <v>44305</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         <v>45377.40043981482</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13932,7 +13932,7 @@
         <v>45698.51711805556</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         <v>45211.43555555555</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         <v>45097.40524305555</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14108,7 +14108,7 @@
         <v>45100.4062962963</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>44832.67608796297</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>45425.57538194444</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>44142</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>44383</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>44476</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>44305.40046296296</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14507,7 +14507,7 @@
         <v>45090</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>44447</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>44418</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>44854</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         <v>45749.60487268519</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>45245.5735300926</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>45450.51092592593</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14916,7 +14916,7 @@
         <v>44824</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14973,7 +14973,7 @@
         <v>44369</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>44742</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15087,7 +15087,7 @@
         <v>44895.62296296296</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>44848.59133101852</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15201,7 +15201,7 @@
         <v>45440.28329861111</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15258,7 +15258,7 @@
         <v>45308.61152777778</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
         <v>45299.47513888889</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>44790.45876157407</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>45891.50216435185</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15486,7 +15486,7 @@
         <v>45539.66027777778</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15543,7 +15543,7 @@
         <v>45632.72635416667</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>44861</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>44879.62173611111</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>45853.87112268519</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>45147</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>44475</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>44987.54104166666</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>45853.87599537037</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>45853.88070601852</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>45202.4209837963</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>45755.44333333334</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>45891</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16227,7 +16227,7 @@
         <v>44852</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>45384.66917824074</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>44943.62954861111</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>44944.73487268519</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>45128.37305555555</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         <v>45897.63520833333</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16569,7 +16569,7 @@
         <v>45481.56722222222</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16626,7 +16626,7 @@
         <v>45114.55136574074</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16683,7 +16683,7 @@
         <v>44900.57393518519</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16740,7 +16740,7 @@
         <v>45761.35990740741</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
         <v>44992</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>45897.88836805556</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>45394.66887731481</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         <v>45897.64208333333</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17030,7 +17030,7 @@
         <v>45257.70313657408</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17087,7 +17087,7 @@
         <v>45898.58861111111</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>44392</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>45897.89737268518</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>45897.88706018519</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>45901.63219907408</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>45901.6327662037</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>45266.32614583334</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>45317.40372685185</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>45858.66019675926</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>45394.50028935185</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>44857.65989583333</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>45309.59487268519</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>44585.50431712963</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>44992.34151620371</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17900,7 +17900,7 @@
         <v>45581.58418981481</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>45359.44837962963</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>44542.90072916666</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>44488.35878472222</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>44867</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>44467.83386574074</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>45581.57333333333</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>45482.52887731481</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>45371.36359953704</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>45371.45865740741</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>45533.63056712963</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>45858.60641203704</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>45359.45038194444</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>45902.47164351852</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>44453.56578703703</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>45588.67070601852</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>44861.52505787037</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>44784.42528935185</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>45533.54429398148</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>45533.60232638889</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>45533.60770833334</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>44431</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19169,7 +19169,7 @@
         <v>44566</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45903.38800925926</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>45743.41148148148</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19340,7 +19340,7 @@
         <v>45446.36774305555</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19402,7 +19402,7 @@
         <v>45261.44914351852</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>45176.72427083334</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19516,7 +19516,7 @@
         <v>45048.59699074074</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>45147.67096064815</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19630,7 +19630,7 @@
         <v>45503.5658912037</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19687,7 +19687,7 @@
         <v>45147.67172453704</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19744,7 +19744,7 @@
         <v>45569.45017361111</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19801,7 +19801,7 @@
         <v>44999.35858796296</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>45713.45311342592</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>44596</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>45170</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>45735.58024305556</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>44952.35775462963</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>45908.57716435185</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>44746.38834490741</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>45526.3865625</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>45093.62777777778</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>45769</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20438,7 +20438,7 @@
         <v>45215.5959375</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20495,7 +20495,7 @@
         <v>45243.84869212963</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>45622</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>45562.46342592593</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>44992.62498842592</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>45434.55831018519</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20785,7 +20785,7 @@
         <v>45434.56398148148</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20847,7 +20847,7 @@
         <v>45075.43059027778</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20904,7 +20904,7 @@
         <v>45867.63094907408</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>45867.69346064814</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21018,7 +21018,7 @@
         <v>44784.62724537037</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21075,7 +21075,7 @@
         <v>45867.50792824074</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21132,7 +21132,7 @@
         <v>45867.51630787037</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>45867.68625</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>45867.56320601852</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>45867.64663194444</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         <v>44967.44255787037</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>44949</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>44600</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21531,7 +21531,7 @@
         <v>45187.60813657408</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21588,7 +21588,7 @@
         <v>45908</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>44237</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>45171.96248842592</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         <v>45869.62276620371</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>45343.68038194445</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21873,7 +21873,7 @@
         <v>44452</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>45908</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21987,7 +21987,7 @@
         <v>45009.4671875</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22044,7 +22044,7 @@
         <v>45705.74418981482</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22101,7 +22101,7 @@
         <v>44270.39765046296</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22163,7 +22163,7 @@
         <v>45030.71012731481</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>45911.47138888889</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22277,7 +22277,7 @@
         <v>45870.51708333333</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22334,7 +22334,7 @@
         <v>45870.52111111111</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22391,7 +22391,7 @@
         <v>45121.61318287037</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22453,7 +22453,7 @@
         <v>44510.52157407408</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>44984</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>44598</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22624,7 +22624,7 @@
         <v>44938</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>45483.82479166667</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22743,7 +22743,7 @@
         <v>45498</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22800,7 +22800,7 @@
         <v>44879</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22857,7 +22857,7 @@
         <v>45617.47570601852</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22914,7 +22914,7 @@
         <v>45911.67798611111</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22971,7 +22971,7 @@
         <v>45482.54108796296</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>44410</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         <v>45111</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23142,7 +23142,7 @@
         <v>45845</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23199,7 +23199,7 @@
         <v>45485.45778935185</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23256,7 +23256,7 @@
         <v>45870.51958333333</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23313,7 +23313,7 @@
         <v>45870.52005787037</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23370,7 +23370,7 @@
         <v>45870.52142361111</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>45618.56787037037</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23484,7 +23484,7 @@
         <v>45467.74417824074</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>44909</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23598,7 +23598,7 @@
         <v>45086</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23655,7 +23655,7 @@
         <v>44159</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23712,7 +23712,7 @@
         <v>45637.66542824074</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23769,7 +23769,7 @@
         <v>44918.50106481482</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>44981.58834490741</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23883,7 +23883,7 @@
         <v>45632.37459490741</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23940,7 +23940,7 @@
         <v>45378.32185185186</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23997,7 +23997,7 @@
         <v>44310</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
         <v>45498.673125</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24111,7 +24111,7 @@
         <v>44893</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24168,7 +24168,7 @@
         <v>45275.32266203704</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24225,7 +24225,7 @@
         <v>45540.50098379629</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>45041.63380787037</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24339,7 +24339,7 @@
         <v>45916.41019675926</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24396,7 +24396,7 @@
         <v>44961</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24453,7 +24453,7 @@
         <v>44916.55414351852</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24510,7 +24510,7 @@
         <v>45916.7103587963</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24567,7 +24567,7 @@
         <v>44127</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24624,7 +24624,7 @@
         <v>45300.3794212963</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24681,7 +24681,7 @@
         <v>45245.36174768519</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24738,7 +24738,7 @@
         <v>45567</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24795,7 +24795,7 @@
         <v>45874.57109953704</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24852,7 +24852,7 @@
         <v>45915.55950231481</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24909,7 +24909,7 @@
         <v>45915.56430555556</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24966,7 +24966,7 @@
         <v>44994.42113425926</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>44999.36081018519</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25080,7 +25080,7 @@
         <v>44958.61047453704</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25137,7 +25137,7 @@
         <v>44630</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25194,7 +25194,7 @@
         <v>44965</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25251,7 +25251,7 @@
         <v>44893</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
         <v>45334.78826388889</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25365,7 +25365,7 @@
         <v>45875.45716435185</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25422,7 +25422,7 @@
         <v>45875.47454861111</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25479,7 +25479,7 @@
         <v>45495</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25536,7 +25536,7 @@
         <v>45128.9325</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25593,7 +25593,7 @@
         <v>45128.93540509259</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25650,7 +25650,7 @@
         <v>45320.89128472222</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>45699.45671296296</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25764,7 +25764,7 @@
         <v>44973.43075231482</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25821,7 +25821,7 @@
         <v>44340</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
         <v>44994.40635416667</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25935,7 +25935,7 @@
         <v>45875.42716435185</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25992,7 +25992,7 @@
         <v>45574.35809027778</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26049,7 +26049,7 @@
         <v>45917.67054398148</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26106,7 +26106,7 @@
         <v>44977</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26163,7 +26163,7 @@
         <v>45919.42387731482</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26220,7 +26220,7 @@
         <v>45921.96395833333</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>45559.38876157408</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26334,7 +26334,7 @@
         <v>45880.51550925926</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26396,7 +26396,7 @@
         <v>44964.44356481481</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>44613</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26510,7 +26510,7 @@
         <v>45880.38380787037</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26567,7 +26567,7 @@
         <v>45610.59094907407</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26624,7 +26624,7 @@
         <v>44587</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26681,7 +26681,7 @@
         <v>44894.49538194444</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26738,7 +26738,7 @@
         <v>44992</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26795,7 +26795,7 @@
         <v>45020</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26852,7 +26852,7 @@
         <v>44992</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26909,7 +26909,7 @@
         <v>45921.95611111111</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26966,7 +26966,7 @@
         <v>44935</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27023,7 +27023,7 @@
         <v>44603</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27080,7 +27080,7 @@
         <v>44999.86172453704</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27137,7 +27137,7 @@
         <v>44999.8625</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27194,7 +27194,7 @@
         <v>45114.49505787037</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27251,7 +27251,7 @@
         <v>45041</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27308,7 +27308,7 @@
         <v>45028</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>44964.50894675926</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27422,7 +27422,7 @@
         <v>45632.36706018518</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27479,7 +27479,7 @@
         <v>45453.36854166666</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27536,7 +27536,7 @@
         <v>44745.84396990741</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27593,7 +27593,7 @@
         <v>45517.8162037037</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27650,7 +27650,7 @@
         <v>45518.40657407408</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27707,7 +27707,7 @@
         <v>44638.55256944444</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27764,7 +27764,7 @@
         <v>45163.63621527778</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27826,7 +27826,7 @@
         <v>45924.57697916667</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27883,7 +27883,7 @@
         <v>45211.55472222222</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27945,7 +27945,7 @@
         <v>45639.56185185185</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28002,7 +28002,7 @@
         <v>45881</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28059,7 +28059,7 @@
         <v>44540</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28116,7 +28116,7 @@
         <v>45174.31395833333</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28173,7 +28173,7 @@
         <v>45666</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28230,7 +28230,7 @@
         <v>45881.59877314815</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28287,7 +28287,7 @@
         <v>45446.36865740741</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>44981.64725694444</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28406,7 +28406,7 @@
         <v>45615.48927083334</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28463,7 +28463,7 @@
         <v>45001.59209490741</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>44587.48847222222</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28577,7 +28577,7 @@
         <v>44918</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28634,7 +28634,7 @@
         <v>44959.66407407408</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28691,7 +28691,7 @@
         <v>44966</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28748,7 +28748,7 @@
         <v>44564.62598379629</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28805,7 +28805,7 @@
         <v>45138</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28862,7 +28862,7 @@
         <v>45635.66695601852</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28919,7 +28919,7 @@
         <v>45495</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28976,7 +28976,7 @@
         <v>44600</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29033,7 +29033,7 @@
         <v>45568.30189814815</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29090,7 +29090,7 @@
         <v>45033.76043981482</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29147,7 +29147,7 @@
         <v>44895.46524305556</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>45699.45392361111</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29261,7 +29261,7 @@
         <v>45154.49831018518</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29318,7 +29318,7 @@
         <v>45026.82216435186</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29375,7 +29375,7 @@
         <v>45674.74094907408</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29432,7 +29432,7 @@
         <v>45700.68672453704</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29489,7 +29489,7 @@
         <v>45630.35827546296</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29546,7 +29546,7 @@
         <v>45163</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29603,7 +29603,7 @@
         <v>44910.54231481482</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29660,7 +29660,7 @@
         <v>44176</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29717,7 +29717,7 @@
         <v>45567.42011574074</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29774,7 +29774,7 @@
         <v>45554.62944444444</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29831,7 +29831,7 @@
         <v>45453.36067129629</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29888,7 +29888,7 @@
         <v>44963.44769675926</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29945,7 +29945,7 @@
         <v>44944.71386574074</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30002,7 +30002,7 @@
         <v>44944.72100694444</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30059,7 +30059,7 @@
         <v>45698.53725694444</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30116,7 +30116,7 @@
         <v>45189</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30173,7 +30173,7 @@
         <v>45658.80232638889</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30230,7 +30230,7 @@
         <v>45658.80827546296</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30287,7 +30287,7 @@
         <v>45063.49936342592</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30344,7 +30344,7 @@
         <v>44769.45805555556</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30401,7 +30401,7 @@
         <v>45250.5278587963</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30458,7 +30458,7 @@
         <v>44803.59118055556</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D495" t="inlineStr">
    